--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -637,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18752</v>
+        <v>25178</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -691,126 +691,122 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>26.675</v>
+        <v>25.24242424242424</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.2261363636363</v>
+        <v>185.9015151515152</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>68.77272727272728</v>
+        <v>71.45454545454545</v>
       </c>
       <c r="T2" t="n">
-        <v>1648238.636363636</v>
+        <v>2948333.333333333</v>
       </c>
       <c r="U2" t="n">
-        <v>72.34659090909091</v>
+        <v>74.88030303030304</v>
       </c>
       <c r="V2" t="n">
-        <v>26.62337662337663</v>
+        <v>24.19277777777778</v>
       </c>
       <c r="W2" t="n">
-        <v>180.5064935064935</v>
+        <v>183.2383333333334</v>
       </c>
       <c r="X2" t="n">
-        <v>1.402597402597403</v>
+        <v>2.237777777777777</v>
       </c>
       <c r="Y2" t="n">
-        <v>77.05194805194806</v>
+        <v>80.72388888888889</v>
       </c>
       <c r="Z2" t="n">
-        <v>13182467.53246753</v>
+        <v>39090555.55555555</v>
       </c>
       <c r="AA2" t="n">
-        <v>79.42857142857143</v>
+        <v>85.03222222222223</v>
       </c>
       <c r="AB2" t="n">
-        <v>24.5224358974359</v>
+        <v>25.04091614906832</v>
       </c>
       <c r="AC2" t="n">
-        <v>182.5160256410257</v>
+        <v>181.1581866804693</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>65.21314102564102</v>
+        <v>69.33653381642512</v>
       </c>
       <c r="AF2" t="n">
-        <v>1102403.846153846</v>
+        <v>2341206.004140787</v>
       </c>
       <c r="AG2" t="n">
-        <v>70.7603021978022</v>
+        <v>73.27387853692203</v>
       </c>
       <c r="AH2" t="n">
-        <v>26.26303854875284</v>
+        <v>23.83827504686085</v>
       </c>
       <c r="AI2" t="n">
-        <v>177.8795351473923</v>
+        <v>183.609871580211</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.374716553287982</v>
+        <v>2.164974147553758</v>
       </c>
       <c r="AK2" t="n">
-        <v>74.23526077097506</v>
+        <v>77.92448611023357</v>
       </c>
       <c r="AL2" t="n">
-        <v>6823299.319727891</v>
+        <v>31973076.99395547</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.27607709750566</v>
+        <v>83.46667219519387</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17924</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -838,124 +834,124 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>lhUkVMh2</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>25.73863636363636</v>
+        <v>26.34848484848485</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.4090909090909</v>
+        <v>181.9242424242424</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>1.318181818181819</v>
       </c>
       <c r="S3" t="n">
-        <v>68.65909090909091</v>
+        <v>74.92424242424242</v>
       </c>
       <c r="T3" t="n">
-        <v>1723579.545454545</v>
+        <v>6925757.575757575</v>
       </c>
       <c r="U3" t="n">
-        <v>71.68181818181819</v>
+        <v>77.25757575757575</v>
       </c>
       <c r="V3" t="n">
-        <v>23.4025974025974</v>
+        <v>27.05909090909091</v>
       </c>
       <c r="W3" t="n">
-        <v>183.9090909090909</v>
+        <v>184.0212121212121</v>
       </c>
       <c r="X3" t="n">
-        <v>1.324675324675325</v>
+        <v>1.703030303030303</v>
       </c>
       <c r="Y3" t="n">
-        <v>75.22077922077922</v>
+        <v>77.27575757575758</v>
       </c>
       <c r="Z3" t="n">
-        <v>12789610.38961039</v>
+        <v>12523484.84848485</v>
       </c>
       <c r="AA3" t="n">
-        <v>80.14285714285714</v>
+        <v>79.18030303030302</v>
       </c>
       <c r="AB3" t="n">
-        <v>23.53084415584416</v>
+        <v>24.55277777777778</v>
       </c>
       <c r="AC3" t="n">
-        <v>180.0397727272727</v>
+        <v>180.1472222222222</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>1.15515873015873</v>
       </c>
       <c r="AE3" t="n">
-        <v>65.61282467532467</v>
+        <v>71.04484126984127</v>
       </c>
       <c r="AF3" t="n">
-        <v>1428571.428571428</v>
+        <v>4555436.507936508</v>
       </c>
       <c r="AG3" t="n">
-        <v>71.59253246753246</v>
+        <v>74.85476190476192</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.94886024585272</v>
+        <v>25.11819581633823</v>
       </c>
       <c r="AI3" t="n">
-        <v>180.7263694951665</v>
+        <v>183.9721480990057</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.325725026852847</v>
+        <v>1.275711746686979</v>
       </c>
       <c r="AK3" t="n">
-        <v>74.00951784222461</v>
+        <v>75.43411756515472</v>
       </c>
       <c r="AL3" t="n">
-        <v>7708321.398734934</v>
+        <v>10037794.03574295</v>
       </c>
       <c r="AM3" t="n">
-        <v>78.50404284520826</v>
+        <v>78.62515971300802</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15220</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -983,124 +979,124 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>26.41558441558442</v>
+        <v>25.77638888888889</v>
       </c>
       <c r="Q4" t="n">
-        <v>182</v>
+        <v>182.5833333333333</v>
       </c>
       <c r="R4" t="n">
-        <v>1.337662337662338</v>
+        <v>1.261805555555556</v>
       </c>
       <c r="S4" t="n">
-        <v>74.96103896103897</v>
+        <v>74.42569444444445</v>
       </c>
       <c r="T4" t="n">
-        <v>6997402.597402598</v>
+        <v>7825746.527777778</v>
       </c>
       <c r="U4" t="n">
-        <v>77.28571428571429</v>
+        <v>78.80486111111111</v>
       </c>
       <c r="V4" t="n">
-        <v>26.92077922077922</v>
+        <v>24.3</v>
       </c>
       <c r="W4" t="n">
-        <v>183.9012987012987</v>
+        <v>180.3818181818181</v>
       </c>
       <c r="X4" t="n">
-        <v>1.693506493506494</v>
+        <v>1.460606060606061</v>
       </c>
       <c r="Y4" t="n">
-        <v>77.19740259740261</v>
+        <v>76.57121212121213</v>
       </c>
       <c r="Z4" t="n">
-        <v>12364285.71428571</v>
+        <v>13136969.6969697</v>
       </c>
       <c r="AA4" t="n">
-        <v>79.19350649350648</v>
+        <v>81.36515151515151</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.55317460317461</v>
+        <v>22.94450013923698</v>
       </c>
       <c r="AC4" t="n">
-        <v>179.9674603174603</v>
+        <v>183.5636730715678</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.132993197278912</v>
+        <v>1.085491506544138</v>
       </c>
       <c r="AE4" t="n">
-        <v>70.91145124716554</v>
+        <v>69.55047340573655</v>
       </c>
       <c r="AF4" t="n">
-        <v>4394342.403628118</v>
+        <v>4120735.867446393</v>
       </c>
       <c r="AG4" t="n">
-        <v>74.68503401360545</v>
+        <v>77.44472291840714</v>
       </c>
       <c r="AH4" t="n">
-        <v>25.05369165209944</v>
+        <v>25.79805282436861</v>
       </c>
       <c r="AI4" t="n">
-        <v>184.0475555134335</v>
+        <v>180.5075573549258</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.260133878112649</v>
+        <v>1.206535569693464</v>
       </c>
       <c r="AK4" t="n">
-        <v>75.1578150558469</v>
+        <v>73.86423109054688</v>
       </c>
       <c r="AL4" t="n">
-        <v>9768109.173493957</v>
+        <v>7619112.846218109</v>
       </c>
       <c r="AM4" t="n">
-        <v>78.55966070638782</v>
+        <v>78.12593021014074</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25178</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1125,123 +1121,127 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>25.25064935064935</v>
+        <v>24.33198653198653</v>
       </c>
       <c r="Q5" t="n">
-        <v>185.8441558441559</v>
+        <v>182.1239057239057</v>
       </c>
       <c r="R5" t="n">
+        <v>1.522558922558922</v>
+      </c>
+      <c r="S5" t="n">
+        <v>76.77239057239058</v>
+      </c>
+      <c r="T5" t="n">
+        <v>14688552.18855219</v>
+      </c>
+      <c r="U5" t="n">
+        <v>81.44074074074074</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.43454545454545</v>
+      </c>
+      <c r="W5" t="n">
+        <v>181.2672727272727</v>
+      </c>
+      <c r="X5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
-        <v>71.51818181818182</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3005714.285714286</v>
-      </c>
-      <c r="U5" t="n">
-        <v>74.96883116883116</v>
-      </c>
-      <c r="V5" t="n">
-        <v>24.27175925925926</v>
-      </c>
-      <c r="W5" t="n">
-        <v>183.4763888888889</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.216666666666666</v>
-      </c>
       <c r="Y5" t="n">
-        <v>80.28842592592594</v>
+        <v>70.26363636363637</v>
       </c>
       <c r="Z5" t="n">
-        <v>36460648.14814814</v>
+        <v>2277727.272727272</v>
       </c>
       <c r="AA5" t="n">
-        <v>84.63796296296296</v>
+        <v>73.91363636363636</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.1303090801538</v>
+        <v>22.69656647746818</v>
       </c>
       <c r="AC5" t="n">
-        <v>181.4213028689737</v>
+        <v>181.0201324389405</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.379398864809081</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>74.95114594083248</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>12125371.0870313</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>81.5780637254902</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25.37042402042402</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>180.4712398712398</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1</v>
       </c>
-      <c r="AE5" t="n">
-        <v>69.2725845410628</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2262303.559104801</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>73.17126096815538</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>23.78706209457467</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>183.4086376326846</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.233638093395253</v>
-      </c>
       <c r="AK5" t="n">
-        <v>78.39821106074008</v>
+        <v>69.10199245199246</v>
       </c>
       <c r="AL5" t="n">
-        <v>36262156.65542533</v>
+        <v>1914997.641247641</v>
       </c>
       <c r="AM5" t="n">
-        <v>83.81905245650893</v>
+        <v>73.45247530247531</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>17924</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1266,99 +1266,99 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
       <c r="P6" t="n">
-        <v>24.41443001443001</v>
+        <v>25.71428571428572</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.132178932179</v>
+        <v>181.4805194805195</v>
       </c>
       <c r="R6" t="n">
-        <v>1.551803751803752</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>76.88282828282829</v>
+        <v>68.64935064935064</v>
       </c>
       <c r="T6" t="n">
-        <v>14999278.4992785</v>
+        <v>1723051.948051948</v>
       </c>
       <c r="U6" t="n">
-        <v>81.45569985569986</v>
+        <v>71.68831168831169</v>
       </c>
       <c r="V6" t="n">
-        <v>25.54049586776859</v>
+        <v>23.42424242424243</v>
       </c>
       <c r="W6" t="n">
-        <v>181.4157024793388</v>
+        <v>184.030303030303</v>
       </c>
       <c r="X6" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>75.16666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>80.10606060606061</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>23.64749536178108</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>180.1270871985158</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" t="n">
-        <v>70.31239669421488</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2263388.429752066</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>73.8396694214876</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>22.57919983782987</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>181.2851135190919</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.343056169836355</v>
-      </c>
       <c r="AE6" t="n">
-        <v>74.85098223499926</v>
+        <v>65.74118738404452</v>
       </c>
       <c r="AF6" t="n">
-        <v>11684246.64602683</v>
+        <v>1444897.959183673</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.53119747899159</v>
+        <v>71.71799628942486</v>
       </c>
       <c r="AH6" t="n">
-        <v>25.07700884973612</v>
+        <v>23.90329991645781</v>
       </c>
       <c r="AI6" t="n">
-        <v>180.2076206621661</v>
+        <v>180.8474310776943</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>1.324456975772766</v>
       </c>
       <c r="AK6" t="n">
-        <v>68.94986326804509</v>
+        <v>74.27036340852131</v>
       </c>
       <c r="AL6" t="n">
-        <v>1933114.738796557</v>
+        <v>8111560.15037594</v>
       </c>
       <c r="AM6" t="n">
-        <v>73.63212040484768</v>
+        <v>78.71767961570593</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1366,27 +1366,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1411,103 +1411,99 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>24.68831168831169</v>
+        <v>26.61558441558442</v>
       </c>
       <c r="Q7" t="n">
-        <v>182.1181818181819</v>
+        <v>183.1935064935064</v>
       </c>
       <c r="R7" t="n">
-        <v>1.319480519480519</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>72.90259740259741</v>
+        <v>68.74025974025975</v>
       </c>
       <c r="T7" t="n">
-        <v>5346753.246753247</v>
+        <v>1644415.584415585</v>
       </c>
       <c r="U7" t="n">
-        <v>77.89740259740259</v>
+        <v>72.3961038961039</v>
       </c>
       <c r="V7" t="n">
-        <v>22.18253968253968</v>
+        <v>26.78787878787879</v>
       </c>
       <c r="W7" t="n">
-        <v>183.0682539682539</v>
+        <v>180.4393939393939</v>
       </c>
       <c r="X7" t="n">
-        <v>1.188888888888889</v>
+        <v>1.393939393939394</v>
       </c>
       <c r="Y7" t="n">
-        <v>71.36031746031746</v>
+        <v>76.95454545454545</v>
       </c>
       <c r="Z7" t="n">
-        <v>4507619.047619048</v>
+        <v>12849242.42424243</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.39206349206349</v>
+        <v>79.24242424242424</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.52467218771566</v>
+        <v>24.54945054945055</v>
       </c>
       <c r="AC7" t="n">
-        <v>181.467692004338</v>
+        <v>182.6373626373627</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.185980479148181</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>71.12885734003746</v>
+        <v>65.26739926739927</v>
       </c>
       <c r="AF7" t="n">
-        <v>3666877.649610569</v>
+        <v>1120009.157509157</v>
       </c>
       <c r="AG7" t="n">
-        <v>76.03582766439909</v>
+        <v>70.72605965463109</v>
       </c>
       <c r="AH7" t="n">
-        <v>23.54197319953623</v>
+        <v>26.01058201058201</v>
       </c>
       <c r="AI7" t="n">
-        <v>182.5731831194016</v>
+        <v>177.7853835978836</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.271416258811217</v>
+        <v>1.381613756613757</v>
       </c>
       <c r="AK7" t="n">
-        <v>70.46462174613436</v>
+        <v>74.23743386243386</v>
       </c>
       <c r="AL7" t="n">
-        <v>3528691.681800925</v>
+        <v>7054034.391534392</v>
       </c>
       <c r="AM7" t="n">
-        <v>77.16448117708622</v>
+        <v>77.43320105820106</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>AaLVdEGK</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1515,27 +1511,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1560,99 +1556,103 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.59888888888889</v>
+        <v>24.53636363636364</v>
       </c>
       <c r="Q8" t="n">
-        <v>182.9111111111111</v>
+        <v>182.6045454545455</v>
       </c>
       <c r="R8" t="n">
-        <v>1.253888888888889</v>
+        <v>1.289393939393939</v>
       </c>
       <c r="S8" t="n">
-        <v>74.38500000000001</v>
+        <v>72.81969696969696</v>
       </c>
       <c r="T8" t="n">
-        <v>7680597.222222222</v>
+        <v>5294545.454545454</v>
       </c>
       <c r="U8" t="n">
-        <v>78.91055555555556</v>
+        <v>77.89696969696969</v>
       </c>
       <c r="V8" t="n">
-        <v>24.38701298701298</v>
+        <v>21.97962962962963</v>
       </c>
       <c r="W8" t="n">
-        <v>180.5090909090909</v>
+        <v>183.2962962962963</v>
       </c>
       <c r="X8" t="n">
-        <v>1.472727272727273</v>
+        <v>1.17037037037037</v>
       </c>
       <c r="Y8" t="n">
-        <v>76.60649350649351</v>
+        <v>71.28703703703704</v>
       </c>
       <c r="Z8" t="n">
-        <v>13120000</v>
+        <v>4523888.888888889</v>
       </c>
       <c r="AA8" t="n">
-        <v>81.32597402597402</v>
+        <v>79.52407407407408</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.85038787444802</v>
+        <v>24.51952495974235</v>
       </c>
       <c r="AC8" t="n">
-        <v>183.5035565103234</v>
+        <v>181.1567517828388</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.07327843418069</v>
+        <v>1.198458707154359</v>
       </c>
       <c r="AE8" t="n">
-        <v>69.28816087838644</v>
+        <v>71.09477800782149</v>
       </c>
       <c r="AF8" t="n">
-        <v>3911140.947607113</v>
+        <v>3678023.924545664</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.34037474638978</v>
+        <v>76.04179894179894</v>
       </c>
       <c r="AH8" t="n">
-        <v>25.77928337326833</v>
+        <v>23.77119095501449</v>
       </c>
       <c r="AI8" t="n">
-        <v>180.5302872566031</v>
+        <v>182.4464914170796</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.200840012118207</v>
+        <v>1.288874524168642</v>
       </c>
       <c r="AK8" t="n">
-        <v>73.57410283951637</v>
+        <v>70.54205870382341</v>
       </c>
       <c r="AL8" t="n">
-        <v>7146739.582472665</v>
+        <v>3561251.406545524</v>
       </c>
       <c r="AM8" t="n">
-        <v>77.84603541821586</v>
+        <v>77.10856137326725</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29778</v>
+        <v>33150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1705,127 +1705,127 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>24.28571428571428</v>
+        <v>23.09090909090909</v>
       </c>
       <c r="Q9" t="n">
-        <v>181.1688311688312</v>
+        <v>184.030303030303</v>
       </c>
       <c r="R9" t="n">
-        <v>1.688311688311688</v>
+        <v>1.075757575757576</v>
       </c>
       <c r="S9" t="n">
-        <v>75.8961038961039</v>
+        <v>72.87878787878788</v>
       </c>
       <c r="T9" t="n">
-        <v>10606493.50649351</v>
+        <v>5827272.727272727</v>
       </c>
       <c r="U9" t="n">
-        <v>80.2987012987013</v>
+        <v>79.03030303030303</v>
       </c>
       <c r="V9" t="n">
-        <v>27.33080808080808</v>
+        <v>26.54545454545454</v>
       </c>
       <c r="W9" t="n">
-        <v>181.9578282828283</v>
+        <v>183.3181818181818</v>
       </c>
       <c r="X9" t="n">
-        <v>2.113131313131313</v>
+        <v>1.515151515151515</v>
       </c>
       <c r="Y9" t="n">
-        <v>76.76376262626263</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="Z9" t="n">
-        <v>9961792.929292928</v>
+        <v>4332575.757575758</v>
       </c>
       <c r="AA9" t="n">
-        <v>78.93901515151515</v>
+        <v>75.36363636363636</v>
       </c>
       <c r="AB9" t="n">
-        <v>23.00918367346939</v>
+        <v>23.09549689440993</v>
       </c>
       <c r="AC9" t="n">
-        <v>181.2886621315193</v>
+        <v>180.4854641131815</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.438151927437642</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>74.08475056689342</v>
+        <v>70.86507936507938</v>
       </c>
       <c r="AF9" t="n">
-        <v>9713390.022675736</v>
+        <v>3670035.369220152</v>
       </c>
       <c r="AG9" t="n">
-        <v>79.74359410430839</v>
+        <v>77.31694271911662</v>
       </c>
       <c r="AH9" t="n">
-        <v>25.10195885770576</v>
+        <v>25.58957980425372</v>
       </c>
       <c r="AI9" t="n">
-        <v>178.6847129521665</v>
+        <v>179.6847002635046</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.572941293742377</v>
+        <v>1.154052167639124</v>
       </c>
       <c r="AK9" t="n">
-        <v>74.35191060874109</v>
+        <v>70.46049783549783</v>
       </c>
       <c r="AL9" t="n">
-        <v>7151296.649042392</v>
+        <v>2770177.12058473</v>
       </c>
       <c r="AM9" t="n">
-        <v>78.74329833608084</v>
+        <v>73.96561500094109</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33150</v>
+        <v>29778</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1850,92 +1850,92 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>23.06493506493506</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="Q10" t="n">
-        <v>183.8441558441559</v>
+        <v>181.3030303030303</v>
       </c>
       <c r="R10" t="n">
-        <v>1.077922077922078</v>
+        <v>1.681818181818182</v>
       </c>
       <c r="S10" t="n">
-        <v>72.81818181818183</v>
+        <v>75.7878787878788</v>
       </c>
       <c r="T10" t="n">
-        <v>5758441.558441558</v>
+        <v>10422727.27272727</v>
       </c>
       <c r="U10" t="n">
-        <v>78.98701298701299</v>
+        <v>80.2878787878788</v>
       </c>
       <c r="V10" t="n">
-        <v>26.48051948051948</v>
+        <v>27.36507936507936</v>
       </c>
       <c r="W10" t="n">
-        <v>183.1298701298701</v>
+        <v>181.9907647907648</v>
       </c>
       <c r="X10" t="n">
-        <v>1.519480519480519</v>
+        <v>2.09033189033189</v>
       </c>
       <c r="Y10" t="n">
-        <v>72.81818181818183</v>
+        <v>76.74300144300143</v>
       </c>
       <c r="Z10" t="n">
-        <v>4483766.233766234</v>
+        <v>9904386.724386726</v>
       </c>
       <c r="AA10" t="n">
-        <v>75.46753246753246</v>
+        <v>78.90432900432901</v>
       </c>
       <c r="AB10" t="n">
-        <v>23.06598146504978</v>
+        <v>22.92738095238096</v>
       </c>
       <c r="AC10" t="n">
-        <v>180.9081755890762</v>
+        <v>181.1284391534392</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>1.448677248677249</v>
       </c>
       <c r="AE10" t="n">
-        <v>70.93197278911565</v>
+        <v>74.16137566137566</v>
       </c>
       <c r="AF10" t="n">
-        <v>3747331.903776004</v>
+        <v>10028121.69312169</v>
       </c>
       <c r="AG10" t="n">
-        <v>77.44626836241743</v>
+        <v>79.80502645502646</v>
       </c>
       <c r="AH10" t="n">
-        <v>25.64821126078891</v>
+        <v>25.13693257207189</v>
       </c>
       <c r="AI10" t="n">
-        <v>180.1106954639563</v>
+        <v>178.5784474555373</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.147917730992265</v>
+        <v>1.654790049991288</v>
       </c>
       <c r="AK10" t="n">
-        <v>70.20423623995053</v>
+        <v>74.44299987937758</v>
       </c>
       <c r="AL10" t="n">
-        <v>2599596.262088499</v>
+        <v>7368828.823395386</v>
       </c>
       <c r="AM10" t="n">
-        <v>73.8911620642987</v>
+        <v>78.86989197592914</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18752</v>
+        <v>25178</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -691,126 +691,122 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>26.675</v>
+        <v>25.24242424242424</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.2261363636363</v>
+        <v>185.9015151515152</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>68.77272727272728</v>
+        <v>71.45454545454545</v>
       </c>
       <c r="T2" t="n">
-        <v>1648238.636363636</v>
+        <v>2948333.333333333</v>
       </c>
       <c r="U2" t="n">
-        <v>72.34659090909091</v>
+        <v>74.88030303030304</v>
       </c>
       <c r="V2" t="n">
-        <v>26.62337662337663</v>
+        <v>24.19277777777778</v>
       </c>
       <c r="W2" t="n">
-        <v>180.5064935064935</v>
+        <v>183.2383333333334</v>
       </c>
       <c r="X2" t="n">
-        <v>1.402597402597403</v>
+        <v>2.237777777777777</v>
       </c>
       <c r="Y2" t="n">
-        <v>77.05194805194806</v>
+        <v>80.72388888888889</v>
       </c>
       <c r="Z2" t="n">
-        <v>13182467.53246753</v>
+        <v>39090555.55555555</v>
       </c>
       <c r="AA2" t="n">
-        <v>79.42857142857143</v>
+        <v>85.03222222222223</v>
       </c>
       <c r="AB2" t="n">
-        <v>24.5224358974359</v>
+        <v>25.04091614906832</v>
       </c>
       <c r="AC2" t="n">
-        <v>182.5160256410257</v>
+        <v>181.1581866804693</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>65.21314102564102</v>
+        <v>69.33653381642512</v>
       </c>
       <c r="AF2" t="n">
-        <v>1102403.846153846</v>
+        <v>2341206.004140787</v>
       </c>
       <c r="AG2" t="n">
-        <v>70.7603021978022</v>
+        <v>73.27387853692203</v>
       </c>
       <c r="AH2" t="n">
-        <v>26.26303854875284</v>
+        <v>23.83827504686085</v>
       </c>
       <c r="AI2" t="n">
-        <v>177.8795351473923</v>
+        <v>183.609871580211</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.374716553287982</v>
+        <v>2.164974147553758</v>
       </c>
       <c r="AK2" t="n">
-        <v>74.23526077097506</v>
+        <v>77.92448611023357</v>
       </c>
       <c r="AL2" t="n">
-        <v>6823299.319727891</v>
+        <v>31973076.99395547</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.27607709750566</v>
+        <v>83.46667219519387</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17924</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -838,124 +834,124 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>lhUkVMh2</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>25.73863636363636</v>
+        <v>26.34848484848485</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.4090909090909</v>
+        <v>181.9242424242424</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>1.318181818181819</v>
       </c>
       <c r="S3" t="n">
-        <v>68.65909090909091</v>
+        <v>74.92424242424242</v>
       </c>
       <c r="T3" t="n">
-        <v>1723579.545454545</v>
+        <v>6925757.575757575</v>
       </c>
       <c r="U3" t="n">
-        <v>71.68181818181819</v>
+        <v>77.25757575757575</v>
       </c>
       <c r="V3" t="n">
-        <v>23.4025974025974</v>
+        <v>27.05909090909091</v>
       </c>
       <c r="W3" t="n">
-        <v>183.9090909090909</v>
+        <v>184.0212121212121</v>
       </c>
       <c r="X3" t="n">
-        <v>1.324675324675325</v>
+        <v>1.703030303030303</v>
       </c>
       <c r="Y3" t="n">
-        <v>75.22077922077922</v>
+        <v>77.27575757575758</v>
       </c>
       <c r="Z3" t="n">
-        <v>12789610.38961039</v>
+        <v>12523484.84848485</v>
       </c>
       <c r="AA3" t="n">
-        <v>80.14285714285714</v>
+        <v>79.18030303030302</v>
       </c>
       <c r="AB3" t="n">
-        <v>23.53084415584416</v>
+        <v>24.55277777777778</v>
       </c>
       <c r="AC3" t="n">
-        <v>180.0397727272727</v>
+        <v>180.1472222222222</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>1.15515873015873</v>
       </c>
       <c r="AE3" t="n">
-        <v>65.61282467532467</v>
+        <v>71.04484126984127</v>
       </c>
       <c r="AF3" t="n">
-        <v>1428571.428571428</v>
+        <v>4555436.507936508</v>
       </c>
       <c r="AG3" t="n">
-        <v>71.59253246753246</v>
+        <v>74.85476190476192</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.94886024585272</v>
+        <v>25.11819581633823</v>
       </c>
       <c r="AI3" t="n">
-        <v>180.7263694951665</v>
+        <v>183.9721480990057</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.325725026852847</v>
+        <v>1.275711746686979</v>
       </c>
       <c r="AK3" t="n">
-        <v>74.00951784222461</v>
+        <v>75.43411756515472</v>
       </c>
       <c r="AL3" t="n">
-        <v>7708321.398734934</v>
+        <v>10037794.03574295</v>
       </c>
       <c r="AM3" t="n">
-        <v>78.50404284520826</v>
+        <v>78.62515971300802</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15220</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -983,124 +979,124 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>26.41558441558442</v>
+        <v>25.77638888888889</v>
       </c>
       <c r="Q4" t="n">
-        <v>182</v>
+        <v>182.5833333333333</v>
       </c>
       <c r="R4" t="n">
-        <v>1.337662337662338</v>
+        <v>1.261805555555556</v>
       </c>
       <c r="S4" t="n">
-        <v>74.96103896103897</v>
+        <v>74.42569444444445</v>
       </c>
       <c r="T4" t="n">
-        <v>6997402.597402598</v>
+        <v>7825746.527777778</v>
       </c>
       <c r="U4" t="n">
-        <v>77.28571428571429</v>
+        <v>78.80486111111111</v>
       </c>
       <c r="V4" t="n">
-        <v>26.92077922077922</v>
+        <v>24.3</v>
       </c>
       <c r="W4" t="n">
-        <v>183.9012987012987</v>
+        <v>180.3818181818181</v>
       </c>
       <c r="X4" t="n">
-        <v>1.693506493506494</v>
+        <v>1.460606060606061</v>
       </c>
       <c r="Y4" t="n">
-        <v>77.19740259740261</v>
+        <v>76.57121212121213</v>
       </c>
       <c r="Z4" t="n">
-        <v>12364285.71428571</v>
+        <v>13136969.6969697</v>
       </c>
       <c r="AA4" t="n">
-        <v>79.19350649350648</v>
+        <v>81.36515151515151</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.55317460317461</v>
+        <v>22.94450013923698</v>
       </c>
       <c r="AC4" t="n">
-        <v>179.9674603174603</v>
+        <v>183.5636730715678</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.132993197278912</v>
+        <v>1.085491506544138</v>
       </c>
       <c r="AE4" t="n">
-        <v>70.91145124716554</v>
+        <v>69.55047340573655</v>
       </c>
       <c r="AF4" t="n">
-        <v>4394342.403628118</v>
+        <v>4120735.867446393</v>
       </c>
       <c r="AG4" t="n">
-        <v>74.68503401360545</v>
+        <v>77.44472291840714</v>
       </c>
       <c r="AH4" t="n">
-        <v>25.05369165209944</v>
+        <v>25.79805282436861</v>
       </c>
       <c r="AI4" t="n">
-        <v>184.0475555134335</v>
+        <v>180.5075573549258</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.260133878112649</v>
+        <v>1.206535569693464</v>
       </c>
       <c r="AK4" t="n">
-        <v>75.1578150558469</v>
+        <v>73.86423109054688</v>
       </c>
       <c r="AL4" t="n">
-        <v>9768109.173493957</v>
+        <v>7619112.846218109</v>
       </c>
       <c r="AM4" t="n">
-        <v>78.55966070638782</v>
+        <v>78.12593021014074</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25178</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1125,123 +1121,127 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>25.25064935064935</v>
+        <v>24.33198653198653</v>
       </c>
       <c r="Q5" t="n">
-        <v>185.8441558441559</v>
+        <v>182.1239057239057</v>
       </c>
       <c r="R5" t="n">
+        <v>1.522558922558922</v>
+      </c>
+      <c r="S5" t="n">
+        <v>76.77239057239058</v>
+      </c>
+      <c r="T5" t="n">
+        <v>14688552.18855219</v>
+      </c>
+      <c r="U5" t="n">
+        <v>81.44074074074074</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.43454545454545</v>
+      </c>
+      <c r="W5" t="n">
+        <v>181.2672727272727</v>
+      </c>
+      <c r="X5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
-        <v>71.51818181818182</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3005714.285714286</v>
-      </c>
-      <c r="U5" t="n">
-        <v>74.96883116883116</v>
-      </c>
-      <c r="V5" t="n">
-        <v>24.27175925925926</v>
-      </c>
-      <c r="W5" t="n">
-        <v>183.4763888888889</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.216666666666666</v>
-      </c>
       <c r="Y5" t="n">
-        <v>80.28842592592594</v>
+        <v>70.26363636363637</v>
       </c>
       <c r="Z5" t="n">
-        <v>36460648.14814814</v>
+        <v>2277727.272727272</v>
       </c>
       <c r="AA5" t="n">
-        <v>84.63796296296296</v>
+        <v>73.91363636363636</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.1303090801538</v>
+        <v>22.69656647746818</v>
       </c>
       <c r="AC5" t="n">
-        <v>181.4213028689737</v>
+        <v>181.0201324389405</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.379398864809081</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>74.95114594083248</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>12125371.0870313</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>81.5780637254902</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25.37042402042402</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>180.4712398712398</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1</v>
       </c>
-      <c r="AE5" t="n">
-        <v>69.2725845410628</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2262303.559104801</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>73.17126096815538</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>23.78706209457467</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>183.4086376326846</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.233638093395253</v>
-      </c>
       <c r="AK5" t="n">
-        <v>78.39821106074008</v>
+        <v>69.10199245199246</v>
       </c>
       <c r="AL5" t="n">
-        <v>36262156.65542533</v>
+        <v>1914997.641247641</v>
       </c>
       <c r="AM5" t="n">
-        <v>83.81905245650893</v>
+        <v>73.45247530247531</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>17924</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1266,99 +1266,99 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
       <c r="P6" t="n">
-        <v>24.41443001443001</v>
+        <v>25.71428571428572</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.132178932179</v>
+        <v>181.4805194805195</v>
       </c>
       <c r="R6" t="n">
-        <v>1.551803751803752</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>76.88282828282829</v>
+        <v>68.64935064935064</v>
       </c>
       <c r="T6" t="n">
-        <v>14999278.4992785</v>
+        <v>1723051.948051948</v>
       </c>
       <c r="U6" t="n">
-        <v>81.45569985569986</v>
+        <v>71.68831168831169</v>
       </c>
       <c r="V6" t="n">
-        <v>25.54049586776859</v>
+        <v>23.42424242424243</v>
       </c>
       <c r="W6" t="n">
-        <v>181.4157024793388</v>
+        <v>184.030303030303</v>
       </c>
       <c r="X6" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>75.16666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>80.10606060606061</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>23.64749536178108</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>180.1270871985158</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" t="n">
-        <v>70.31239669421488</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2263388.429752066</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>73.8396694214876</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>22.57919983782987</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>181.2851135190919</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.343056169836355</v>
-      </c>
       <c r="AE6" t="n">
-        <v>74.85098223499926</v>
+        <v>65.74118738404452</v>
       </c>
       <c r="AF6" t="n">
-        <v>11684246.64602683</v>
+        <v>1444897.959183673</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.53119747899159</v>
+        <v>71.71799628942486</v>
       </c>
       <c r="AH6" t="n">
-        <v>25.07700884973612</v>
+        <v>23.90329991645781</v>
       </c>
       <c r="AI6" t="n">
-        <v>180.2076206621661</v>
+        <v>180.8474310776943</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>1.324456975772766</v>
       </c>
       <c r="AK6" t="n">
-        <v>68.94986326804509</v>
+        <v>74.27036340852131</v>
       </c>
       <c r="AL6" t="n">
-        <v>1933114.738796557</v>
+        <v>8111560.15037594</v>
       </c>
       <c r="AM6" t="n">
-        <v>73.63212040484768</v>
+        <v>78.71767961570593</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1366,27 +1366,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1411,103 +1411,99 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>24.68831168831169</v>
+        <v>26.61558441558442</v>
       </c>
       <c r="Q7" t="n">
-        <v>182.1181818181819</v>
+        <v>183.1935064935064</v>
       </c>
       <c r="R7" t="n">
-        <v>1.319480519480519</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>72.90259740259741</v>
+        <v>68.74025974025975</v>
       </c>
       <c r="T7" t="n">
-        <v>5346753.246753247</v>
+        <v>1644415.584415585</v>
       </c>
       <c r="U7" t="n">
-        <v>77.89740259740259</v>
+        <v>72.3961038961039</v>
       </c>
       <c r="V7" t="n">
-        <v>22.18253968253968</v>
+        <v>26.78787878787879</v>
       </c>
       <c r="W7" t="n">
-        <v>183.0682539682539</v>
+        <v>180.4393939393939</v>
       </c>
       <c r="X7" t="n">
-        <v>1.188888888888889</v>
+        <v>1.393939393939394</v>
       </c>
       <c r="Y7" t="n">
-        <v>71.36031746031746</v>
+        <v>76.95454545454545</v>
       </c>
       <c r="Z7" t="n">
-        <v>4507619.047619048</v>
+        <v>12849242.42424243</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.39206349206349</v>
+        <v>79.24242424242424</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.52467218771566</v>
+        <v>24.54945054945055</v>
       </c>
       <c r="AC7" t="n">
-        <v>181.467692004338</v>
+        <v>182.6373626373627</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.185980479148181</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>71.12885734003746</v>
+        <v>65.26739926739927</v>
       </c>
       <c r="AF7" t="n">
-        <v>3666877.649610569</v>
+        <v>1120009.157509157</v>
       </c>
       <c r="AG7" t="n">
-        <v>76.03582766439909</v>
+        <v>70.72605965463109</v>
       </c>
       <c r="AH7" t="n">
-        <v>23.54197319953623</v>
+        <v>26.01058201058201</v>
       </c>
       <c r="AI7" t="n">
-        <v>182.5731831194016</v>
+        <v>177.7853835978836</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.271416258811217</v>
+        <v>1.381613756613757</v>
       </c>
       <c r="AK7" t="n">
-        <v>70.46462174613436</v>
+        <v>74.23743386243386</v>
       </c>
       <c r="AL7" t="n">
-        <v>3528691.681800925</v>
+        <v>7054034.391534392</v>
       </c>
       <c r="AM7" t="n">
-        <v>77.16448117708622</v>
+        <v>77.43320105820106</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>AaLVdEGK</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1515,27 +1511,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1560,99 +1556,103 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.59888888888889</v>
+        <v>24.53636363636364</v>
       </c>
       <c r="Q8" t="n">
-        <v>182.9111111111111</v>
+        <v>182.6045454545455</v>
       </c>
       <c r="R8" t="n">
-        <v>1.253888888888889</v>
+        <v>1.289393939393939</v>
       </c>
       <c r="S8" t="n">
-        <v>74.38500000000001</v>
+        <v>72.81969696969696</v>
       </c>
       <c r="T8" t="n">
-        <v>7680597.222222222</v>
+        <v>5294545.454545454</v>
       </c>
       <c r="U8" t="n">
-        <v>78.91055555555556</v>
+        <v>77.89696969696969</v>
       </c>
       <c r="V8" t="n">
-        <v>24.38701298701298</v>
+        <v>21.97962962962963</v>
       </c>
       <c r="W8" t="n">
-        <v>180.5090909090909</v>
+        <v>183.2962962962963</v>
       </c>
       <c r="X8" t="n">
-        <v>1.472727272727273</v>
+        <v>1.17037037037037</v>
       </c>
       <c r="Y8" t="n">
-        <v>76.60649350649351</v>
+        <v>71.28703703703704</v>
       </c>
       <c r="Z8" t="n">
-        <v>13120000</v>
+        <v>4523888.888888889</v>
       </c>
       <c r="AA8" t="n">
-        <v>81.32597402597402</v>
+        <v>79.52407407407408</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.85038787444802</v>
+        <v>24.51952495974235</v>
       </c>
       <c r="AC8" t="n">
-        <v>183.5035565103234</v>
+        <v>181.1567517828388</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.07327843418069</v>
+        <v>1.198458707154359</v>
       </c>
       <c r="AE8" t="n">
-        <v>69.28816087838644</v>
+        <v>71.09477800782149</v>
       </c>
       <c r="AF8" t="n">
-        <v>3911140.947607113</v>
+        <v>3678023.924545664</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.34037474638978</v>
+        <v>76.04179894179894</v>
       </c>
       <c r="AH8" t="n">
-        <v>25.77928337326833</v>
+        <v>23.77119095501449</v>
       </c>
       <c r="AI8" t="n">
-        <v>180.5302872566031</v>
+        <v>182.4464914170796</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.200840012118207</v>
+        <v>1.288874524168642</v>
       </c>
       <c r="AK8" t="n">
-        <v>73.57410283951637</v>
+        <v>70.54205870382341</v>
       </c>
       <c r="AL8" t="n">
-        <v>7146739.582472665</v>
+        <v>3561251.406545524</v>
       </c>
       <c r="AM8" t="n">
-        <v>77.84603541821586</v>
+        <v>77.10856137326725</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29778</v>
+        <v>33150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1705,237 +1705,1542 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>24.28571428571428</v>
+        <v>23.09090909090909</v>
       </c>
       <c r="Q9" t="n">
-        <v>181.1688311688312</v>
+        <v>184.030303030303</v>
       </c>
       <c r="R9" t="n">
-        <v>1.688311688311688</v>
+        <v>1.075757575757576</v>
       </c>
       <c r="S9" t="n">
-        <v>75.8961038961039</v>
+        <v>72.87878787878788</v>
       </c>
       <c r="T9" t="n">
-        <v>10606493.50649351</v>
+        <v>5827272.727272727</v>
       </c>
       <c r="U9" t="n">
-        <v>80.2987012987013</v>
+        <v>79.03030303030303</v>
       </c>
       <c r="V9" t="n">
-        <v>27.33080808080808</v>
+        <v>26.54545454545454</v>
       </c>
       <c r="W9" t="n">
-        <v>181.9578282828283</v>
+        <v>183.3181818181818</v>
       </c>
       <c r="X9" t="n">
-        <v>2.113131313131313</v>
+        <v>1.515151515151515</v>
       </c>
       <c r="Y9" t="n">
-        <v>76.76376262626263</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="Z9" t="n">
-        <v>9961792.929292928</v>
+        <v>4332575.757575758</v>
       </c>
       <c r="AA9" t="n">
-        <v>78.93901515151515</v>
+        <v>75.36363636363636</v>
       </c>
       <c r="AB9" t="n">
-        <v>23.00918367346939</v>
+        <v>23.09549689440993</v>
       </c>
       <c r="AC9" t="n">
-        <v>181.2886621315193</v>
+        <v>180.4854641131815</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.438151927437642</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>74.08475056689342</v>
+        <v>70.86507936507938</v>
       </c>
       <c r="AF9" t="n">
-        <v>9713390.022675736</v>
+        <v>3670035.369220152</v>
       </c>
       <c r="AG9" t="n">
-        <v>79.74359410430839</v>
+        <v>77.31694271911662</v>
       </c>
       <c r="AH9" t="n">
-        <v>25.10195885770576</v>
+        <v>25.58957980425372</v>
       </c>
       <c r="AI9" t="n">
-        <v>178.6847129521665</v>
+        <v>179.6847002635046</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.572941293742377</v>
+        <v>1.154052167639124</v>
       </c>
       <c r="AK9" t="n">
-        <v>74.35191060874109</v>
+        <v>70.46049783549783</v>
       </c>
       <c r="AL9" t="n">
-        <v>7151296.649042392</v>
+        <v>2770177.12058473</v>
       </c>
       <c r="AM9" t="n">
-        <v>78.74329833608084</v>
+        <v>73.96561500094109</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>181.3030303030303</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75.7878787878788</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10422727.27272727</v>
+      </c>
+      <c r="U10" t="n">
+        <v>80.2878787878788</v>
+      </c>
+      <c r="V10" t="n">
+        <v>27.36507936507936</v>
+      </c>
+      <c r="W10" t="n">
+        <v>181.9907647907648</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.09033189033189</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>76.74300144300143</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9904386.724386726</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>78.90432900432901</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>22.92738095238096</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>181.1284391534392</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.448677248677249</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>74.16137566137566</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10028121.69312169</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>79.80502645502646</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>25.13693257207189</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>178.5784474555373</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.654790049991288</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>74.44299987937758</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>7368828.823395386</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>78.86989197592914</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>SIFtcwDc</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>26.78787878787879</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>180.4393939393939</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.393939393939394</v>
+      </c>
+      <c r="S11" t="n">
+        <v>76.95454545454545</v>
+      </c>
+      <c r="T11" t="n">
+        <v>12849242.42424243</v>
+      </c>
+      <c r="U11" t="n">
+        <v>79.24242424242424</v>
+      </c>
+      <c r="V11" t="n">
+        <v>26.34848484848485</v>
+      </c>
+      <c r="W11" t="n">
+        <v>181.9242424242424</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.318181818181819</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>74.92424242424242</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6925757.575757575</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>77.25757575757575</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>26.01058201058201</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>177.7853835978836</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.381613756613757</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>74.23743386243386</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>7054034.391534392</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>77.43320105820106</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>24.55277777777778</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>180.1472222222222</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.15515873015873</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>71.04484126984127</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4555436.507936508</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>74.85476190476192</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>180.3818181818181</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.460606060606061</v>
+      </c>
+      <c r="S12" t="n">
+        <v>76.57121212121213</v>
+      </c>
+      <c r="T12" t="n">
+        <v>13136969.6969697</v>
+      </c>
+      <c r="U12" t="n">
+        <v>81.36515151515151</v>
+      </c>
+      <c r="V12" t="n">
+        <v>26.61558441558442</v>
+      </c>
+      <c r="W12" t="n">
+        <v>183.1935064935064</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>68.74025974025975</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1644415.584415585</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>72.3961038961039</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>25.79805282436861</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>180.5075573549258</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.206535569693464</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>73.86423109054688</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>7619112.846218109</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>78.12593021014074</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24.54945054945055</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>182.6373626373627</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>65.26739926739927</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1120009.157509157</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>70.72605965463109</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>27.36507936507936</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>181.9907647907648</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.09033189033189</v>
+      </c>
+      <c r="S13" t="n">
+        <v>76.74300144300143</v>
+      </c>
+      <c r="T13" t="n">
+        <v>9904386.724386726</v>
+      </c>
+      <c r="U13" t="n">
+        <v>78.90432900432901</v>
+      </c>
+      <c r="V13" t="n">
+        <v>24.33198653198653</v>
+      </c>
+      <c r="W13" t="n">
+        <v>182.1239057239057</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.522558922558922</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>76.77239057239058</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>14688552.18855219</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>81.44074074074074</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>25.13693257207189</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>178.5784474555373</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.654790049991288</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>74.44299987937758</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>7368828.823395386</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>78.86989197592914</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22.69656647746818</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>181.0201324389405</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.379398864809081</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>74.95114594083248</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>12125371.0870313</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>81.5780637254902</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>27.05909090909091</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>184.0212121212121</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.703030303030303</v>
+      </c>
+      <c r="S14" t="n">
+        <v>77.27575757575758</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12523484.84848485</v>
+      </c>
+      <c r="U14" t="n">
+        <v>79.18030303030302</v>
+      </c>
+      <c r="V14" t="n">
+        <v>25.77638888888889</v>
+      </c>
+      <c r="W14" t="n">
+        <v>182.5833333333333</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.261805555555556</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>74.42569444444445</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7825746.527777778</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>78.80486111111111</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>25.11819581633823</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>183.9721480990057</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.275711746686979</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>75.43411756515472</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>10037794.03574295</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>78.62515971300802</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>22.94450013923698</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>183.5636730715678</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.085491506544138</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>69.55047340573655</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>4120735.867446393</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>77.44472291840714</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rainville n 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>26.54545454545454</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>183.3181818181818</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.515151515151515</v>
+      </c>
+      <c r="S15" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4332575.757575758</v>
+      </c>
+      <c r="U15" t="n">
+        <v>75.36363636363636</v>
+      </c>
+      <c r="V15" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="W15" t="n">
+        <v>181.4805194805195</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>68.64935064935064</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1723051.948051948</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>71.68831168831169</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>25.58957980425372</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>179.6847002635046</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.154052167639124</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>70.46049783549783</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2770177.12058473</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>73.96561500094109</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>23.64749536178108</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>180.1270871985158</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>65.74118738404452</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1444897.959183673</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>71.71799628942486</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>MLmY2yB1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>23.42424242424243</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>184.030303030303</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="S16" t="n">
+        <v>75.16666666666667</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="U16" t="n">
+        <v>80.10606060606061</v>
+      </c>
+      <c r="V16" t="n">
+        <v>23.09090909090909</v>
+      </c>
+      <c r="W16" t="n">
+        <v>184.030303030303</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.075757575757576</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>72.87878787878788</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5827272.727272727</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>79.03030303030303</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>23.90329991645781</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>180.8474310776943</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.324456975772766</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>74.27036340852131</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>8111560.15037594</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>78.71767961570593</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23.09549689440993</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>180.4854641131815</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>70.86507936507938</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>3670035.369220152</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>77.31694271911662</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>24.19277777777778</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>183.2383333333334</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.237777777777777</v>
+      </c>
+      <c r="S17" t="n">
+        <v>80.72388888888889</v>
+      </c>
+      <c r="T17" t="n">
+        <v>39090555.55555555</v>
+      </c>
+      <c r="U17" t="n">
+        <v>85.03222222222223</v>
+      </c>
+      <c r="V17" t="n">
+        <v>24.53636363636364</v>
+      </c>
+      <c r="W17" t="n">
+        <v>182.6045454545455</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.289393939393939</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>72.81969696969696</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5294545.454545454</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>77.89696969696969</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>23.83827504686085</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>183.609871580211</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.164974147553758</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>77.92448611023357</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>31973076.99395547</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>83.46667219519387</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>24.51952495974235</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>181.1567517828388</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.198458707154359</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>71.09477800782149</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3678023.924545664</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>76.04179894179894</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>25.43454545454545</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>181.2672727272727</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>70.26363636363637</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2277727.272727272</v>
+      </c>
+      <c r="U18" t="n">
+        <v>73.91363636363636</v>
+      </c>
+      <c r="V18" t="n">
+        <v>25.24242424242424</v>
+      </c>
+      <c r="W18" t="n">
+        <v>185.9015151515152</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>71.45454545454545</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2948333.333333333</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>74.88030303030304</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>25.37042402042402</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>180.4712398712398</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>69.10199245199246</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1914997.641247641</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>73.45247530247531</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>25.04091614906832</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>181.1581866804693</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>69.33653381642512</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2341206.004140787</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>73.27387853692203</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>KYsw3uKl</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>551</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>23.06493506493506</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>183.8441558441559</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.077922077922078</v>
-      </c>
-      <c r="S10" t="n">
-        <v>72.81818181818183</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5758441.558441558</v>
-      </c>
-      <c r="U10" t="n">
-        <v>78.98701298701299</v>
-      </c>
-      <c r="V10" t="n">
-        <v>26.48051948051948</v>
-      </c>
-      <c r="W10" t="n">
-        <v>183.1298701298701</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.519480519480519</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>72.81818181818183</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4483766.233766234</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>75.46753246753246</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>23.06598146504978</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>180.9081755890762</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>70.93197278911565</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3747331.903776004</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>77.44626836241743</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>25.64821126078891</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>180.1106954639563</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.147917730992265</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>70.20423623995053</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2599596.262088499</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>73.8911620642987</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
+      <c r="P19" t="n">
+        <v>21.97962962962963</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>183.2962962962963</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.17037037037037</v>
+      </c>
+      <c r="S19" t="n">
+        <v>71.28703703703704</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4523888.888888889</v>
+      </c>
+      <c r="U19" t="n">
+        <v>79.52407407407408</v>
+      </c>
+      <c r="V19" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="W19" t="n">
+        <v>181.3030303030303</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.681818181818182</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>75.7878787878788</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>10422727.27272727</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>80.2878787878788</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>23.77119095501449</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>182.4464914170796</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.288874524168642</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70.54205870382341</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3561251.406545524</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>77.10856137326725</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>22.92738095238096</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>181.1284391534392</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.448677248677249</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>74.16137566137566</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>10028121.69312169</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>79.80502645502646</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO19"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1936,1311 +1936,6 @@
       <c r="AO10" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>26.78787878787879</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>180.4393939393939</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.393939393939394</v>
-      </c>
-      <c r="S11" t="n">
-        <v>76.95454545454545</v>
-      </c>
-      <c r="T11" t="n">
-        <v>12849242.42424243</v>
-      </c>
-      <c r="U11" t="n">
-        <v>79.24242424242424</v>
-      </c>
-      <c r="V11" t="n">
-        <v>26.34848484848485</v>
-      </c>
-      <c r="W11" t="n">
-        <v>181.9242424242424</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.318181818181819</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>74.92424242424242</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6925757.575757575</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>77.25757575757575</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>26.01058201058201</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>177.7853835978836</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.381613756613757</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>74.23743386243386</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>7054034.391534392</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>77.43320105820106</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>24.55277777777778</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>180.1472222222222</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.15515873015873</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>71.04484126984127</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>4555436.507936508</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>74.85476190476192</v>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>180.3818181818181</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.460606060606061</v>
-      </c>
-      <c r="S12" t="n">
-        <v>76.57121212121213</v>
-      </c>
-      <c r="T12" t="n">
-        <v>13136969.6969697</v>
-      </c>
-      <c r="U12" t="n">
-        <v>81.36515151515151</v>
-      </c>
-      <c r="V12" t="n">
-        <v>26.61558441558442</v>
-      </c>
-      <c r="W12" t="n">
-        <v>183.1935064935064</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>68.74025974025975</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1644415.584415585</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>72.3961038961039</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>25.79805282436861</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>180.5075573549258</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.206535569693464</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>73.86423109054688</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>7619112.846218109</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>78.12593021014074</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>24.54945054945055</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>182.6373626373627</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>65.26739926739927</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1120009.157509157</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>70.72605965463109</v>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>lb31RXzP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>551</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>27.36507936507936</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>181.9907647907648</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.09033189033189</v>
-      </c>
-      <c r="S13" t="n">
-        <v>76.74300144300143</v>
-      </c>
-      <c r="T13" t="n">
-        <v>9904386.724386726</v>
-      </c>
-      <c r="U13" t="n">
-        <v>78.90432900432901</v>
-      </c>
-      <c r="V13" t="n">
-        <v>24.33198653198653</v>
-      </c>
-      <c r="W13" t="n">
-        <v>182.1239057239057</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.522558922558922</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>76.77239057239058</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>14688552.18855219</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>81.44074074074074</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>25.13693257207189</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>178.5784474555373</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.654790049991288</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>74.44299987937758</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>7368828.823395386</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>78.86989197592914</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>22.69656647746818</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>181.0201324389405</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.379398864809081</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>74.95114594083248</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>12125371.0870313</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>81.5780637254902</v>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>551</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>27.05909090909091</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>184.0212121212121</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.703030303030303</v>
-      </c>
-      <c r="S14" t="n">
-        <v>77.27575757575758</v>
-      </c>
-      <c r="T14" t="n">
-        <v>12523484.84848485</v>
-      </c>
-      <c r="U14" t="n">
-        <v>79.18030303030302</v>
-      </c>
-      <c r="V14" t="n">
-        <v>25.77638888888889</v>
-      </c>
-      <c r="W14" t="n">
-        <v>182.5833333333333</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.261805555555556</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>74.42569444444445</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>7825746.527777778</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>78.80486111111111</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>25.11819581633823</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>183.9721480990057</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.275711746686979</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>75.43411756515472</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>10037794.03574295</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>78.62515971300802</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>22.94450013923698</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>183.5636730715678</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.085491506544138</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>69.55047340573655</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>4120735.867446393</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>77.44472291840714</v>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rainville n 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>551</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>26.54545454545454</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>183.3181818181818</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.515151515151515</v>
-      </c>
-      <c r="S15" t="n">
-        <v>72.66666666666667</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4332575.757575758</v>
-      </c>
-      <c r="U15" t="n">
-        <v>75.36363636363636</v>
-      </c>
-      <c r="V15" t="n">
-        <v>25.71428571428572</v>
-      </c>
-      <c r="W15" t="n">
-        <v>181.4805194805195</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>68.64935064935064</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1723051.948051948</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>71.68831168831169</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>25.58957980425372</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>179.6847002635046</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.154052167639124</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>70.46049783549783</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2770177.12058473</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>73.96561500094109</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>23.64749536178108</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>180.1270871985158</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>65.74118738404452</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1444897.959183673</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>71.71799628942486</v>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>h89kUbu5</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="n">
-        <v>551</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>23.42424242424243</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>184.030303030303</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="S16" t="n">
-        <v>75.16666666666667</v>
-      </c>
-      <c r="T16" t="n">
-        <v>12700000</v>
-      </c>
-      <c r="U16" t="n">
-        <v>80.10606060606061</v>
-      </c>
-      <c r="V16" t="n">
-        <v>23.09090909090909</v>
-      </c>
-      <c r="W16" t="n">
-        <v>184.030303030303</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.075757575757576</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>72.87878787878788</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5827272.727272727</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>79.03030303030303</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>23.90329991645781</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>180.8474310776943</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.324456975772766</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>74.27036340852131</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>8111560.15037594</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>78.71767961570593</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>23.09549689440993</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>180.4854641131815</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>70.86507936507938</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>3670035.369220152</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>77.31694271911662</v>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>551</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>24.19277777777778</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>183.2383333333334</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.237777777777777</v>
-      </c>
-      <c r="S17" t="n">
-        <v>80.72388888888889</v>
-      </c>
-      <c r="T17" t="n">
-        <v>39090555.55555555</v>
-      </c>
-      <c r="U17" t="n">
-        <v>85.03222222222223</v>
-      </c>
-      <c r="V17" t="n">
-        <v>24.53636363636364</v>
-      </c>
-      <c r="W17" t="n">
-        <v>182.6045454545455</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.289393939393939</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>72.81969696969696</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5294545.454545454</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>77.89696969696969</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>23.83827504686085</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>183.609871580211</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.164974147553758</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>77.92448611023357</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>31973076.99395547</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>83.46667219519387</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>24.51952495974235</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>181.1567517828388</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.198458707154359</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>71.09477800782149</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>3678023.924545664</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>76.04179894179894</v>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="n">
-        <v>551</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>25.43454545454545</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>181.2672727272727</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>70.26363636363637</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2277727.272727272</v>
-      </c>
-      <c r="U18" t="n">
-        <v>73.91363636363636</v>
-      </c>
-      <c r="V18" t="n">
-        <v>25.24242424242424</v>
-      </c>
-      <c r="W18" t="n">
-        <v>185.9015151515152</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>71.45454545454545</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2948333.333333333</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>74.88030303030304</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>25.37042402042402</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>180.4712398712398</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>69.10199245199246</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1914997.641247641</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>73.45247530247531</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>25.04091614906832</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>181.1581866804693</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>69.33653381642512</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2341206.004140787</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>73.27387853692203</v>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>KYsw3uKl</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>EgvyJSJo</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>551</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>21.97962962962963</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>183.2962962962963</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.17037037037037</v>
-      </c>
-      <c r="S19" t="n">
-        <v>71.28703703703704</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4523888.888888889</v>
-      </c>
-      <c r="U19" t="n">
-        <v>79.52407407407408</v>
-      </c>
-      <c r="V19" t="n">
-        <v>24.27272727272727</v>
-      </c>
-      <c r="W19" t="n">
-        <v>181.3030303030303</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.681818181818182</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>75.7878787878788</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>10422727.27272727</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>80.2878787878788</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>23.77119095501449</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>182.4464914170796</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.288874524168642</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>70.54205870382341</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>3561251.406545524</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>77.10856137326725</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>22.92738095238096</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>181.1284391534392</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.448677248677249</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>74.16137566137566</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>10028121.69312169</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>79.80502645502646</v>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,76 +693,76 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>25.24242424242424</v>
+        <v>25.42828282828283</v>
       </c>
       <c r="Q2" t="n">
-        <v>185.9015151515152</v>
+        <v>186.0010101010101</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>71.45454545454545</v>
+        <v>71.62525252525252</v>
       </c>
       <c r="T2" t="n">
-        <v>2948333.333333333</v>
+        <v>3053333.333333333</v>
       </c>
       <c r="U2" t="n">
-        <v>74.88030303030304</v>
+        <v>74.96464646464648</v>
       </c>
       <c r="V2" t="n">
-        <v>24.19277777777778</v>
+        <v>24.09873737373737</v>
       </c>
       <c r="W2" t="n">
-        <v>183.2383333333334</v>
+        <v>183.334696969697</v>
       </c>
       <c r="X2" t="n">
-        <v>2.237777777777777</v>
+        <v>2.368636363636363</v>
       </c>
       <c r="Y2" t="n">
-        <v>80.72388888888889</v>
+        <v>81.41737373737374</v>
       </c>
       <c r="Z2" t="n">
-        <v>39090555.55555555</v>
+        <v>45821388.88888888</v>
       </c>
       <c r="AA2" t="n">
-        <v>85.03222222222223</v>
+        <v>85.47505050505052</v>
       </c>
       <c r="AB2" t="n">
-        <v>25.04091614906832</v>
+        <v>25.0766601487616</v>
       </c>
       <c r="AC2" t="n">
-        <v>181.1581866804693</v>
+        <v>181.4758281573499</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>69.33653381642512</v>
+        <v>69.05151637144391</v>
       </c>
       <c r="AF2" t="n">
-        <v>2341206.004140787</v>
+        <v>2152162.027451883</v>
       </c>
       <c r="AG2" t="n">
-        <v>73.27387853692203</v>
+        <v>73.07147458017023</v>
       </c>
       <c r="AH2" t="n">
-        <v>23.83827504686085</v>
+        <v>24.35357711066883</v>
       </c>
       <c r="AI2" t="n">
-        <v>183.609871580211</v>
+        <v>183.7778814376628</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.164974147553758</v>
+        <v>2.170970369141809</v>
       </c>
       <c r="AK2" t="n">
-        <v>77.92448611023357</v>
+        <v>78.33921742673677</v>
       </c>
       <c r="AL2" t="n">
-        <v>31973076.99395547</v>
+        <v>31346844.5163153</v>
       </c>
       <c r="AM2" t="n">
-        <v>83.46667219519387</v>
+        <v>83.30446751068848</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -838,76 +838,76 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26.34848484848485</v>
+        <v>26.41414141414142</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.9242424242424</v>
+        <v>181.969696969697</v>
       </c>
       <c r="R3" t="n">
-        <v>1.318181818181819</v>
+        <v>1.313131313131313</v>
       </c>
       <c r="S3" t="n">
-        <v>74.92424242424242</v>
+        <v>75.02020202020202</v>
       </c>
       <c r="T3" t="n">
-        <v>6925757.575757575</v>
+        <v>7049494.94949495</v>
       </c>
       <c r="U3" t="n">
-        <v>77.25757575757575</v>
+        <v>77.34343434343434</v>
       </c>
       <c r="V3" t="n">
-        <v>27.05909090909091</v>
+        <v>26.87676767676767</v>
       </c>
       <c r="W3" t="n">
-        <v>184.0212121212121</v>
+        <v>183.6626262626263</v>
       </c>
       <c r="X3" t="n">
-        <v>1.703030303030303</v>
+        <v>1.697979797979798</v>
       </c>
       <c r="Y3" t="n">
-        <v>77.27575757575758</v>
+        <v>77.2848484848485</v>
       </c>
       <c r="Z3" t="n">
-        <v>12523484.84848485</v>
+        <v>12612626.26262626</v>
       </c>
       <c r="AA3" t="n">
-        <v>79.18030303030302</v>
+        <v>79.32222222222222</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.55277777777778</v>
+        <v>24.36851851851852</v>
       </c>
       <c r="AC3" t="n">
-        <v>180.1472222222222</v>
+        <v>180.1598765432099</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.15515873015873</v>
+        <v>1.152821869488536</v>
       </c>
       <c r="AE3" t="n">
-        <v>71.04484126984127</v>
+        <v>70.44964726631393</v>
       </c>
       <c r="AF3" t="n">
-        <v>4555436.507936508</v>
+        <v>4106093.474426808</v>
       </c>
       <c r="AG3" t="n">
-        <v>74.85476190476192</v>
+        <v>74.53280423280424</v>
       </c>
       <c r="AH3" t="n">
-        <v>25.11819581633823</v>
+        <v>25.04176017385512</v>
       </c>
       <c r="AI3" t="n">
-        <v>183.9721480990057</v>
+        <v>184.1004796850515</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.275711746686979</v>
+        <v>1.234072381389203</v>
       </c>
       <c r="AK3" t="n">
-        <v>75.43411756515472</v>
+        <v>74.91639583708726</v>
       </c>
       <c r="AL3" t="n">
-        <v>10037794.03574295</v>
+        <v>9224402.373034984</v>
       </c>
       <c r="AM3" t="n">
-        <v>78.62515971300802</v>
+        <v>78.35592658115878</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -983,76 +983,76 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>25.77638888888889</v>
+        <v>25.44365079365079</v>
       </c>
       <c r="Q4" t="n">
-        <v>182.5833333333333</v>
+        <v>182.6825396825397</v>
       </c>
       <c r="R4" t="n">
-        <v>1.261805555555556</v>
+        <v>1.24484126984127</v>
       </c>
       <c r="S4" t="n">
-        <v>74.42569444444445</v>
+        <v>74.30674603174603</v>
       </c>
       <c r="T4" t="n">
-        <v>7825746.527777778</v>
+        <v>7487728.174603174</v>
       </c>
       <c r="U4" t="n">
-        <v>78.80486111111111</v>
+        <v>78.9202380952381</v>
       </c>
       <c r="V4" t="n">
-        <v>24.3</v>
+        <v>24.28080808080808</v>
       </c>
       <c r="W4" t="n">
-        <v>180.3818181818181</v>
+        <v>180.6585858585859</v>
       </c>
       <c r="X4" t="n">
-        <v>1.460606060606061</v>
+        <v>1.468686868686869</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.57121212121213</v>
+        <v>76.64343434343434</v>
       </c>
       <c r="Z4" t="n">
-        <v>13136969.6969697</v>
+        <v>13280202.02020202</v>
       </c>
       <c r="AA4" t="n">
-        <v>81.36515151515151</v>
+        <v>81.41515151515152</v>
       </c>
       <c r="AB4" t="n">
-        <v>22.94450013923698</v>
+        <v>22.73019586002042</v>
       </c>
       <c r="AC4" t="n">
-        <v>183.5636730715678</v>
+        <v>183.7276338995637</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.085491506544138</v>
+        <v>1.056994337696092</v>
       </c>
       <c r="AE4" t="n">
-        <v>69.55047340573655</v>
+        <v>69.22677063027942</v>
       </c>
       <c r="AF4" t="n">
-        <v>4120735.867446393</v>
+        <v>3807276.29258331</v>
       </c>
       <c r="AG4" t="n">
-        <v>77.44472291840714</v>
+        <v>77.3546830038058</v>
       </c>
       <c r="AH4" t="n">
-        <v>25.79805282436861</v>
+        <v>25.9434108776214</v>
       </c>
       <c r="AI4" t="n">
-        <v>180.5075573549258</v>
+        <v>180.4779218345008</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.206535569693464</v>
+        <v>1.215732707837971</v>
       </c>
       <c r="AK4" t="n">
-        <v>73.86423109054688</v>
+        <v>73.18065141486194</v>
       </c>
       <c r="AL4" t="n">
-        <v>7619112.846218109</v>
+        <v>6348505.786367629</v>
       </c>
       <c r="AM4" t="n">
-        <v>78.12593021014074</v>
+        <v>77.36636088083456</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1128,76 +1128,76 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>24.33198653198653</v>
+        <v>24.46374859708193</v>
       </c>
       <c r="Q5" t="n">
-        <v>182.1239057239057</v>
+        <v>182.1129068462402</v>
       </c>
       <c r="R5" t="n">
-        <v>1.522558922558922</v>
+        <v>1.580695847362514</v>
       </c>
       <c r="S5" t="n">
-        <v>76.77239057239058</v>
+        <v>76.90886644219978</v>
       </c>
       <c r="T5" t="n">
-        <v>14688552.18855219</v>
+        <v>15121661.05499439</v>
       </c>
       <c r="U5" t="n">
-        <v>81.44074074074074</v>
+        <v>81.48574635241302</v>
       </c>
       <c r="V5" t="n">
-        <v>25.43454545454545</v>
+        <v>25.52657342657342</v>
       </c>
       <c r="W5" t="n">
-        <v>181.2672727272727</v>
+        <v>181.4825174825175</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>70.26363636363637</v>
+        <v>70.33356643356643</v>
       </c>
       <c r="Z5" t="n">
-        <v>2277727.272727272</v>
+        <v>2269790.20979021</v>
       </c>
       <c r="AA5" t="n">
-        <v>73.91363636363636</v>
+        <v>73.87202797202798</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.69656647746818</v>
+        <v>22.35326654053434</v>
       </c>
       <c r="AC5" t="n">
-        <v>181.0201324389405</v>
+        <v>181.2356438481826</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.379398864809081</v>
+        <v>1.294599243206054</v>
       </c>
       <c r="AE5" t="n">
-        <v>74.95114594083248</v>
+        <v>74.56465284944387</v>
       </c>
       <c r="AF5" t="n">
-        <v>12125371.0870313</v>
+        <v>11093302.94690976</v>
       </c>
       <c r="AG5" t="n">
-        <v>81.5780637254902</v>
+        <v>81.46870915032679</v>
       </c>
       <c r="AH5" t="n">
-        <v>25.37042402042402</v>
+        <v>24.98823825746903</v>
       </c>
       <c r="AI5" t="n">
-        <v>180.4712398712398</v>
+        <v>180.1866680328218</v>
       </c>
       <c r="AJ5" t="n">
         <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>69.10199245199246</v>
+        <v>68.90263155647771</v>
       </c>
       <c r="AL5" t="n">
-        <v>1914997.641247641</v>
+        <v>1932415.767992691</v>
       </c>
       <c r="AM5" t="n">
-        <v>73.45247530247531</v>
+        <v>73.67772825465134</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1273,76 +1273,76 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>25.71428571428572</v>
+        <v>25.77272727272727</v>
       </c>
       <c r="Q6" t="n">
-        <v>181.4805194805195</v>
+        <v>181.4909090909091</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>68.64935064935064</v>
+        <v>68.52727272727273</v>
       </c>
       <c r="T6" t="n">
-        <v>1723051.948051948</v>
+        <v>1701590.909090909</v>
       </c>
       <c r="U6" t="n">
-        <v>71.68831168831169</v>
+        <v>71.52727272727273</v>
       </c>
       <c r="V6" t="n">
-        <v>23.42424242424243</v>
+        <v>23.55454545454545</v>
       </c>
       <c r="W6" t="n">
-        <v>184.030303030303</v>
+        <v>183.5363636363636</v>
       </c>
       <c r="X6" t="n">
-        <v>1.333333333333334</v>
+        <v>1.327272727272728</v>
       </c>
       <c r="Y6" t="n">
-        <v>75.16666666666667</v>
+        <v>75.16363636363636</v>
       </c>
       <c r="Z6" t="n">
-        <v>12700000</v>
+        <v>12521818.18181818</v>
       </c>
       <c r="AA6" t="n">
-        <v>80.10606060606061</v>
+        <v>79.92727272727272</v>
       </c>
       <c r="AB6" t="n">
-        <v>23.64749536178108</v>
+        <v>23.31038961038961</v>
       </c>
       <c r="AC6" t="n">
-        <v>180.1270871985158</v>
+        <v>180.4461038961039</v>
       </c>
       <c r="AD6" t="n">
         <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>65.74118738404452</v>
+        <v>65.23311688311688</v>
       </c>
       <c r="AF6" t="n">
-        <v>1444897.959183673</v>
+        <v>1382142.857142857</v>
       </c>
       <c r="AG6" t="n">
-        <v>71.71799628942486</v>
+        <v>71.67402597402597</v>
       </c>
       <c r="AH6" t="n">
-        <v>23.90329991645781</v>
+        <v>23.79634502923977</v>
       </c>
       <c r="AI6" t="n">
-        <v>180.8474310776943</v>
+        <v>180.637030075188</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.324456975772766</v>
+        <v>1.295864661654135</v>
       </c>
       <c r="AK6" t="n">
-        <v>74.27036340852131</v>
+        <v>73.51023391812866</v>
       </c>
       <c r="AL6" t="n">
-        <v>8111560.15037594</v>
+        <v>7142789.264828739</v>
       </c>
       <c r="AM6" t="n">
-        <v>78.71767961570593</v>
+        <v>78.34925856307436</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1418,76 +1418,76 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>26.61558441558442</v>
+        <v>26.90272727272727</v>
       </c>
       <c r="Q7" t="n">
-        <v>183.1935064935064</v>
+        <v>183.6363636363636</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>68.74025974025975</v>
+        <v>69.04727272727273</v>
       </c>
       <c r="T7" t="n">
-        <v>1644415.584415585</v>
+        <v>1686795.454545455</v>
       </c>
       <c r="U7" t="n">
-        <v>72.3961038961039</v>
+        <v>72.39272727272727</v>
       </c>
       <c r="V7" t="n">
-        <v>26.78787878787879</v>
+        <v>26.49494949494949</v>
       </c>
       <c r="W7" t="n">
-        <v>180.4393939393939</v>
+        <v>180.3636363636363</v>
       </c>
       <c r="X7" t="n">
-        <v>1.393939393939394</v>
+        <v>1.404040404040404</v>
       </c>
       <c r="Y7" t="n">
-        <v>76.95454545454545</v>
+        <v>77.08080808080808</v>
       </c>
       <c r="Z7" t="n">
-        <v>12849242.42424243</v>
+        <v>13345959.5959596</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.24242424242424</v>
+        <v>79.56565656565657</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.54945054945055</v>
+        <v>24.23699633699634</v>
       </c>
       <c r="AC7" t="n">
-        <v>182.6373626373627</v>
+        <v>182.3485347985348</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>65.26739926739927</v>
+        <v>64.90622710622711</v>
       </c>
       <c r="AF7" t="n">
-        <v>1120009.157509157</v>
+        <v>1070911.172161172</v>
       </c>
       <c r="AG7" t="n">
-        <v>70.72605965463109</v>
+        <v>70.84871794871795</v>
       </c>
       <c r="AH7" t="n">
-        <v>26.01058201058201</v>
+        <v>26.3805114638448</v>
       </c>
       <c r="AI7" t="n">
-        <v>177.7853835978836</v>
+        <v>178.4634038800706</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.381613756613757</v>
+        <v>1.384038800705468</v>
       </c>
       <c r="AK7" t="n">
-        <v>74.23743386243386</v>
+        <v>74.26631393298061</v>
       </c>
       <c r="AL7" t="n">
-        <v>7054034.391534392</v>
+        <v>6771748.23633157</v>
       </c>
       <c r="AM7" t="n">
-        <v>77.43320105820106</v>
+        <v>77.20392416225749</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -1567,76 +1567,76 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>24.53636363636364</v>
+        <v>24.77979797979798</v>
       </c>
       <c r="Q8" t="n">
-        <v>182.6045454545455</v>
+        <v>181.8383838383838</v>
       </c>
       <c r="R8" t="n">
-        <v>1.289393939393939</v>
+        <v>1.312121212121212</v>
       </c>
       <c r="S8" t="n">
-        <v>72.81969696969696</v>
+        <v>72.87676767676767</v>
       </c>
       <c r="T8" t="n">
-        <v>5294545.454545454</v>
+        <v>5334949.494949494</v>
       </c>
       <c r="U8" t="n">
-        <v>77.89696969696969</v>
+        <v>77.87171717171718</v>
       </c>
       <c r="V8" t="n">
-        <v>21.97962962962963</v>
+        <v>22.34197530864198</v>
       </c>
       <c r="W8" t="n">
-        <v>183.2962962962963</v>
+        <v>182.8086419753087</v>
       </c>
       <c r="X8" t="n">
-        <v>1.17037037037037</v>
+        <v>1.21358024691358</v>
       </c>
       <c r="Y8" t="n">
-        <v>71.28703703703704</v>
+        <v>71.41358024691358</v>
       </c>
       <c r="Z8" t="n">
-        <v>4523888.888888889</v>
+        <v>4474814.814814814</v>
       </c>
       <c r="AA8" t="n">
-        <v>79.52407407407408</v>
+        <v>79.32716049382715</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.51952495974235</v>
+        <v>24.33929529944023</v>
       </c>
       <c r="AC8" t="n">
-        <v>181.1567517828388</v>
+        <v>181.6953301127214</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.198458707154359</v>
+        <v>1.17287017866728</v>
       </c>
       <c r="AE8" t="n">
-        <v>71.09477800782149</v>
+        <v>70.81098075300973</v>
       </c>
       <c r="AF8" t="n">
-        <v>3678023.924545664</v>
+        <v>3520005.367686527</v>
       </c>
       <c r="AG8" t="n">
-        <v>76.04179894179894</v>
+        <v>76.01199294532628</v>
       </c>
       <c r="AH8" t="n">
-        <v>23.77119095501449</v>
+        <v>23.50724899646468</v>
       </c>
       <c r="AI8" t="n">
-        <v>182.4464914170796</v>
+        <v>182.9505709976298</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.288874524168642</v>
+        <v>1.249196772726185</v>
       </c>
       <c r="AK8" t="n">
-        <v>70.54205870382341</v>
+        <v>69.72645183429498</v>
       </c>
       <c r="AL8" t="n">
-        <v>3561251.406545524</v>
+        <v>3209204.64140072</v>
       </c>
       <c r="AM8" t="n">
-        <v>77.10856137326725</v>
+        <v>76.59459647106706</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1712,76 +1712,76 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>23.09090909090909</v>
+        <v>23.07070707070707</v>
       </c>
       <c r="Q9" t="n">
-        <v>184.030303030303</v>
+        <v>183.7979797979798</v>
       </c>
       <c r="R9" t="n">
-        <v>1.075757575757576</v>
+        <v>1.080808080808081</v>
       </c>
       <c r="S9" t="n">
-        <v>72.87878787878788</v>
+        <v>72.77777777777777</v>
       </c>
       <c r="T9" t="n">
-        <v>5827272.727272727</v>
+        <v>5702020.202020202</v>
       </c>
       <c r="U9" t="n">
-        <v>79.03030303030303</v>
+        <v>78.96969696969697</v>
       </c>
       <c r="V9" t="n">
-        <v>26.54545454545454</v>
+        <v>26.41414141414141</v>
       </c>
       <c r="W9" t="n">
-        <v>183.3181818181818</v>
+        <v>182.959595959596</v>
       </c>
       <c r="X9" t="n">
-        <v>1.515151515151515</v>
+        <v>1.535353535353535</v>
       </c>
       <c r="Y9" t="n">
-        <v>72.66666666666667</v>
+        <v>73</v>
       </c>
       <c r="Z9" t="n">
-        <v>4332575.757575758</v>
+        <v>4680303.030303031</v>
       </c>
       <c r="AA9" t="n">
-        <v>75.36363636363636</v>
+        <v>75.63636363636364</v>
       </c>
       <c r="AB9" t="n">
-        <v>23.09549689440993</v>
+        <v>22.97724484318687</v>
       </c>
       <c r="AC9" t="n">
-        <v>180.4854641131815</v>
+        <v>180.9038896557012</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>70.86507936507938</v>
+        <v>70.81128747795414</v>
       </c>
       <c r="AF9" t="n">
-        <v>3670035.369220152</v>
+        <v>3713356.912813435</v>
       </c>
       <c r="AG9" t="n">
-        <v>77.31694271911662</v>
+        <v>77.50759144237405</v>
       </c>
       <c r="AH9" t="n">
-        <v>25.58957980425372</v>
+        <v>25.81280628925557</v>
       </c>
       <c r="AI9" t="n">
-        <v>179.6847002635046</v>
+        <v>180.5799236324599</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.154052167639124</v>
+        <v>1.139738482129786</v>
       </c>
       <c r="AK9" t="n">
-        <v>70.46049783549783</v>
+        <v>70.22057880391213</v>
       </c>
       <c r="AL9" t="n">
-        <v>2770177.12058473</v>
+        <v>2470797.092735499</v>
       </c>
       <c r="AM9" t="n">
-        <v>73.96561500094109</v>
+        <v>73.81658284013355</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1857,76 +1857,76 @@
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>24.27272727272727</v>
+        <v>24.43636363636363</v>
       </c>
       <c r="Q10" t="n">
-        <v>181.3030303030303</v>
+        <v>181.6272727272728</v>
       </c>
       <c r="R10" t="n">
-        <v>1.681818181818182</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
-        <v>75.7878787878788</v>
+        <v>75.94545454545455</v>
       </c>
       <c r="T10" t="n">
-        <v>10422727.27272727</v>
+        <v>10700909.09090909</v>
       </c>
       <c r="U10" t="n">
-        <v>80.2878787878788</v>
+        <v>80.17272727272727</v>
       </c>
       <c r="V10" t="n">
-        <v>27.36507936507936</v>
+        <v>27.32139577594123</v>
       </c>
       <c r="W10" t="n">
-        <v>181.9907647907648</v>
+        <v>182.1897153351699</v>
       </c>
       <c r="X10" t="n">
-        <v>2.09033189033189</v>
+        <v>2.110743801652893</v>
       </c>
       <c r="Y10" t="n">
-        <v>76.74300144300143</v>
+        <v>76.74462809917355</v>
       </c>
       <c r="Z10" t="n">
-        <v>9904386.724386726</v>
+        <v>9928227.731864097</v>
       </c>
       <c r="AA10" t="n">
-        <v>78.90432900432901</v>
+        <v>78.92075298438935</v>
       </c>
       <c r="AB10" t="n">
-        <v>22.92738095238096</v>
+        <v>22.79789682539683</v>
       </c>
       <c r="AC10" t="n">
-        <v>181.1284391534392</v>
+        <v>181.006626984127</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.448677248677249</v>
+        <v>1.381111111111111</v>
       </c>
       <c r="AE10" t="n">
-        <v>74.16137566137566</v>
+        <v>73.49960317460318</v>
       </c>
       <c r="AF10" t="n">
-        <v>10028121.69312169</v>
+        <v>8770315.476190476</v>
       </c>
       <c r="AG10" t="n">
-        <v>79.80502645502646</v>
+        <v>79.63281746031745</v>
       </c>
       <c r="AH10" t="n">
-        <v>25.13693257207189</v>
+        <v>24.9947868171482</v>
       </c>
       <c r="AI10" t="n">
-        <v>178.5784474555373</v>
+        <v>178.8774824356305</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.654790049991288</v>
+        <v>1.547997708580315</v>
       </c>
       <c r="AK10" t="n">
-        <v>74.44299987937758</v>
+        <v>74.13616586840622</v>
       </c>
       <c r="AL10" t="n">
-        <v>7368828.823395386</v>
+        <v>6738461.055003413</v>
       </c>
       <c r="AM10" t="n">
-        <v>78.86989197592914</v>
+        <v>78.61128767876586</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1936,6 +1936,1166 @@
       <c r="AO10" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45527.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>24.09873737373737</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>183.334696969697</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.368636363636363</v>
+      </c>
+      <c r="S11" t="n">
+        <v>81.41737373737374</v>
+      </c>
+      <c r="T11" t="n">
+        <v>45821388.88888888</v>
+      </c>
+      <c r="U11" t="n">
+        <v>85.47505050505052</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24.77979797979798</v>
+      </c>
+      <c r="W11" t="n">
+        <v>181.8383838383838</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.312121212121212</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>72.87676767676767</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5334949.494949494</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>77.87171717171718</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>24.35357711066883</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>183.7778814376628</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.170970369141809</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>78.33921742673677</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>31346844.5163153</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>83.30446751068848</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>24.33929529944023</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>181.6953301127214</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.17287017866728</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>70.81098075300973</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3520005.367686527</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>76.01199294532628</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>27.32139577594123</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>182.1897153351699</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.110743801652893</v>
+      </c>
+      <c r="S12" t="n">
+        <v>76.74462809917355</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9928227.731864097</v>
+      </c>
+      <c r="U12" t="n">
+        <v>78.92075298438935</v>
+      </c>
+      <c r="V12" t="n">
+        <v>24.46374859708193</v>
+      </c>
+      <c r="W12" t="n">
+        <v>182.1129068462402</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.580695847362514</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>76.90886644219978</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>15121661.05499439</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>81.48574635241302</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24.9947868171482</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>178.8774824356305</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.547997708580315</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>74.13616586840622</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>6738461.055003413</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>78.61128767876586</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22.35326654053434</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>181.2356438481826</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.294599243206054</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>74.56465284944387</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>11093302.94690976</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>81.46870915032679</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>24.28080808080808</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>180.6585858585859</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.468686868686869</v>
+      </c>
+      <c r="S13" t="n">
+        <v>76.64343434343434</v>
+      </c>
+      <c r="T13" t="n">
+        <v>13280202.02020202</v>
+      </c>
+      <c r="U13" t="n">
+        <v>81.41515151515152</v>
+      </c>
+      <c r="V13" t="n">
+        <v>26.90272727272727</v>
+      </c>
+      <c r="W13" t="n">
+        <v>183.6363636363636</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>69.04727272727273</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1686795.454545455</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>72.39272727272727</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>25.9434108776214</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>180.4779218345008</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.215732707837971</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>73.18065141486194</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>6348505.786367629</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>77.36636088083456</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24.23699633699634</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>182.3485347985348</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>64.90622710622711</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1070911.172161172</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>70.84871794871795</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>25.52657342657342</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>181.4825174825175</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>70.33356643356643</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2269790.20979021</v>
+      </c>
+      <c r="U14" t="n">
+        <v>73.87202797202798</v>
+      </c>
+      <c r="V14" t="n">
+        <v>25.42828282828283</v>
+      </c>
+      <c r="W14" t="n">
+        <v>186.0010101010101</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>71.62525252525252</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3053333.333333333</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>74.96464646464648</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>24.98823825746903</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>180.1866680328218</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>68.90263155647771</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1932415.767992691</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>73.67772825465134</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25.0766601487616</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>181.4758281573499</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>69.05151637144391</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2152162.027451883</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>73.07147458017023</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>KYsw3uKl</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>26.49494949494949</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>180.3636363636363</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.404040404040404</v>
+      </c>
+      <c r="S15" t="n">
+        <v>77.08080808080808</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13345959.5959596</v>
+      </c>
+      <c r="U15" t="n">
+        <v>79.56565656565657</v>
+      </c>
+      <c r="V15" t="n">
+        <v>26.41414141414142</v>
+      </c>
+      <c r="W15" t="n">
+        <v>181.969696969697</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.313131313131313</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>75.02020202020202</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7049494.94949495</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>77.34343434343434</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>26.3805114638448</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>178.4634038800706</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.384038800705468</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>74.26631393298061</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>6771748.23633157</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>77.20392416225749</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24.36851851851852</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>180.1598765432099</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.152821869488536</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>70.44964726631393</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4106093.474426808</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>74.53280423280424</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rainville n 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>26.41414141414141</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>182.959595959596</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.535353535353535</v>
+      </c>
+      <c r="S16" t="n">
+        <v>73</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4680303.030303031</v>
+      </c>
+      <c r="U16" t="n">
+        <v>75.63636363636364</v>
+      </c>
+      <c r="V16" t="n">
+        <v>25.77272727272727</v>
+      </c>
+      <c r="W16" t="n">
+        <v>181.4909090909091</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>68.52727272727273</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1701590.909090909</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>71.52727272727273</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>25.81280628925557</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>180.5799236324599</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.139738482129786</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>70.22057880391213</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2470797.092735499</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>73.81658284013355</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23.31038961038961</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>180.4461038961039</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>65.23311688311688</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1382142.857142857</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>71.67402597402597</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>23.55454545454545</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>183.5363636363636</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.327272727272728</v>
+      </c>
+      <c r="S17" t="n">
+        <v>75.16363636363636</v>
+      </c>
+      <c r="T17" t="n">
+        <v>12521818.18181818</v>
+      </c>
+      <c r="U17" t="n">
+        <v>79.92727272727272</v>
+      </c>
+      <c r="V17" t="n">
+        <v>23.07070707070707</v>
+      </c>
+      <c r="W17" t="n">
+        <v>183.7979797979798</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.080808080808081</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5702020.202020202</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>78.96969696969697</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>23.79634502923977</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>180.637030075188</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.295864661654135</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>73.51023391812866</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>7142789.264828739</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>78.34925856307436</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>22.97724484318687</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>180.9038896557012</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>70.81128747795414</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3713356.912813435</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>77.50759144237405</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>22.34197530864198</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>182.8086419753087</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.21358024691358</v>
+      </c>
+      <c r="S18" t="n">
+        <v>71.41358024691358</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4474814.814814814</v>
+      </c>
+      <c r="U18" t="n">
+        <v>79.32716049382715</v>
+      </c>
+      <c r="V18" t="n">
+        <v>24.43636363636363</v>
+      </c>
+      <c r="W18" t="n">
+        <v>181.6272727272728</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>75.94545454545455</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>10700909.09090909</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>80.17272727272727</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>23.50724899646468</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>182.9505709976298</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.249196772726185</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>69.72645183429498</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3209204.64140072</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>76.59459647106706</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>22.79789682539683</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>181.006626984127</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.381111111111111</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>73.49960317460318</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>8770315.476190476</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>79.63281746031745</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO18"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45527.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25178</v>
+        <v>48229</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -691,122 +691,126 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
       <c r="P2" t="n">
-        <v>25.42828282828283</v>
+        <v>24.22654671717171</v>
       </c>
       <c r="Q2" t="n">
-        <v>186.0010101010101</v>
+        <v>183.3402462121213</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2.335795454545454</v>
       </c>
       <c r="S2" t="n">
-        <v>71.62525252525252</v>
+        <v>81.08421717171717</v>
       </c>
       <c r="T2" t="n">
-        <v>3053333.333333333</v>
+        <v>42712673.6111111</v>
       </c>
       <c r="U2" t="n">
-        <v>74.96464646464648</v>
+        <v>85.15318813131313</v>
       </c>
       <c r="V2" t="n">
-        <v>24.09873737373737</v>
+        <v>24.84646464646465</v>
       </c>
       <c r="W2" t="n">
-        <v>183.334696969697</v>
+        <v>181.9141414141415</v>
       </c>
       <c r="X2" t="n">
-        <v>2.368636363636363</v>
+        <v>1.326262626262626</v>
       </c>
       <c r="Y2" t="n">
-        <v>81.41737373737374</v>
+        <v>73.07979797979799</v>
       </c>
       <c r="Z2" t="n">
-        <v>45821388.88888888</v>
+        <v>5501919.191919192</v>
       </c>
       <c r="AA2" t="n">
-        <v>85.47505050505052</v>
+        <v>77.96464646464648</v>
       </c>
       <c r="AB2" t="n">
-        <v>25.0766601487616</v>
+        <v>24.2928133914589</v>
       </c>
       <c r="AC2" t="n">
-        <v>181.4758281573499</v>
+        <v>183.5945186779165</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>2.256332199791952</v>
       </c>
       <c r="AE2" t="n">
-        <v>69.05151637144391</v>
+        <v>78.85379385836042</v>
       </c>
       <c r="AF2" t="n">
-        <v>2152162.027451883</v>
+        <v>34468818.72642322</v>
       </c>
       <c r="AG2" t="n">
-        <v>73.07147458017023</v>
+        <v>83.68346172661188</v>
       </c>
       <c r="AH2" t="n">
-        <v>24.35357711066883</v>
+        <v>24.30159688674182</v>
       </c>
       <c r="AI2" t="n">
-        <v>183.7778814376628</v>
+        <v>181.5365999539912</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.170970369141809</v>
+        <v>1.156997162794264</v>
       </c>
       <c r="AK2" t="n">
-        <v>78.33921742673677</v>
+        <v>70.97367916570813</v>
       </c>
       <c r="AL2" t="n">
-        <v>31346844.5163153</v>
+        <v>3587664.097845257</v>
       </c>
       <c r="AM2" t="n">
-        <v>83.30446751068848</v>
+        <v>76.09731040564374</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.5</v>
+        <v>45528.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15220</v>
+        <v>59186</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -834,124 +838,124 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26.41414141414142</v>
+        <v>27.16712580348944</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.969696969697</v>
+        <v>182.1786960514233</v>
       </c>
       <c r="R3" t="n">
-        <v>1.313131313131313</v>
+        <v>2.063911845730027</v>
       </c>
       <c r="S3" t="n">
-        <v>75.02020202020202</v>
+        <v>76.70881542699725</v>
       </c>
       <c r="T3" t="n">
-        <v>7049494.94949495</v>
+        <v>9975518.824609734</v>
       </c>
       <c r="U3" t="n">
-        <v>77.34343434343434</v>
+        <v>79.01166207529845</v>
       </c>
       <c r="V3" t="n">
-        <v>26.87676767676767</v>
+        <v>24.3314253647587</v>
       </c>
       <c r="W3" t="n">
-        <v>183.6626262626263</v>
+        <v>182.1017957351291</v>
       </c>
       <c r="X3" t="n">
-        <v>1.697979797979798</v>
+        <v>1.544332210998878</v>
       </c>
       <c r="Y3" t="n">
-        <v>77.2848484848485</v>
+        <v>76.8098765432099</v>
       </c>
       <c r="Z3" t="n">
-        <v>12612626.26262626</v>
+        <v>14793883.27721661</v>
       </c>
       <c r="AA3" t="n">
-        <v>79.32222222222222</v>
+        <v>81.42312008978676</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.36851851851852</v>
+        <v>25.05617996945044</v>
       </c>
       <c r="AC3" t="n">
-        <v>180.1598765432099</v>
+        <v>178.7930668512149</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.152821869488536</v>
+        <v>1.609981179654695</v>
       </c>
       <c r="AE3" t="n">
-        <v>70.44964726631393</v>
+        <v>74.20464284597412</v>
       </c>
       <c r="AF3" t="n">
-        <v>4106093.474426808</v>
+        <v>6782085.612264334</v>
       </c>
       <c r="AG3" t="n">
-        <v>74.53280423280424</v>
+        <v>78.63371979210707</v>
       </c>
       <c r="AH3" t="n">
-        <v>25.04176017385512</v>
+        <v>22.31067394794175</v>
       </c>
       <c r="AI3" t="n">
-        <v>184.1004796850515</v>
+        <v>181.6569401444789</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.234072381389203</v>
+        <v>1.302932576539388</v>
       </c>
       <c r="AK3" t="n">
-        <v>74.91639583708726</v>
+        <v>74.46557877536981</v>
       </c>
       <c r="AL3" t="n">
-        <v>9224402.373034984</v>
+        <v>11055339.98394679</v>
       </c>
       <c r="AM3" t="n">
-        <v>78.35592658115878</v>
+        <v>81.51037581699346</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21029</v>
+        <v>50186</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -976,127 +980,127 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>25.44365079365079</v>
+        <v>24.39823232323232</v>
       </c>
       <c r="Q4" t="n">
-        <v>182.6825396825397</v>
+        <v>180.6156565656566</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24484126984127</v>
+        <v>1.445959595959596</v>
       </c>
       <c r="S4" t="n">
-        <v>74.30674603174603</v>
+        <v>76.52853535353535</v>
       </c>
       <c r="T4" t="n">
-        <v>7487728.174603174</v>
+        <v>12835126.26262626</v>
       </c>
       <c r="U4" t="n">
-        <v>78.9202380952381</v>
+        <v>81.25858585858586</v>
       </c>
       <c r="V4" t="n">
-        <v>24.28080808080808</v>
+        <v>26.68272727272727</v>
       </c>
       <c r="W4" t="n">
-        <v>180.6585858585859</v>
+        <v>183.4763636363636</v>
       </c>
       <c r="X4" t="n">
-        <v>1.468686868686869</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>76.64343434343434</v>
+        <v>68.82727272727273</v>
       </c>
       <c r="Z4" t="n">
-        <v>13280202.02020202</v>
+        <v>1660295.454545455</v>
       </c>
       <c r="AA4" t="n">
-        <v>81.41515151515152</v>
+        <v>72.40272727272728</v>
       </c>
       <c r="AB4" t="n">
-        <v>22.73019586002042</v>
+        <v>25.56378124799177</v>
       </c>
       <c r="AC4" t="n">
-        <v>183.7276338995637</v>
+        <v>180.2263786246242</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.056994337696092</v>
+        <v>1.237337646109576</v>
       </c>
       <c r="AE4" t="n">
-        <v>69.22677063027942</v>
+        <v>73.25163906918293</v>
       </c>
       <c r="AF4" t="n">
-        <v>3807276.29258331</v>
+        <v>6901785.107355283</v>
       </c>
       <c r="AG4" t="n">
-        <v>77.3546830038058</v>
+        <v>77.86790409071111</v>
       </c>
       <c r="AH4" t="n">
-        <v>25.9434108776214</v>
+        <v>24.52128205128205</v>
       </c>
       <c r="AI4" t="n">
-        <v>180.4779218345008</v>
+        <v>182.4528205128206</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.215732707837971</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>73.18065141486194</v>
+        <v>65.16551282051282</v>
       </c>
       <c r="AL4" t="n">
-        <v>6348505.786367629</v>
+        <v>1097714.743589744</v>
       </c>
       <c r="AM4" t="n">
-        <v>77.36636088083456</v>
+        <v>70.87657509157509</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.66666666666</v>
+        <v>45528.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18523</v>
+        <v>42000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1121,83 +1125,79 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>24.46374859708193</v>
+        <v>25.51212121212121</v>
       </c>
       <c r="Q5" t="n">
-        <v>182.1129068462402</v>
+        <v>181.4060606060606</v>
       </c>
       <c r="R5" t="n">
-        <v>1.580695847362514</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>76.90886644219978</v>
+        <v>70.31969696969696</v>
       </c>
       <c r="T5" t="n">
-        <v>15121661.05499439</v>
+        <v>2270606.060606061</v>
       </c>
       <c r="U5" t="n">
-        <v>81.48574635241302</v>
+        <v>73.88636363636364</v>
       </c>
       <c r="V5" t="n">
-        <v>25.52657342657342</v>
+        <v>25.4040404040404</v>
       </c>
       <c r="W5" t="n">
-        <v>181.4825174825175</v>
+        <v>185.7424242424242</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>70.33356643356643</v>
+        <v>71.54343434343434</v>
       </c>
       <c r="Z5" t="n">
-        <v>2269790.20979021</v>
+        <v>3006161.616161617</v>
       </c>
       <c r="AA5" t="n">
-        <v>73.87202797202798</v>
+        <v>74.93131313131315</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.35326654053434</v>
+        <v>24.90132517055594</v>
       </c>
       <c r="AC5" t="n">
-        <v>181.2356438481826</v>
+        <v>180.5193353654892</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.294599243206054</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>74.56465284944387</v>
+        <v>68.72381037765653</v>
       </c>
       <c r="AF5" t="n">
-        <v>11093302.94690976</v>
+        <v>1895552.631129554</v>
       </c>
       <c r="AG5" t="n">
-        <v>81.46870915032679</v>
+        <v>73.66574024266332</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.98823825746903</v>
+        <v>24.75644409937888</v>
       </c>
       <c r="AI5" t="n">
-        <v>180.1866680328218</v>
+        <v>181.2975874166092</v>
       </c>
       <c r="AJ5" t="n">
         <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>68.90263155647771</v>
+        <v>68.76139291465377</v>
       </c>
       <c r="AL5" t="n">
-        <v>1932415.767992691</v>
+        <v>2122551.68794571</v>
       </c>
       <c r="AM5" t="n">
-        <v>73.67772825465134</v>
+        <v>73.08073383942948</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1206,42 +1206,42 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>17924</v>
+        <v>38223</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1266,127 +1266,127 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>25.77272727272727</v>
+        <v>26.62626262626263</v>
       </c>
       <c r="Q6" t="n">
-        <v>181.4909090909091</v>
+        <v>180.3737373737374</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>1.404040404040404</v>
       </c>
       <c r="S6" t="n">
-        <v>68.52727272727273</v>
+        <v>77.02020202020202</v>
       </c>
       <c r="T6" t="n">
-        <v>1701590.909090909</v>
+        <v>13086363.63636363</v>
       </c>
       <c r="U6" t="n">
-        <v>71.52727272727273</v>
+        <v>79.40404040404042</v>
       </c>
       <c r="V6" t="n">
-        <v>23.55454545454545</v>
+        <v>26.60707070707071</v>
       </c>
       <c r="W6" t="n">
-        <v>183.5363636363636</v>
+        <v>182.0050505050505</v>
       </c>
       <c r="X6" t="n">
-        <v>1.327272727272728</v>
+        <v>1.316161616161616</v>
       </c>
       <c r="Y6" t="n">
-        <v>75.16363636363636</v>
+        <v>74.84949494949495</v>
       </c>
       <c r="Z6" t="n">
-        <v>12521818.18181818</v>
+        <v>6760202.020202019</v>
       </c>
       <c r="AA6" t="n">
-        <v>79.92727272727272</v>
+        <v>77.03030303030303</v>
       </c>
       <c r="AB6" t="n">
-        <v>23.31038961038961</v>
+        <v>26.11115119448453</v>
       </c>
       <c r="AC6" t="n">
-        <v>180.4461038961039</v>
+        <v>178.3595879429213</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>1.357102773769441</v>
       </c>
       <c r="AE6" t="n">
-        <v>65.23311688311688</v>
+        <v>74.14510181176848</v>
       </c>
       <c r="AF6" t="n">
-        <v>1382142.857142857</v>
+        <v>6809851.491101491</v>
       </c>
       <c r="AG6" t="n">
-        <v>71.67402597402597</v>
+        <v>77.35487814654481</v>
       </c>
       <c r="AH6" t="n">
-        <v>23.79634502923977</v>
+        <v>24.1842151675485</v>
       </c>
       <c r="AI6" t="n">
-        <v>180.637030075188</v>
+        <v>179.7189594356261</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.295864661654135</v>
+        <v>1.159876543209877</v>
       </c>
       <c r="AK6" t="n">
-        <v>73.51023391812866</v>
+        <v>70.26975308641974</v>
       </c>
       <c r="AL6" t="n">
-        <v>7142789.264828739</v>
+        <v>4269320.987654322</v>
       </c>
       <c r="AM6" t="n">
-        <v>78.34925856307436</v>
+        <v>74.59276895943563</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18752</v>
+        <v>35322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1411,127 +1411,127 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>26.90272727272727</v>
+        <v>26.25050505050505</v>
       </c>
       <c r="Q7" t="n">
-        <v>183.6363636363636</v>
+        <v>182.8787878787879</v>
       </c>
       <c r="R7" t="n">
+        <v>1.509090909090909</v>
+      </c>
+      <c r="S7" t="n">
+        <v>72.91717171717171</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4676363.636363637</v>
+      </c>
+      <c r="U7" t="n">
+        <v>75.61818181818181</v>
+      </c>
+      <c r="V7" t="n">
+        <v>25.74848484848485</v>
+      </c>
+      <c r="W7" t="n">
+        <v>181.569696969697</v>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
-        <v>69.04727272727273</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1686795.454545455</v>
-      </c>
-      <c r="U7" t="n">
-        <v>72.39272727272727</v>
-      </c>
-      <c r="V7" t="n">
-        <v>26.49494949494949</v>
-      </c>
-      <c r="W7" t="n">
-        <v>180.3636363636363</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.404040404040404</v>
-      </c>
       <c r="Y7" t="n">
-        <v>77.08080808080808</v>
+        <v>68.55858585858586</v>
       </c>
       <c r="Z7" t="n">
-        <v>13345959.5959596</v>
+        <v>1716969.696969697</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.56565656565657</v>
+        <v>71.62121212121211</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.23699633699634</v>
+        <v>25.79900817741824</v>
       </c>
       <c r="AC7" t="n">
-        <v>182.3485347985348</v>
+        <v>180.6714269004337</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.173144437104369</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>70.33023748219827</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2599500.796439203</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>73.89428799627009</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>23.54729437229437</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>180.3294372294372</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1</v>
       </c>
-      <c r="AE7" t="n">
-        <v>64.90622710622711</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1070911.172161172</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>70.84871794871795</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>26.3805114638448</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>178.4634038800706</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.384038800705468</v>
-      </c>
       <c r="AK7" t="n">
-        <v>74.26631393298061</v>
+        <v>65.29859307359308</v>
       </c>
       <c r="AL7" t="n">
-        <v>6771748.23633157</v>
+        <v>1353750</v>
       </c>
       <c r="AM7" t="n">
-        <v>77.20392416225749</v>
+        <v>71.37045454545455</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20484</v>
+        <v>36178</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1558,129 +1558,125 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>24.77979797979798</v>
+        <v>23.43232323232323</v>
       </c>
       <c r="Q8" t="n">
-        <v>181.8383838383838</v>
+        <v>183.5656565656566</v>
       </c>
       <c r="R8" t="n">
-        <v>1.312121212121212</v>
+        <v>1.305050505050505</v>
       </c>
       <c r="S8" t="n">
-        <v>72.87676767676767</v>
+        <v>74.92626262626261</v>
       </c>
       <c r="T8" t="n">
-        <v>5334949.494949494</v>
+        <v>12150303.03030303</v>
       </c>
       <c r="U8" t="n">
-        <v>77.87171717171718</v>
+        <v>79.8979797979798</v>
       </c>
       <c r="V8" t="n">
-        <v>22.34197530864198</v>
+        <v>23.04949494949495</v>
       </c>
       <c r="W8" t="n">
-        <v>182.8086419753087</v>
+        <v>183.4858585858586</v>
       </c>
       <c r="X8" t="n">
-        <v>1.21358024691358</v>
+        <v>1.081818181818182</v>
       </c>
       <c r="Y8" t="n">
-        <v>71.41358024691358</v>
+        <v>72.76161616161615</v>
       </c>
       <c r="Z8" t="n">
-        <v>4474814.814814814</v>
+        <v>5654545.454545455</v>
       </c>
       <c r="AA8" t="n">
-        <v>79.32716049382715</v>
+        <v>78.95656565656566</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.33929529944023</v>
+        <v>23.81578019121879</v>
       </c>
       <c r="AC8" t="n">
-        <v>181.6953301127214</v>
+        <v>180.5411445279866</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17287017866728</v>
+        <v>1.280325814536341</v>
       </c>
       <c r="AE8" t="n">
-        <v>70.81098075300973</v>
+        <v>73.81533927411121</v>
       </c>
       <c r="AF8" t="n">
-        <v>3520005.367686527</v>
+        <v>7407900.77044463</v>
       </c>
       <c r="AG8" t="n">
-        <v>76.01199294532628</v>
+        <v>78.43489046690802</v>
       </c>
       <c r="AH8" t="n">
-        <v>23.50724899646468</v>
+        <v>23.10070163331032</v>
       </c>
       <c r="AI8" t="n">
-        <v>182.9505709976298</v>
+        <v>180.6862970631087</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.249196772726185</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>69.72645183429498</v>
+        <v>70.72872574955909</v>
       </c>
       <c r="AL8" t="n">
-        <v>3209204.64140072</v>
+        <v>3597076.048615904</v>
       </c>
       <c r="AM8" t="n">
-        <v>76.59459647106706</v>
+        <v>77.24756057817652</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>AaLVdEGK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>33150</v>
+        <v>26109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1705,127 +1701,131 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>23.07070707070707</v>
+        <v>22.15555555555556</v>
       </c>
       <c r="Q9" t="n">
-        <v>183.7979797979798</v>
+        <v>183.2024691358025</v>
       </c>
       <c r="R9" t="n">
-        <v>1.080808080808081</v>
+        <v>1.180246913580247</v>
       </c>
       <c r="S9" t="n">
-        <v>72.77777777777777</v>
+        <v>71.32222222222224</v>
       </c>
       <c r="T9" t="n">
-        <v>5702020.202020202</v>
+        <v>4479567.901234568</v>
       </c>
       <c r="U9" t="n">
-        <v>78.96969696969697</v>
+        <v>79.41481481481482</v>
       </c>
       <c r="V9" t="n">
-        <v>26.41414141414141</v>
+        <v>24.52386363636364</v>
       </c>
       <c r="W9" t="n">
-        <v>182.959595959596</v>
+        <v>181.4045454545455</v>
       </c>
       <c r="X9" t="n">
-        <v>1.535353535353535</v>
+        <v>1.693181818181818</v>
       </c>
       <c r="Y9" t="n">
-        <v>73</v>
+        <v>75.88068181818183</v>
       </c>
       <c r="Z9" t="n">
-        <v>4680303.030303031</v>
+        <v>10511136.36363636</v>
       </c>
       <c r="AA9" t="n">
-        <v>75.63636363636364</v>
+        <v>80.15227272727273</v>
       </c>
       <c r="AB9" t="n">
-        <v>22.97724484318687</v>
+        <v>23.13780455202024</v>
       </c>
       <c r="AC9" t="n">
-        <v>180.9038896557012</v>
+        <v>182.322793219852</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>1.226974550503962</v>
       </c>
       <c r="AE9" t="n">
-        <v>70.81128747795414</v>
+        <v>69.85839627873942</v>
       </c>
       <c r="AF9" t="n">
-        <v>3713356.912813435</v>
+        <v>3337593.530289609</v>
       </c>
       <c r="AG9" t="n">
-        <v>77.50759144237405</v>
+        <v>77.01681869328928</v>
       </c>
       <c r="AH9" t="n">
-        <v>25.81280628925557</v>
+        <v>23.08347374847375</v>
       </c>
       <c r="AI9" t="n">
-        <v>180.5799236324599</v>
+        <v>181.0864346764347</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.139738482129786</v>
+        <v>1.422457264957265</v>
       </c>
       <c r="AK9" t="n">
-        <v>70.22057880391213</v>
+        <v>73.84479548229548</v>
       </c>
       <c r="AL9" t="n">
-        <v>2470797.092735499</v>
+        <v>9227575.091575092</v>
       </c>
       <c r="AM9" t="n">
-        <v>73.81658284013355</v>
+        <v>79.46166361416361</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29778</v>
+        <v>67394</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1852,125 +1852,125 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>lhUkVMh2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>24.43636363636363</v>
+        <v>26.87386363636364</v>
       </c>
       <c r="Q10" t="n">
-        <v>181.6272727272728</v>
+        <v>183.7204545454545</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7</v>
+        <v>1.697727272727273</v>
       </c>
       <c r="S10" t="n">
-        <v>75.94545454545455</v>
+        <v>77.19545454545455</v>
       </c>
       <c r="T10" t="n">
-        <v>10700909.09090909</v>
+        <v>12426704.54545454</v>
       </c>
       <c r="U10" t="n">
-        <v>80.17272727272727</v>
+        <v>79.2375</v>
       </c>
       <c r="V10" t="n">
-        <v>27.32139577594123</v>
+        <v>25.49907407407407</v>
       </c>
       <c r="W10" t="n">
-        <v>182.1897153351699</v>
+        <v>182.8518518518518</v>
       </c>
       <c r="X10" t="n">
-        <v>2.110743801652893</v>
+        <v>1.248611111111111</v>
       </c>
       <c r="Y10" t="n">
-        <v>76.74462809917355</v>
+        <v>74.37638888888888</v>
       </c>
       <c r="Z10" t="n">
-        <v>9928227.731864097</v>
+        <v>7611608.796296296</v>
       </c>
       <c r="AA10" t="n">
-        <v>78.92075298438935</v>
+        <v>78.96249999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>22.79789682539683</v>
+        <v>24.90756103965598</v>
       </c>
       <c r="AC10" t="n">
-        <v>181.006626984127</v>
+        <v>183.7455013300731</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.381111111111111</v>
+        <v>1.268704416021238</v>
       </c>
       <c r="AE10" t="n">
-        <v>73.49960317460318</v>
+        <v>74.98421690490834</v>
       </c>
       <c r="AF10" t="n">
-        <v>8770315.476190476</v>
+        <v>9547201.795834405</v>
       </c>
       <c r="AG10" t="n">
-        <v>79.63281746031745</v>
+        <v>78.56660479183701</v>
       </c>
       <c r="AH10" t="n">
-        <v>24.9947868171482</v>
+        <v>22.50400538382994</v>
       </c>
       <c r="AI10" t="n">
-        <v>178.8774824356305</v>
+        <v>183.3731365450664</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.547997708580315</v>
+        <v>1.056994337696092</v>
       </c>
       <c r="AK10" t="n">
-        <v>74.13616586840622</v>
+        <v>69.0204214239302</v>
       </c>
       <c r="AL10" t="n">
-        <v>6738461.055003413</v>
+        <v>3689683.699990717</v>
       </c>
       <c r="AM10" t="n">
-        <v>78.61128767876586</v>
+        <v>77.42214332126613</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45527.65625</v>
+        <v>45534.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48229</v>
+        <v>59186</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1998,124 +1998,124 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>4v0yqlWc</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>24.09873737373737</v>
+        <v>27.16712580348944</v>
       </c>
       <c r="Q11" t="n">
-        <v>183.334696969697</v>
+        <v>182.1786960514233</v>
       </c>
       <c r="R11" t="n">
-        <v>2.368636363636363</v>
+        <v>2.063911845730027</v>
       </c>
       <c r="S11" t="n">
-        <v>81.41737373737374</v>
+        <v>76.70881542699725</v>
       </c>
       <c r="T11" t="n">
-        <v>45821388.88888888</v>
+        <v>9975518.824609734</v>
       </c>
       <c r="U11" t="n">
-        <v>85.47505050505052</v>
+        <v>79.01166207529845</v>
       </c>
       <c r="V11" t="n">
-        <v>24.77979797979798</v>
+        <v>22.15555555555556</v>
       </c>
       <c r="W11" t="n">
-        <v>181.8383838383838</v>
+        <v>183.2024691358025</v>
       </c>
       <c r="X11" t="n">
-        <v>1.312121212121212</v>
+        <v>1.180246913580247</v>
       </c>
       <c r="Y11" t="n">
-        <v>72.87676767676767</v>
+        <v>71.32222222222224</v>
       </c>
       <c r="Z11" t="n">
-        <v>5334949.494949494</v>
+        <v>4479567.901234568</v>
       </c>
       <c r="AA11" t="n">
-        <v>77.87171717171718</v>
+        <v>79.41481481481482</v>
       </c>
       <c r="AB11" t="n">
-        <v>24.35357711066883</v>
+        <v>25.05617996945044</v>
       </c>
       <c r="AC11" t="n">
-        <v>183.7778814376628</v>
+        <v>178.7930668512149</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.170970369141809</v>
+        <v>1.609981179654695</v>
       </c>
       <c r="AE11" t="n">
-        <v>78.33921742673677</v>
+        <v>74.20464284597412</v>
       </c>
       <c r="AF11" t="n">
-        <v>31346844.5163153</v>
+        <v>6782085.612264334</v>
       </c>
       <c r="AG11" t="n">
-        <v>83.30446751068848</v>
+        <v>78.63371979210707</v>
       </c>
       <c r="AH11" t="n">
-        <v>24.33929529944023</v>
+        <v>23.13780455202024</v>
       </c>
       <c r="AI11" t="n">
-        <v>181.6953301127214</v>
+        <v>182.322793219852</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17287017866728</v>
+        <v>1.226974550503962</v>
       </c>
       <c r="AK11" t="n">
-        <v>70.81098075300973</v>
+        <v>69.85839627873942</v>
       </c>
       <c r="AL11" t="n">
-        <v>3520005.367686527</v>
+        <v>3337593.530289609</v>
       </c>
       <c r="AM11" t="n">
-        <v>76.01199294532628</v>
+        <v>77.01681869328928</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.5</v>
+        <v>45535.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59186</v>
+        <v>15220</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2141,126 +2141,122 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>27.32139577594123</v>
+        <v>26.60707070707071</v>
       </c>
       <c r="Q12" t="n">
-        <v>182.1897153351699</v>
+        <v>182.0050505050505</v>
       </c>
       <c r="R12" t="n">
-        <v>2.110743801652893</v>
+        <v>1.316161616161616</v>
       </c>
       <c r="S12" t="n">
-        <v>76.74462809917355</v>
+        <v>74.84949494949495</v>
       </c>
       <c r="T12" t="n">
-        <v>9928227.731864097</v>
+        <v>6760202.020202019</v>
       </c>
       <c r="U12" t="n">
-        <v>78.92075298438935</v>
+        <v>77.03030303030303</v>
       </c>
       <c r="V12" t="n">
-        <v>24.46374859708193</v>
+        <v>25.51212121212121</v>
       </c>
       <c r="W12" t="n">
-        <v>182.1129068462402</v>
+        <v>181.4060606060606</v>
       </c>
       <c r="X12" t="n">
-        <v>1.580695847362514</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>76.90886644219978</v>
+        <v>70.31969696969696</v>
       </c>
       <c r="Z12" t="n">
-        <v>15121661.05499439</v>
+        <v>2270606.060606061</v>
       </c>
       <c r="AA12" t="n">
-        <v>81.48574635241302</v>
+        <v>73.88636363636364</v>
       </c>
       <c r="AB12" t="n">
-        <v>24.9947868171482</v>
+        <v>24.1842151675485</v>
       </c>
       <c r="AC12" t="n">
-        <v>178.8774824356305</v>
+        <v>179.7189594356261</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.547997708580315</v>
+        <v>1.159876543209877</v>
       </c>
       <c r="AE12" t="n">
-        <v>74.13616586840622</v>
+        <v>70.26975308641974</v>
       </c>
       <c r="AF12" t="n">
-        <v>6738461.055003413</v>
+        <v>4269320.987654322</v>
       </c>
       <c r="AG12" t="n">
-        <v>78.61128767876586</v>
+        <v>74.59276895943563</v>
       </c>
       <c r="AH12" t="n">
-        <v>22.35326654053434</v>
+        <v>24.90132517055594</v>
       </c>
       <c r="AI12" t="n">
-        <v>181.2356438481826</v>
+        <v>180.5193353654892</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.294599243206054</v>
+        <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>74.56465284944387</v>
+        <v>68.72381037765653</v>
       </c>
       <c r="AL12" t="n">
-        <v>11093302.94690976</v>
+        <v>1895552.631129554</v>
       </c>
       <c r="AM12" t="n">
-        <v>81.46870915032679</v>
+        <v>73.66574024266332</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>50186</v>
+        <v>20484</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2287,125 +2283,129 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
       <c r="P13" t="n">
-        <v>24.28080808080808</v>
+        <v>24.84646464646465</v>
       </c>
       <c r="Q13" t="n">
-        <v>180.6585858585859</v>
+        <v>181.9141414141415</v>
       </c>
       <c r="R13" t="n">
-        <v>1.468686868686869</v>
+        <v>1.326262626262626</v>
       </c>
       <c r="S13" t="n">
-        <v>76.64343434343434</v>
+        <v>73.07979797979799</v>
       </c>
       <c r="T13" t="n">
-        <v>13280202.02020202</v>
+        <v>5501919.191919192</v>
       </c>
       <c r="U13" t="n">
-        <v>81.41515151515152</v>
+        <v>77.96464646464648</v>
       </c>
       <c r="V13" t="n">
-        <v>26.90272727272727</v>
+        <v>26.25050505050505</v>
       </c>
       <c r="W13" t="n">
-        <v>183.6363636363636</v>
+        <v>182.8787878787879</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.509090909090909</v>
       </c>
       <c r="Y13" t="n">
-        <v>69.04727272727273</v>
+        <v>72.91717171717171</v>
       </c>
       <c r="Z13" t="n">
-        <v>1686795.454545455</v>
+        <v>4676363.636363637</v>
       </c>
       <c r="AA13" t="n">
-        <v>72.39272727272727</v>
+        <v>75.61818181818181</v>
       </c>
       <c r="AB13" t="n">
-        <v>25.9434108776214</v>
+        <v>24.30159688674182</v>
       </c>
       <c r="AC13" t="n">
-        <v>180.4779218345008</v>
+        <v>181.5365999539912</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.215732707837971</v>
+        <v>1.156997162794264</v>
       </c>
       <c r="AE13" t="n">
-        <v>73.18065141486194</v>
+        <v>70.97367916570813</v>
       </c>
       <c r="AF13" t="n">
-        <v>6348505.786367629</v>
+        <v>3587664.097845257</v>
       </c>
       <c r="AG13" t="n">
-        <v>77.36636088083456</v>
+        <v>76.09731040564374</v>
       </c>
       <c r="AH13" t="n">
-        <v>24.23699633699634</v>
+        <v>25.79900817741824</v>
       </c>
       <c r="AI13" t="n">
-        <v>182.3485347985348</v>
+        <v>180.6714269004337</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1</v>
+        <v>1.173144437104369</v>
       </c>
       <c r="AK13" t="n">
-        <v>64.90622710622711</v>
+        <v>70.33023748219827</v>
       </c>
       <c r="AL13" t="n">
-        <v>1070911.172161172</v>
+        <v>2599500.796439203</v>
       </c>
       <c r="AM13" t="n">
-        <v>70.84871794871795</v>
+        <v>73.89428799627009</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45535.66666666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>42000</v>
+        <v>33150</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2431,122 +2431,126 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="P14" t="n">
-        <v>25.52657342657342</v>
+        <v>23.04949494949495</v>
       </c>
       <c r="Q14" t="n">
-        <v>181.4825174825175</v>
+        <v>183.4858585858586</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>1.081818181818182</v>
       </c>
       <c r="S14" t="n">
-        <v>70.33356643356643</v>
+        <v>72.76161616161615</v>
       </c>
       <c r="T14" t="n">
-        <v>2269790.20979021</v>
+        <v>5654545.454545455</v>
       </c>
       <c r="U14" t="n">
-        <v>73.87202797202798</v>
+        <v>78.95656565656566</v>
       </c>
       <c r="V14" t="n">
-        <v>25.42828282828283</v>
+        <v>26.87386363636364</v>
       </c>
       <c r="W14" t="n">
-        <v>186.0010101010101</v>
+        <v>183.7204545454545</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.697727272727273</v>
       </c>
       <c r="Y14" t="n">
-        <v>71.62525252525252</v>
+        <v>77.19545454545455</v>
       </c>
       <c r="Z14" t="n">
-        <v>3053333.333333333</v>
+        <v>12426704.54545454</v>
       </c>
       <c r="AA14" t="n">
-        <v>74.96464646464648</v>
+        <v>79.2375</v>
       </c>
       <c r="AB14" t="n">
-        <v>24.98823825746903</v>
+        <v>23.10070163331032</v>
       </c>
       <c r="AC14" t="n">
-        <v>180.1866680328218</v>
+        <v>180.6862970631087</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>68.90263155647771</v>
+        <v>70.72872574955909</v>
       </c>
       <c r="AF14" t="n">
-        <v>1932415.767992691</v>
+        <v>3597076.048615904</v>
       </c>
       <c r="AG14" t="n">
-        <v>73.67772825465134</v>
+        <v>77.24756057817652</v>
       </c>
       <c r="AH14" t="n">
-        <v>25.0766601487616</v>
+        <v>24.90756103965598</v>
       </c>
       <c r="AI14" t="n">
-        <v>181.4758281573499</v>
+        <v>183.7455013300731</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1</v>
+        <v>1.268704416021238</v>
       </c>
       <c r="AK14" t="n">
-        <v>69.05151637144391</v>
+        <v>74.98421690490834</v>
       </c>
       <c r="AL14" t="n">
-        <v>2152162.027451883</v>
+        <v>9547201.795834405</v>
       </c>
       <c r="AM14" t="n">
-        <v>73.07147458017023</v>
+        <v>78.56660479183701</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>KYsw3uKl</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>38223</v>
+        <v>18523</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2573,125 +2577,129 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>pfDZL71o</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>26.49494949494949</v>
+        <v>24.3314253647587</v>
       </c>
       <c r="Q15" t="n">
-        <v>180.3636363636363</v>
+        <v>182.1017957351291</v>
       </c>
       <c r="R15" t="n">
+        <v>1.544332210998878</v>
+      </c>
+      <c r="S15" t="n">
+        <v>76.8098765432099</v>
+      </c>
+      <c r="T15" t="n">
+        <v>14793883.27721661</v>
+      </c>
+      <c r="U15" t="n">
+        <v>81.42312008978676</v>
+      </c>
+      <c r="V15" t="n">
+        <v>26.62626262626263</v>
+      </c>
+      <c r="W15" t="n">
+        <v>180.3737373737374</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.404040404040404</v>
       </c>
-      <c r="S15" t="n">
-        <v>77.08080808080808</v>
-      </c>
-      <c r="T15" t="n">
-        <v>13345959.5959596</v>
-      </c>
-      <c r="U15" t="n">
-        <v>79.56565656565657</v>
-      </c>
-      <c r="V15" t="n">
-        <v>26.41414141414142</v>
-      </c>
-      <c r="W15" t="n">
-        <v>181.969696969697</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.313131313131313</v>
-      </c>
       <c r="Y15" t="n">
-        <v>75.02020202020202</v>
+        <v>77.02020202020202</v>
       </c>
       <c r="Z15" t="n">
-        <v>7049494.94949495</v>
+        <v>13086363.63636363</v>
       </c>
       <c r="AA15" t="n">
-        <v>77.34343434343434</v>
+        <v>79.40404040404042</v>
       </c>
       <c r="AB15" t="n">
-        <v>26.3805114638448</v>
+        <v>22.31067394794175</v>
       </c>
       <c r="AC15" t="n">
-        <v>178.4634038800706</v>
+        <v>181.6569401444789</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.384038800705468</v>
+        <v>1.302932576539388</v>
       </c>
       <c r="AE15" t="n">
-        <v>74.26631393298061</v>
+        <v>74.46557877536981</v>
       </c>
       <c r="AF15" t="n">
-        <v>6771748.23633157</v>
+        <v>11055339.98394679</v>
       </c>
       <c r="AG15" t="n">
-        <v>77.20392416225749</v>
+        <v>81.51037581699346</v>
       </c>
       <c r="AH15" t="n">
-        <v>24.36851851851852</v>
+        <v>26.11115119448453</v>
       </c>
       <c r="AI15" t="n">
-        <v>180.1598765432099</v>
+        <v>178.3595879429213</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.152821869488536</v>
+        <v>1.357102773769441</v>
       </c>
       <c r="AK15" t="n">
-        <v>70.44964726631393</v>
+        <v>74.14510181176848</v>
       </c>
       <c r="AL15" t="n">
-        <v>4106093.474426808</v>
+        <v>6809851.491101491</v>
       </c>
       <c r="AM15" t="n">
-        <v>74.53280423280424</v>
+        <v>77.35487814654481</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45529.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">rainville n 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35322</v>
+        <v>18752</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2716,127 +2724,127 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
       <c r="P16" t="n">
-        <v>26.41414141414141</v>
+        <v>26.68272727272727</v>
       </c>
       <c r="Q16" t="n">
-        <v>182.959595959596</v>
+        <v>183.4763636363636</v>
       </c>
       <c r="R16" t="n">
-        <v>1.535353535353535</v>
+        <v>1.01</v>
       </c>
       <c r="S16" t="n">
-        <v>73</v>
+        <v>68.82727272727273</v>
       </c>
       <c r="T16" t="n">
-        <v>4680303.030303031</v>
+        <v>1660295.454545455</v>
       </c>
       <c r="U16" t="n">
-        <v>75.63636363636364</v>
+        <v>72.40272727272728</v>
       </c>
       <c r="V16" t="n">
-        <v>25.77272727272727</v>
+        <v>23.43232323232323</v>
       </c>
       <c r="W16" t="n">
-        <v>181.4909090909091</v>
+        <v>183.5656565656566</v>
       </c>
       <c r="X16" t="n">
+        <v>1.305050505050505</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>74.92626262626261</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>12150303.03030303</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>79.8979797979798</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>24.52128205128205</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>182.4528205128206</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" t="n">
-        <v>68.52727272727273</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1701590.909090909</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>71.52727272727273</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>25.81280628925557</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>180.5799236324599</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.139738482129786</v>
-      </c>
       <c r="AE16" t="n">
-        <v>70.22057880391213</v>
+        <v>65.16551282051282</v>
       </c>
       <c r="AF16" t="n">
-        <v>2470797.092735499</v>
+        <v>1097714.743589744</v>
       </c>
       <c r="AG16" t="n">
-        <v>73.81658284013355</v>
+        <v>70.87657509157509</v>
       </c>
       <c r="AH16" t="n">
-        <v>23.31038961038961</v>
+        <v>23.81578019121879</v>
       </c>
       <c r="AI16" t="n">
-        <v>180.4461038961039</v>
+        <v>180.5411445279866</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1</v>
+        <v>1.280325814536341</v>
       </c>
       <c r="AK16" t="n">
-        <v>65.23311688311688</v>
+        <v>73.81533927411121</v>
       </c>
       <c r="AL16" t="n">
-        <v>1382142.857142857</v>
+        <v>7407900.77044463</v>
       </c>
       <c r="AM16" t="n">
-        <v>71.67402597402597</v>
+        <v>78.43489046690802</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45529.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>36178</v>
+        <v>25178</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2861,122 +2869,118 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>23.55454545454545</v>
+        <v>25.4040404040404</v>
       </c>
       <c r="Q17" t="n">
-        <v>183.5363636363636</v>
+        <v>185.7424242424242</v>
       </c>
       <c r="R17" t="n">
-        <v>1.327272727272728</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>75.16363636363636</v>
+        <v>71.54343434343434</v>
       </c>
       <c r="T17" t="n">
-        <v>12521818.18181818</v>
+        <v>3006161.616161617</v>
       </c>
       <c r="U17" t="n">
-        <v>79.92727272727272</v>
+        <v>74.93131313131315</v>
       </c>
       <c r="V17" t="n">
-        <v>23.07070707070707</v>
+        <v>25.74848484848485</v>
       </c>
       <c r="W17" t="n">
-        <v>183.7979797979798</v>
+        <v>181.569696969697</v>
       </c>
       <c r="X17" t="n">
-        <v>1.080808080808081</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>72.77777777777777</v>
+        <v>68.55858585858586</v>
       </c>
       <c r="Z17" t="n">
-        <v>5702020.202020202</v>
+        <v>1716969.696969697</v>
       </c>
       <c r="AA17" t="n">
-        <v>78.96969696969697</v>
+        <v>71.62121212121211</v>
       </c>
       <c r="AB17" t="n">
-        <v>23.79634502923977</v>
+        <v>24.75644409937888</v>
       </c>
       <c r="AC17" t="n">
-        <v>180.637030075188</v>
+        <v>181.2975874166092</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.295864661654135</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>73.51023391812866</v>
+        <v>68.76139291465377</v>
       </c>
       <c r="AF17" t="n">
-        <v>7142789.264828739</v>
+        <v>2122551.68794571</v>
       </c>
       <c r="AG17" t="n">
-        <v>78.34925856307436</v>
+        <v>73.08073383942948</v>
       </c>
       <c r="AH17" t="n">
-        <v>22.97724484318687</v>
+        <v>23.54729437229437</v>
       </c>
       <c r="AI17" t="n">
-        <v>180.9038896557012</v>
+        <v>180.3294372294372</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>70.81128747795414</v>
+        <v>65.29859307359308</v>
       </c>
       <c r="AL17" t="n">
-        <v>3713356.912813435</v>
+        <v>1353750</v>
       </c>
       <c r="AM17" t="n">
-        <v>77.50759144237405</v>
+        <v>71.37045454545455</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45529.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>26109</v>
+        <v>21029</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3006,96 +3010,237 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>22.34197530864198</v>
+        <v>25.49907407407407</v>
       </c>
       <c r="Q18" t="n">
-        <v>182.8086419753087</v>
+        <v>182.8518518518518</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21358024691358</v>
+        <v>1.248611111111111</v>
       </c>
       <c r="S18" t="n">
-        <v>71.41358024691358</v>
+        <v>74.37638888888888</v>
       </c>
       <c r="T18" t="n">
-        <v>4474814.814814814</v>
+        <v>7611608.796296296</v>
       </c>
       <c r="U18" t="n">
-        <v>79.32716049382715</v>
+        <v>78.96249999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>24.43636363636363</v>
+        <v>24.52386363636364</v>
       </c>
       <c r="W18" t="n">
-        <v>181.6272727272728</v>
+        <v>181.4045454545455</v>
       </c>
       <c r="X18" t="n">
-        <v>1.7</v>
+        <v>1.693181818181818</v>
       </c>
       <c r="Y18" t="n">
-        <v>75.94545454545455</v>
+        <v>75.88068181818183</v>
       </c>
       <c r="Z18" t="n">
-        <v>10700909.09090909</v>
+        <v>10511136.36363636</v>
       </c>
       <c r="AA18" t="n">
-        <v>80.17272727272727</v>
+        <v>80.15227272727273</v>
       </c>
       <c r="AB18" t="n">
-        <v>23.50724899646468</v>
+        <v>22.50400538382994</v>
       </c>
       <c r="AC18" t="n">
-        <v>182.9505709976298</v>
+        <v>183.3731365450664</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.249196772726185</v>
+        <v>1.056994337696092</v>
       </c>
       <c r="AE18" t="n">
-        <v>69.72645183429498</v>
+        <v>69.0204214239302</v>
       </c>
       <c r="AF18" t="n">
-        <v>3209204.64140072</v>
+        <v>3689683.699990717</v>
       </c>
       <c r="AG18" t="n">
-        <v>76.59459647106706</v>
+        <v>77.42214332126613</v>
       </c>
       <c r="AH18" t="n">
-        <v>22.79789682539683</v>
+        <v>23.08347374847375</v>
       </c>
       <c r="AI18" t="n">
-        <v>181.006626984127</v>
+        <v>181.0864346764347</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.381111111111111</v>
+        <v>1.422457264957265</v>
       </c>
       <c r="AK18" t="n">
-        <v>73.49960317460318</v>
+        <v>73.84479548229548</v>
       </c>
       <c r="AL18" t="n">
-        <v>8770315.476190476</v>
+        <v>9227575.091575092</v>
       </c>
       <c r="AM18" t="n">
-        <v>79.63281746031745</v>
+        <v>79.46166361416361</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
           <t>YHU1oFVQ</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>24.39823232323232</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>180.6156565656566</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.445959595959596</v>
+      </c>
+      <c r="S19" t="n">
+        <v>76.52853535353535</v>
+      </c>
+      <c r="T19" t="n">
+        <v>12835126.26262626</v>
+      </c>
+      <c r="U19" t="n">
+        <v>81.25858585858586</v>
+      </c>
+      <c r="V19" t="n">
+        <v>24.22654671717171</v>
+      </c>
+      <c r="W19" t="n">
+        <v>183.3402462121213</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.335795454545454</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>81.08421717171717</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>42712673.6111111</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>85.15318813131313</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>25.56378124799177</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>180.2263786246242</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.237337646109576</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>73.25163906918293</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>6901785.107355283</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>77.86790409071111</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>24.2928133914589</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>183.5945186779165</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>2.256332199791952</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>78.85379385836042</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>34468818.72642322</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>83.68346172661188</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO19"/>
+  <dimension ref="A1:BC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,130 +505,200 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -697,83 +767,125 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>165</v>
+      </c>
+      <c r="U2" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>167</v>
+      </c>
+      <c r="W2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>74</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>74</v>
+      </c>
+      <c r="AD2" t="n">
         <v>24.22654671717171</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AE2" t="n">
         <v>183.3402462121213</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AF2" t="n">
         <v>2.335795454545454</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AG2" t="n">
         <v>81.08421717171717</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AH2" t="n">
         <v>42712673.6111111</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AI2" t="n">
         <v>85.15318813131313</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AJ2" t="n">
         <v>24.84646464646465</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AK2" t="n">
         <v>181.9141414141415</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AL2" t="n">
         <v>1.326262626262626</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AM2" t="n">
         <v>73.07979797979799</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AN2" t="n">
         <v>5501919.191919192</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AO2" t="n">
         <v>77.96464646464648</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AP2" t="n">
         <v>24.2928133914589</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AQ2" t="n">
         <v>183.5945186779165</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AR2" t="n">
         <v>2.256332199791952</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AS2" t="n">
         <v>78.85379385836042</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AT2" t="n">
         <v>34468818.72642322</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AU2" t="n">
         <v>83.68346172661188</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AV2" t="n">
         <v>24.30159688674182</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AW2" t="n">
         <v>181.5365999539912</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AX2" t="n">
         <v>1.156997162794264</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AY2" t="n">
         <v>70.97367916570813</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AZ2" t="n">
         <v>3587664.097845257</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="BA2" t="n">
         <v>76.09731040564374</v>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>dWZTBmVT</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
         </is>
@@ -841,84 +953,98 @@
           <t>YagoQJpq</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
         <v>27.16712580348944</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="AE3" t="n">
         <v>182.1786960514233</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AF3" t="n">
         <v>2.063911845730027</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AG3" t="n">
         <v>76.70881542699725</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AH3" t="n">
         <v>9975518.824609734</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AI3" t="n">
         <v>79.01166207529845</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AJ3" t="n">
         <v>24.3314253647587</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AK3" t="n">
         <v>182.1017957351291</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AL3" t="n">
         <v>1.544332210998878</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AM3" t="n">
         <v>76.8098765432099</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AN3" t="n">
         <v>14793883.27721661</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AO3" t="n">
         <v>81.42312008978676</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AP3" t="n">
         <v>25.05617996945044</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AQ3" t="n">
         <v>178.7930668512149</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AR3" t="n">
         <v>1.609981179654695</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AS3" t="n">
         <v>74.20464284597412</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AT3" t="n">
         <v>6782085.612264334</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AU3" t="n">
         <v>78.63371979210707</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AV3" t="n">
         <v>22.31067394794175</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AW3" t="n">
         <v>181.6569401444789</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AX3" t="n">
         <v>1.302932576539388</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AY3" t="n">
         <v>74.46557877536981</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AZ3" t="n">
         <v>11055339.98394679</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="BA3" t="n">
         <v>81.51037581699346</v>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>pCcFFE7M</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
@@ -986,84 +1112,98 @@
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
         <v>24.39823232323232</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="AE4" t="n">
         <v>180.6156565656566</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AF4" t="n">
         <v>1.445959595959596</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AG4" t="n">
         <v>76.52853535353535</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AH4" t="n">
         <v>12835126.26262626</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AI4" t="n">
         <v>81.25858585858586</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AJ4" t="n">
         <v>26.68272727272727</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AK4" t="n">
         <v>183.4763636363636</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AL4" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AM4" t="n">
         <v>68.82727272727273</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AN4" t="n">
         <v>1660295.454545455</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AO4" t="n">
         <v>72.40272727272728</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AP4" t="n">
         <v>25.56378124799177</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AQ4" t="n">
         <v>180.2263786246242</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AR4" t="n">
         <v>1.237337646109576</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AS4" t="n">
         <v>73.25163906918293</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AT4" t="n">
         <v>6901785.107355283</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AU4" t="n">
         <v>77.86790409071111</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AV4" t="n">
         <v>24.52128205128205</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AW4" t="n">
         <v>182.4528205128206</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AX4" t="n">
         <v>1</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AY4" t="n">
         <v>65.16551282051282</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AZ4" t="n">
         <v>1097714.743589744</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="BA4" t="n">
         <v>70.87657509157509</v>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>K6b7RoBp</t>
         </is>
@@ -1127,84 +1267,98 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
         <v>25.51212121212121</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="AE5" t="n">
         <v>181.4060606060606</v>
       </c>
-      <c r="R5" t="n">
+      <c r="AF5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AG5" t="n">
         <v>70.31969696969696</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AH5" t="n">
         <v>2270606.060606061</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AI5" t="n">
         <v>73.88636363636364</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AJ5" t="n">
         <v>25.4040404040404</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AK5" t="n">
         <v>185.7424242424242</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AL5" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AM5" t="n">
         <v>71.54343434343434</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AN5" t="n">
         <v>3006161.616161617</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AO5" t="n">
         <v>74.93131313131315</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AP5" t="n">
         <v>24.90132517055594</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AQ5" t="n">
         <v>180.5193353654892</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AR5" t="n">
         <v>1</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AS5" t="n">
         <v>68.72381037765653</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AT5" t="n">
         <v>1895552.631129554</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AU5" t="n">
         <v>73.66574024266332</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AV5" t="n">
         <v>24.75644409937888</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AW5" t="n">
         <v>181.2975874166092</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AX5" t="n">
         <v>1</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AY5" t="n">
         <v>68.76139291465377</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AZ5" t="n">
         <v>2122551.68794571</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="BA5" t="n">
         <v>73.08073383942948</v>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
         </is>
@@ -1272,84 +1426,98 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
         <v>26.62626262626263</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="AE6" t="n">
         <v>180.3737373737374</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AF6" t="n">
         <v>1.404040404040404</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AG6" t="n">
         <v>77.02020202020202</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AH6" t="n">
         <v>13086363.63636363</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AI6" t="n">
         <v>79.40404040404042</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AJ6" t="n">
         <v>26.60707070707071</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AK6" t="n">
         <v>182.0050505050505</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AL6" t="n">
         <v>1.316161616161616</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AM6" t="n">
         <v>74.84949494949495</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AN6" t="n">
         <v>6760202.020202019</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AO6" t="n">
         <v>77.03030303030303</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AP6" t="n">
         <v>26.11115119448453</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AQ6" t="n">
         <v>178.3595879429213</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AR6" t="n">
         <v>1.357102773769441</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AS6" t="n">
         <v>74.14510181176848</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AT6" t="n">
         <v>6809851.491101491</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AU6" t="n">
         <v>77.35487814654481</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AV6" t="n">
         <v>24.1842151675485</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AW6" t="n">
         <v>179.7189594356261</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AX6" t="n">
         <v>1.159876543209877</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AY6" t="n">
         <v>70.26975308641974</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AZ6" t="n">
         <v>4269320.987654322</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="BA6" t="n">
         <v>74.59276895943563</v>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>
@@ -1417,84 +1585,98 @@
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
         <v>26.25050505050505</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="AE7" t="n">
         <v>182.8787878787879</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AF7" t="n">
         <v>1.509090909090909</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AG7" t="n">
         <v>72.91717171717171</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AH7" t="n">
         <v>4676363.636363637</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AI7" t="n">
         <v>75.61818181818181</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AJ7" t="n">
         <v>25.74848484848485</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AK7" t="n">
         <v>181.569696969697</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AL7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AM7" t="n">
         <v>68.55858585858586</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AN7" t="n">
         <v>1716969.696969697</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AO7" t="n">
         <v>71.62121212121211</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AP7" t="n">
         <v>25.79900817741824</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AQ7" t="n">
         <v>180.6714269004337</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AR7" t="n">
         <v>1.173144437104369</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AS7" t="n">
         <v>70.33023748219827</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AT7" t="n">
         <v>2599500.796439203</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AU7" t="n">
         <v>73.89428799627009</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AV7" t="n">
         <v>23.54729437229437</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AW7" t="n">
         <v>180.3294372294372</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AX7" t="n">
         <v>1</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AY7" t="n">
         <v>65.29859307359308</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AZ7" t="n">
         <v>1353750</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="BA7" t="n">
         <v>71.37045454545455</v>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>UapruDaf</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
         </is>
@@ -1562,84 +1744,98 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
         <v>23.43232323232323</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="AE8" t="n">
         <v>183.5656565656566</v>
       </c>
-      <c r="R8" t="n">
+      <c r="AF8" t="n">
         <v>1.305050505050505</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AG8" t="n">
         <v>74.92626262626261</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AH8" t="n">
         <v>12150303.03030303</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AI8" t="n">
         <v>79.8979797979798</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AJ8" t="n">
         <v>23.04949494949495</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AK8" t="n">
         <v>183.4858585858586</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AL8" t="n">
         <v>1.081818181818182</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AM8" t="n">
         <v>72.76161616161615</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AN8" t="n">
         <v>5654545.454545455</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AO8" t="n">
         <v>78.95656565656566</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AP8" t="n">
         <v>23.81578019121879</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AQ8" t="n">
         <v>180.5411445279866</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AR8" t="n">
         <v>1.280325814536341</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AS8" t="n">
         <v>73.81533927411121</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AT8" t="n">
         <v>7407900.77044463</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AU8" t="n">
         <v>78.43489046690802</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AV8" t="n">
         <v>23.10070163331032</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AW8" t="n">
         <v>180.6862970631087</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AX8" t="n">
         <v>1</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AY8" t="n">
         <v>70.72872574955909</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AZ8" t="n">
         <v>3597076.048615904</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="BA8" t="n">
         <v>77.24756057817652</v>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>OpNm82MB</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>YTLwacK1</t>
         </is>
@@ -1711,84 +1907,98 @@
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
         <v>22.15555555555556</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="AE9" t="n">
         <v>183.2024691358025</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AF9" t="n">
         <v>1.180246913580247</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AG9" t="n">
         <v>71.32222222222224</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AH9" t="n">
         <v>4479567.901234568</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AI9" t="n">
         <v>79.41481481481482</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AJ9" t="n">
         <v>24.52386363636364</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AK9" t="n">
         <v>181.4045454545455</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AL9" t="n">
         <v>1.693181818181818</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AM9" t="n">
         <v>75.88068181818183</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AN9" t="n">
         <v>10511136.36363636</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AO9" t="n">
         <v>80.15227272727273</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AP9" t="n">
         <v>23.13780455202024</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AQ9" t="n">
         <v>182.322793219852</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AR9" t="n">
         <v>1.226974550503962</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AS9" t="n">
         <v>69.85839627873942</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AT9" t="n">
         <v>3337593.530289609</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AU9" t="n">
         <v>77.01681869328928</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AV9" t="n">
         <v>23.08347374847375</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AW9" t="n">
         <v>181.0864346764347</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AX9" t="n">
         <v>1.422457264957265</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AY9" t="n">
         <v>73.84479548229548</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AZ9" t="n">
         <v>9227575.091575092</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="BA9" t="n">
         <v>79.46166361416361</v>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>YHU1oFVQ</t>
         </is>
@@ -1856,84 +2066,98 @@
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
         <v>26.87386363636364</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="AE10" t="n">
         <v>183.7204545454545</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AF10" t="n">
         <v>1.697727272727273</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AG10" t="n">
         <v>77.19545454545455</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AH10" t="n">
         <v>12426704.54545454</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AI10" t="n">
         <v>79.2375</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AJ10" t="n">
         <v>25.49907407407407</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AK10" t="n">
         <v>182.8518518518518</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AL10" t="n">
         <v>1.248611111111111</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AM10" t="n">
         <v>74.37638888888888</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AN10" t="n">
         <v>7611608.796296296</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AO10" t="n">
         <v>78.96249999999999</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AP10" t="n">
         <v>24.90756103965598</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AQ10" t="n">
         <v>183.7455013300731</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AR10" t="n">
         <v>1.268704416021238</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AS10" t="n">
         <v>74.98421690490834</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AT10" t="n">
         <v>9547201.795834405</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AU10" t="n">
         <v>78.56660479183701</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AV10" t="n">
         <v>22.50400538382994</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AW10" t="n">
         <v>183.3731365450664</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AX10" t="n">
         <v>1.056994337696092</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AY10" t="n">
         <v>69.0204214239302</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AZ10" t="n">
         <v>3689683.699990717</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="BA10" t="n">
         <v>77.42214332126613</v>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0tIbS515</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
         </is>
@@ -2001,84 +2225,98 @@
           <t>4v0yqlWc</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
         <v>27.16712580348944</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="AE11" t="n">
         <v>182.1786960514233</v>
       </c>
-      <c r="R11" t="n">
+      <c r="AF11" t="n">
         <v>2.063911845730027</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AG11" t="n">
         <v>76.70881542699725</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AH11" t="n">
         <v>9975518.824609734</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AI11" t="n">
         <v>79.01166207529845</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AJ11" t="n">
         <v>22.15555555555556</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AK11" t="n">
         <v>183.2024691358025</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AL11" t="n">
         <v>1.180246913580247</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AM11" t="n">
         <v>71.32222222222224</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AN11" t="n">
         <v>4479567.901234568</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AO11" t="n">
         <v>79.41481481481482</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AP11" t="n">
         <v>25.05617996945044</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AQ11" t="n">
         <v>178.7930668512149</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AR11" t="n">
         <v>1.609981179654695</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AS11" t="n">
         <v>74.20464284597412</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AT11" t="n">
         <v>6782085.612264334</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AU11" t="n">
         <v>78.63371979210707</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AV11" t="n">
         <v>23.13780455202024</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AW11" t="n">
         <v>182.322793219852</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AX11" t="n">
         <v>1.226974550503962</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AY11" t="n">
         <v>69.85839627873942</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AZ11" t="n">
         <v>3337593.530289609</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="BA11" t="n">
         <v>77.01681869328928</v>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>pCcFFE7M</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
         </is>
@@ -2142,84 +2380,98 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
         <v>26.60707070707071</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AE12" t="n">
         <v>182.0050505050505</v>
       </c>
-      <c r="R12" t="n">
+      <c r="AF12" t="n">
         <v>1.316161616161616</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AG12" t="n">
         <v>74.84949494949495</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AH12" t="n">
         <v>6760202.020202019</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AI12" t="n">
         <v>77.03030303030303</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AJ12" t="n">
         <v>25.51212121212121</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AK12" t="n">
         <v>181.4060606060606</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AL12" t="n">
         <v>1</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AM12" t="n">
         <v>70.31969696969696</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AN12" t="n">
         <v>2270606.060606061</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AO12" t="n">
         <v>73.88636363636364</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AP12" t="n">
         <v>24.1842151675485</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AQ12" t="n">
         <v>179.7189594356261</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AR12" t="n">
         <v>1.159876543209877</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AS12" t="n">
         <v>70.26975308641974</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AT12" t="n">
         <v>4269320.987654322</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AU12" t="n">
         <v>74.59276895943563</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AV12" t="n">
         <v>24.90132517055594</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AW12" t="n">
         <v>180.5193353654892</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AX12" t="n">
         <v>1</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AY12" t="n">
         <v>68.72381037765653</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AZ12" t="n">
         <v>1895552.631129554</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="BA12" t="n">
         <v>73.66574024266332</v>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>0tIbS515</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
@@ -2291,84 +2543,98 @@
           <t>d2nnj1IE</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
         <v>24.84646464646465</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="AE13" t="n">
         <v>181.9141414141415</v>
       </c>
-      <c r="R13" t="n">
+      <c r="AF13" t="n">
         <v>1.326262626262626</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AG13" t="n">
         <v>73.07979797979799</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AH13" t="n">
         <v>5501919.191919192</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AI13" t="n">
         <v>77.96464646464648</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AJ13" t="n">
         <v>26.25050505050505</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AK13" t="n">
         <v>182.8787878787879</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AL13" t="n">
         <v>1.509090909090909</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AM13" t="n">
         <v>72.91717171717171</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AN13" t="n">
         <v>4676363.636363637</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AO13" t="n">
         <v>75.61818181818181</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AP13" t="n">
         <v>24.30159688674182</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AQ13" t="n">
         <v>181.5365999539912</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AR13" t="n">
         <v>1.156997162794264</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AS13" t="n">
         <v>70.97367916570813</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AT13" t="n">
         <v>3587664.097845257</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AU13" t="n">
         <v>76.09731040564374</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AV13" t="n">
         <v>25.79900817741824</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AW13" t="n">
         <v>180.6714269004337</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AX13" t="n">
         <v>1.173144437104369</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AY13" t="n">
         <v>70.33023748219827</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AZ13" t="n">
         <v>2599500.796439203</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="BA13" t="n">
         <v>73.89428799627009</v>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="BB13" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>YTLwacK1</t>
         </is>
@@ -2436,84 +2702,98 @@
           <t>lhUkVMh2</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
         <v>23.04949494949495</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="AE14" t="n">
         <v>183.4858585858586</v>
       </c>
-      <c r="R14" t="n">
+      <c r="AF14" t="n">
         <v>1.081818181818182</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AG14" t="n">
         <v>72.76161616161615</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AH14" t="n">
         <v>5654545.454545455</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AI14" t="n">
         <v>78.95656565656566</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AJ14" t="n">
         <v>26.87386363636364</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AK14" t="n">
         <v>183.7204545454545</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AL14" t="n">
         <v>1.697727272727273</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AM14" t="n">
         <v>77.19545454545455</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AN14" t="n">
         <v>12426704.54545454</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AO14" t="n">
         <v>79.2375</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AP14" t="n">
         <v>23.10070163331032</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AQ14" t="n">
         <v>180.6862970631087</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AR14" t="n">
         <v>1</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AS14" t="n">
         <v>70.72872574955909</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AT14" t="n">
         <v>3597076.048615904</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AU14" t="n">
         <v>77.24756057817652</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AV14" t="n">
         <v>24.90756103965598</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AW14" t="n">
         <v>183.7455013300731</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AX14" t="n">
         <v>1.268704416021238</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AY14" t="n">
         <v>74.98421690490834</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AZ14" t="n">
         <v>9547201.795834405</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="BA14" t="n">
         <v>78.56660479183701</v>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="BB14" t="inlineStr">
         <is>
           <t>UapruDaf</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>
@@ -2585,84 +2865,98 @@
           <t>pfDZL71o</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
         <v>24.3314253647587</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="AE15" t="n">
         <v>182.1017957351291</v>
       </c>
-      <c r="R15" t="n">
+      <c r="AF15" t="n">
         <v>1.544332210998878</v>
       </c>
-      <c r="S15" t="n">
+      <c r="AG15" t="n">
         <v>76.8098765432099</v>
       </c>
-      <c r="T15" t="n">
+      <c r="AH15" t="n">
         <v>14793883.27721661</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AI15" t="n">
         <v>81.42312008978676</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AJ15" t="n">
         <v>26.62626262626263</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AK15" t="n">
         <v>180.3737373737374</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AL15" t="n">
         <v>1.404040404040404</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AM15" t="n">
         <v>77.02020202020202</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AN15" t="n">
         <v>13086363.63636363</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AO15" t="n">
         <v>79.40404040404042</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AP15" t="n">
         <v>22.31067394794175</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AQ15" t="n">
         <v>181.6569401444789</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AR15" t="n">
         <v>1.302932576539388</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AS15" t="n">
         <v>74.46557877536981</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AT15" t="n">
         <v>11055339.98394679</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AU15" t="n">
         <v>81.51037581699346</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AV15" t="n">
         <v>26.11115119448453</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AW15" t="n">
         <v>178.3595879429213</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AX15" t="n">
         <v>1.357102773769441</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AY15" t="n">
         <v>74.14510181176848</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AZ15" t="n">
         <v>6809851.491101491</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="BA15" t="n">
         <v>77.35487814654481</v>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="BB15" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>K6b7RoBp</t>
         </is>
@@ -2730,84 +3024,98 @@
           <t>2PIvr8o4</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="n">
         <v>26.68272727272727</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="AE16" t="n">
         <v>183.4763636363636</v>
       </c>
-      <c r="R16" t="n">
+      <c r="AF16" t="n">
         <v>1.01</v>
       </c>
-      <c r="S16" t="n">
+      <c r="AG16" t="n">
         <v>68.82727272727273</v>
       </c>
-      <c r="T16" t="n">
+      <c r="AH16" t="n">
         <v>1660295.454545455</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AI16" t="n">
         <v>72.40272727272728</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AJ16" t="n">
         <v>23.43232323232323</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AK16" t="n">
         <v>183.5656565656566</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AL16" t="n">
         <v>1.305050505050505</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AM16" t="n">
         <v>74.92626262626261</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AN16" t="n">
         <v>12150303.03030303</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AO16" t="n">
         <v>79.8979797979798</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AP16" t="n">
         <v>24.52128205128205</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AQ16" t="n">
         <v>182.4528205128206</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AR16" t="n">
         <v>1</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AS16" t="n">
         <v>65.16551282051282</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AT16" t="n">
         <v>1097714.743589744</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AU16" t="n">
         <v>70.87657509157509</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AV16" t="n">
         <v>23.81578019121879</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AW16" t="n">
         <v>180.5411445279866</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AX16" t="n">
         <v>1.280325814536341</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AY16" t="n">
         <v>73.81533927411121</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AZ16" t="n">
         <v>7407900.77044463</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="BA16" t="n">
         <v>78.43489046690802</v>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="BB16" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
         </is>
@@ -2871,84 +3179,98 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="n">
         <v>25.4040404040404</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="AE17" t="n">
         <v>185.7424242424242</v>
       </c>
-      <c r="R17" t="n">
+      <c r="AF17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="AG17" t="n">
         <v>71.54343434343434</v>
       </c>
-      <c r="T17" t="n">
+      <c r="AH17" t="n">
         <v>3006161.616161617</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AI17" t="n">
         <v>74.93131313131315</v>
       </c>
-      <c r="V17" t="n">
+      <c r="AJ17" t="n">
         <v>25.74848484848485</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AK17" t="n">
         <v>181.569696969697</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AL17" t="n">
         <v>1</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AM17" t="n">
         <v>68.55858585858586</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AN17" t="n">
         <v>1716969.696969697</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AO17" t="n">
         <v>71.62121212121211</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AP17" t="n">
         <v>24.75644409937888</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AQ17" t="n">
         <v>181.2975874166092</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AR17" t="n">
         <v>1</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AS17" t="n">
         <v>68.76139291465377</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AT17" t="n">
         <v>2122551.68794571</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AU17" t="n">
         <v>73.08073383942948</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AV17" t="n">
         <v>23.54729437229437</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AW17" t="n">
         <v>180.3294372294372</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AX17" t="n">
         <v>1</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AY17" t="n">
         <v>65.29859307359308</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AZ17" t="n">
         <v>1353750</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="BA17" t="n">
         <v>71.37045454545455</v>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="BB17" t="inlineStr">
         <is>
           <t>dWZTBmVT</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
         </is>
@@ -3016,84 +3338,98 @@
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="n">
         <v>25.49907407407407</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="AE18" t="n">
         <v>182.8518518518518</v>
       </c>
-      <c r="R18" t="n">
+      <c r="AF18" t="n">
         <v>1.248611111111111</v>
       </c>
-      <c r="S18" t="n">
+      <c r="AG18" t="n">
         <v>74.37638888888888</v>
       </c>
-      <c r="T18" t="n">
+      <c r="AH18" t="n">
         <v>7611608.796296296</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AI18" t="n">
         <v>78.96249999999999</v>
       </c>
-      <c r="V18" t="n">
+      <c r="AJ18" t="n">
         <v>24.52386363636364</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AK18" t="n">
         <v>181.4045454545455</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AL18" t="n">
         <v>1.693181818181818</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AM18" t="n">
         <v>75.88068181818183</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AN18" t="n">
         <v>10511136.36363636</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AO18" t="n">
         <v>80.15227272727273</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AP18" t="n">
         <v>22.50400538382994</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AQ18" t="n">
         <v>183.3731365450664</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AR18" t="n">
         <v>1.056994337696092</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AS18" t="n">
         <v>69.0204214239302</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AT18" t="n">
         <v>3689683.699990717</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AU18" t="n">
         <v>77.42214332126613</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AV18" t="n">
         <v>23.08347374847375</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AW18" t="n">
         <v>181.0864346764347</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AX18" t="n">
         <v>1.422457264957265</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AY18" t="n">
         <v>73.84479548229548</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AZ18" t="n">
         <v>9227575.091575092</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="BA18" t="n">
         <v>79.46166361416361</v>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="BB18" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>YHU1oFVQ</t>
         </is>
@@ -3161,84 +3497,98 @@
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="n">
         <v>24.39823232323232</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="AE19" t="n">
         <v>180.6156565656566</v>
       </c>
-      <c r="R19" t="n">
+      <c r="AF19" t="n">
         <v>1.445959595959596</v>
       </c>
-      <c r="S19" t="n">
+      <c r="AG19" t="n">
         <v>76.52853535353535</v>
       </c>
-      <c r="T19" t="n">
+      <c r="AH19" t="n">
         <v>12835126.26262626</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AI19" t="n">
         <v>81.25858585858586</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AJ19" t="n">
         <v>24.22654671717171</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AK19" t="n">
         <v>183.3402462121213</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AL19" t="n">
         <v>2.335795454545454</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AM19" t="n">
         <v>81.08421717171717</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AN19" t="n">
         <v>42712673.6111111</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AO19" t="n">
         <v>85.15318813131313</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AP19" t="n">
         <v>25.56378124799177</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AQ19" t="n">
         <v>180.2263786246242</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AR19" t="n">
         <v>1.237337646109576</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AS19" t="n">
         <v>73.25163906918293</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AT19" t="n">
         <v>6901785.107355283</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AU19" t="n">
         <v>77.86790409071111</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AV19" t="n">
         <v>24.2928133914589</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AW19" t="n">
         <v>183.5945186779165</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AX19" t="n">
         <v>2.256332199791952</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AY19" t="n">
         <v>78.85379385836042</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AZ19" t="n">
         <v>34468818.72642322</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="BA19" t="n">
         <v>83.68346172661188</v>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="BB19" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC4"/>
+  <dimension ref="A1:BC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,35 +707,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>38223</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,24 +760,38 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>179</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>298</v>
+      </c>
+      <c r="U2" t="n">
+        <v>28600000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>310</v>
+      </c>
       <c r="W2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="X2" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
@@ -786,129 +800,129 @@
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2200000</v>
+        <v>11500000</v>
       </c>
       <c r="AC2" t="n">
         <v>82</v>
       </c>
       <c r="AD2" t="n">
-        <v>27.16712580348944</v>
+        <v>26.62626262626263</v>
       </c>
       <c r="AE2" t="n">
-        <v>182.1786960514233</v>
+        <v>180.3737373737374</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.063911845730027</v>
+        <v>1.404040404040404</v>
       </c>
       <c r="AG2" t="n">
-        <v>76.70881542699725</v>
+        <v>77.02020202020202</v>
       </c>
       <c r="AH2" t="n">
-        <v>9975518.824609734</v>
+        <v>13086363.63636363</v>
       </c>
       <c r="AI2" t="n">
-        <v>79.01166207529845</v>
+        <v>79.40404040404042</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24.3314253647587</v>
+        <v>26.60707070707071</v>
       </c>
       <c r="AK2" t="n">
-        <v>182.1017957351291</v>
+        <v>182.0050505050505</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.544332210998878</v>
+        <v>1.316161616161616</v>
       </c>
       <c r="AM2" t="n">
-        <v>76.8098765432099</v>
+        <v>74.84949494949495</v>
       </c>
       <c r="AN2" t="n">
-        <v>14793883.27721661</v>
+        <v>6760202.020202019</v>
       </c>
       <c r="AO2" t="n">
-        <v>81.42312008978676</v>
+        <v>77.03030303030303</v>
       </c>
       <c r="AP2" t="n">
-        <v>25.05617996945044</v>
+        <v>26.11115119448453</v>
       </c>
       <c r="AQ2" t="n">
-        <v>178.7930668512149</v>
+        <v>178.3595879429213</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.609981179654695</v>
+        <v>1.357102773769441</v>
       </c>
       <c r="AS2" t="n">
-        <v>74.20464284597412</v>
+        <v>74.14510181176848</v>
       </c>
       <c r="AT2" t="n">
-        <v>6782085.612264334</v>
+        <v>6809851.491101491</v>
       </c>
       <c r="AU2" t="n">
-        <v>78.63371979210707</v>
+        <v>77.35487814654481</v>
       </c>
       <c r="AV2" t="n">
-        <v>22.31067394794175</v>
+        <v>24.1842151675485</v>
       </c>
       <c r="AW2" t="n">
-        <v>181.6569401444789</v>
+        <v>179.7189594356261</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.302932576539388</v>
+        <v>1.159876543209877</v>
       </c>
       <c r="AY2" t="n">
-        <v>74.46557877536981</v>
+        <v>70.26975308641974</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11055339.98394679</v>
+        <v>4269320.987654322</v>
       </c>
       <c r="BA2" t="n">
-        <v>81.51037581699346</v>
+        <v>74.59276895943563</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>35322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -935,167 +949,167 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>27.33333333333333</v>
+        <v>25.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>178</v>
+        <v>177.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.666666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>461</v>
+        <v>280</v>
       </c>
       <c r="U3" t="n">
-        <v>66800000</v>
+        <v>10425000</v>
       </c>
       <c r="V3" t="n">
-        <v>471</v>
+        <v>293</v>
       </c>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X3" t="n">
-        <v>176</v>
+        <v>181.6</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>131</v>
+        <v>322</v>
       </c>
       <c r="AB3" t="n">
-        <v>2325000</v>
+        <v>6050000</v>
       </c>
       <c r="AC3" t="n">
-        <v>144</v>
+        <v>363</v>
       </c>
       <c r="AD3" t="n">
-        <v>24.39823232323232</v>
+        <v>26.25050505050505</v>
       </c>
       <c r="AE3" t="n">
-        <v>180.6156565656566</v>
+        <v>182.8787878787879</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.445959595959596</v>
+        <v>1.509090909090909</v>
       </c>
       <c r="AG3" t="n">
-        <v>76.52853535353535</v>
+        <v>72.91717171717171</v>
       </c>
       <c r="AH3" t="n">
-        <v>12835126.26262626</v>
+        <v>4676363.636363637</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.25858585858586</v>
+        <v>75.61818181818181</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26.68272727272727</v>
+        <v>25.74848484848485</v>
       </c>
       <c r="AK3" t="n">
-        <v>183.4763636363636</v>
+        <v>181.569696969697</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>68.82727272727273</v>
+        <v>68.55858585858586</v>
       </c>
       <c r="AN3" t="n">
-        <v>1660295.454545455</v>
+        <v>1716969.696969697</v>
       </c>
       <c r="AO3" t="n">
-        <v>72.40272727272728</v>
+        <v>71.62121212121211</v>
       </c>
       <c r="AP3" t="n">
-        <v>25.56378124799177</v>
+        <v>25.79900817741824</v>
       </c>
       <c r="AQ3" t="n">
-        <v>180.2263786246242</v>
+        <v>180.6714269004337</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.237337646109576</v>
+        <v>1.173144437104369</v>
       </c>
       <c r="AS3" t="n">
-        <v>73.25163906918293</v>
+        <v>70.33023748219827</v>
       </c>
       <c r="AT3" t="n">
-        <v>6901785.107355283</v>
+        <v>2599500.796439203</v>
       </c>
       <c r="AU3" t="n">
-        <v>77.86790409071111</v>
+        <v>73.89428799627009</v>
       </c>
       <c r="AV3" t="n">
-        <v>24.52128205128205</v>
+        <v>23.54729437229437</v>
       </c>
       <c r="AW3" t="n">
-        <v>182.4528205128206</v>
+        <v>180.3294372294372</v>
       </c>
       <c r="AX3" t="n">
         <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>65.16551282051282</v>
+        <v>65.29859307359308</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1097714.743589744</v>
+        <v>1353750</v>
       </c>
       <c r="BA3" t="n">
-        <v>70.87657509157509</v>
+        <v>71.37045454545455</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45529.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42000</v>
+        <v>36178</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1120,116 +1134,1915 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>19</v>
-      </c>
-      <c r="X4" t="n">
-        <v>188</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>64</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>74</v>
-      </c>
+      <c r="P4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>179</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>308</v>
+      </c>
+      <c r="U4" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>317</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>25.51212121212121</v>
+        <v>23.43232323232323</v>
       </c>
       <c r="AE4" t="n">
-        <v>181.4060606060606</v>
+        <v>183.5656565656566</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>1.305050505050505</v>
       </c>
       <c r="AG4" t="n">
-        <v>70.31969696969696</v>
+        <v>74.92626262626261</v>
       </c>
       <c r="AH4" t="n">
-        <v>2270606.060606061</v>
+        <v>12150303.03030303</v>
       </c>
       <c r="AI4" t="n">
-        <v>73.88636363636364</v>
+        <v>79.8979797979798</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25.4040404040404</v>
+        <v>23.04949494949495</v>
       </c>
       <c r="AK4" t="n">
-        <v>185.7424242424242</v>
+        <v>183.4858585858586</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>1.081818181818182</v>
       </c>
       <c r="AM4" t="n">
-        <v>71.54343434343434</v>
+        <v>72.76161616161615</v>
       </c>
       <c r="AN4" t="n">
-        <v>3006161.616161617</v>
+        <v>5654545.454545455</v>
       </c>
       <c r="AO4" t="n">
-        <v>74.93131313131315</v>
+        <v>78.95656565656566</v>
       </c>
       <c r="AP4" t="n">
-        <v>24.90132517055594</v>
+        <v>23.81578019121879</v>
       </c>
       <c r="AQ4" t="n">
-        <v>180.5193353654892</v>
+        <v>180.5411445279866</v>
       </c>
       <c r="AR4" t="n">
-        <v>1</v>
+        <v>1.280325814536341</v>
       </c>
       <c r="AS4" t="n">
-        <v>68.72381037765653</v>
+        <v>73.81533927411121</v>
       </c>
       <c r="AT4" t="n">
-        <v>1895552.631129554</v>
+        <v>7407900.77044463</v>
       </c>
       <c r="AU4" t="n">
-        <v>73.66574024266332</v>
+        <v>78.43489046690802</v>
       </c>
       <c r="AV4" t="n">
-        <v>24.75644409937888</v>
+        <v>23.10070163331032</v>
       </c>
       <c r="AW4" t="n">
-        <v>181.2975874166092</v>
+        <v>180.6862970631087</v>
       </c>
       <c r="AX4" t="n">
         <v>1</v>
       </c>
       <c r="AY4" t="n">
+        <v>70.72872574955909</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3597076.048615904</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>77.24756057817652</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>55</v>
+      </c>
+      <c r="I5" t="n">
+        <v>551</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>20</v>
+      </c>
+      <c r="X5" t="n">
+        <v>189</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>22.15555555555556</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>183.2024691358025</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.180246913580247</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>71.32222222222224</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>4479567.901234568</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>79.41481481481482</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>24.52386363636364</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>181.4045454545455</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.693181818181818</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>75.88068181818183</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10511136.36363636</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>80.15227272727273</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>23.13780455202024</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>182.322793219852</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.226974550503962</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>69.85839627873942</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3337593.530289609</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>77.01681869328928</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>23.08347374847375</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>181.0864346764347</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.422457264957265</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>73.84479548229548</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>9227575.091575092</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>79.46166361416361</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>551</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>179</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>63</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>74</v>
+      </c>
+      <c r="W6" t="n">
+        <v>21</v>
+      </c>
+      <c r="X6" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26.87386363636364</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>183.7204545454545</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.697727272727273</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>77.19545454545455</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>12426704.54545454</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>79.2375</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>25.49907407407407</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>182.8518518518518</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.248611111111111</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>74.37638888888888</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7611608.796296296</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>78.96249999999999</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>24.90756103965598</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>183.7455013300731</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.268704416021238</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>74.98421690490834</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9547201.795834405</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>78.56660479183701</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>22.50400538382994</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>183.3731365450664</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.056994337696092</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>69.0204214239302</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3689683.699990717</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>77.42214332126613</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>26.98653198653199</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>181.9786195286195</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.030808080808081</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>76.6219696969697</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>10002558.92255892</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>79.07550505050506</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>22.15555555555556</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>183.2024691358025</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.180246913580247</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>71.32222222222224</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>4479567.901234568</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>79.41481481481482</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>25.04787511692378</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>178.9552388165122</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.620743617582021</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>74.22019797112844</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6800607.46341622</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>78.7040982152286</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>23.13780455202024</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>182.322793219852</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.226974550503962</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>69.85839627873942</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3337593.530289609</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>77.01681869328928</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>26.60707070707071</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>182.0050505050505</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.316161616161616</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>74.84949494949495</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>6760202.020202019</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>77.03030303030303</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>25.51212121212121</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>181.4060606060606</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>70.31969696969696</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2270606.060606061</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>73.88636363636364</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>24.1842151675485</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>179.7189594356261</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.159876543209877</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>70.26975308641974</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4269320.987654322</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>74.59276895943563</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>24.90132517055594</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>180.5193353654892</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>68.72381037765653</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1895552.631129554</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>73.66574024266332</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>25.00727272727273</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.339090909090909</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>73.16272727272728</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>5504454.545454545</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>77.89545454545456</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>26.25050505050505</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>182.8787878787879</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.509090909090909</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>72.91717171717171</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4676363.636363637</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>75.61818181818181</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>24.37977053140096</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>181.5579399585921</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.166297446514838</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>71.00964458247067</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3767231.021394065</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>76.1209126984127</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>25.79900817741824</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>180.6714269004337</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.173144437104369</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>70.33023748219827</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2599500.796439203</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>73.89428799627009</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>23.04949494949495</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>183.4858585858586</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.081818181818182</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>72.76161616161615</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5654545.454545455</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>78.95656565656566</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>26.87386363636364</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>183.7204545454545</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.697727272727273</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>77.19545454545455</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>12426704.54545454</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>79.2375</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>23.10070163331032</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>180.6862970631087</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>70.72872574955909</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3597076.048615904</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>77.24756057817652</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>24.90756103965598</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>183.7455013300731</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.268704416021238</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>74.98421690490834</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>9547201.795834405</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>78.56660479183701</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>24.28828282828283</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>182.2316161616162</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.52989898989899</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>76.71888888888888</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>14474494.94949495</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>81.36080808080808</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>26.62626262626263</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>180.3737373737374</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.404040404040404</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>77.02020202020202</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>13086363.63636363</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>79.40404040404042</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>22.19627321981424</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>181.8079127966976</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.294861541107671</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>74.39124312005504</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>11073417.09666323</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>81.55933823529412</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>26.11115119448453</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>178.3595879429213</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.357102773769441</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>74.14510181176848</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>6809851.491101491</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>77.35487814654481</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>26.53884297520661</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>183.6512396694215</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.009090909090909</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>68.68842975206611</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1646404.958677686</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>72.45702479338843</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>23.43232323232323</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>183.5656565656566</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.305050505050505</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>74.92626262626261</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12150303.03030303</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>79.8979797979798</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>24.56480186480186</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>182.3365561974258</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>65.27299584473498</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1115412.612749569</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>70.97475205953468</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>23.81578019121879</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>180.5411445279866</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.280325814536341</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>73.81533927411121</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7407900.77044463</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>78.43489046690802</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>25.4040404040404</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>185.7424242424242</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>71.54343434343434</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3006161.616161617</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>74.93131313131315</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>25.74848484848485</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>181.569696969697</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>68.55858585858586</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1716969.696969697</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>71.62121212121211</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>24.75644409937888</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>181.2975874166092</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="n">
         <v>68.76139291465377</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="AT13" t="n">
         <v>2122551.68794571</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="AU13" t="n">
         <v>73.08073383942948</v>
       </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
+      <c r="AV13" t="n">
+        <v>23.54729437229437</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>180.3294372294372</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>65.29859307359308</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1353750</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>71.37045454545455</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>25.49907407407407</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>182.8518518518518</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.248611111111111</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>74.37638888888888</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>7611608.796296296</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>78.96249999999999</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>24.52386363636364</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>181.4045454545455</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.693181818181818</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75.88068181818183</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>10511136.36363636</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>80.15227272727273</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>22.50400538382994</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>183.3731365450664</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.056994337696092</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>69.0204214239302</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3689683.699990717</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>77.42214332126613</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>23.08347374847375</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>181.0864346764347</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.422457264957265</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>73.84479548229548</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>9227575.091575092</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>79.46166361416361</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>24.22090909090909</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>180.7290909090909</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.438863636363636</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>76.32568181818182</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>12714113.63636363</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>81.28272727272727</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24.22654671717171</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>183.3402462121213</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.335795454545454</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>81.08421717171717</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>42712673.6111111</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>85.15318813131313</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>25.51454598033545</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>180.1394550478761</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.249318167212904</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>73.22647516226463</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6864106.596619755</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>77.9453993959257</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>24.11841227550399</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>183.6283087880902</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.223860072031512</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>78.77708881460815</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>33889750.49922129</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>83.73761769383867</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -856,22 +856,22 @@
         <v>76.87727272727273</v>
       </c>
       <c r="V3" t="n">
-        <v>25.51212121212121</v>
+        <v>25.54049586776859</v>
       </c>
       <c r="W3" t="n">
-        <v>181.4060606060606</v>
+        <v>181.4157024793388</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>70.31969696969696</v>
+        <v>70.31239669421488</v>
       </c>
       <c r="Z3" t="n">
-        <v>2270606.060606061</v>
+        <v>2263388.429752066</v>
       </c>
       <c r="AA3" t="n">
-        <v>73.88636363636364</v>
+        <v>73.8396694214876</v>
       </c>
       <c r="AB3" t="n">
         <v>24.16579365079365</v>
@@ -892,22 +892,22 @@
         <v>74.60015873015874</v>
       </c>
       <c r="AH3" t="n">
-        <v>24.92518009534816</v>
+        <v>24.90843570707824</v>
       </c>
       <c r="AI3" t="n">
-        <v>180.4948450242568</v>
+        <v>180.3570858502985</v>
       </c>
       <c r="AJ3" t="n">
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>68.56286593891636</v>
+        <v>68.51825123092091</v>
       </c>
       <c r="AL3" t="n">
-        <v>1850177.023023662</v>
+        <v>1845245.585234273</v>
       </c>
       <c r="AM3" t="n">
-        <v>73.54255711608653</v>
+        <v>73.55132524589538</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
@@ -1186,22 +1186,22 @@
         <v>77.11030452035887</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.90756103965598</v>
+        <v>24.79680493569039</v>
       </c>
       <c r="AI5" t="n">
-        <v>183.7455013300731</v>
+        <v>183.1709511970658</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.268704416021238</v>
+        <v>1.301833974419114</v>
       </c>
       <c r="AK5" t="n">
-        <v>74.98421690490834</v>
+        <v>74.90579521441751</v>
       </c>
       <c r="AL5" t="n">
-        <v>9547201.795834405</v>
+        <v>9724481.616250966</v>
       </c>
       <c r="AM5" t="n">
-        <v>78.56660479183701</v>
+        <v>78.5899443126533</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
@@ -1281,76 +1281,76 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>24.28828282828283</v>
+        <v>24.30011223344557</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.2316161616162</v>
+        <v>182.3583613916947</v>
       </c>
       <c r="R6" t="n">
-        <v>1.52989898989899</v>
+        <v>1.518069584736252</v>
       </c>
       <c r="S6" t="n">
-        <v>76.71888888888888</v>
+        <v>76.69775533108867</v>
       </c>
       <c r="T6" t="n">
-        <v>14474494.94949495</v>
+        <v>14360549.94388328</v>
       </c>
       <c r="U6" t="n">
-        <v>81.36080808080808</v>
+        <v>81.30998877665544</v>
       </c>
       <c r="V6" t="n">
-        <v>26.55363636363636</v>
+        <v>26.65555555555556</v>
       </c>
       <c r="W6" t="n">
-        <v>180.6163636363637</v>
+        <v>180.6848484848485</v>
       </c>
       <c r="X6" t="n">
-        <v>1.403636363636364</v>
+        <v>1.408080808080808</v>
       </c>
       <c r="Y6" t="n">
-        <v>76.91818181818181</v>
+        <v>76.92929292929291</v>
       </c>
       <c r="Z6" t="n">
-        <v>13071727.27272727</v>
+        <v>13066565.65656566</v>
       </c>
       <c r="AA6" t="n">
-        <v>79.44363636363637</v>
+        <v>79.39191919191919</v>
       </c>
       <c r="AB6" t="n">
-        <v>22.19627321981424</v>
+        <v>22.23197024423805</v>
       </c>
       <c r="AC6" t="n">
-        <v>181.8079127966976</v>
+        <v>181.7587919963307</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.294861541107671</v>
+        <v>1.31373504567519</v>
       </c>
       <c r="AE6" t="n">
-        <v>74.39124312005504</v>
+        <v>74.49027013339449</v>
       </c>
       <c r="AF6" t="n">
-        <v>11073417.09666323</v>
+        <v>11345463.44073692</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.55933823529412</v>
+        <v>81.63537581699346</v>
       </c>
       <c r="AH6" t="n">
-        <v>25.95503607503607</v>
+        <v>25.81115119448453</v>
       </c>
       <c r="AI6" t="n">
-        <v>178.6936291486292</v>
+        <v>178.5345879429213</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.351392496392496</v>
+        <v>1.334880551547218</v>
       </c>
       <c r="AK6" t="n">
-        <v>74.15059163059163</v>
+        <v>74.08399070065737</v>
       </c>
       <c r="AL6" t="n">
-        <v>6850366.341991341</v>
+        <v>6784434.824434824</v>
       </c>
       <c r="AM6" t="n">
-        <v>77.42439033189032</v>
+        <v>77.45765592432258</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1426,22 +1426,22 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>26.53884297520661</v>
+        <v>26.42000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>183.6512396694215</v>
+        <v>183.5709090909091</v>
       </c>
       <c r="R7" t="n">
-        <v>1.009090909090909</v>
+        <v>1.01</v>
       </c>
       <c r="S7" t="n">
-        <v>68.68842975206611</v>
+        <v>68.54818181818182</v>
       </c>
       <c r="T7" t="n">
-        <v>1646404.958677686</v>
+        <v>1628090.909090909</v>
       </c>
       <c r="U7" t="n">
-        <v>72.45702479338843</v>
+        <v>72.45727272727272</v>
       </c>
       <c r="V7" t="n">
         <v>23.40020202020202</v>
@@ -1462,22 +1462,22 @@
         <v>79.89707070707071</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.56480186480186</v>
+        <v>24.68794871794872</v>
       </c>
       <c r="AC7" t="n">
-        <v>182.3365561974258</v>
+        <v>182.5202118171684</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>65.27299584473498</v>
+        <v>65.45029542920847</v>
       </c>
       <c r="AF7" t="n">
-        <v>1115412.612749569</v>
+        <v>1139037.20735786</v>
       </c>
       <c r="AG7" t="n">
-        <v>70.97475205953468</v>
+        <v>70.98889393215481</v>
       </c>
       <c r="AH7" t="n">
         <v>23.66545217209691</v>
@@ -1748,22 +1748,22 @@
         <v>80.08161157024793</v>
       </c>
       <c r="AB9" t="n">
-        <v>22.50400538382994</v>
+        <v>22.37360484544695</v>
       </c>
       <c r="AC9" t="n">
-        <v>183.3731365450664</v>
+        <v>183.429156223893</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.056994337696092</v>
+        <v>1.05796157059315</v>
       </c>
       <c r="AE9" t="n">
-        <v>69.0204214239302</v>
+        <v>68.90504594820383</v>
       </c>
       <c r="AF9" t="n">
-        <v>3689683.699990717</v>
+        <v>3659381.996658312</v>
       </c>
       <c r="AG9" t="n">
-        <v>77.42214332126613</v>
+        <v>77.46659565580619</v>
       </c>
       <c r="AH9" t="n">
         <v>23.09406704406705</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1857,22 +1857,22 @@
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>24.22090909090909</v>
+        <v>24.24545454545454</v>
       </c>
       <c r="Q10" t="n">
-        <v>180.7290909090909</v>
+        <v>180.6181818181818</v>
       </c>
       <c r="R10" t="n">
-        <v>1.438863636363636</v>
+        <v>1.437121212121212</v>
       </c>
       <c r="S10" t="n">
-        <v>76.32568181818182</v>
+        <v>76.29116161616162</v>
       </c>
       <c r="T10" t="n">
-        <v>12714113.63636363</v>
+        <v>12641944.44444444</v>
       </c>
       <c r="U10" t="n">
-        <v>81.28272727272727</v>
+        <v>81.25353535353536</v>
       </c>
       <c r="V10" t="n">
         <v>24.22654671717171</v>
@@ -1893,22 +1893,22 @@
         <v>85.15318813131313</v>
       </c>
       <c r="AB10" t="n">
-        <v>25.51454598033545</v>
+        <v>25.42886061307114</v>
       </c>
       <c r="AC10" t="n">
-        <v>180.1394550478761</v>
+        <v>180.1866960849417</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.249318167212904</v>
+        <v>1.245274154046084</v>
       </c>
       <c r="AE10" t="n">
-        <v>73.22647516226463</v>
+        <v>73.37862319616706</v>
       </c>
       <c r="AF10" t="n">
-        <v>6864106.596619755</v>
+        <v>7224007.329577505</v>
       </c>
       <c r="AG10" t="n">
-        <v>77.9453993959257</v>
+        <v>78.16155488436191</v>
       </c>
       <c r="AH10" t="n">
         <v>24.11841227550399</v>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:BC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,130 +505,200 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -637,35 +707,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>15220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -691,126 +761,150 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>26.98653198653199</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="n">
-        <v>181.9786195286195</v>
+        <v>180</v>
       </c>
       <c r="R2" t="n">
-        <v>2.030808080808081</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>76.6219696969697</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>10002558.92255892</v>
+        <v>76</v>
       </c>
       <c r="U2" t="n">
-        <v>79.07550505050506</v>
+        <v>11500000</v>
       </c>
       <c r="V2" t="n">
-        <v>22.05111111111111</v>
-      </c>
-      <c r="W2" t="n">
-        <v>183.3377777777778</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.162222222222222</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>71.24555555555555</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4460777.777777778</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>79.49555555555555</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>25.05226108183606</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>178.9420809217754</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>1.61197168775746</v>
+        <v>26.76767676767677</v>
       </c>
       <c r="AE2" t="n">
-        <v>74.228969900953</v>
+        <v>181.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>6817274.130082887</v>
+        <v>1.340404040404041</v>
       </c>
       <c r="AG2" t="n">
-        <v>78.68216839066719</v>
+        <v>74.79191919191919</v>
       </c>
       <c r="AH2" t="n">
-        <v>22.8086394814336</v>
+        <v>6737979.797979797</v>
       </c>
       <c r="AI2" t="n">
-        <v>182.3982062055591</v>
+        <v>76.83333333333333</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.204277095453566</v>
+        <v>25.54049586776859</v>
       </c>
       <c r="AK2" t="n">
-        <v>69.81871049701932</v>
+        <v>181.4157024793388</v>
       </c>
       <c r="AL2" t="n">
-        <v>3367680.331106802</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.39975220857573</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+        <v>70.31239669421488</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2263388.429752066</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>73.8396694214876</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>24.29532627865962</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>179.9535273368607</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>70.40308641975308</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4324382.716049383</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>74.65449735449735</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>24.90843570707824</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>180.3570858502985</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>68.51825123092091</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1845245.585234273</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>73.55132524589538</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15220</v>
+        <v>20484</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -835,123 +929,173 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
       <c r="P3" t="n">
-        <v>26.73636363636364</v>
+        <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.7845454545455</v>
+        <v>196</v>
       </c>
       <c r="R3" t="n">
-        <v>1.324545454545455</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>74.79454545454546</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>6704181.818181818</v>
+        <v>74</v>
       </c>
       <c r="U3" t="n">
-        <v>76.87727272727273</v>
+        <v>3500000</v>
       </c>
       <c r="V3" t="n">
-        <v>25.54049586776859</v>
+        <v>74</v>
       </c>
       <c r="W3" t="n">
-        <v>181.4157024793388</v>
+        <v>25.5</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>177.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>70.31239669421488</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>2263388.429752066</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>73.8396694214876</v>
+        <v>280</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.16579365079365</v>
+        <v>10425000</v>
       </c>
       <c r="AC3" t="n">
-        <v>179.9137301587302</v>
+        <v>293</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.157222222222222</v>
+        <v>24.98585858585859</v>
       </c>
       <c r="AE3" t="n">
-        <v>70.19611111111109</v>
+        <v>181.7333333333333</v>
       </c>
       <c r="AF3" t="n">
-        <v>4239722.222222222</v>
+        <v>1.343434343434344</v>
       </c>
       <c r="AG3" t="n">
-        <v>74.60015873015874</v>
+        <v>73.14747474747475</v>
       </c>
       <c r="AH3" t="n">
-        <v>24.90843570707824</v>
+        <v>5476060.606060605</v>
       </c>
       <c r="AI3" t="n">
-        <v>180.3570858502985</v>
+        <v>77.86161616161615</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>26.00707070707071</v>
       </c>
       <c r="AK3" t="n">
-        <v>68.51825123092091</v>
+        <v>182.8010101010101</v>
       </c>
       <c r="AL3" t="n">
-        <v>1845245.585234273</v>
+        <v>1.492929292929293</v>
       </c>
       <c r="AM3" t="n">
-        <v>73.55132524589538</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
+        <v>72.82525252525254</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>4687373.737373738</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>75.71919191919191</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>24.45900429414922</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>181.5582048922629</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.172429261559696</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>71.10948163484396</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3870997.43117859</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>76.13434744268076</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>25.724052269129</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>180.7331552954954</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.208417805711071</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>70.55334153863565</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2833812.965751371</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>73.97277124142001</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45535.66666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20484</v>
+        <v>33150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -976,131 +1120,155 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>25.00727272727273</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>181.75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.339090909090909</v>
-      </c>
-      <c r="S4" t="n">
-        <v>73.16272727272728</v>
-      </c>
-      <c r="T4" t="n">
-        <v>5504454.545454545</v>
-      </c>
-      <c r="U4" t="n">
-        <v>77.89545454545456</v>
-      </c>
-      <c r="V4" t="n">
-        <v>26.01545454545455</v>
-      </c>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>182.7209090909091</v>
+        <v>19</v>
       </c>
       <c r="X4" t="n">
-        <v>1.498181818181818</v>
+        <v>179</v>
       </c>
       <c r="Y4" t="n">
-        <v>72.91545454545455</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>4757727.272727273</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>75.75636363636363</v>
+        <v>63</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.37977053140096</v>
+        <v>1000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>181.5579399585921</v>
+        <v>74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.166297446514838</v>
+        <v>23.06408529741863</v>
       </c>
       <c r="AE4" t="n">
-        <v>71.00964458247067</v>
+        <v>183.1861952861953</v>
       </c>
       <c r="AF4" t="n">
-        <v>3767231.021394065</v>
+        <v>1.084062850729517</v>
       </c>
       <c r="AG4" t="n">
-        <v>76.1209126984127</v>
+        <v>72.75488215488215</v>
       </c>
       <c r="AH4" t="n">
-        <v>25.84053593110499</v>
+        <v>5651627.384960718</v>
       </c>
       <c r="AI4" t="n">
-        <v>180.9042842103904</v>
+        <v>78.87014590347924</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.198687136251075</v>
+        <v>26.92077922077922</v>
       </c>
       <c r="AK4" t="n">
-        <v>70.47578516254987</v>
+        <v>183.9012987012987</v>
       </c>
       <c r="AL4" t="n">
-        <v>2725265.002509568</v>
+        <v>1.693506493506494</v>
       </c>
       <c r="AM4" t="n">
-        <v>73.89771633950022</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
+        <v>77.19740259740261</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12364285.71428571</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>79.19350649350648</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>23.28048558392761</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>180.4424699026148</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>70.74570105820106</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3525008.147381336</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>77.04848650410244</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>24.83771976981471</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>182.9359775205492</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.319498066814889</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>75.05405817474961</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>10020852.5894852</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>78.6554936807259</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1125,127 +1293,173 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>lhUkVMh2</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>23.06676767676768</v>
+        <v>18</v>
       </c>
       <c r="Q5" t="n">
-        <v>183.2039393939394</v>
+        <v>173</v>
       </c>
       <c r="R5" t="n">
-        <v>1.084747474747475</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>72.75212121212121</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>5624646.464646464</v>
+        <v>66</v>
       </c>
       <c r="U5" t="n">
-        <v>78.88313131313132</v>
+        <v>2200000</v>
       </c>
       <c r="V5" t="n">
-        <v>26.87386363636364</v>
+        <v>82</v>
       </c>
       <c r="W5" t="n">
-        <v>183.7204545454545</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>1.697727272727273</v>
+        <v>176</v>
       </c>
       <c r="Y5" t="n">
-        <v>77.19545454545455</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>12426704.54545454</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>79.2375</v>
+        <v>222</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.19688146997929</v>
+        <v>21100000</v>
       </c>
       <c r="AC5" t="n">
-        <v>180.5426673567978</v>
+        <v>233</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>24.30011223344557</v>
       </c>
       <c r="AE5" t="n">
-        <v>70.69335317460317</v>
+        <v>182.3583613916947</v>
       </c>
       <c r="AF5" t="n">
-        <v>3523618.443754314</v>
+        <v>1.518069584736252</v>
       </c>
       <c r="AG5" t="n">
-        <v>77.11030452035887</v>
+        <v>76.69775533108867</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.79680493569039</v>
+        <v>14360549.94388328</v>
       </c>
       <c r="AI5" t="n">
-        <v>183.1709511970658</v>
+        <v>81.30998877665544</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.301833974419114</v>
+        <v>26.65555555555556</v>
       </c>
       <c r="AK5" t="n">
-        <v>74.90579521441751</v>
+        <v>180.6848484848485</v>
       </c>
       <c r="AL5" t="n">
-        <v>9724481.616250966</v>
+        <v>1.408080808080808</v>
       </c>
       <c r="AM5" t="n">
-        <v>78.5899443126533</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
+        <v>76.92929292929291</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13066565.65656566</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>79.39191919191919</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>22.23197024423805</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>181.7587919963307</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.31373504567519</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>74.49027013339449</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11345463.44073692</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>81.63537581699346</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>25.81115119448453</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>178.5345879429213</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.334880551547218</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>74.08399070065737</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6784434.824434824</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>77.45765592432258</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>18752</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1270,103 +1484,141 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>24.30011223344557</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.3583613916947</v>
+        <v>176</v>
       </c>
       <c r="R6" t="n">
-        <v>1.518069584736252</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>76.69775533108867</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>14360549.94388328</v>
+        <v>131</v>
       </c>
       <c r="U6" t="n">
-        <v>81.30998877665544</v>
+        <v>2325000</v>
       </c>
       <c r="V6" t="n">
-        <v>26.65555555555556</v>
+        <v>144</v>
       </c>
       <c r="W6" t="n">
-        <v>180.6848484848485</v>
+        <v>25.5</v>
       </c>
       <c r="X6" t="n">
-        <v>1.408080808080808</v>
+        <v>179</v>
       </c>
       <c r="Y6" t="n">
-        <v>76.92929292929291</v>
+        <v>1.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>13066565.65656566</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>79.39191919191919</v>
+        <v>308</v>
       </c>
       <c r="AB6" t="n">
-        <v>22.23197024423805</v>
+        <v>52500000</v>
       </c>
       <c r="AC6" t="n">
-        <v>181.7587919963307</v>
+        <v>317</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31373504567519</v>
+        <v>26.42000000000001</v>
       </c>
       <c r="AE6" t="n">
-        <v>74.49027013339449</v>
+        <v>183.5709090909091</v>
       </c>
       <c r="AF6" t="n">
-        <v>11345463.44073692</v>
+        <v>1.01</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.63537581699346</v>
+        <v>68.54818181818182</v>
       </c>
       <c r="AH6" t="n">
-        <v>25.81115119448453</v>
+        <v>1628090.909090909</v>
       </c>
       <c r="AI6" t="n">
-        <v>178.5345879429213</v>
+        <v>72.45727272727272</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.334880551547218</v>
+        <v>23.41436588103254</v>
       </c>
       <c r="AK6" t="n">
-        <v>74.08399070065737</v>
+        <v>183.8428731762065</v>
       </c>
       <c r="AL6" t="n">
-        <v>6784434.824434824</v>
+        <v>1.287093153759821</v>
       </c>
       <c r="AM6" t="n">
-        <v>77.45765592432258</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
+        <v>74.91616161616162</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12108215.48821549</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>79.97654320987655</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>24.68794871794872</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>182.5202118171684</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>65.45029542920847</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1139037.20735786</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>70.98889393215481</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>23.62828019121879</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>180.5718984962406</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.264452798663325</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>73.71018054395248</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7257999.976793837</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>78.45175554627309</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1374,27 +1626,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18752</v>
+        <v>25178</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1420,98 +1672,136 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>26.42000000000001</v>
+        <v>19</v>
       </c>
       <c r="Q7" t="n">
-        <v>183.5709090909091</v>
+        <v>188</v>
       </c>
       <c r="R7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>68.54818181818182</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1628090.909090909</v>
+        <v>64</v>
       </c>
       <c r="U7" t="n">
-        <v>72.45727272727272</v>
+        <v>1300000</v>
       </c>
       <c r="V7" t="n">
-        <v>23.40020202020202</v>
+        <v>74</v>
       </c>
       <c r="W7" t="n">
-        <v>183.5313131313131</v>
+        <v>23.2</v>
       </c>
       <c r="X7" t="n">
-        <v>1.285656565656566</v>
+        <v>181.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>74.83363636363636</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>11951939.39393939</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.89707070707071</v>
+        <v>330</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.68794871794872</v>
+        <v>7050000</v>
       </c>
       <c r="AC7" t="n">
-        <v>182.5202118171684</v>
+        <v>363</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>25.12626262626263</v>
       </c>
       <c r="AE7" t="n">
-        <v>65.45029542920847</v>
+        <v>185.8979797979798</v>
       </c>
       <c r="AF7" t="n">
-        <v>1139037.20735786</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
-        <v>70.98889393215481</v>
+        <v>71.45454545454545</v>
       </c>
       <c r="AH7" t="n">
-        <v>23.66545217209691</v>
+        <v>3000606.060606061</v>
       </c>
       <c r="AI7" t="n">
-        <v>180.543280075188</v>
+        <v>75.06464646464646</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.252293233082707</v>
+        <v>25.78257575757576</v>
       </c>
       <c r="AK7" t="n">
-        <v>73.69630534670009</v>
+        <v>181.585606060606</v>
       </c>
       <c r="AL7" t="n">
-        <v>7256485.693400169</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="n">
-        <v>78.43515142021721</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
+        <v>68.66199494949494</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1733134.469696969</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>71.7121212121212</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>24.75476059769538</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>181.1679577869796</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>68.86857585517005</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2168960.217687573</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>73.16603125806024</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>23.72391774891775</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>180.2424242424242</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>65.42586580086581</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1356834.415584416</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>71.3172077922078</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1519,27 +1809,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25178</v>
+        <v>21029</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1565,122 +1855,168 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
       <c r="P8" t="n">
-        <v>25.28363636363636</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>185.8581818181818</v>
+        <v>180</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>71.49909090909091</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>3007545.454545455</v>
+        <v>74</v>
       </c>
       <c r="U8" t="n">
-        <v>75.01818181818183</v>
+        <v>9500000</v>
       </c>
       <c r="V8" t="n">
-        <v>25.79407713498623</v>
+        <v>82</v>
       </c>
       <c r="W8" t="n">
-        <v>181.6315426997245</v>
+        <v>20</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="Y8" t="n">
-        <v>68.61007805325987</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1727642.906336088</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>71.65564738292011</v>
+        <v>72</v>
       </c>
       <c r="AB8" t="n">
-        <v>24.71261787125918</v>
+        <v>2900000</v>
       </c>
       <c r="AC8" t="n">
-        <v>181.2178286749483</v>
+        <v>78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>25.59888888888889</v>
       </c>
       <c r="AE8" t="n">
-        <v>68.82616271409749</v>
+        <v>182.9111111111111</v>
       </c>
       <c r="AF8" t="n">
-        <v>2139841.973696593</v>
+        <v>1.253888888888889</v>
       </c>
       <c r="AG8" t="n">
-        <v>73.12720591003199</v>
+        <v>74.38500000000001</v>
       </c>
       <c r="AH8" t="n">
-        <v>23.5801849665486</v>
+        <v>7680597.222222222</v>
       </c>
       <c r="AI8" t="n">
-        <v>180.4151908697363</v>
+        <v>78.91055555555556</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>24.52045454545454</v>
       </c>
       <c r="AK8" t="n">
-        <v>65.20533254624165</v>
+        <v>181.0840909090909</v>
       </c>
       <c r="AL8" t="n">
-        <v>1328615.702479339</v>
+        <v>1.704545454545454</v>
       </c>
       <c r="AM8" t="n">
-        <v>71.35330578512396</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
+        <v>75.81477272727273</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>10319090.90909091</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>80.08068181818183</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>22.37807945790402</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>183.3472106191404</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.0644017451035</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>68.98708809059686</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3781257.774064791</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>77.55547665459946</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>23.1606166056166</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>181.222148962149</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.443885836385836</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>73.88479548229547</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>9292646.520146519</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>79.34880647130646</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.65625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21029</v>
+        <v>50186</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1705,235 +2041,132 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>25.49907407407407</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="n">
-        <v>182.8518518518518</v>
+        <v>177.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.248611111111111</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>74.37638888888888</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>7611608.796296296</v>
+        <v>383</v>
       </c>
       <c r="U9" t="n">
-        <v>78.96249999999999</v>
+        <v>47800000</v>
       </c>
       <c r="V9" t="n">
-        <v>24.55578512396694</v>
+        <v>390</v>
       </c>
       <c r="W9" t="n">
-        <v>181.2995867768595</v>
+        <v>27</v>
       </c>
       <c r="X9" t="n">
-        <v>1.698347107438016</v>
+        <v>186.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>75.82334710743802</v>
+        <v>3</v>
       </c>
       <c r="Z9" t="n">
-        <v>10348760.33057851</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>80.08161157024793</v>
+        <v>165</v>
       </c>
       <c r="AB9" t="n">
-        <v>22.37360484544695</v>
+        <v>68000000</v>
       </c>
       <c r="AC9" t="n">
-        <v>183.429156223893</v>
+        <v>167</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.05796157059315</v>
+        <v>24.24545454545454</v>
       </c>
       <c r="AE9" t="n">
-        <v>68.90504594820383</v>
+        <v>180.6181818181818</v>
       </c>
       <c r="AF9" t="n">
-        <v>3659381.996658312</v>
+        <v>1.437121212121212</v>
       </c>
       <c r="AG9" t="n">
-        <v>77.46659565580619</v>
+        <v>76.29116161616162</v>
       </c>
       <c r="AH9" t="n">
-        <v>23.09406704406705</v>
+        <v>12641944.44444444</v>
       </c>
       <c r="AI9" t="n">
-        <v>181.0331224331224</v>
+        <v>81.25353535353536</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.429506604506605</v>
+        <v>24.23293650793651</v>
       </c>
       <c r="AK9" t="n">
-        <v>73.80435952935953</v>
+        <v>183.3369047619048</v>
       </c>
       <c r="AL9" t="n">
-        <v>9103704.62870463</v>
+        <v>2.292857142857142</v>
       </c>
       <c r="AM9" t="n">
-        <v>79.35605783105784</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>551</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>24.24545454545454</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>180.6181818181818</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.437121212121212</v>
-      </c>
-      <c r="S10" t="n">
-        <v>76.29116161616162</v>
-      </c>
-      <c r="T10" t="n">
-        <v>12641944.44444444</v>
-      </c>
-      <c r="U10" t="n">
-        <v>81.25353535353536</v>
-      </c>
-      <c r="V10" t="n">
-        <v>24.22654671717171</v>
-      </c>
-      <c r="W10" t="n">
-        <v>183.3402462121213</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.335795454545454</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>81.08421717171717</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>42712673.6111111</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>85.15318813131313</v>
-      </c>
-      <c r="AB10" t="n">
+        <v>80.83650793650794</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>40885912.69841269</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>84.99325396825397</v>
+      </c>
+      <c r="AP9" t="n">
         <v>25.42886061307114</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AQ9" t="n">
         <v>180.1866960849417</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AR9" t="n">
         <v>1.245274154046084</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AS9" t="n">
         <v>73.37862319616706</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AT9" t="n">
         <v>7224007.329577505</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AU9" t="n">
         <v>78.16155488436191</v>
       </c>
-      <c r="AH10" t="n">
-        <v>24.11841227550399</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>183.6283087880902</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.223860072031512</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>78.77708881460815</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>33889750.49922129</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>83.73761769383867</v>
-      </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AV9" t="n">
+        <v>23.96034585899137</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>183.6075056909035</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2.231223974683727</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>78.79578520035176</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>35044662.88226737</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>83.84363488678504</v>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC9"/>
+  <dimension ref="A1:BC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,35 +707,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15220</v>
+        <v>18523</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,13 +760,21 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q2" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -775,136 +783,150 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="U2" t="n">
-        <v>11500000</v>
+        <v>2200000</v>
       </c>
       <c r="V2" t="n">
         <v>82</v>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="X2" t="n">
+        <v>176.3333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>222</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>18100000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>230</v>
+      </c>
       <c r="AD2" t="n">
-        <v>26.76767676767677</v>
+        <v>24.30011223344557</v>
       </c>
       <c r="AE2" t="n">
-        <v>181.7</v>
+        <v>182.3583613916947</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.340404040404041</v>
+        <v>1.518069584736252</v>
       </c>
       <c r="AG2" t="n">
-        <v>74.79191919191919</v>
+        <v>76.69775533108867</v>
       </c>
       <c r="AH2" t="n">
-        <v>6737979.797979797</v>
+        <v>14360549.94388328</v>
       </c>
       <c r="AI2" t="n">
-        <v>76.83333333333333</v>
+        <v>81.30998877665544</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25.54049586776859</v>
+        <v>26.65555555555556</v>
       </c>
       <c r="AK2" t="n">
-        <v>181.4157024793388</v>
+        <v>180.6848484848485</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>1.408080808080808</v>
       </c>
       <c r="AM2" t="n">
-        <v>70.31239669421488</v>
+        <v>76.92929292929291</v>
       </c>
       <c r="AN2" t="n">
-        <v>2263388.429752066</v>
+        <v>13066565.65656566</v>
       </c>
       <c r="AO2" t="n">
-        <v>73.8396694214876</v>
+        <v>79.39191919191919</v>
       </c>
       <c r="AP2" t="n">
-        <v>24.29532627865962</v>
+        <v>22.23197024423805</v>
       </c>
       <c r="AQ2" t="n">
-        <v>179.9535273368607</v>
+        <v>181.7587919963307</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.15</v>
+        <v>1.31373504567519</v>
       </c>
       <c r="AS2" t="n">
-        <v>70.40308641975308</v>
+        <v>74.49027013339449</v>
       </c>
       <c r="AT2" t="n">
-        <v>4324382.716049383</v>
+        <v>11345463.44073692</v>
       </c>
       <c r="AU2" t="n">
-        <v>74.65449735449735</v>
+        <v>81.63537581699346</v>
       </c>
       <c r="AV2" t="n">
-        <v>24.90843570707824</v>
+        <v>25.81115119448453</v>
       </c>
       <c r="AW2" t="n">
-        <v>180.3570858502985</v>
+        <v>178.5345879429213</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>1.334880551547218</v>
       </c>
       <c r="AY2" t="n">
-        <v>68.51825123092091</v>
+        <v>74.08399070065737</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1845245.585234273</v>
+        <v>6784434.824434824</v>
       </c>
       <c r="BA2" t="n">
-        <v>73.55132524589538</v>
+        <v>77.45765592432258</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -929,173 +951,169 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
       <c r="T3" t="n">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="U3" t="n">
-        <v>3500000</v>
+        <v>2325000</v>
       </c>
       <c r="V3" t="n">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="W3" t="n">
         <v>25.5</v>
       </c>
       <c r="X3" t="n">
-        <v>177.5</v>
+        <v>179</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
         <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="AB3" t="n">
-        <v>10425000</v>
+        <v>52500000</v>
       </c>
       <c r="AC3" t="n">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="AD3" t="n">
-        <v>24.98585858585859</v>
+        <v>26.42000000000001</v>
       </c>
       <c r="AE3" t="n">
-        <v>181.7333333333333</v>
+        <v>183.5709090909091</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.343434343434344</v>
+        <v>1.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>73.14747474747475</v>
+        <v>68.54818181818182</v>
       </c>
       <c r="AH3" t="n">
-        <v>5476060.606060605</v>
+        <v>1628090.909090909</v>
       </c>
       <c r="AI3" t="n">
-        <v>77.86161616161615</v>
+        <v>72.45727272727272</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26.00707070707071</v>
+        <v>23.41436588103254</v>
       </c>
       <c r="AK3" t="n">
-        <v>182.8010101010101</v>
+        <v>183.8428731762065</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.492929292929293</v>
+        <v>1.287093153759821</v>
       </c>
       <c r="AM3" t="n">
-        <v>72.82525252525254</v>
+        <v>74.91616161616162</v>
       </c>
       <c r="AN3" t="n">
-        <v>4687373.737373738</v>
+        <v>12108215.48821549</v>
       </c>
       <c r="AO3" t="n">
-        <v>75.71919191919191</v>
+        <v>79.97654320987655</v>
       </c>
       <c r="AP3" t="n">
-        <v>24.45900429414922</v>
+        <v>24.68794871794872</v>
       </c>
       <c r="AQ3" t="n">
-        <v>181.5582048922629</v>
+        <v>182.5202118171684</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.172429261559696</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>71.10948163484396</v>
+        <v>65.45029542920847</v>
       </c>
       <c r="AT3" t="n">
-        <v>3870997.43117859</v>
+        <v>1139037.20735786</v>
       </c>
       <c r="AU3" t="n">
-        <v>76.13434744268076</v>
+        <v>70.98889393215481</v>
       </c>
       <c r="AV3" t="n">
-        <v>25.724052269129</v>
+        <v>23.62828019121879</v>
       </c>
       <c r="AW3" t="n">
-        <v>180.7331552954954</v>
+        <v>180.5718984962406</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.208417805711071</v>
+        <v>1.264452798663325</v>
       </c>
       <c r="AY3" t="n">
-        <v>70.55334153863565</v>
+        <v>73.71018054395248</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2833812.965751371</v>
+        <v>7257999.976793837</v>
       </c>
       <c r="BA3" t="n">
-        <v>73.97277124142001</v>
+        <v>78.45175554627309</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33150</v>
+        <v>25178</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1121,154 +1139,164 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>188</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>64</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>74</v>
+      </c>
       <c r="W4" t="n">
-        <v>19</v>
+        <v>23.2</v>
       </c>
       <c r="X4" t="n">
-        <v>179</v>
+        <v>181.6</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>330</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7050000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>363</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>25.12626262626263</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>185.8979797979798</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1</v>
       </c>
-      <c r="AA4" t="n">
-        <v>63</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>74</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>23.06408529741863</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>183.1861952861953</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.084062850729517</v>
-      </c>
       <c r="AG4" t="n">
-        <v>72.75488215488215</v>
+        <v>71.45454545454545</v>
       </c>
       <c r="AH4" t="n">
-        <v>5651627.384960718</v>
+        <v>3000606.060606061</v>
       </c>
       <c r="AI4" t="n">
-        <v>78.87014590347924</v>
+        <v>75.06464646464646</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26.92077922077922</v>
+        <v>25.78257575757576</v>
       </c>
       <c r="AK4" t="n">
-        <v>183.9012987012987</v>
+        <v>181.585606060606</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.693506493506494</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>77.19740259740261</v>
+        <v>68.66199494949494</v>
       </c>
       <c r="AN4" t="n">
-        <v>12364285.71428571</v>
+        <v>1733134.469696969</v>
       </c>
       <c r="AO4" t="n">
-        <v>79.19350649350648</v>
+        <v>71.7121212121212</v>
       </c>
       <c r="AP4" t="n">
-        <v>23.28048558392761</v>
+        <v>24.75476059769538</v>
       </c>
       <c r="AQ4" t="n">
-        <v>180.4424699026148</v>
+        <v>181.1679577869796</v>
       </c>
       <c r="AR4" t="n">
         <v>1</v>
       </c>
       <c r="AS4" t="n">
-        <v>70.74570105820106</v>
+        <v>68.86857585517005</v>
       </c>
       <c r="AT4" t="n">
-        <v>3525008.147381336</v>
+        <v>2168960.217687573</v>
       </c>
       <c r="AU4" t="n">
-        <v>77.04848650410244</v>
+        <v>73.16603125806024</v>
       </c>
       <c r="AV4" t="n">
-        <v>24.83771976981471</v>
+        <v>23.72391774891775</v>
       </c>
       <c r="AW4" t="n">
-        <v>182.9359775205492</v>
+        <v>180.2424242424242</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.319498066814889</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
-        <v>75.05405817474961</v>
+        <v>65.42586580086581</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10020852.5894852</v>
+        <v>1356834.415584416</v>
       </c>
       <c r="BA4" t="n">
-        <v>78.6554936807259</v>
+        <v>71.3172077922078</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18523</v>
+        <v>21029</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1293,173 +1321,169 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="n">
-        <v>173</v>
+        <v>177.5</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="U5" t="n">
-        <v>2200000</v>
+        <v>16000000</v>
       </c>
       <c r="V5" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="W5" t="n">
-        <v>24.33333333333333</v>
+        <v>20</v>
       </c>
       <c r="X5" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>222</v>
+        <v>72</v>
       </c>
       <c r="AB5" t="n">
-        <v>21100000</v>
+        <v>2900000</v>
       </c>
       <c r="AC5" t="n">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="AD5" t="n">
-        <v>24.30011223344557</v>
+        <v>25.59888888888889</v>
       </c>
       <c r="AE5" t="n">
-        <v>182.3583613916947</v>
+        <v>182.9111111111111</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.518069584736252</v>
+        <v>1.253888888888889</v>
       </c>
       <c r="AG5" t="n">
-        <v>76.69775533108867</v>
+        <v>74.38500000000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>14360549.94388328</v>
+        <v>7680597.222222222</v>
       </c>
       <c r="AI5" t="n">
-        <v>81.30998877665544</v>
+        <v>78.91055555555556</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26.65555555555556</v>
+        <v>24.52777777777778</v>
       </c>
       <c r="AK5" t="n">
-        <v>180.6848484848485</v>
+        <v>180.9924242424243</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.408080808080808</v>
+        <v>1.702020202020202</v>
       </c>
       <c r="AM5" t="n">
-        <v>76.92929292929291</v>
+        <v>75.79419191919192</v>
       </c>
       <c r="AN5" t="n">
-        <v>13066565.65656566</v>
+        <v>10271717.17171717</v>
       </c>
       <c r="AO5" t="n">
-        <v>79.39191919191919</v>
+        <v>80.07954545454545</v>
       </c>
       <c r="AP5" t="n">
-        <v>22.23197024423805</v>
+        <v>22.37807945790402</v>
       </c>
       <c r="AQ5" t="n">
-        <v>181.7587919963307</v>
+        <v>183.3472106191404</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.31373504567519</v>
+        <v>1.0644017451035</v>
       </c>
       <c r="AS5" t="n">
-        <v>74.49027013339449</v>
+        <v>68.98708809059686</v>
       </c>
       <c r="AT5" t="n">
-        <v>11345463.44073692</v>
+        <v>3781257.774064791</v>
       </c>
       <c r="AU5" t="n">
-        <v>81.63537581699346</v>
+        <v>77.55547665459946</v>
       </c>
       <c r="AV5" t="n">
-        <v>25.81115119448453</v>
+        <v>23.16611721611722</v>
       </c>
       <c r="AW5" t="n">
-        <v>178.5345879429213</v>
+        <v>181.2715235381902</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.334880551547218</v>
+        <v>1.456169447836115</v>
       </c>
       <c r="AY5" t="n">
-        <v>74.08399070065737</v>
+        <v>73.89668633835299</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6784434.824434824</v>
+        <v>9381952.923619591</v>
       </c>
       <c r="BA5" t="n">
-        <v>77.45765592432258</v>
+        <v>79.3381800298467</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18752</v>
+        <v>50186</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1484,125 +1508,125 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
-        <v>176</v>
+        <v>177.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>383</v>
+      </c>
+      <c r="U6" t="n">
+        <v>47800000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>390</v>
+      </c>
+      <c r="W6" t="n">
+        <v>27</v>
+      </c>
+      <c r="X6" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
-        <v>131</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2325000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>144</v>
-      </c>
-      <c r="W6" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>179</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
       <c r="AA6" t="n">
-        <v>308</v>
+        <v>165</v>
       </c>
       <c r="AB6" t="n">
-        <v>52500000</v>
+        <v>68000000</v>
       </c>
       <c r="AC6" t="n">
-        <v>317</v>
+        <v>167</v>
       </c>
       <c r="AD6" t="n">
-        <v>26.42000000000001</v>
+        <v>24.24545454545454</v>
       </c>
       <c r="AE6" t="n">
-        <v>183.5709090909091</v>
+        <v>180.6181818181818</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.01</v>
+        <v>1.437121212121212</v>
       </c>
       <c r="AG6" t="n">
-        <v>68.54818181818182</v>
+        <v>76.29116161616162</v>
       </c>
       <c r="AH6" t="n">
-        <v>1628090.909090909</v>
+        <v>12641944.44444444</v>
       </c>
       <c r="AI6" t="n">
-        <v>72.45727272727272</v>
+        <v>81.25353535353536</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23.41436588103254</v>
+        <v>24.27175925925926</v>
       </c>
       <c r="AK6" t="n">
-        <v>183.8428731762065</v>
+        <v>183.4763888888889</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.287093153759821</v>
+        <v>2.216666666666666</v>
       </c>
       <c r="AM6" t="n">
-        <v>74.91616161616162</v>
+        <v>80.28842592592594</v>
       </c>
       <c r="AN6" t="n">
-        <v>12108215.48821549</v>
+        <v>36460648.14814814</v>
       </c>
       <c r="AO6" t="n">
-        <v>79.97654320987655</v>
+        <v>84.63796296296296</v>
       </c>
       <c r="AP6" t="n">
-        <v>24.68794871794872</v>
+        <v>25.42886061307114</v>
       </c>
       <c r="AQ6" t="n">
-        <v>182.5202118171684</v>
+        <v>180.1866960849417</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>1.245274154046084</v>
       </c>
       <c r="AS6" t="n">
-        <v>65.45029542920847</v>
+        <v>73.37862319616706</v>
       </c>
       <c r="AT6" t="n">
-        <v>1139037.20735786</v>
+        <v>7224007.329577505</v>
       </c>
       <c r="AU6" t="n">
-        <v>70.98889393215481</v>
+        <v>78.16155488436191</v>
       </c>
       <c r="AV6" t="n">
-        <v>23.62828019121879</v>
+        <v>23.6188804448905</v>
       </c>
       <c r="AW6" t="n">
-        <v>180.5718984962406</v>
+        <v>183.4807562599939</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.264452798663325</v>
+        <v>2.204346372152099</v>
       </c>
       <c r="AY6" t="n">
-        <v>73.71018054395248</v>
+        <v>78.55036372038694</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7257999.976793837</v>
+        <v>35967879.17049411</v>
       </c>
       <c r="BA6" t="n">
-        <v>78.45175554627309</v>
+        <v>83.96549837546354</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1610,563 +1634,6 @@
         </is>
       </c>
       <c r="BC6" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I7" t="n">
-        <v>551</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>188</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>64</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>74</v>
-      </c>
-      <c r="W7" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>330</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7050000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>363</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>25.12626262626263</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>185.8979797979798</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>71.45454545454545</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>3000606.060606061</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>75.06464646464646</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>25.78257575757576</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>181.585606060606</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>68.66199494949494</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1733134.469696969</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>71.7121212121212</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>24.75476059769538</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>181.1679577869796</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>68.86857585517005</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2168960.217687573</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>73.16603125806024</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>23.72391774891775</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>180.2424242424242</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>65.42586580086581</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1356834.415584416</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>71.3172077922078</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>55</v>
-      </c>
-      <c r="I8" t="n">
-        <v>551</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>180</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>74</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>82</v>
-      </c>
-      <c r="W8" t="n">
-        <v>20</v>
-      </c>
-      <c r="X8" t="n">
-        <v>189</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>72</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>78</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25.59888888888889</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>182.9111111111111</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.253888888888889</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>74.38500000000001</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>7680597.222222222</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>78.91055555555556</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>24.52045454545454</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>181.0840909090909</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.704545454545454</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>75.81477272727273</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>10319090.90909091</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>80.08068181818183</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>22.37807945790402</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>183.3472106191404</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.0644017451035</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>68.98708809059686</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3781257.774064791</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>77.55547665459946</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>23.1606166056166</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>181.222148962149</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.443885836385836</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>73.88479548229547</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>9292646.520146519</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>79.34880647130646</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="n">
-        <v>551</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>177.4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>383</v>
-      </c>
-      <c r="U9" t="n">
-        <v>47800000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>390</v>
-      </c>
-      <c r="W9" t="n">
-        <v>27</v>
-      </c>
-      <c r="X9" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>165</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>167</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>24.24545454545454</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>180.6181818181818</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.437121212121212</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>76.29116161616162</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>12641944.44444444</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>81.25353535353536</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>24.23293650793651</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>183.3369047619048</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.292857142857142</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>80.83650793650794</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>40885912.69841269</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>84.99325396825397</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>25.42886061307114</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>180.1866960849417</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.245274154046084</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>73.37862319616706</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7224007.329577505</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>78.16155488436191</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>23.96034585899137</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>183.6075056909035</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>2.231223974683727</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>78.79578520035176</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>35044662.88226737</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>83.84363488678504</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC6"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>vsYzkTIc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45548.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18523</v>
+        <v>42000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,149 +690,103 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>18</v>
+        <v>25.375</v>
       </c>
       <c r="Q2" t="n">
-        <v>173</v>
+        <v>181.75</v>
       </c>
       <c r="R2" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S2" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2278125</v>
+      </c>
+      <c r="U2" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="V2" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>181.1666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.241666666666667</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>75.29166666666667</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10989166.66666667</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>81.06666666666666</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>24.74509803921569</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>181.2860962566845</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>66</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>82</v>
-      </c>
-      <c r="W2" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>176.3333333333333</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>222</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>18100000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>230</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>24.30011223344557</v>
-      </c>
       <c r="AE2" t="n">
-        <v>182.3583613916947</v>
+        <v>66.80837789661318</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.518069584736252</v>
+        <v>1423128.342245989</v>
       </c>
       <c r="AG2" t="n">
-        <v>76.69775533108867</v>
+        <v>72.88948306595366</v>
       </c>
       <c r="AH2" t="n">
-        <v>14360549.94388328</v>
+        <v>24.74098124098124</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.30998877665544</v>
+        <v>178.1106301106301</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26.65555555555556</v>
+        <v>1.53992303992304</v>
       </c>
       <c r="AK2" t="n">
-        <v>180.6848484848485</v>
+        <v>73.6144781144781</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.408080808080808</v>
+        <v>9092508.417508416</v>
       </c>
       <c r="AM2" t="n">
-        <v>76.92929292929291</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>13066565.65656566</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>79.39191919191919</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>22.23197024423805</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>181.7587919963307</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.31373504567519</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>74.49027013339449</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>11345463.44073692</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>81.63537581699346</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>25.81115119448453</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>178.5345879429213</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.334880551547218</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>74.08399070065737</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6784434.824434824</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>77.45765592432258</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
+        <v>79.23785473785473</v>
+      </c>
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>0dMqm7mA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -912,16 +796,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>67394</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -951,169 +835,119 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>2PIvr8o4</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>176</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>131</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2325000</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>144</v>
+        <v>23.22962962962963</v>
       </c>
       <c r="W3" t="n">
-        <v>25.5</v>
+        <v>182.9259259259259</v>
       </c>
       <c r="X3" t="n">
-        <v>179</v>
+        <v>1.140740740740741</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.75</v>
+        <v>73.97407407407407</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>10034074.07407408</v>
       </c>
       <c r="AA3" t="n">
-        <v>308</v>
+        <v>79.67037037037038</v>
       </c>
       <c r="AB3" t="n">
-        <v>52500000</v>
+        <v>24.63787878787879</v>
       </c>
       <c r="AC3" t="n">
-        <v>317</v>
+        <v>178.905303030303</v>
       </c>
       <c r="AD3" t="n">
-        <v>26.42000000000001</v>
+        <v>1.601515151515152</v>
       </c>
       <c r="AE3" t="n">
-        <v>183.5709090909091</v>
+        <v>75.62727272727273</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.01</v>
+        <v>12316136.36363637</v>
       </c>
       <c r="AG3" t="n">
-        <v>68.54818181818182</v>
+        <v>79.16060606060607</v>
       </c>
       <c r="AH3" t="n">
-        <v>1628090.909090909</v>
+        <v>22.85833333333333</v>
       </c>
       <c r="AI3" t="n">
-        <v>72.45727272727272</v>
+        <v>180.875</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23.41436588103254</v>
+        <v>1.054166666666667</v>
       </c>
       <c r="AK3" t="n">
-        <v>183.8428731762065</v>
+        <v>72.67083333333333</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.287093153759821</v>
+        <v>5938437.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>74.91616161616162</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>12108215.48821549</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>79.97654320987655</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>24.68794871794872</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>182.5202118171684</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>65.45029542920847</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1139037.20735786</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>70.98889393215481</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>23.62828019121879</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>180.5718984962406</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.264452798663325</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>73.71018054395248</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>7257999.976793837</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>78.45175554627309</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
+        <v>78.11666666666666</v>
+      </c>
+      <c r="AN3" t="inlineStr">
         <is>
           <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CGH7Enso</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25178</v>
+        <v>17924</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1139,164 +973,126 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
       <c r="P4" t="n">
-        <v>19</v>
+        <v>25.95833333333334</v>
       </c>
       <c r="Q4" t="n">
-        <v>188</v>
+        <v>182.2916666666666</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
+        <v>68.67361111111111</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1771354.166666667</v>
+      </c>
+      <c r="U4" t="n">
+        <v>71.83333333333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23.13333333333334</v>
+      </c>
+      <c r="W4" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>75.53333333333333</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>11860000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>23.93398268398268</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>181.2099567099567</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="n">
-        <v>64</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>74</v>
-      </c>
-      <c r="W4" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>330</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7050000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>363</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>25.12626262626263</v>
-      </c>
       <c r="AE4" t="n">
-        <v>185.8979797979798</v>
+        <v>64.7536075036075</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>1217225.82972583</v>
       </c>
       <c r="AG4" t="n">
-        <v>71.45454545454545</v>
+        <v>70.77886002886002</v>
       </c>
       <c r="AH4" t="n">
-        <v>3000606.060606061</v>
+        <v>21.82777777777778</v>
       </c>
       <c r="AI4" t="n">
-        <v>75.06464646464646</v>
+        <v>182.4611111111111</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25.78257575757576</v>
+        <v>1.407407407407407</v>
       </c>
       <c r="AK4" t="n">
-        <v>181.585606060606</v>
+        <v>74.03518518518518</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>11438981.48148148</v>
       </c>
       <c r="AM4" t="n">
-        <v>68.66199494949494</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1733134.469696969</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>71.7121212121212</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>24.75476059769538</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>181.1679577869796</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>68.86857585517005</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2168960.217687573</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>73.16603125806024</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>23.72391774891775</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>180.2424242424242</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>65.42586580086581</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1356834.415584416</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>71.3172077922078</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
+        <v>81.58333333333333</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21029</v>
+        <v>48229</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1322,168 +1118,122 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>177.5</v>
+        <v>181.875</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2.125</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>81.75</v>
       </c>
       <c r="T5" t="n">
-        <v>149</v>
+        <v>47000000</v>
       </c>
       <c r="U5" t="n">
-        <v>16000000</v>
+        <v>86.75</v>
       </c>
       <c r="V5" t="n">
-        <v>159</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="W5" t="n">
-        <v>20</v>
+        <v>180.2111111111111</v>
       </c>
       <c r="X5" t="n">
-        <v>189</v>
+        <v>1.344444444444444</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>74.31851851851853</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>6138518.518518519</v>
       </c>
       <c r="AA5" t="n">
-        <v>72</v>
+        <v>75.46296296296296</v>
       </c>
       <c r="AB5" t="n">
-        <v>2900000</v>
+        <v>22.7974358974359</v>
       </c>
       <c r="AC5" t="n">
-        <v>78</v>
+        <v>183.994301994302</v>
       </c>
       <c r="AD5" t="n">
-        <v>25.59888888888889</v>
+        <v>2.039601139601139</v>
       </c>
       <c r="AE5" t="n">
-        <v>182.9111111111111</v>
+        <v>78.34672364672365</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.253888888888889</v>
+        <v>31636438.74643875</v>
       </c>
       <c r="AG5" t="n">
-        <v>74.38500000000001</v>
+        <v>84.27492877492877</v>
       </c>
       <c r="AH5" t="n">
-        <v>7680597.222222222</v>
+        <v>23.77170868347339</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.91055555555556</v>
+        <v>179.3482726423903</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24.52777777777778</v>
+        <v>1.237721755368814</v>
       </c>
       <c r="AK5" t="n">
-        <v>180.9924242424243</v>
+        <v>68.59234360410831</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.702020202020202</v>
+        <v>3805957.049486461</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.79419191919192</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>10271717.17171717</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>80.07954545454545</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>22.37807945790402</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>183.3472106191404</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.0644017451035</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>68.98708809059686</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3781257.774064791</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>77.55547665459946</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>23.16611721611722</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>181.2715235381902</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.456169447836115</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>73.89668633835299</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>9381952.923619591</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>79.3381800298467</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+        <v>74.16900093370681</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45550.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>50186</v>
+        <v>29778</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1510,132 +1260,658 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>180.375</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75.4375</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9100000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>79.3125</v>
+      </c>
+      <c r="V6" t="n">
+        <v>26.08484848484848</v>
+      </c>
+      <c r="W6" t="n">
+        <v>180.6575757575758</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.418181818181818</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>74.03636363636363</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6009090.909090909</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>77.69090909090909</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>23.85787545787545</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>180.7124542124542</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.489010989010989</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>73.13516483516484</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>7734853.47985348</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>77.99377289377288</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>24.05753968253968</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>180.6547619047619</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.178571428571429</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>70.69444444444444</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4054563.492063493</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>76.5813492063492</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>24.53333333333333</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>72.63333333333334</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5110833.333333333</v>
+      </c>
+      <c r="U7" t="n">
+        <v>76.36666666666667</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>25.57077497665733</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>182.118954248366</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.369000933706816</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>71.89458450046686</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3875158.73015873</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>74.57226890756304</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>21.77745098039216</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>182.9058823529412</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.041830065359477</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>69.23006535947712</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4398169.934640523</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>78.10751633986928</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>21.07777777777778</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>70.44444444444444</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4245648.148148148</v>
+      </c>
+      <c r="U8" t="n">
+        <v>80.13703703703703</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>184.3666666666667</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1594166.666666667</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>72.83333333333333</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>20.82371794871795</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>181.3311965811966</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>68.04967948717949</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2950320.512820513</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>78.05982905982906</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>26.11666666666666</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>182.0746376811594</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>67.0659420289855</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1378713.768115942</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>72.06884057971014</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>23.22592592592592</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>180.8481481481482</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.107407407407407</v>
+      </c>
+      <c r="S9" t="n">
+        <v>72.72592592592594</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5314814.814814814</v>
+      </c>
+      <c r="U9" t="n">
+        <v>78.34444444444445</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24.91515151515151</v>
+      </c>
+      <c r="W9" t="n">
+        <v>185.7848484848485</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>71.21515151515152</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2918787.878787879</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>75.23636363636363</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>23.82083333333334</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>178.8972222222222</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>70.21805555555555</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2949027.777777778</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>75.94861111111111</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23.47133838383838</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>180.8541666666667</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>68.16969696969697</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2181505.681818182</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>73.63181818181818</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>177.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>383</v>
-      </c>
-      <c r="U6" t="n">
-        <v>47800000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>390</v>
-      </c>
-      <c r="W6" t="n">
-        <v>27</v>
-      </c>
-      <c r="X6" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>165</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>167</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>24.24545454545454</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>180.6181818181818</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.437121212121212</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>76.29116161616162</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>12641944.44444444</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>81.25353535353536</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>24.27175925925926</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>183.4763888888889</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.216666666666666</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>80.28842592592594</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>36460648.14814814</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>84.63796296296296</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>25.42886061307114</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>180.1866960849417</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.245274154046084</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>73.37862319616706</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7224007.329577505</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>78.16155488436191</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>23.6188804448905</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>183.4807562599939</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>2.204346372152099</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>78.55036372038694</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>35967879.17049411</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>83.96549837546354</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>26.57878787878788</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>181.2393939393939</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.384848484848485</v>
+      </c>
+      <c r="S10" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="T10" t="n">
+        <v>12107272.72727273</v>
+      </c>
+      <c r="U10" t="n">
+        <v>79.27575757575757</v>
+      </c>
+      <c r="V10" t="n">
+        <v>25.96296296296296</v>
+      </c>
+      <c r="W10" t="n">
+        <v>181.7777777777777</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>76.18518518518518</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>10025925.92592593</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>79.51851851851852</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24.48636363636363</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>179.7552188552189</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.222895622895623</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>73.36969696969697</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6589865.31986532</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>77.78434343434344</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23.9761832370528</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>180.4386845039019</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.576213641431033</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>73.6269382791122</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>6183384.00729705</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>79.53471166514645</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,22 +715,22 @@
         <v>74.875</v>
       </c>
       <c r="V2" t="n">
-        <v>23.6</v>
+        <v>24.61851851851852</v>
       </c>
       <c r="W2" t="n">
-        <v>181.1666666666667</v>
+        <v>181.8016835016835</v>
       </c>
       <c r="X2" t="n">
-        <v>1.241666666666667</v>
+        <v>1.271043771043771</v>
       </c>
       <c r="Y2" t="n">
-        <v>75.29166666666667</v>
+        <v>75.41144781144781</v>
       </c>
       <c r="Z2" t="n">
-        <v>10989166.66666667</v>
+        <v>10184680.13468014</v>
       </c>
       <c r="AA2" t="n">
-        <v>81.06666666666666</v>
+        <v>80.37575757575758</v>
       </c>
       <c r="AB2" t="n">
         <v>24.74509803921569</v>
@@ -751,22 +751,22 @@
         <v>72.88948306595366</v>
       </c>
       <c r="AH2" t="n">
-        <v>24.74098124098124</v>
+        <v>25.7979797979798</v>
       </c>
       <c r="AI2" t="n">
-        <v>178.1106301106301</v>
+        <v>180.2707070707071</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.53992303992304</v>
+        <v>1.701010101010101</v>
       </c>
       <c r="AK2" t="n">
-        <v>73.6144781144781</v>
+        <v>73.94848484848485</v>
       </c>
       <c r="AL2" t="n">
-        <v>9092508.417508416</v>
+        <v>8267979.797979799</v>
       </c>
       <c r="AM2" t="n">
-        <v>79.23785473785473</v>
+        <v>78.66060606060607</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -845,65 +845,77 @@
           <t>2PIvr8o4</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>23.85185185185185</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>182.5185185185186</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.462962962962963</v>
+      </c>
+      <c r="S3" t="n">
+        <v>76.48888888888888</v>
+      </c>
+      <c r="T3" t="n">
+        <v>15397777.77777778</v>
+      </c>
+      <c r="U3" t="n">
+        <v>80.48888888888889</v>
+      </c>
       <c r="V3" t="n">
-        <v>23.22962962962963</v>
+        <v>23.48484848484848</v>
       </c>
       <c r="W3" t="n">
-        <v>182.9259259259259</v>
+        <v>183.2121212121212</v>
       </c>
       <c r="X3" t="n">
-        <v>1.140740740740741</v>
+        <v>1.212121212121212</v>
       </c>
       <c r="Y3" t="n">
-        <v>73.97407407407407</v>
+        <v>73.60606060606061</v>
       </c>
       <c r="Z3" t="n">
-        <v>10034074.07407408</v>
+        <v>10127272.72727273</v>
       </c>
       <c r="AA3" t="n">
-        <v>79.67037037037038</v>
+        <v>79.03030303030303</v>
       </c>
       <c r="AB3" t="n">
-        <v>24.63787878787879</v>
+        <v>23.44065656565656</v>
       </c>
       <c r="AC3" t="n">
-        <v>178.905303030303</v>
+        <v>180.0164141414141</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.601515151515152</v>
+        <v>1.432070707070707</v>
       </c>
       <c r="AE3" t="n">
-        <v>75.62727272727273</v>
+        <v>73.3189393939394</v>
       </c>
       <c r="AF3" t="n">
-        <v>12316136.36363637</v>
+        <v>9875303.030303029</v>
       </c>
       <c r="AG3" t="n">
-        <v>79.16060606060607</v>
+        <v>79.88838383838385</v>
       </c>
       <c r="AH3" t="n">
-        <v>22.85833333333333</v>
+        <v>22.97276688453159</v>
       </c>
       <c r="AI3" t="n">
-        <v>180.875</v>
+        <v>180.8341255694197</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.054166666666667</v>
+        <v>1.135769459298871</v>
       </c>
       <c r="AK3" t="n">
-        <v>72.67083333333333</v>
+        <v>73.11507229154289</v>
       </c>
       <c r="AL3" t="n">
-        <v>5938437.5</v>
+        <v>7032350.465438701</v>
       </c>
       <c r="AM3" t="n">
-        <v>78.11666666666666</v>
+        <v>78.41552782729254</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -979,76 +991,76 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>25.95833333333334</v>
+        <v>25.36666666666666</v>
       </c>
       <c r="Q4" t="n">
-        <v>182.2916666666666</v>
+        <v>182.4333333333333</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>68.67361111111111</v>
+        <v>69</v>
       </c>
       <c r="T4" t="n">
-        <v>1771354.166666667</v>
+        <v>2240833.333333333</v>
       </c>
       <c r="U4" t="n">
-        <v>71.83333333333334</v>
+        <v>72.96666666666665</v>
       </c>
       <c r="V4" t="n">
         <v>23.13333333333334</v>
       </c>
       <c r="W4" t="n">
-        <v>183.1</v>
+        <v>183.4</v>
       </c>
       <c r="X4" t="n">
         <v>1.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>75.53333333333333</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>11860000</v>
+        <v>12760000</v>
       </c>
       <c r="AA4" t="n">
-        <v>81.33333333333333</v>
+        <v>81.53333333333333</v>
       </c>
       <c r="AB4" t="n">
-        <v>23.93398268398268</v>
+        <v>23.87121212121212</v>
       </c>
       <c r="AC4" t="n">
-        <v>181.2099567099567</v>
+        <v>181.2828282828283</v>
       </c>
       <c r="AD4" t="n">
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>64.7536075036075</v>
+        <v>64.90656565656565</v>
       </c>
       <c r="AF4" t="n">
-        <v>1217225.82972583</v>
+        <v>1270959.595959596</v>
       </c>
       <c r="AG4" t="n">
-        <v>70.77886002886002</v>
+        <v>70.98989898989899</v>
       </c>
       <c r="AH4" t="n">
         <v>21.82777777777778</v>
       </c>
       <c r="AI4" t="n">
-        <v>182.4611111111111</v>
+        <v>182.5388888888889</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.407407407407407</v>
       </c>
       <c r="AK4" t="n">
-        <v>74.03518518518518</v>
+        <v>74.0925925925926</v>
       </c>
       <c r="AL4" t="n">
-        <v>11438981.48148148</v>
+        <v>12193611.11111111</v>
       </c>
       <c r="AM4" t="n">
-        <v>81.58333333333333</v>
+        <v>81.71481481481483</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1120,76 +1132,76 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>22.5</v>
+        <v>23.22222222222222</v>
       </c>
       <c r="Q5" t="n">
-        <v>181.875</v>
+        <v>182.4222222222223</v>
       </c>
       <c r="R5" t="n">
-        <v>2.125</v>
+        <v>2.161111111111111</v>
       </c>
       <c r="S5" t="n">
-        <v>81.75</v>
+        <v>82.28333333333333</v>
       </c>
       <c r="T5" t="n">
-        <v>47000000</v>
+        <v>49605555.55555555</v>
       </c>
       <c r="U5" t="n">
-        <v>86.75</v>
+        <v>86.73888888888888</v>
       </c>
       <c r="V5" t="n">
-        <v>27.77777777777778</v>
+        <v>27.89393939393939</v>
       </c>
       <c r="W5" t="n">
-        <v>180.2111111111111</v>
+        <v>181.7909090909091</v>
       </c>
       <c r="X5" t="n">
-        <v>1.344444444444444</v>
+        <v>1.406060606060606</v>
       </c>
       <c r="Y5" t="n">
-        <v>74.31851851851853</v>
+        <v>74.47575757575758</v>
       </c>
       <c r="Z5" t="n">
-        <v>6138518.518518519</v>
+        <v>6264545.454545456</v>
       </c>
       <c r="AA5" t="n">
-        <v>75.46296296296296</v>
+        <v>75.51212121212122</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.7974358974359</v>
+        <v>23.12916666666667</v>
       </c>
       <c r="AC5" t="n">
-        <v>183.994301994302</v>
+        <v>183.9606481481482</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.039601139601139</v>
+        <v>2.08287037037037</v>
       </c>
       <c r="AE5" t="n">
-        <v>78.34672364672365</v>
+        <v>78.76018518518519</v>
       </c>
       <c r="AF5" t="n">
-        <v>31636438.74643875</v>
+        <v>33601342.59259259</v>
       </c>
       <c r="AG5" t="n">
-        <v>84.27492877492877</v>
+        <v>84.47685185185185</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.77170868347339</v>
+        <v>23.7375</v>
       </c>
       <c r="AI5" t="n">
-        <v>179.3482726423903</v>
+        <v>180.675</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.237721755368814</v>
+        <v>1.256944444444444</v>
       </c>
       <c r="AK5" t="n">
-        <v>68.59234360410831</v>
+        <v>68.73472222222222</v>
       </c>
       <c r="AL5" t="n">
-        <v>3805957.049486461</v>
+        <v>3870138.888888889</v>
       </c>
       <c r="AM5" t="n">
-        <v>74.16900093370681</v>
+        <v>74.41111111111111</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1269,28 +1281,28 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>25.375</v>
+        <v>25.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>180.375</v>
+        <v>180.5666666666667</v>
       </c>
       <c r="R6" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
-        <v>75.4375</v>
+        <v>75.7</v>
       </c>
       <c r="T6" t="n">
-        <v>9100000</v>
+        <v>8713333.333333334</v>
       </c>
       <c r="U6" t="n">
-        <v>79.3125</v>
+        <v>78.93333333333334</v>
       </c>
       <c r="V6" t="n">
         <v>26.08484848484848</v>
       </c>
       <c r="W6" t="n">
-        <v>180.6575757575758</v>
+        <v>180.8393939393939</v>
       </c>
       <c r="X6" t="n">
         <v>1.418181818181818</v>
@@ -1305,28 +1317,28 @@
         <v>77.69090909090909</v>
       </c>
       <c r="AB6" t="n">
-        <v>23.85787545787545</v>
+        <v>23.71895424836601</v>
       </c>
       <c r="AC6" t="n">
-        <v>180.7124542124542</v>
+        <v>180.5294117647059</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.489010989010989</v>
+        <v>1.597572362278245</v>
       </c>
       <c r="AE6" t="n">
-        <v>73.13516483516484</v>
+        <v>72.95144724556489</v>
       </c>
       <c r="AF6" t="n">
-        <v>7734853.47985348</v>
+        <v>7236811.391223155</v>
       </c>
       <c r="AG6" t="n">
-        <v>77.99377289377288</v>
+        <v>78.07282913165265</v>
       </c>
       <c r="AH6" t="n">
         <v>24.05753968253968</v>
       </c>
       <c r="AI6" t="n">
-        <v>180.6547619047619</v>
+        <v>181.25</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.178571428571429</v>
@@ -1414,22 +1426,22 @@
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>24.53333333333333</v>
+        <v>24.48484848484848</v>
       </c>
       <c r="Q7" t="n">
-        <v>182.1</v>
+        <v>182.3636363636364</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="S7" t="n">
-        <v>72.63333333333334</v>
+        <v>72.57575757575758</v>
       </c>
       <c r="T7" t="n">
-        <v>5110833.333333333</v>
+        <v>4937121.212121212</v>
       </c>
       <c r="U7" t="n">
-        <v>76.36666666666667</v>
+        <v>76.24242424242424</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -1438,40 +1450,40 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
-        <v>25.57077497665733</v>
+        <v>25.47361111111111</v>
       </c>
       <c r="AC7" t="n">
-        <v>182.118954248366</v>
+        <v>182.2967592592593</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.369000933706816</v>
+        <v>1.346296296296297</v>
       </c>
       <c r="AE7" t="n">
-        <v>71.89458450046686</v>
+        <v>71.90092592592593</v>
       </c>
       <c r="AF7" t="n">
-        <v>3875158.73015873</v>
+        <v>3832627.314814815</v>
       </c>
       <c r="AG7" t="n">
-        <v>74.57226890756304</v>
+        <v>74.59953703703704</v>
       </c>
       <c r="AH7" t="n">
-        <v>21.77745098039216</v>
+        <v>22.32600732600732</v>
       </c>
       <c r="AI7" t="n">
-        <v>182.9058823529412</v>
+        <v>183.994301994302</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.041830065359477</v>
+        <v>1.034391534391535</v>
       </c>
       <c r="AK7" t="n">
-        <v>69.23006535947712</v>
+        <v>69.87871387871388</v>
       </c>
       <c r="AL7" t="n">
-        <v>4398169.934640523</v>
+        <v>4372975.172975173</v>
       </c>
       <c r="AM7" t="n">
-        <v>78.10751633986928</v>
+        <v>77.68030118030119</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -1547,22 +1559,22 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>21.07777777777778</v>
+        <v>20.78181818181818</v>
       </c>
       <c r="Q8" t="n">
-        <v>184.7</v>
+        <v>184.0545454545454</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>70.44444444444444</v>
+        <v>69.94242424242424</v>
       </c>
       <c r="T8" t="n">
-        <v>4245648.148148148</v>
+        <v>4019090.909090909</v>
       </c>
       <c r="U8" t="n">
-        <v>80.13703703703703</v>
+        <v>80.12727272727273</v>
       </c>
       <c r="V8" t="n">
         <v>25.16666666666667</v>
@@ -1583,22 +1595,22 @@
         <v>72.83333333333333</v>
       </c>
       <c r="AB8" t="n">
-        <v>20.82371794871795</v>
+        <v>20.20793650793651</v>
       </c>
       <c r="AC8" t="n">
-        <v>181.3311965811966</v>
+        <v>180.731746031746</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>68.04967948717949</v>
+        <v>67.91507936507936</v>
       </c>
       <c r="AF8" t="n">
-        <v>2950320.512820513</v>
+        <v>2863095.238095238</v>
       </c>
       <c r="AG8" t="n">
-        <v>78.05982905982906</v>
+        <v>78.62910052910054</v>
       </c>
       <c r="AH8" t="n">
         <v>26.11666666666666</v>
@@ -1688,22 +1700,22 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>23.22592592592592</v>
+        <v>22.91212121212122</v>
       </c>
       <c r="Q9" t="n">
-        <v>180.8481481481482</v>
+        <v>181.8333333333333</v>
       </c>
       <c r="R9" t="n">
-        <v>1.107407407407407</v>
+        <v>1.096969696969697</v>
       </c>
       <c r="S9" t="n">
-        <v>72.72592592592594</v>
+        <v>72.46060606060607</v>
       </c>
       <c r="T9" t="n">
-        <v>5314814.814814814</v>
+        <v>5119090.909090909</v>
       </c>
       <c r="U9" t="n">
-        <v>78.34444444444445</v>
+        <v>78.60303030303031</v>
       </c>
       <c r="V9" t="n">
         <v>24.91515151515151</v>
@@ -1724,22 +1736,22 @@
         <v>75.23636363636363</v>
       </c>
       <c r="AB9" t="n">
-        <v>23.82083333333334</v>
+        <v>23.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>178.8972222222222</v>
+        <v>179.1458333333333</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>70.21805555555555</v>
+        <v>70.20833333333333</v>
       </c>
       <c r="AF9" t="n">
-        <v>2949027.777777778</v>
+        <v>2947916.666666667</v>
       </c>
       <c r="AG9" t="n">
-        <v>75.94861111111111</v>
+        <v>76.04166666666667</v>
       </c>
       <c r="AH9" t="n">
         <v>23.47133838383838</v>
@@ -1833,76 +1845,76 @@
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>26.57878787878788</v>
+        <v>26.33333333333334</v>
       </c>
       <c r="Q10" t="n">
-        <v>181.2393939393939</v>
+        <v>180.5151515151515</v>
       </c>
       <c r="R10" t="n">
-        <v>1.384848484848485</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="S10" t="n">
-        <v>76.33333333333333</v>
+        <v>76.2121212121212</v>
       </c>
       <c r="T10" t="n">
-        <v>12107272.72727273</v>
+        <v>11957575.75757576</v>
       </c>
       <c r="U10" t="n">
-        <v>79.27575757575757</v>
+        <v>79.48484848484848</v>
       </c>
       <c r="V10" t="n">
-        <v>25.96296296296296</v>
+        <v>26.06666666666667</v>
       </c>
       <c r="W10" t="n">
-        <v>181.7777777777777</v>
+        <v>182.4</v>
       </c>
       <c r="X10" t="n">
-        <v>1.777777777777778</v>
+        <v>1.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>76.18518518518518</v>
+        <v>76.26666666666667</v>
       </c>
       <c r="Z10" t="n">
-        <v>10025925.92592593</v>
+        <v>10140000</v>
       </c>
       <c r="AA10" t="n">
-        <v>79.51851851851852</v>
+        <v>79.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>24.48636363636363</v>
+        <v>24.39309241483155</v>
       </c>
       <c r="AC10" t="n">
-        <v>179.7552188552189</v>
+        <v>179.970606687998</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.222895622895623</v>
+        <v>1.199259677520547</v>
       </c>
       <c r="AE10" t="n">
-        <v>73.36969696969697</v>
+        <v>73.49055775142732</v>
       </c>
       <c r="AF10" t="n">
-        <v>6589865.31986532</v>
+        <v>6789778.530648096</v>
       </c>
       <c r="AG10" t="n">
-        <v>77.78434343434344</v>
+        <v>77.99153020892152</v>
       </c>
       <c r="AH10" t="n">
-        <v>23.9761832370528</v>
+        <v>23.84156785243742</v>
       </c>
       <c r="AI10" t="n">
-        <v>180.4386845039019</v>
+        <v>180.7350131752306</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.576213641431033</v>
+        <v>1.556982872200264</v>
       </c>
       <c r="AK10" t="n">
-        <v>73.6269382791122</v>
+        <v>73.48270750988142</v>
       </c>
       <c r="AL10" t="n">
-        <v>6183384.00729705</v>
+        <v>6071763.833992095</v>
       </c>
       <c r="AM10" t="n">
-        <v>79.53471166514645</v>
+        <v>79.60762516469038</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1912,6 +1924,1299 @@
       <c r="AO10" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>23.48484848484848</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>183.2121212121212</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.212121212121212</v>
+      </c>
+      <c r="S11" t="n">
+        <v>73.60606060606061</v>
+      </c>
+      <c r="T11" t="n">
+        <v>10127272.72727273</v>
+      </c>
+      <c r="U11" t="n">
+        <v>79.03030303030303</v>
+      </c>
+      <c r="V11" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="W11" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2278125</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>22.97276688453159</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>180.8341255694197</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.135769459298871</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>73.11507229154289</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>7032350.465438701</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>78.41552782729254</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>24.74509803921569</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>181.2860962566845</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>66.80837789661318</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1423128.342245989</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>72.88948306595366</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>24.61851851851852</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>181.8016835016835</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.271043771043771</v>
+      </c>
+      <c r="S12" t="n">
+        <v>75.41144781144781</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10184680.13468014</v>
+      </c>
+      <c r="U12" t="n">
+        <v>80.37575757575758</v>
+      </c>
+      <c r="V12" t="n">
+        <v>20.78181818181818</v>
+      </c>
+      <c r="W12" t="n">
+        <v>184.0545454545454</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>69.94242424242424</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4019090.909090909</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>80.12727272727273</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>25.7979797979798</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>180.2707070707071</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.701010101010101</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>73.94848484848485</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>8267979.797979799</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>78.66060606060607</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>20.20793650793651</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>180.731746031746</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>67.91507936507936</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2863095.238095238</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>78.62910052910054</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>180.5666666666667</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S13" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8713333.333333334</v>
+      </c>
+      <c r="U13" t="n">
+        <v>78.93333333333334</v>
+      </c>
+      <c r="V13" t="n">
+        <v>26.33333333333334</v>
+      </c>
+      <c r="W13" t="n">
+        <v>180.5151515151515</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>76.2121212121212</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>11957575.75757576</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>79.48484848484848</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>23.71895424836601</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>180.5294117647059</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.597572362278245</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>72.95144724556489</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>7236811.391223155</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>78.07282913165265</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24.39309241483155</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>179.970606687998</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.199259677520547</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>73.49055775142732</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>6789778.530648096</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>77.99153020892152</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>23.22222222222222</v>
+      </c>
+      <c r="W14" t="n">
+        <v>182.4222222222223</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.161111111111111</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>82.28333333333333</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>49605555.55555555</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>86.73888888888888</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>22.32600732600732</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>183.994301994302</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.034391534391535</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>69.87871387871388</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>4372975.172975173</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>77.68030118030119</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23.12916666666667</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>183.9606481481482</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.08287037037037</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>78.76018518518519</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>33601342.59259259</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>84.47685185185185</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>23.13333333333334</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="T15" t="n">
+        <v>12760000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>81.53333333333333</v>
+      </c>
+      <c r="V15" t="n">
+        <v>24.91515151515151</v>
+      </c>
+      <c r="W15" t="n">
+        <v>185.7848484848485</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>71.21515151515152</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2918787.878787879</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>75.23636363636363</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>21.82777777777778</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>182.5388888888889</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.407407407407407</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>74.0925925925926</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12193611.11111111</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>81.71481481481483</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>23.47133838383838</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>180.8541666666667</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>68.16969696969697</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2181505.681818182</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>73.63181818181818</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>184.3666666666667</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="S16" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1594166.666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>72.83333333333333</v>
+      </c>
+      <c r="V16" t="n">
+        <v>24.48484848484848</v>
+      </c>
+      <c r="W16" t="n">
+        <v>182.3636363636364</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>72.57575757575758</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4937121.212121212</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>76.24242424242424</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>26.11666666666666</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>182.0746376811594</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>67.0659420289855</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1378713.768115942</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>72.06884057971014</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>25.47361111111111</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>182.2967592592593</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.346296296296297</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>71.90092592592593</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>3832627.314814815</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>74.59953703703704</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>27.89393939393939</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>181.7909090909091</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.406060606060606</v>
+      </c>
+      <c r="S17" t="n">
+        <v>74.47575757575758</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6264545.454545456</v>
+      </c>
+      <c r="U17" t="n">
+        <v>75.51212121212122</v>
+      </c>
+      <c r="V17" t="n">
+        <v>22.91212121212122</v>
+      </c>
+      <c r="W17" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.096969696969697</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>72.46060606060607</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5119090.909090909</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>78.60303030303031</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>23.7375</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>180.675</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.256944444444444</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>68.73472222222222</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3870138.888888889</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>74.41111111111111</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>179.1458333333333</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>70.20833333333333</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2947916.666666667</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>76.04166666666667</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>26.08484848484848</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>180.8393939393939</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.418181818181818</v>
+      </c>
+      <c r="S18" t="n">
+        <v>74.03636363636363</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6009090.909090909</v>
+      </c>
+      <c r="U18" t="n">
+        <v>77.69090909090909</v>
+      </c>
+      <c r="V18" t="n">
+        <v>25.36666666666666</v>
+      </c>
+      <c r="W18" t="n">
+        <v>182.4333333333333</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2240833.333333333</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>72.96666666666665</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24.05753968253968</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.178571428571429</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>70.69444444444444</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4054563.492063493</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>76.5813492063492</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23.87121212121212</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>181.2828282828283</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>64.90656565656565</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1270959.595959596</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>70.98989898989899</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>26.06666666666667</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>76.26666666666667</v>
+      </c>
+      <c r="T19" t="n">
+        <v>10140000</v>
+      </c>
+      <c r="U19" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>23.85185185185185</v>
+      </c>
+      <c r="W19" t="n">
+        <v>182.5185185185186</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.462962962962963</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>76.48888888888888</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>15397777.77777778</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>80.48888888888889</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>23.84156785243742</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>180.7350131752306</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.556982872200264</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>73.48270750988142</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>6071763.833992095</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>79.60762516469038</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23.44065656565656</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>180.0164141414141</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.432070707070707</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>73.3189393939394</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>9875303.030303029</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>79.88838383838385</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC6"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45555.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29778</v>
+        <v>36178</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -762,171 +692,125 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>21.5</v>
+        <v>23.66363636363636</v>
       </c>
       <c r="Q2" t="n">
-        <v>187</v>
+        <v>182.9840909090909</v>
       </c>
       <c r="R2" t="n">
+        <v>1.209090909090909</v>
+      </c>
+      <c r="S2" t="n">
+        <v>74.02954545454546</v>
+      </c>
+      <c r="T2" t="n">
+        <v>10557954.54545455</v>
+      </c>
+      <c r="U2" t="n">
+        <v>79.24772727272727</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25.8125</v>
+      </c>
+      <c r="W2" t="n">
+        <v>181.9375</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2376562.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>22.84321152703506</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>180.5460487225193</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.181372549019608</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>72.88175876411171</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>7200399.212715389</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>78.4707367795603</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>24.96266968325792</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>181.5414952694364</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>145</v>
-      </c>
-      <c r="U2" t="n">
-        <v>8400000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>158</v>
-      </c>
-      <c r="W2" t="n">
-        <v>24</v>
-      </c>
-      <c r="X2" t="n">
-        <v>185.6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>358</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>19600000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>383</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>180.5666666666667</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>8713333.333333334</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>78.93333333333334</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>26.08484848484848</v>
-      </c>
       <c r="AK2" t="n">
-        <v>180.8393939393939</v>
+        <v>67.14474496092143</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.418181818181818</v>
+        <v>1477442.410530646</v>
       </c>
       <c r="AM2" t="n">
-        <v>74.03636363636363</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6009090.909090909</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>77.69090909090909</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23.71895424836601</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>180.5294117647059</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.597572362278245</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>72.95144724556489</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7236811.391223155</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>78.07282913165265</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>24.05753968253968</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.178571428571429</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>70.69444444444444</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4054563.492063493</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>76.5813492063492</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
+        <v>72.85941999177294</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.5</v>
+        <v>45556.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35322</v>
+        <v>50186</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -953,155 +837,129 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>24.83888888888889</v>
       </c>
       <c r="Q3" t="n">
-        <v>179.2</v>
+        <v>182.1012626262626</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.303282828282828</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>75.53358585858587</v>
       </c>
       <c r="T3" t="n">
-        <v>355</v>
+        <v>10151010.1010101</v>
       </c>
       <c r="U3" t="n">
-        <v>15925000</v>
+        <v>80.23181818181818</v>
       </c>
       <c r="V3" t="n">
-        <v>369</v>
+        <v>20.44747474747475</v>
       </c>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>183.8742424242424</v>
       </c>
       <c r="X3" t="n">
-        <v>177.5</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
+        <v>70.12348484848485</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4155984.848484849</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>80.51212121212122</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>25.61410984848485</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>179.8749053030303</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.650757575757576</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>74.30511363636364</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8973641.098484848</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>78.83920454545455</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>20.42157738095239</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>181.3925595238095</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>1</v>
       </c>
-      <c r="Z3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>149</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>159</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24.48484848484848</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>182.3636363636364</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.363636363636364</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>72.57575757575758</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>4937121.212121212</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>76.24242424242424</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>25.47361111111111</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>182.2967592592593</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.346296296296297</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>71.90092592592593</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3832627.314814815</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>74.59953703703704</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>22.32600732600732</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>183.994301994302</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.034391534391535</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>69.87871387871388</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4372975.172975173</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>77.68030118030119</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+      <c r="AK3" t="n">
+        <v>68.03005952380953</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2896149.553571429</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>78.50307539682541</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.5</v>
+        <v>45556.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26109</v>
+        <v>29778</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1128,167 +986,129 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>25.325</v>
       </c>
       <c r="Q4" t="n">
-        <v>188</v>
+        <v>180.475</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>75.75</v>
       </c>
       <c r="T4" t="n">
-        <v>65</v>
+        <v>8617500</v>
       </c>
       <c r="U4" t="n">
-        <v>1400000</v>
+        <v>78.92500000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>76</v>
+        <v>26.34090909090909</v>
       </c>
       <c r="W4" t="n">
-        <v>25.66666666666667</v>
+        <v>180.2727272727273</v>
       </c>
       <c r="X4" t="n">
-        <v>177.6666666666667</v>
+        <v>1.340909090909091</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>76.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>11775000</v>
       </c>
       <c r="AA4" t="n">
-        <v>200</v>
+        <v>79.36363636363637</v>
       </c>
       <c r="AB4" t="n">
-        <v>3300000</v>
+        <v>23.30237358101135</v>
       </c>
       <c r="AC4" t="n">
-        <v>213</v>
+        <v>180.1075851393189</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.78181818181818</v>
+        <v>1.540284534866578</v>
       </c>
       <c r="AE4" t="n">
-        <v>184.0545454545454</v>
+        <v>72.5030591183842</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>7153924.332891051</v>
       </c>
       <c r="AG4" t="n">
-        <v>69.94242424242424</v>
+        <v>78.08093763821319</v>
       </c>
       <c r="AH4" t="n">
-        <v>4019090.909090909</v>
+        <v>24.08429299533419</v>
       </c>
       <c r="AI4" t="n">
-        <v>80.12727272727273</v>
+        <v>180.3069023844195</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25.16666666666667</v>
+        <v>1.175760547614094</v>
       </c>
       <c r="AK4" t="n">
-        <v>184.3666666666667</v>
+        <v>73.3416025240968</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.066666666666667</v>
+        <v>6842333.897986071</v>
       </c>
       <c r="AM4" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1594166.666666667</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>72.83333333333333</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>20.20793650793651</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>180.731746031746</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>67.91507936507936</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2863095.238095238</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>78.62910052910054</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>26.11666666666666</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>182.0746376811594</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.016666666666667</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>67.0659420289855</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1378713.768115942</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>72.06884057971014</v>
-      </c>
-      <c r="BB4" t="inlineStr">
+        <v>78.28312134090166</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.5</v>
+        <v>45556.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>21029</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1315,315 +1135,2088 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>178</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>72</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3700000</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>78</v>
+        <v>23.60648148148148</v>
       </c>
       <c r="W5" t="n">
-        <v>19</v>
+        <v>183.3648148148148</v>
       </c>
       <c r="X5" t="n">
-        <v>188</v>
+        <v>2.232407407407407</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>82.1888888888889</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>47674537.03703704</v>
       </c>
       <c r="AA5" t="n">
-        <v>64</v>
+        <v>86.20092592592592</v>
       </c>
       <c r="AB5" t="n">
-        <v>1300000</v>
+        <v>22.71325549450549</v>
       </c>
       <c r="AC5" t="n">
-        <v>74</v>
+        <v>184.1051014957265</v>
       </c>
       <c r="AD5" t="n">
-        <v>22.91212121212122</v>
+        <v>1.025793650793651</v>
       </c>
       <c r="AE5" t="n">
-        <v>181.8333333333333</v>
+        <v>70.19028540903541</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.096969696969697</v>
+        <v>4547075.129731379</v>
       </c>
       <c r="AG5" t="n">
-        <v>72.46060606060607</v>
+        <v>77.60397588522588</v>
       </c>
       <c r="AH5" t="n">
-        <v>5119090.909090909</v>
+        <v>22.690625</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.60303030303031</v>
+        <v>183.9079861111111</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24.91515151515151</v>
+        <v>1.999652777777778</v>
       </c>
       <c r="AK5" t="n">
-        <v>185.7848484848485</v>
+        <v>78.16388888888889</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>32285381.94444444</v>
       </c>
       <c r="AM5" t="n">
-        <v>71.21515151515152</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>2918787.878787879</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>75.23636363636363</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>179.1458333333333</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>70.20833333333333</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2947916.666666667</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>76.04166666666667</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>23.47133838383838</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>180.8541666666667</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>68.16969696969697</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2181505.681818182</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>73.63181818181818</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
+        <v>84.57638888888889</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45557.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>551</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183.425</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75.82499999999999</v>
+      </c>
+      <c r="T6" t="n">
+        <v>12970000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>81.47499999999999</v>
+      </c>
+      <c r="V6" t="n">
+        <v>24.89090909090909</v>
+      </c>
+      <c r="W6" t="n">
+        <v>185.2931818181818</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>71.25227272727273</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2959545.454545454</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>75.17727272727274</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>21.87083333333334</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>182.4541666666667</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.355555555555556</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>74.34444444444443</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12995833.33333333</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>81.79861111111111</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>24.01600378787879</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>181.140625</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>68.55227272727274</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2151129.261363636</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>73.46136363636364</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>25.29166666666666</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>183.525</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.077777777777778</v>
+      </c>
+      <c r="S7" t="n">
+        <v>68.10833333333333</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1703958.333333333</v>
+      </c>
+      <c r="U7" t="n">
+        <v>72.93055555555556</v>
+      </c>
+      <c r="V7" t="n">
+        <v>24.79545454545455</v>
+      </c>
+      <c r="W7" t="n">
+        <v>182.1136363636364</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.386363636363637</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>72.77272727272728</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4976136.363636363</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>76.06818181818181</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>25.85220588235294</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>181.7912723785166</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.027205882352941</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>66.71122122762148</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1325947.090792839</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>71.87515984654732</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>25.21047149122807</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>182.3804641812866</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.259722222222222</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>71.75464181286549</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3660983.644005848</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>74.54175804093566</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>27.89545454545454</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>181.9931818181818</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.379545454545455</v>
+      </c>
+      <c r="S8" t="n">
+        <v>74.58181818181819</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6240909.090909092</v>
+      </c>
+      <c r="U8" t="n">
+        <v>75.63409090909092</v>
+      </c>
+      <c r="V8" t="n">
+        <v>23.05909090909091</v>
+      </c>
+      <c r="W8" t="n">
+        <v>181.90625</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.103977272727273</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>72.53295454545454</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5220568.181818182</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>78.42102272727273</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>24.178125</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>180.7221590909091</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.249526515151515</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>69.55104166666666</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3917376.893939394</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>74.58106060606062</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>23.60661764705882</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>179.5211397058823</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>70.40625</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>3062408.088235294</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>76.38419117647058</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>25.78585858585858</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>180.5462121212121</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.369191919191919</v>
+      </c>
+      <c r="S9" t="n">
+        <v>73.69393939393939</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5865151.515151516</v>
+      </c>
+      <c r="U9" t="n">
+        <v>77.68484848484849</v>
+      </c>
+      <c r="V9" t="n">
+        <v>25.22954545454546</v>
+      </c>
+      <c r="W9" t="n">
+        <v>182.4386363636364</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>69.09090909090909</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2395965.909090909</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>73.08863636363637</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>24.66815476190476</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>180.7708333333333</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.258928571428572</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>70.97916666666666</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3920089.285714286</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>76.4985119047619</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>24.00340909090909</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>181.0996212121212</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>65.20492424242424</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1307594.696969697</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>71.15492424242424</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>26.49444444444445</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>182.9111111111111</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.877777777777778</v>
+      </c>
+      <c r="S10" t="n">
+        <v>76.42222222222222</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10063333.33333333</v>
+      </c>
+      <c r="U10" t="n">
+        <v>79.20833333333333</v>
+      </c>
+      <c r="V10" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>182.2222222222222</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.458333333333333</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>76.64444444444445</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>15398333.33333333</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>80.22777777777779</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>23.94696536301227</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>180.4328388287913</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.549316101518619</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>73.78308326399002</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6818296.559704597</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>79.92940308404411</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23.50696301247772</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>180.6005459001782</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.382876559714795</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>73.29802807486632</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>9384418.44919786</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>79.43099376114083</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.58333333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>25.22954545454546</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>182.4386363636364</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>69.09090909090909</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2395965.909090909</v>
+      </c>
+      <c r="U11" t="n">
+        <v>73.08863636363637</v>
+      </c>
+      <c r="V11" t="n">
+        <v>27.89545454545454</v>
+      </c>
+      <c r="W11" t="n">
+        <v>181.9931818181818</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.379545454545455</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>74.58181818181819</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6240909.090909092</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>75.63409090909092</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>24.00340909090909</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>181.0996212121212</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>65.20492424242424</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1307594.696969697</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>71.15492424242424</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>24.178125</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>180.7221590909091</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.249526515151515</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>69.55104166666666</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3917376.893939394</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>74.58106060606062</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>23.60648148148148</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>183.3648148148148</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.232407407407407</v>
+      </c>
+      <c r="S12" t="n">
+        <v>82.1888888888889</v>
+      </c>
+      <c r="T12" t="n">
+        <v>47674537.03703704</v>
+      </c>
+      <c r="U12" t="n">
+        <v>86.20092592592592</v>
+      </c>
+      <c r="V12" t="n">
+        <v>25.325</v>
+      </c>
+      <c r="W12" t="n">
+        <v>180.475</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8617500</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>78.92500000000001</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>22.690625</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>183.9079861111111</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.999652777777778</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>78.16388888888889</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>32285381.94444444</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>84.57638888888889</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>23.30237358101135</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>180.1075851393189</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.540284534866578</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>72.5030591183842</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>7153924.332891051</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>78.08093763821319</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>26.34090909090909</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>180.2727272727273</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.340909090909091</v>
+      </c>
+      <c r="S13" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>11775000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>79.36363636363637</v>
+      </c>
+      <c r="V13" t="n">
+        <v>23.66363636363636</v>
+      </c>
+      <c r="W13" t="n">
+        <v>182.9840909090909</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.209090909090909</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>74.02954545454546</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>10557954.54545455</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>79.24772727272727</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>24.08429299533419</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>180.3069023844195</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.175760547614094</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>73.3416025240968</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>6842333.897986071</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>78.28312134090166</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22.84321152703506</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>180.5460487225193</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.181372549019608</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>72.88175876411171</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>7200399.212715389</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>78.4707367795603</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.58333333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>24.89090909090909</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>185.2931818181818</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>71.25227272727273</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2959545.454545454</v>
+      </c>
+      <c r="U14" t="n">
+        <v>75.17727272727274</v>
+      </c>
+      <c r="V14" t="n">
+        <v>24.83888888888889</v>
+      </c>
+      <c r="W14" t="n">
+        <v>182.1012626262626</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.303282828282828</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>75.53358585858587</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>10151010.1010101</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>80.23181818181818</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>24.01600378787879</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>181.140625</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>68.55227272727274</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2151129.261363636</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>73.46136363636364</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25.61410984848485</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>179.8749053030303</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.650757575757576</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>74.30511363636364</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>8973641.098484848</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>78.83920454545455</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>183.425</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>75.82499999999999</v>
+      </c>
+      <c r="T15" t="n">
+        <v>12970000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>81.47499999999999</v>
+      </c>
+      <c r="V15" t="n">
+        <v>25.78585858585858</v>
+      </c>
+      <c r="W15" t="n">
+        <v>180.5462121212121</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.369191919191919</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>73.69393939393939</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5865151.515151516</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>77.68484848484849</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>21.87083333333334</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>182.4541666666667</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.355555555555556</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>74.34444444444443</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12995833.33333333</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>81.79861111111111</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24.66815476190476</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>180.7708333333333</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.258928571428572</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>70.97916666666666</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>3920089.285714286</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>76.4985119047619</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>2akflumR</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H16" t="n">
         <v>55</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I16" t="n">
         <v>551</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K16" t="n">
         <v>20242025</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>174.5</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>23.05909090909091</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>181.90625</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.103977272727273</v>
+      </c>
+      <c r="S16" t="n">
+        <v>72.53295454545454</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5220568.181818182</v>
+      </c>
+      <c r="U16" t="n">
+        <v>78.42102272727273</v>
+      </c>
+      <c r="V16" t="n">
+        <v>26.49444444444445</v>
+      </c>
+      <c r="W16" t="n">
+        <v>182.9111111111111</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.877777777777778</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>76.42222222222222</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>10063333.33333333</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>79.20833333333333</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>23.60661764705882</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>179.5211397058823</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>146</v>
-      </c>
-      <c r="U6" t="n">
-        <v>11600000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>154</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>175</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>152</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>164</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>26.33333333333334</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>180.5151515151515</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.363636363636364</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>76.2121212121212</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>11957575.75757576</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>79.48484848484848</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>26.06666666666667</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>182.4</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>76.26666666666667</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>10140000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>24.39309241483155</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>179.970606687998</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.199259677520547</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>73.49055775142732</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6789778.530648096</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>77.99153020892152</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>23.84156785243742</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>180.7350131752306</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.556982872200264</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>73.48270750988142</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6071763.833992095</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>79.60762516469038</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
+      <c r="AE16" t="n">
+        <v>70.40625</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3062408.088235294</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>76.38419117647058</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23.94696536301227</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>180.4328388287913</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.549316101518619</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>73.78308326399002</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>6818296.559704597</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>79.92940308404411</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>25.29166666666666</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>183.525</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.077777777777778</v>
+      </c>
+      <c r="S17" t="n">
+        <v>68.10833333333333</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1703958.333333333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>72.93055555555556</v>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="n">
+        <v>25.85220588235294</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>181.7912723785166</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.027205882352941</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>66.71122122762148</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1325947.090792839</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>71.87515984654732</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>22.71325549450549</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>184.1051014957265</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.025793650793651</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>70.19028540903541</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>4547075.129731379</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>77.60397588522588</v>
+      </c>
+      <c r="AN17" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>24.79545454545455</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>182.1136363636364</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.386363636363637</v>
+      </c>
+      <c r="S18" t="n">
+        <v>72.77272727272728</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4976136.363636363</v>
+      </c>
+      <c r="U18" t="n">
+        <v>76.06818181818181</v>
+      </c>
+      <c r="V18" t="n">
+        <v>25.8125</v>
+      </c>
+      <c r="W18" t="n">
+        <v>181.9375</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2376562.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>25.21047149122807</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>182.3804641812866</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.259722222222222</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>71.75464181286549</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3660983.644005848</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>74.54175804093566</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24.96266968325792</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>181.5414952694364</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>67.14474496092143</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1477442.410530646</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>72.85941999177294</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>20.44747474747475</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>183.8742424242424</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>70.12348484848485</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4155984.848484849</v>
+      </c>
+      <c r="U19" t="n">
+        <v>80.51212121212122</v>
+      </c>
+      <c r="V19" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>182.2222222222222</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.458333333333333</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>76.64444444444445</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>15398333.33333333</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>80.22777777777779</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>20.42157738095239</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>181.3925595238095</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>68.03005952380953</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2896149.553571429</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>78.50307539682541</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23.50696301247772</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>180.6005459001782</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.382876559714795</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>73.29802807486632</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>9384418.44919786</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>79.43099376114083</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC6"/>
+  <dimension ref="A1:AG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,90 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,35 +597,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45562.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29778</v>
+        <v>17924</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,173 +650,97 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>21.5</v>
+        <v>24.96545454545455</v>
       </c>
       <c r="Q2" t="n">
-        <v>187</v>
+        <v>182.7327272727273</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>68.78181818181818</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>8427.272727272728</v>
       </c>
       <c r="T2" t="n">
-        <v>145</v>
+        <v>27.45636363636364</v>
       </c>
       <c r="U2" t="n">
-        <v>8400000</v>
+        <v>181.6745454545455</v>
       </c>
       <c r="V2" t="n">
-        <v>158</v>
+        <v>74.00545454545455</v>
       </c>
       <c r="W2" t="n">
-        <v>24</v>
+        <v>20288.63636363636</v>
       </c>
       <c r="X2" t="n">
-        <v>185.6</v>
+        <v>24.20272727272727</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>180.8225541125541</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>358</v>
-      </c>
+        <v>65.87822510822511</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>19600000</v>
+        <v>24.61869047619048</v>
       </c>
       <c r="AC2" t="n">
-        <v>383</v>
+        <v>181.0253463203463</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.3</v>
+        <v>70.25988095238095</v>
       </c>
       <c r="AE2" t="n">
-        <v>180.5666666666667</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>8713333.333333334</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>78.93333333333334</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>26.08484848484848</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>180.8393939393939</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.418181818181818</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>74.03636363636363</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6009090.909090909</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>77.69090909090909</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23.71895424836601</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>180.5294117647059</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.597572362278245</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>72.95144724556489</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7236811.391223155</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>78.07282913165265</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>24.05753968253968</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.178571428571429</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>70.69444444444444</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4054563.492063493</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>76.5813492063492</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
+        <v>17839.82683982684</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>zBdshgV6</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.5</v>
+        <v>45562.66666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35322</v>
+        <v>48229</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -951,157 +765,103 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>23.04861111111111</v>
       </c>
       <c r="Q3" t="n">
-        <v>179.2</v>
+        <v>182.9923611111111</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>81.45416666666668</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>77229.16666666667</v>
       </c>
       <c r="T3" t="n">
-        <v>355</v>
+        <v>25.34</v>
       </c>
       <c r="U3" t="n">
-        <v>15925000</v>
+        <v>180.42</v>
       </c>
       <c r="V3" t="n">
-        <v>369</v>
+        <v>75.78</v>
       </c>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>33400</v>
       </c>
       <c r="X3" t="n">
-        <v>177.5</v>
+        <v>22.72392857142857</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>183.669246031746</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>77.85968253968254</v>
       </c>
       <c r="AA3" t="n">
-        <v>149</v>
+        <v>68942.22222222222</v>
       </c>
       <c r="AB3" t="n">
-        <v>16000000</v>
+        <v>22.95954592363261</v>
       </c>
       <c r="AC3" t="n">
-        <v>159</v>
+        <v>180.3095975232198</v>
       </c>
       <c r="AD3" t="n">
-        <v>24.48484848484848</v>
+        <v>72.1671531770603</v>
       </c>
       <c r="AE3" t="n">
-        <v>182.3636363636364</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.363636363636364</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>72.57575757575758</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>4937121.212121212</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>76.24242424242424</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>25.47361111111111</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>182.2967592592593</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.346296296296297</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>71.90092592592593</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3832627.314814815</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>74.59953703703704</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>22.32600732600732</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>183.994301994302</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.034391534391535</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>69.87871387871388</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4372975.172975173</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>77.68030118030119</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+        <v>25412.5313283208</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>v3PZcqJP</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.5</v>
+        <v>45563.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26109</v>
+        <v>38223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1128,167 +888,105 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>26.05454545454545</v>
       </c>
       <c r="Q4" t="n">
-        <v>188</v>
+        <v>180.5818181818182</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>30181.81818181818</v>
       </c>
       <c r="T4" t="n">
-        <v>65</v>
+        <v>23.60363636363636</v>
       </c>
       <c r="U4" t="n">
-        <v>1400000</v>
+        <v>183.1145454545454</v>
       </c>
       <c r="V4" t="n">
-        <v>76</v>
+        <v>74.04181818181819</v>
       </c>
       <c r="W4" t="n">
-        <v>25.66666666666667</v>
+        <v>29520</v>
       </c>
       <c r="X4" t="n">
-        <v>177.6666666666667</v>
+        <v>24.52743439626735</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>180.2455219075356</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>73.67328201927744</v>
       </c>
       <c r="AA4" t="n">
-        <v>200</v>
+        <v>30790.40486591974</v>
       </c>
       <c r="AB4" t="n">
-        <v>3300000</v>
+        <v>22.80088501110173</v>
       </c>
       <c r="AC4" t="n">
-        <v>213</v>
+        <v>180.3631547674891</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.78181818181818</v>
+        <v>72.71593332707884</v>
       </c>
       <c r="AE4" t="n">
-        <v>184.0545454545454</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>69.94242424242424</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>4019090.909090909</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>80.12727272727273</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>25.16666666666667</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>184.3666666666667</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.066666666666667</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1594166.666666667</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>72.83333333333333</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>20.20793650793651</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>180.731746031746</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>67.91507936507936</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2863095.238095238</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>78.62910052910054</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>26.11666666666666</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>182.0746376811594</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.016666666666667</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>67.0659420289855</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1378713.768115942</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>72.06884057971014</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
+        <v>23588.40729274166</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>xb7MlutC</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.5</v>
+        <v>45563.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>25178</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1314,164 +1012,102 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>25.13090909090909</v>
       </c>
       <c r="Q5" t="n">
-        <v>178</v>
+        <v>185.2890909090909</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>71.40181818181819</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>11021.81818181818</v>
       </c>
       <c r="T5" t="n">
-        <v>72</v>
+        <v>25.18020202020202</v>
       </c>
       <c r="U5" t="n">
-        <v>3700000</v>
+        <v>181.9173737373737</v>
       </c>
       <c r="V5" t="n">
-        <v>78</v>
+        <v>75.77232323232323</v>
       </c>
       <c r="W5" t="n">
-        <v>19</v>
+        <v>25463.23232323233</v>
       </c>
       <c r="X5" t="n">
-        <v>188</v>
+        <v>23.7258465085639</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>181.3298913043478</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>68.52007905138341</v>
       </c>
       <c r="AA5" t="n">
-        <v>64</v>
+        <v>8942.995169082125</v>
       </c>
       <c r="AB5" t="n">
-        <v>1300000</v>
+        <v>25.45795454545455</v>
       </c>
       <c r="AC5" t="n">
-        <v>74</v>
+        <v>180.4665909090909</v>
       </c>
       <c r="AD5" t="n">
-        <v>22.91212121212122</v>
+        <v>74.02186868686869</v>
       </c>
       <c r="AE5" t="n">
-        <v>181.8333333333333</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.096969696969697</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>72.46060606060607</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>5119090.909090909</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>78.60303030303031</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>24.91515151515151</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>185.7848484848485</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>71.21515151515152</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>2918787.878787879</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>75.23636363636363</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>179.1458333333333</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>70.20833333333333</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2947916.666666667</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>76.04166666666667</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>23.47133838383838</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>180.8541666666667</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>68.16969696969697</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2181505.681818182</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>73.63181818181818</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
+        <v>25315.625</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45563.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38223</v>
+        <v>18523</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1498,132 +1134,1621 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>23.505</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183.29</v>
+      </c>
+      <c r="R6" t="n">
+        <v>76.05999999999999</v>
+      </c>
+      <c r="S6" t="n">
+        <v>40630</v>
+      </c>
+      <c r="T6" t="n">
+        <v>25.40646464646465</v>
+      </c>
+      <c r="U6" t="n">
+        <v>180.370303030303</v>
+      </c>
+      <c r="V6" t="n">
+        <v>73.42181818181818</v>
+      </c>
+      <c r="W6" t="n">
+        <v>16521.61616161616</v>
+      </c>
+      <c r="X6" t="n">
+        <v>21.9252380952381</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>182.2490476190476</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>74.29460317460318</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>33103.49206349206</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>24.66785714285714</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>181.1611111111111</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>71.02777777777779</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>13665.47619047619</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>23.04727272727273</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>181.9916666666666</v>
+      </c>
+      <c r="R7" t="n">
+        <v>72.55969696969697</v>
+      </c>
+      <c r="S7" t="n">
+        <v>14218.93939393939</v>
+      </c>
+      <c r="T7" t="n">
+        <v>26.97333333333334</v>
+      </c>
+      <c r="U7" t="n">
+        <v>182.8622222222222</v>
+      </c>
+      <c r="V7" t="n">
+        <v>76.60444444444445</v>
+      </c>
+      <c r="W7" t="n">
+        <v>34733.33333333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>23.59957983193277</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>179.5169117647059</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>70.58214285714286</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>12829.51680672269</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>23.79967755356771</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>180.0515342209278</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>73.98436134803413</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>20972.65706261702</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>25.36666666666667</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183.02</v>
+      </c>
+      <c r="R8" t="n">
+        <v>68.35333333333332</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="U8" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="V8" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>25.63176470588235</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>181.5130179028133</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>66.48897698209718</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>22.79282661782662</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>183.7174145299145</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>70.53000610500609</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>14778.76984126984</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>24.98181818181818</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>181.9636363636364</v>
+      </c>
+      <c r="R9" t="n">
+        <v>72.8909090909091</v>
+      </c>
+      <c r="S9" t="n">
+        <v>16400</v>
+      </c>
+      <c r="T9" t="n">
+        <v>25.95833333333333</v>
+      </c>
+      <c r="U9" t="n">
+        <v>182</v>
+      </c>
+      <c r="V9" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7250</v>
+      </c>
+      <c r="X9" t="n">
+        <v>25.07948830409357</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>182.482149122807</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>71.94815789473685</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>17400</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>24.916802413273</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>181.5531962155491</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>67.47579596873715</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>4138.461538461539</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>184.29</v>
+      </c>
+      <c r="R10" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11537.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>182.6577777777778</v>
+      </c>
+      <c r="V10" t="n">
+        <v>76.61555555555556</v>
+      </c>
+      <c r="W10" t="n">
+        <v>40946.66666666666</v>
+      </c>
+      <c r="X10" t="n">
+        <v>20.6681862745098</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>182.081339869281</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>68.13872549019608</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>23.75001485442662</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>180.324881164587</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>73.46064468211527</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>28725.39512774807</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>182.6577777777778</v>
+      </c>
+      <c r="R11" t="n">
+        <v>76.61555555555556</v>
+      </c>
+      <c r="S11" t="n">
+        <v>40946.66666666666</v>
+      </c>
+      <c r="T11" t="n">
+        <v>25.36666666666667</v>
+      </c>
+      <c r="U11" t="n">
+        <v>183.02</v>
+      </c>
+      <c r="V11" t="n">
+        <v>68.35333333333332</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>23.75001485442662</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>180.324881164587</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>73.46064468211527</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>28725.39512774807</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>25.63176470588235</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>181.5130179028133</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>66.48897698209718</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>25.95833333333333</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>182</v>
+      </c>
+      <c r="R12" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7250</v>
+      </c>
+      <c r="T12" t="n">
+        <v>24.96545454545455</v>
+      </c>
+      <c r="U12" t="n">
+        <v>182.7327272727273</v>
+      </c>
+      <c r="V12" t="n">
+        <v>68.78181818181818</v>
+      </c>
+      <c r="W12" t="n">
+        <v>8427.272727272728</v>
+      </c>
+      <c r="X12" t="n">
+        <v>24.916802413273</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>181.5531962155491</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>67.47579596873715</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4138.461538461539</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24.20272727272727</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>180.8225541125541</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>65.87822510822511</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>pfDZL71o</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>174.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>146</v>
-      </c>
-      <c r="U6" t="n">
-        <v>11600000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>154</v>
-      </c>
-      <c r="W6" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>175</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>152</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>164</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>26.33333333333334</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>180.5151515151515</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.363636363636364</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>76.2121212121212</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>11957575.75757576</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>79.48484848484848</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>26.06666666666667</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>182.4</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>76.26666666666667</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>10140000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>24.39309241483155</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>179.970606687998</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.199259677520547</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>73.49055775142732</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6789778.530648096</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>77.99153020892152</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>23.84156785243742</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>180.7350131752306</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.556982872200264</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>73.48270750988142</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6071763.833992095</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>79.60762516469038</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>25.18020202020202</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>181.9173737373737</v>
+      </c>
+      <c r="R13" t="n">
+        <v>75.77232323232323</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25463.23232323233</v>
+      </c>
+      <c r="T13" t="n">
+        <v>23.04727272727273</v>
+      </c>
+      <c r="U13" t="n">
+        <v>181.9916666666666</v>
+      </c>
+      <c r="V13" t="n">
+        <v>72.55969696969697</v>
+      </c>
+      <c r="W13" t="n">
+        <v>14218.93939393939</v>
+      </c>
+      <c r="X13" t="n">
+        <v>25.45795454545455</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>180.4665909090909</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>74.02186868686869</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>25315.625</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>23.59957983193277</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>179.5169117647059</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>70.58214285714286</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>12829.51680672269</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>180.42</v>
+      </c>
+      <c r="R14" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="S14" t="n">
+        <v>33400</v>
+      </c>
+      <c r="T14" t="n">
+        <v>23.505</v>
+      </c>
+      <c r="U14" t="n">
+        <v>183.29</v>
+      </c>
+      <c r="V14" t="n">
+        <v>76.05999999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>40630</v>
+      </c>
+      <c r="X14" t="n">
+        <v>22.95954592363261</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>180.3095975232198</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>72.1671531770603</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>25412.5313283208</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>21.9252380952381</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>182.2490476190476</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>74.29460317460318</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>33103.49206349206</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>26.97333333333334</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>182.8622222222222</v>
+      </c>
+      <c r="R15" t="n">
+        <v>76.60444444444445</v>
+      </c>
+      <c r="S15" t="n">
+        <v>34733.33333333333</v>
+      </c>
+      <c r="T15" t="n">
+        <v>24.98181818181818</v>
+      </c>
+      <c r="U15" t="n">
+        <v>181.9636363636364</v>
+      </c>
+      <c r="V15" t="n">
+        <v>72.8909090909091</v>
+      </c>
+      <c r="W15" t="n">
+        <v>16400</v>
+      </c>
+      <c r="X15" t="n">
+        <v>23.79967755356771</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>180.0515342209278</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>73.98436134803413</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>20972.65706261702</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>25.07948830409357</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>182.482149122807</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>71.94815789473685</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>17400</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>27.45636363636364</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>181.6745454545455</v>
+      </c>
+      <c r="R16" t="n">
+        <v>74.00545454545455</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20288.63636363636</v>
+      </c>
+      <c r="T16" t="n">
+        <v>25.13090909090909</v>
+      </c>
+      <c r="U16" t="n">
+        <v>185.2890909090909</v>
+      </c>
+      <c r="V16" t="n">
+        <v>71.40181818181819</v>
+      </c>
+      <c r="W16" t="n">
+        <v>11021.81818181818</v>
+      </c>
+      <c r="X16" t="n">
+        <v>24.61869047619048</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>181.0253463203463</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>70.25988095238095</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>17839.82683982684</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>23.7258465085639</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>181.3298913043478</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>68.52007905138341</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>8942.995169082125</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="R17" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>25.40646464646465</v>
+      </c>
+      <c r="U17" t="n">
+        <v>180.370303030303</v>
+      </c>
+      <c r="V17" t="n">
+        <v>73.42181818181818</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16521.61616161616</v>
+      </c>
+      <c r="X17" t="n">
+        <v>22.79282661782662</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>183.7174145299145</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>70.53000610500609</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>14778.76984126984</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>24.66785714285714</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>181.1611111111111</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>71.02777777777779</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>13665.47619047619</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>20.295</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>184.29</v>
+      </c>
+      <c r="R18" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11537.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>26.05454545454545</v>
+      </c>
+      <c r="U18" t="n">
+        <v>180.5818181818182</v>
+      </c>
+      <c r="V18" t="n">
+        <v>76</v>
+      </c>
+      <c r="W18" t="n">
+        <v>30181.81818181818</v>
+      </c>
+      <c r="X18" t="n">
+        <v>20.6681862745098</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>182.081339869281</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>68.13872549019608</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>24.52743439626735</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>180.2455219075356</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>73.67328201927744</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>30790.40486591974</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>23.60363636363636</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>183.1145454545454</v>
+      </c>
+      <c r="R19" t="n">
+        <v>74.04181818181819</v>
+      </c>
+      <c r="S19" t="n">
+        <v>29520</v>
+      </c>
+      <c r="T19" t="n">
+        <v>23.04861111111111</v>
+      </c>
+      <c r="U19" t="n">
+        <v>182.9923611111111</v>
+      </c>
+      <c r="V19" t="n">
+        <v>81.45416666666668</v>
+      </c>
+      <c r="W19" t="n">
+        <v>77229.16666666667</v>
+      </c>
+      <c r="X19" t="n">
+        <v>22.80088501110173</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>180.3631547674891</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>72.71593332707884</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>23588.40729274166</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>22.72392857142857</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>183.669246031746</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>77.85968253968254</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>68942.22222222222</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,90 +505,150 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -605,7 +665,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
@@ -653,57 +713,91 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>129</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>183</v>
+      </c>
+      <c r="X2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>154</v>
+      </c>
+      <c r="AB2" t="n">
         <v>24.96545454545455</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AC2" t="n">
         <v>182.7327272727273</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AD2" t="n">
         <v>68.78181818181818</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AE2" t="n">
         <v>8427.272727272728</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AF2" t="n">
         <v>27.45636363636364</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AG2" t="n">
         <v>181.6745454545455</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AH2" t="n">
         <v>74.00545454545455</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AI2" t="n">
         <v>20288.63636363636</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AJ2" t="n">
         <v>24.20272727272727</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AK2" t="n">
         <v>180.8225541125541</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AL2" t="n">
         <v>65.87822510822511</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
         <v>24.61869047619048</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AO2" t="n">
         <v>181.0253463203463</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AP2" t="n">
         <v>70.25988095238095</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AQ2" t="n">
         <v>17839.82683982684</v>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>UapruDaf</t>
         </is>
@@ -720,7 +814,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
@@ -772,59 +866,95 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>185</v>
+      </c>
+      <c r="R3" t="n">
+        <v>82.66666666666667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100333.3333333333</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>248</v>
+      </c>
+      <c r="V3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" t="n">
+        <v>189</v>
+      </c>
+      <c r="X3" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB3" t="n">
         <v>23.04861111111111</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="AC3" t="n">
         <v>182.9923611111111</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AD3" t="n">
         <v>81.45416666666668</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AE3" t="n">
         <v>77229.16666666667</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AF3" t="n">
         <v>25.34</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AG3" t="n">
         <v>180.42</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AH3" t="n">
         <v>75.78</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AI3" t="n">
         <v>33400</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AJ3" t="n">
         <v>22.72392857142857</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AK3" t="n">
         <v>183.669246031746</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AL3" t="n">
         <v>77.85968253968254</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AM3" t="n">
         <v>68942.22222222222</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AN3" t="n">
         <v>22.95954592363261</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AO3" t="n">
         <v>180.3095975232198</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AP3" t="n">
         <v>72.1671531770603</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AQ3" t="n">
         <v>25412.5313283208</v>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>K6b7RoBp</t>
         </is>
@@ -841,7 +971,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
@@ -897,59 +1027,95 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="R4" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="S4" t="n">
+        <v>36000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>226</v>
+      </c>
+      <c r="V4" t="n">
+        <v>27</v>
+      </c>
+      <c r="W4" t="n">
+        <v>183</v>
+      </c>
+      <c r="X4" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>52333.33333333334</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>231</v>
+      </c>
+      <c r="AB4" t="n">
         <v>26.05454545454545</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="AC4" t="n">
         <v>180.5818181818182</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AD4" t="n">
         <v>76</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AE4" t="n">
         <v>30181.81818181818</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AF4" t="n">
         <v>23.60363636363636</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AG4" t="n">
         <v>183.1145454545454</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AH4" t="n">
         <v>74.04181818181819</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AI4" t="n">
         <v>29520</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AJ4" t="n">
         <v>24.52743439626735</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AK4" t="n">
         <v>180.2455219075356</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AL4" t="n">
         <v>73.67328201927744</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AM4" t="n">
         <v>30790.40486591974</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AN4" t="n">
         <v>22.80088501110173</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AO4" t="n">
         <v>180.3631547674891</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AP4" t="n">
         <v>72.71593332707884</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AQ4" t="n">
         <v>23588.40729274166</v>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>pCcFFE7M</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
@@ -966,7 +1132,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
@@ -1018,59 +1184,95 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>188</v>
+      </c>
+      <c r="R5" t="n">
+        <v>64</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>64</v>
+      </c>
+      <c r="V5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>28000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>305</v>
+      </c>
+      <c r="AB5" t="n">
         <v>25.13090909090909</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="AC5" t="n">
         <v>185.2890909090909</v>
       </c>
-      <c r="R5" t="n">
+      <c r="AD5" t="n">
         <v>71.40181818181819</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AE5" t="n">
         <v>11021.81818181818</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AF5" t="n">
         <v>25.18020202020202</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AG5" t="n">
         <v>181.9173737373737</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AH5" t="n">
         <v>75.77232323232323</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AI5" t="n">
         <v>25463.23232323233</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AJ5" t="n">
         <v>23.7258465085639</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AK5" t="n">
         <v>181.3298913043478</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AL5" t="n">
         <v>68.52007905138341</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AM5" t="n">
         <v>8942.995169082125</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AN5" t="n">
         <v>25.45795454545455</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AO5" t="n">
         <v>180.4665909090909</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AP5" t="n">
         <v>74.02186868686869</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AQ5" t="n">
         <v>25315.625</v>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
         </is>
@@ -1087,7 +1289,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
@@ -1143,59 +1345,95 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183</v>
+      </c>
+      <c r="R6" t="n">
+        <v>70</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>140</v>
+      </c>
+      <c r="V6" t="n">
+        <v>26</v>
+      </c>
+      <c r="W6" t="n">
+        <v>184</v>
+      </c>
+      <c r="X6" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>14750</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB6" t="n">
         <v>23.505</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="AC6" t="n">
         <v>183.29</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AD6" t="n">
         <v>76.05999999999999</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AE6" t="n">
         <v>40630</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AF6" t="n">
         <v>25.40646464646465</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AG6" t="n">
         <v>180.370303030303</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AH6" t="n">
         <v>73.42181818181818</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AI6" t="n">
         <v>16521.61616161616</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AJ6" t="n">
         <v>21.9252380952381</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AK6" t="n">
         <v>182.2490476190476</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AL6" t="n">
         <v>74.29460317460318</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AM6" t="n">
         <v>33103.49206349206</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AN6" t="n">
         <v>24.66785714285714</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AO6" t="n">
         <v>181.1611111111111</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AP6" t="n">
         <v>71.02777777777779</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AQ6" t="n">
         <v>13665.47619047619</v>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>OpNm82MB</t>
         </is>
@@ -1212,7 +1450,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
@@ -1259,60 +1497,72 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
         <v>23.04727272727273</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="AC7" t="n">
         <v>181.9916666666666</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AD7" t="n">
         <v>72.55969696969697</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AE7" t="n">
         <v>14218.93939393939</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AF7" t="n">
         <v>26.97333333333334</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AG7" t="n">
         <v>182.8622222222222</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AH7" t="n">
         <v>76.60444444444445</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AI7" t="n">
         <v>34733.33333333333</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AJ7" t="n">
         <v>23.59957983193277</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AK7" t="n">
         <v>179.5169117647059</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AL7" t="n">
         <v>70.58214285714286</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AM7" t="n">
         <v>12829.51680672269</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AN7" t="n">
         <v>23.79967755356771</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AO7" t="n">
         <v>180.0515342209278</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AP7" t="n">
         <v>73.98436134803413</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AQ7" t="n">
         <v>20972.65706261702</v>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>0tIbS515</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>
@@ -1329,7 +1579,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
@@ -1377,53 +1627,87 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>25.36666666666667</v>
+        <v>22.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>183.02</v>
+        <v>180.5</v>
       </c>
       <c r="R8" t="n">
-        <v>68.35333333333332</v>
+        <v>65.75</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>263</v>
+      </c>
+      <c r="V8" t="n">
+        <v>26</v>
+      </c>
+      <c r="W8" t="n">
+        <v>193</v>
+      </c>
+      <c r="X8" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>74</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>25.36666666666667</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>183.02</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>68.35333333333332</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="n">
         <v>24.375</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AG8" t="n">
         <v>180.625</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AH8" t="n">
         <v>74.375</v>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="n">
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="n">
         <v>25.63176470588235</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AK8" t="n">
         <v>181.5130179028133</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AL8" t="n">
         <v>66.48897698209718</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="n">
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
         <v>22.79282661782662</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AO8" t="n">
         <v>183.7174145299145</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AP8" t="n">
         <v>70.53000610500609</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AQ8" t="n">
         <v>14778.76984126984</v>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
         </is>
@@ -1440,7 +1724,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
@@ -1492,59 +1776,95 @@
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>73</v>
+      </c>
+      <c r="S9" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>219</v>
+      </c>
+      <c r="V9" t="n">
+        <v>28</v>
+      </c>
+      <c r="W9" t="n">
+        <v>180</v>
+      </c>
+      <c r="X9" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5250</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB9" t="n">
         <v>24.98181818181818</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="AC9" t="n">
         <v>181.9636363636364</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AD9" t="n">
         <v>72.8909090909091</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AE9" t="n">
         <v>16400</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AF9" t="n">
         <v>25.95833333333333</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AG9" t="n">
         <v>182</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AH9" t="n">
         <v>70.75</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AI9" t="n">
         <v>7250</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AJ9" t="n">
         <v>25.07948830409357</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AK9" t="n">
         <v>182.482149122807</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AL9" t="n">
         <v>71.94815789473685</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AM9" t="n">
         <v>17400</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AN9" t="n">
         <v>24.916802413273</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AO9" t="n">
         <v>181.5531962155491</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AP9" t="n">
         <v>67.47579596873715</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AQ9" t="n">
         <v>4138.461538461539</v>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
@@ -1561,7 +1881,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
@@ -1617,1138 +1937,93 @@
         </is>
       </c>
       <c r="P10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>183</v>
+      </c>
+      <c r="R10" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>129</v>
+      </c>
+      <c r="V10" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="W10" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>49500</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>293</v>
+      </c>
+      <c r="AB10" t="n">
         <v>20.295</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="AC10" t="n">
         <v>184.29</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AD10" t="n">
         <v>70.25</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AE10" t="n">
         <v>11537.5</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AF10" t="n">
         <v>24.2</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AG10" t="n">
         <v>182.6577777777778</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AH10" t="n">
         <v>76.61555555555556</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AI10" t="n">
         <v>40946.66666666666</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AJ10" t="n">
         <v>20.6681862745098</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AK10" t="n">
         <v>182.081339869281</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AL10" t="n">
         <v>68.13872549019608</v>
       </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="n">
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="n">
         <v>23.75001485442662</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AO10" t="n">
         <v>180.324881164587</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AP10" t="n">
         <v>73.46064468211527</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AQ10" t="n">
         <v>28725.39512774807</v>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.65625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>182.6577777777778</v>
-      </c>
-      <c r="R11" t="n">
-        <v>76.61555555555556</v>
-      </c>
-      <c r="S11" t="n">
-        <v>40946.66666666666</v>
-      </c>
-      <c r="T11" t="n">
-        <v>25.36666666666667</v>
-      </c>
-      <c r="U11" t="n">
-        <v>183.02</v>
-      </c>
-      <c r="V11" t="n">
-        <v>68.35333333333332</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="n">
-        <v>23.75001485442662</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>180.324881164587</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>73.46064468211527</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>28725.39512774807</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>25.63176470588235</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>181.5130179028133</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>66.48897698209718</v>
-      </c>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>551</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>25.95833333333333</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>182</v>
-      </c>
-      <c r="R12" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="S12" t="n">
-        <v>7250</v>
-      </c>
-      <c r="T12" t="n">
-        <v>24.96545454545455</v>
-      </c>
-      <c r="U12" t="n">
-        <v>182.7327272727273</v>
-      </c>
-      <c r="V12" t="n">
-        <v>68.78181818181818</v>
-      </c>
-      <c r="W12" t="n">
-        <v>8427.272727272728</v>
-      </c>
-      <c r="X12" t="n">
-        <v>24.916802413273</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>181.5531962155491</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>67.47579596873715</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4138.461538461539</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>24.20272727272727</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>180.8225541125541</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>65.87822510822511</v>
-      </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.58333333334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>551</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>25.18020202020202</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>181.9173737373737</v>
-      </c>
-      <c r="R13" t="n">
-        <v>75.77232323232323</v>
-      </c>
-      <c r="S13" t="n">
-        <v>25463.23232323233</v>
-      </c>
-      <c r="T13" t="n">
-        <v>23.04727272727273</v>
-      </c>
-      <c r="U13" t="n">
-        <v>181.9916666666666</v>
-      </c>
-      <c r="V13" t="n">
-        <v>72.55969696969697</v>
-      </c>
-      <c r="W13" t="n">
-        <v>14218.93939393939</v>
-      </c>
-      <c r="X13" t="n">
-        <v>25.45795454545455</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>180.4665909090909</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>74.02186868686869</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>25315.625</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>23.59957983193277</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>179.5169117647059</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>70.58214285714286</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>12829.51680672269</v>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.66666666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frappart s 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>551</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>180.42</v>
-      </c>
-      <c r="R14" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="S14" t="n">
-        <v>33400</v>
-      </c>
-      <c r="T14" t="n">
-        <v>23.505</v>
-      </c>
-      <c r="U14" t="n">
-        <v>183.29</v>
-      </c>
-      <c r="V14" t="n">
-        <v>76.05999999999999</v>
-      </c>
-      <c r="W14" t="n">
-        <v>40630</v>
-      </c>
-      <c r="X14" t="n">
-        <v>22.95954592363261</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>180.3095975232198</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>72.1671531770603</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>25412.5313283208</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>21.9252380952381</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>182.2490476190476</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>74.29460317460318</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>33103.49206349206</v>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>551</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>26.97333333333334</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>182.8622222222222</v>
-      </c>
-      <c r="R15" t="n">
-        <v>76.60444444444445</v>
-      </c>
-      <c r="S15" t="n">
-        <v>34733.33333333333</v>
-      </c>
-      <c r="T15" t="n">
-        <v>24.98181818181818</v>
-      </c>
-      <c r="U15" t="n">
-        <v>181.9636363636364</v>
-      </c>
-      <c r="V15" t="n">
-        <v>72.8909090909091</v>
-      </c>
-      <c r="W15" t="n">
-        <v>16400</v>
-      </c>
-      <c r="X15" t="n">
-        <v>23.79967755356771</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>180.0515342209278</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>73.98436134803413</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>20972.65706261702</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>25.07948830409357</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>182.482149122807</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>71.94815789473685</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>17400</v>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frappart s 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" t="n">
-        <v>551</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>27.45636363636364</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>181.6745454545455</v>
-      </c>
-      <c r="R16" t="n">
-        <v>74.00545454545455</v>
-      </c>
-      <c r="S16" t="n">
-        <v>20288.63636363636</v>
-      </c>
-      <c r="T16" t="n">
-        <v>25.13090909090909</v>
-      </c>
-      <c r="U16" t="n">
-        <v>185.2890909090909</v>
-      </c>
-      <c r="V16" t="n">
-        <v>71.40181818181819</v>
-      </c>
-      <c r="W16" t="n">
-        <v>11021.81818181818</v>
-      </c>
-      <c r="X16" t="n">
-        <v>24.61869047619048</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>181.0253463203463</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>70.25988095238095</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>17839.82683982684</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>23.7258465085639</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>181.3298913043478</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>68.52007905138341</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>8942.995169082125</v>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="n">
-        <v>551</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>24.375</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>180.625</v>
-      </c>
-      <c r="R17" t="n">
-        <v>74.375</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="n">
-        <v>25.40646464646465</v>
-      </c>
-      <c r="U17" t="n">
-        <v>180.370303030303</v>
-      </c>
-      <c r="V17" t="n">
-        <v>73.42181818181818</v>
-      </c>
-      <c r="W17" t="n">
-        <v>16521.61616161616</v>
-      </c>
-      <c r="X17" t="n">
-        <v>22.79282661782662</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>183.7174145299145</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>70.53000610500609</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>14778.76984126984</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>24.66785714285714</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>181.1611111111111</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>71.02777777777779</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>13665.47619047619</v>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="n">
-        <v>551</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>20.295</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>184.29</v>
-      </c>
-      <c r="R18" t="n">
-        <v>70.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>11537.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>26.05454545454545</v>
-      </c>
-      <c r="U18" t="n">
-        <v>180.5818181818182</v>
-      </c>
-      <c r="V18" t="n">
-        <v>76</v>
-      </c>
-      <c r="W18" t="n">
-        <v>30181.81818181818</v>
-      </c>
-      <c r="X18" t="n">
-        <v>20.6681862745098</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>182.081339869281</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>68.13872549019608</v>
-      </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="n">
-        <v>24.52743439626735</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>180.2455219075356</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>73.67328201927744</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>30790.40486591974</v>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>551</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>23.60363636363636</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>183.1145454545454</v>
-      </c>
-      <c r="R19" t="n">
-        <v>74.04181818181819</v>
-      </c>
-      <c r="S19" t="n">
-        <v>29520</v>
-      </c>
-      <c r="T19" t="n">
-        <v>23.04861111111111</v>
-      </c>
-      <c r="U19" t="n">
-        <v>182.9923611111111</v>
-      </c>
-      <c r="V19" t="n">
-        <v>81.45416666666668</v>
-      </c>
-      <c r="W19" t="n">
-        <v>77229.16666666667</v>
-      </c>
-      <c r="X19" t="n">
-        <v>22.80088501110173</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>180.3631547674891</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>72.71593332707884</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>23588.40729274166</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>22.72392857142857</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>183.669246031746</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>77.85968253968254</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>68942.22222222222</v>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,35 +657,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.58333333334</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17924</v>
+        <v>33150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -712,129 +712,109 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>64.5</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>129</v>
-      </c>
-      <c r="V2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>183</v>
-      </c>
-      <c r="X2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>16500</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>154</v>
-      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>24.96545454545455</v>
+        <v>23.04727272727273</v>
       </c>
       <c r="AC2" t="n">
-        <v>182.7327272727273</v>
+        <v>181.9916666666666</v>
       </c>
       <c r="AD2" t="n">
-        <v>68.78181818181818</v>
+        <v>72.55969696969697</v>
       </c>
       <c r="AE2" t="n">
-        <v>8427.272727272728</v>
+        <v>14218.93939393939</v>
       </c>
       <c r="AF2" t="n">
-        <v>27.45636363636364</v>
+        <v>26.97333333333334</v>
       </c>
       <c r="AG2" t="n">
-        <v>181.6745454545455</v>
+        <v>182.8622222222222</v>
       </c>
       <c r="AH2" t="n">
-        <v>74.00545454545455</v>
+        <v>76.60444444444445</v>
       </c>
       <c r="AI2" t="n">
-        <v>20288.63636363636</v>
+        <v>34733.33333333333</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24.20272727272727</v>
+        <v>23.59957983193277</v>
       </c>
       <c r="AK2" t="n">
-        <v>180.8225541125541</v>
+        <v>179.5169117647059</v>
       </c>
       <c r="AL2" t="n">
-        <v>65.87822510822511</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>70.58214285714286</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>12829.51680672269</v>
+      </c>
       <c r="AN2" t="n">
-        <v>24.61869047619048</v>
+        <v>23.79967755356771</v>
       </c>
       <c r="AO2" t="n">
-        <v>181.0253463203463</v>
+        <v>180.0515342209278</v>
       </c>
       <c r="AP2" t="n">
-        <v>70.25988095238095</v>
+        <v>73.98436134803413</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17839.82683982684</v>
+        <v>20972.65706261702</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48229</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -860,138 +840,126 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>27</v>
+        <v>22.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>185</v>
+        <v>180.5</v>
       </c>
       <c r="R3" t="n">
-        <v>82.66666666666667</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100333.3333333333</v>
-      </c>
+        <v>65.75</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="W3" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="X3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Y3" t="n">
-        <v>14000</v>
+        <v>19000</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AB3" t="n">
-        <v>23.04861111111111</v>
+        <v>25.36666666666667</v>
       </c>
       <c r="AC3" t="n">
-        <v>182.9923611111111</v>
+        <v>183.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>81.45416666666668</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>77229.16666666667</v>
-      </c>
+        <v>68.35333333333332</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>25.34</v>
+        <v>24.375</v>
       </c>
       <c r="AG3" t="n">
-        <v>180.42</v>
+        <v>180.625</v>
       </c>
       <c r="AH3" t="n">
-        <v>75.78</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>33400</v>
-      </c>
+        <v>74.375</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>22.72392857142857</v>
+        <v>25.63176470588235</v>
       </c>
       <c r="AK3" t="n">
-        <v>183.669246031746</v>
+        <v>181.5130179028133</v>
       </c>
       <c r="AL3" t="n">
-        <v>77.85968253968254</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>68942.22222222222</v>
-      </c>
+        <v>66.48897698209718</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>22.95954592363261</v>
+        <v>22.79282661782662</v>
       </c>
       <c r="AO3" t="n">
-        <v>180.3095975232198</v>
+        <v>183.7174145299145</v>
       </c>
       <c r="AP3" t="n">
-        <v>72.1671531770603</v>
+        <v>70.53000610500609</v>
       </c>
       <c r="AQ3" t="n">
-        <v>25412.5313283208</v>
+        <v>14778.76984126984</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.5</v>
+        <v>45564.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38223</v>
+        <v>35322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1018,101 +986,97 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>26.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>180.3333333333333</v>
+        <v>179.8</v>
       </c>
       <c r="R4" t="n">
-        <v>75.33333333333333</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>36000</v>
+        <v>18400</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>226</v>
+        <v>362</v>
       </c>
       <c r="V4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W4" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="X4" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Y4" t="n">
-        <v>52333.33333333334</v>
+        <v>5250</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.05454545454545</v>
+        <v>24.98181818181818</v>
       </c>
       <c r="AC4" t="n">
-        <v>180.5818181818182</v>
+        <v>181.9636363636364</v>
       </c>
       <c r="AD4" t="n">
-        <v>76</v>
+        <v>72.8909090909091</v>
       </c>
       <c r="AE4" t="n">
-        <v>30181.81818181818</v>
+        <v>16400</v>
       </c>
       <c r="AF4" t="n">
-        <v>23.60363636363636</v>
+        <v>25.95833333333333</v>
       </c>
       <c r="AG4" t="n">
-        <v>183.1145454545454</v>
+        <v>182</v>
       </c>
       <c r="AH4" t="n">
-        <v>74.04181818181819</v>
+        <v>70.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>29520</v>
+        <v>7250</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24.52743439626735</v>
+        <v>25.07948830409357</v>
       </c>
       <c r="AK4" t="n">
-        <v>180.2455219075356</v>
+        <v>182.482149122807</v>
       </c>
       <c r="AL4" t="n">
-        <v>73.67328201927744</v>
+        <v>71.94815789473685</v>
       </c>
       <c r="AM4" t="n">
-        <v>30790.40486591974</v>
+        <v>17400</v>
       </c>
       <c r="AN4" t="n">
-        <v>22.80088501110173</v>
+        <v>24.916802413273</v>
       </c>
       <c r="AO4" t="n">
-        <v>180.3631547674891</v>
+        <v>181.5531962155491</v>
       </c>
       <c r="AP4" t="n">
-        <v>72.71593332707884</v>
+        <v>67.47579596873715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23588.40729274166</v>
+        <v>4138.461538461539</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1124,35 +1088,35 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.58333333334</v>
+        <v>45564.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25178</v>
+        <v>26109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1177,851 +1141,102 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>lhUkVMh2</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="R5" t="n">
-        <v>64</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3000</v>
-      </c>
+        <v>64.5</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="V5" t="n">
-        <v>27.5</v>
+        <v>22.75</v>
       </c>
       <c r="W5" t="n">
-        <v>181.5</v>
+        <v>182.5</v>
       </c>
       <c r="X5" t="n">
-        <v>76.25</v>
+        <v>73.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>28000</v>
+        <v>49500</v>
       </c>
       <c r="Z5" t="n">
         <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.13090909090909</v>
+        <v>20.295</v>
       </c>
       <c r="AC5" t="n">
-        <v>185.2890909090909</v>
+        <v>184.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>71.40181818181819</v>
+        <v>70.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>11021.81818181818</v>
+        <v>11537.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>25.18020202020202</v>
+        <v>24.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>181.9173737373737</v>
+        <v>182.6577777777778</v>
       </c>
       <c r="AH5" t="n">
-        <v>75.77232323232323</v>
+        <v>76.61555555555556</v>
       </c>
       <c r="AI5" t="n">
-        <v>25463.23232323233</v>
+        <v>40946.66666666666</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23.7258465085639</v>
+        <v>20.6681862745098</v>
       </c>
       <c r="AK5" t="n">
-        <v>181.3298913043478</v>
+        <v>182.081339869281</v>
       </c>
       <c r="AL5" t="n">
-        <v>68.52007905138341</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>8942.995169082125</v>
-      </c>
+        <v>68.13872549019608</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>25.45795454545455</v>
+        <v>23.75001485442662</v>
       </c>
       <c r="AO5" t="n">
-        <v>180.4665909090909</v>
+        <v>180.324881164587</v>
       </c>
       <c r="AP5" t="n">
-        <v>74.02186868686869</v>
+        <v>73.46064468211527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>25315.625</v>
+        <v>28725.39512774807</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>55</v>
-      </c>
-      <c r="I6" t="n">
-        <v>551</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>183</v>
-      </c>
-      <c r="R6" t="n">
-        <v>70</v>
-      </c>
-      <c r="S6" t="n">
-        <v>14500</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>140</v>
-      </c>
-      <c r="V6" t="n">
-        <v>26</v>
-      </c>
-      <c r="W6" t="n">
-        <v>184</v>
-      </c>
-      <c r="X6" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>14750</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>23.505</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>183.29</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>76.05999999999999</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>40630</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>25.40646464646465</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>180.370303030303</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>73.42181818181818</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>16521.61616161616</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>21.9252380952381</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>182.2490476190476</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>74.29460317460318</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>33103.49206349206</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>24.66785714285714</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>181.1611111111111</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>71.02777777777779</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13665.47619047619</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I7" t="n">
-        <v>551</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="n">
-        <v>23.04727272727273</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>181.9916666666666</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>72.55969696969697</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>14218.93939393939</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>26.97333333333334</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>182.8622222222222</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>76.60444444444445</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>34733.33333333333</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>23.59957983193277</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>179.5169117647059</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>70.58214285714286</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>12829.51680672269</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>23.79967755356771</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>180.0515342209278</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>73.98436134803413</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>20972.65706261702</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>55</v>
-      </c>
-      <c r="I8" t="n">
-        <v>551</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>65.75</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>263</v>
-      </c>
-      <c r="V8" t="n">
-        <v>26</v>
-      </c>
-      <c r="W8" t="n">
-        <v>193</v>
-      </c>
-      <c r="X8" t="n">
-        <v>74</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>19000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>74</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>25.36666666666667</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>183.02</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>68.35333333333332</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="n">
-        <v>24.375</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>180.625</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>74.375</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="n">
-        <v>25.63176470588235</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>181.5130179028133</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>66.48897698209718</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
-        <v>22.79282661782662</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>183.7174145299145</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>70.53000610500609</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>14778.76984126984</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kherradji a 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="n">
-        <v>551</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>177.3333333333333</v>
-      </c>
-      <c r="R9" t="n">
-        <v>73</v>
-      </c>
-      <c r="S9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>219</v>
-      </c>
-      <c r="V9" t="n">
-        <v>28</v>
-      </c>
-      <c r="W9" t="n">
-        <v>180</v>
-      </c>
-      <c r="X9" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>5250</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>24.98181818181818</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>181.9636363636364</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>72.8909090909091</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>16400</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>25.95833333333333</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>182</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>7250</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>25.07948830409357</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>182.482149122807</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>71.94815789473685</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>17400</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>24.916802413273</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>181.5531962155491</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>67.47579596873715</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>4138.461538461539</v>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>551</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>183</v>
-      </c>
-      <c r="R10" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>129</v>
-      </c>
-      <c r="V10" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="W10" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>73.25</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>49500</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>293</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>20.295</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>184.29</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>70.25</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>11537.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>182.6577777777778</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>76.61555555555556</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>40946.66666666666</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>20.6681862745098</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>182.081339869281</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>68.13872549019608</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
-        <v>23.75001485442662</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>180.324881164587</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>73.46064468211527</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>28725.39512774807</v>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:BG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,42 +495,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_home</t>
+          <t>sum_wage_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_home</t>
+          <t>sum_value_player_miss_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rep_player_miss_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -545,110 +545,180 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>sum_value_player_miss_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -657,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45569.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>33150</v>
+        <v>67394</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -718,103 +788,123 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="W2" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>188</v>
+      </c>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>2200000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>23.04727272727273</v>
+        <v>217</v>
       </c>
       <c r="AC2" t="n">
-        <v>181.9916666666666</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>72.55969696969697</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>14218.93939393939</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>26.97333333333334</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>182.8622222222222</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>76.60444444444445</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>34733.33333333333</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>23.59957983193277</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>179.5169117647059</v>
+        <v>24.88518518518518</v>
       </c>
       <c r="AL2" t="n">
-        <v>70.58214285714286</v>
+        <v>184.2074074074074</v>
       </c>
       <c r="AM2" t="n">
-        <v>12829.51680672269</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>23.79967755356771</v>
-      </c>
+        <v>67.39629629629628</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>180.0515342209278</v>
+        <v>1545092.592592592</v>
       </c>
       <c r="AP2" t="n">
-        <v>73.98436134803413</v>
+        <v>72.88888888888889</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20972.65706261702</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
+        <v>1</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>25.76997549019608</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>181.187542625746</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>66.16597755044046</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>1167694.302358625</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>71.4583581983518</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>42000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -839,127 +929,177 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O3" t="n">
+        <v>180.25</v>
+      </c>
       <c r="P3" t="n">
-        <v>22.75</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>180.5</v>
+        <v>280</v>
       </c>
       <c r="R3" t="n">
-        <v>65.75</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>21000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6675000</v>
+      </c>
       <c r="T3" t="n">
+        <v>284</v>
+      </c>
+      <c r="U3" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="n">
-        <v>263</v>
-      </c>
       <c r="V3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="W3" t="n">
-        <v>193</v>
+        <v>186.5</v>
       </c>
       <c r="X3" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>19000</v>
-      </c>
-      <c r="Z3" t="n">
+        <v>129</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>2350000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>149</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>182.9375</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>69.9375</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2276562.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>1</v>
       </c>
-      <c r="AA3" t="n">
-        <v>74</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>25.36666666666667</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>183.02</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>68.35333333333332</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="n">
-        <v>24.375</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>180.625</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>74.375</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="n">
-        <v>25.63176470588235</v>
-      </c>
       <c r="AK3" t="n">
-        <v>181.5130179028133</v>
+        <v>25.80555555555556</v>
       </c>
       <c r="AL3" t="n">
-        <v>66.48897698209718</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>182.4027777777777</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>68.44907407407408</v>
+      </c>
       <c r="AN3" t="n">
-        <v>22.79282661782662</v>
+        <v>4162.037037037037</v>
       </c>
       <c r="AO3" t="n">
-        <v>183.7174145299145</v>
+        <v>1726620.37037037</v>
       </c>
       <c r="AP3" t="n">
-        <v>70.53000610500609</v>
+        <v>71.72685185185185</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14778.76984126984</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>25.17319023569023</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>181.5318813131313</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>68.17561026936026</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4794.19191919192</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1727354.271885522</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>73.12931397306397</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>24.52982899167109</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>180.5138268651426</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>65.95807637781321</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
+        <v>1384126.351231614</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>71.17333421938685</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35322</v>
+        <v>50186</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -984,261 +1124,895 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O4" t="n">
+        <v>187</v>
+      </c>
       <c r="P4" t="n">
-        <v>26.8</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>179.8</v>
+        <v>75</v>
       </c>
       <c r="R4" t="n">
-        <v>72.40000000000001</v>
+        <v>9000</v>
       </c>
       <c r="S4" t="n">
-        <v>18400</v>
+        <v>5500000</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="U4" t="n">
-        <v>362</v>
-      </c>
-      <c r="V4" t="n">
-        <v>28</v>
-      </c>
-      <c r="W4" t="n">
-        <v>180</v>
-      </c>
-      <c r="X4" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>24.98181818181818</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>181.9636363636364</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>72.8909090909091</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>16400</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>25.95833333333333</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>182</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>7250</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>25.07948830409357</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>182.482149122807</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>71.94815789473685</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>17400</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>24.916802413273</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>181.5531962155491</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>67.47579596873715</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4138.461538461539</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
+        <v>2</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45570.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>55</v>
+      </c>
+      <c r="I5" t="n">
+        <v>551</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>551</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>186</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">stade de la meinau
   strasbourg </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E9" t="n">
         <v>26109</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>55</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I9" t="n">
         <v>551</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K9" t="n">
         <v>20242025</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>4v0yqlWc</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>lhUkVMh2</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>183</v>
-      </c>
-      <c r="R5" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>129</v>
-      </c>
-      <c r="V5" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="W5" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>73.25</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>49500</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>293</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>20.295</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>184.29</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>70.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>11537.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>182.6577777777778</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>76.61555555555556</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>40946.66666666666</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>20.6681862745098</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>182.081339869281</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>68.13872549019608</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
-        <v>23.75001485442662</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>180.324881164587</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>73.46064468211527</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>28725.39512774807</v>
-      </c>
-      <c r="AR5" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>20</v>
+      </c>
+      <c r="W9" t="n">
+        <v>184</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2725000</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,230 +495,190 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_home</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_home</t>
+          <t>sum_value_player_miss_away</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rep_player_miss_home</t>
+          <t>sum_rep_player_miss_away</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_away</t>
+          <t>mean_value_player_start_home</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_away</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_rep_player_start_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_rep_player_miss_away</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_home</t>
+          <t>mean_value_player_start_away</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_home</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_rep_player_start_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_start_home</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_away</t>
+          <t>mean_value_player_sub_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_away</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_start_away</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_sub_home</t>
+          <t>mean_value_player_sub_away</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_sub_home</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_home</t>
+          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_sub_home</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -727,35 +687,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67394</v>
+        <v>59186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -788,28 +748,14 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>21.66666666666667</v>
-      </c>
-      <c r="W2" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>188</v>
-      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>217</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3</v>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -817,94 +763,62 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>24.88518518518518</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>184.2074074074074</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>67.39629629629628</v>
-      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>1545092.592592592</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>72.88888888888889</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>25.76997549019608</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>181.187542625746</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>66.16597755044046</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="n">
-        <v>1167694.302358625</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>71.4583581983518</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.5</v>
+        <v>45571.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42000</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -929,177 +843,85 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>28</v>
-      </c>
-      <c r="O3" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>280</v>
-      </c>
-      <c r="R3" t="n">
-        <v>21000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6675000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>284</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W3" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>129</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>2350000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>149</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>182.9375</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>69.9375</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>5500</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2276562.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>74.25</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>25.80555555555556</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>182.4027777777777</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>68.44907407407408</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>4162.037037037037</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1726620.37037037</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>71.72685185185185</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>25.17319023569023</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>181.5318813131313</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>68.17561026936026</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4794.19191919192</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1727354.271885522</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>73.12931397306397</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>24.52982899167109</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>180.5138268651426</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>65.95807637781321</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="n">
-        <v>1384126.351231614</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>71.17333421938685</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.58333333334</v>
+        <v>45571.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50186</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1124,30 +946,14 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>28</v>
-      </c>
-      <c r="O4" t="n">
-        <v>187</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>9000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>76</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -1162,13 +968,27 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>186</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -1176,57 +996,49 @@
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45571.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29778</v>
+        <v>26109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1251,14 +1063,30 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O5" t="n">
+        <v>184</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>64</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>76</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1273,13 +1101,27 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2725000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
@@ -1287,57 +1129,49 @@
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45571.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59186</v>
+        <v>36178</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1398,57 +1232,49 @@
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.5</v>
+        <v>45583.65625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15220</v>
+        <v>18523</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1509,57 +1335,49 @@
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>15220</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1614,72 +1432,50 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>186</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>77</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26109</v>
+        <v>42000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1718,77 +1514,67 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>20</v>
+        <v>25.20833333333333</v>
       </c>
       <c r="W9" t="n">
-        <v>184</v>
+        <v>183.2083333333333</v>
       </c>
       <c r="X9" t="n">
+        <v>70.04166666666667</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5500</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2276041.666666667</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1</v>
       </c>
-      <c r="Y9" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>76</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AJ9" t="n">
+        <v>25.19046558017146</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>181.2374108734403</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>68.242960062813</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>4698.585115864527</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1752228.031364061</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>73.13605063237415</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>183.8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3600</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2725000</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
         </is>
@@ -1797,35 +1583,35 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36178</v>
+        <v>48229</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1879,64 +1665,70 @@
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+      <c r="AQ10" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2725000</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45583.65625</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18523</v>
+        <v>25178</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1997,22 +1789,490 @@
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>25.80555555555556</v>
+      </c>
+      <c r="W12" t="n">
+        <v>182.4027777777777</v>
+      </c>
+      <c r="X12" t="n">
+        <v>68.44907407407408</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4162.037037037037</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1726620.37037037</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>71.72685185185185</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="n">
+        <v>24.61955266955267</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>180.470498215235</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>66.26481734639628</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="n">
+        <v>1442597.022860181</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>71.2538353459406</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>186</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>77</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>25.07013888888889</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>183.7805555555555</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>67.73472222222222</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="n">
+        <v>1621319.444444444</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>72.88541666666666</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>25.65997899159664</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>180.9702746315918</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>66.17083790037753</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>1177785.592497869</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>71.48811655096821</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,190 +495,150 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_away</t>
+          <t>mean_value_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_away</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_rep_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rep_player_miss_away</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_home</t>
+          <t>mean_value_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_home</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_rep_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_start_home</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_away</t>
+          <t>mean_value_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_away</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_start_away</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_sub_home</t>
+          <t>mean_value_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_sub_home</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_home</t>
+          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_sub_home</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -687,35 +647,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45583.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>18523</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -768,37 +728,29 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
@@ -818,7 +770,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -871,57 +823,49 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21029</v>
+        <v>42000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -946,13 +890,27 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>25.20833333333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>183.2083333333333</v>
+      </c>
+      <c r="P4" t="n">
+        <v>70.04166666666667</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2276041.666666667</v>
+      </c>
+      <c r="S4" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -960,85 +918,77 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>25.19046558017146</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>181.2374108734403</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>68.242960062813</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4698.585115864527</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1752228.031364061</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>73.13605063237415</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>186</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>77</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26109</v>
+        <v>48229</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1063,30 +1013,14 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>20</v>
-      </c>
-      <c r="O5" t="n">
-        <v>184</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>64</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>76</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1100,78 +1034,70 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>22.6</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>22.6</v>
+        <v>183.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>183.8</v>
+        <v>69.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>69.2</v>
+        <v>3600</v>
       </c>
       <c r="AM5" t="n">
-        <v>3600</v>
+        <v>2725000</v>
       </c>
       <c r="AN5" t="n">
-        <v>2725000</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="AP5" t="n">
         <v>1</v>
       </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>36178</v>
+        <v>25178</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1224,57 +1150,49 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45583.65625</v>
+        <v>45585.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18523</v>
+        <v>17924</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1299,13 +1217,27 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>25.80555555555556</v>
+      </c>
+      <c r="O7" t="n">
+        <v>182.4027777777777</v>
+      </c>
+      <c r="P7" t="n">
+        <v>68.44907407407408</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4162.037037037037</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1726620.37037037</v>
+      </c>
+      <c r="S7" t="n">
+        <v>71.72685185185185</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -1313,71 +1245,89 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>24.61955266955267</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>180.470498215235</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>66.26481734639628</v>
+      </c>
       <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
+      <c r="AF7" t="n">
+        <v>1442597.022860181</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>71.2538353459406</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>186</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.5</v>
+        <v>45585.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15220</v>
+        <v>35322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1430,57 +1380,49 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.58333333334</v>
+        <v>45585.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42000</v>
+        <v>33150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1512,106 +1454,94 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>25.07013888888889</v>
+      </c>
       <c r="V9" t="n">
-        <v>25.20833333333333</v>
+        <v>183.7805555555555</v>
       </c>
       <c r="W9" t="n">
-        <v>183.2083333333333</v>
-      </c>
-      <c r="X9" t="n">
-        <v>70.04166666666667</v>
-      </c>
+        <v>67.73472222222222</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>5500</v>
+        <v>1621319.444444444</v>
       </c>
       <c r="Z9" t="n">
-        <v>2276041.666666667</v>
+        <v>72.88541666666666</v>
       </c>
       <c r="AA9" t="n">
-        <v>74.25</v>
-      </c>
-      <c r="AB9" t="n">
         <v>1</v>
       </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>25.65997899159664</v>
+      </c>
       <c r="AJ9" t="n">
-        <v>25.19046558017146</v>
+        <v>180.9702746315918</v>
       </c>
       <c r="AK9" t="n">
-        <v>181.2374108734403</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>68.242960062813</v>
-      </c>
+        <v>66.17083790037753</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
-        <v>4698.585115864527</v>
+        <v>1177785.592497869</v>
       </c>
       <c r="AN9" t="n">
-        <v>1752228.031364061</v>
+        <v>71.48811655096821</v>
       </c>
       <c r="AO9" t="n">
-        <v>73.13605063237415</v>
-      </c>
-      <c r="AP9" t="n">
         <v>1</v>
       </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45584.66666666666</v>
+        <v>45585.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48229</v>
+        <v>20484</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1664,71 +1594,49 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>183.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3600</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2725000</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>25178</v>
+        <v>29778</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1781,57 +1689,49 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17924</v>
+        <v>18752</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1856,125 +1756,129 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>25.07013888888889</v>
+      </c>
+      <c r="O12" t="n">
+        <v>183.7805555555555</v>
+      </c>
+      <c r="P12" t="n">
+        <v>67.73472222222222</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>1621319.444444444</v>
+      </c>
+      <c r="S12" t="n">
+        <v>72.88541666666666</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>25.20833333333333</v>
+      </c>
       <c r="V12" t="n">
-        <v>25.80555555555556</v>
+        <v>183.2083333333333</v>
       </c>
       <c r="W12" t="n">
-        <v>182.4027777777777</v>
+        <v>70.04166666666667</v>
       </c>
       <c r="X12" t="n">
-        <v>68.44907407407408</v>
+        <v>5500</v>
       </c>
       <c r="Y12" t="n">
-        <v>4162.037037037037</v>
+        <v>2276041.666666667</v>
       </c>
       <c r="Z12" t="n">
-        <v>1726620.37037037</v>
+        <v>74.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>71.72685185185185</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
+        <v>25.65997899159664</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>180.9702746315918</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>66.17083790037753</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>1177785.592497869</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>71.48811655096821</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1</v>
       </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>25.19046558017146</v>
+      </c>
       <c r="AJ12" t="n">
-        <v>24.61955266955267</v>
+        <v>181.2374108734403</v>
       </c>
       <c r="AK12" t="n">
-        <v>180.470498215235</v>
+        <v>68.242960062813</v>
       </c>
       <c r="AL12" t="n">
-        <v>66.26481734639628</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
+        <v>4698.585115864527</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1752228.031364061</v>
+      </c>
       <c r="AN12" t="n">
-        <v>1442597.022860181</v>
+        <v>73.13605063237415</v>
       </c>
       <c r="AO12" t="n">
-        <v>71.2538353459406</v>
-      </c>
-      <c r="AP12" t="n">
         <v>1</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>186</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>77</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>35322</v>
+        <v>21029</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2013,13 +1917,27 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>186</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
@@ -2027,57 +1945,49 @@
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.66666666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>33150</v>
+        <v>38223</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2117,94 +2027,62 @@
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="n">
-        <v>25.07013888888889</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>183.7805555555555</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>67.73472222222222</v>
-      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="n">
-        <v>1621319.444444444</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>72.88541666666666</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1</v>
-      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="n">
-        <v>25.65997899159664</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>180.9702746315918</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>66.17083790037753</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="n">
-        <v>1177785.592497869</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>71.48811655096821</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45585.65625</v>
+        <v>45592.45833333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20484</v>
+        <v>59186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2236,13 +2114,27 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>25.80555555555556</v>
+      </c>
+      <c r="V15" t="n">
+        <v>182.4027777777777</v>
+      </c>
+      <c r="W15" t="n">
+        <v>68.44907407407408</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4162.037037037037</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1726620.37037037</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>71.72685185185185</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
@@ -2250,29 +2142,427 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>24.61955266955267</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>180.470498215235</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>66.26481734639628</v>
+      </c>
       <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr">
+      <c r="AM15" t="n">
+        <v>1442597.022860181</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>71.2538353459406</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2725000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,150 +495,230 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -700,40 +780,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
+      <c r="N2" t="n">
+        <v>23.03166666666667</v>
+      </c>
+      <c r="O2" t="n">
+        <v>179.5224761904762</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="R2" t="n">
+        <v>163160</v>
+      </c>
+      <c r="S2" t="n">
+        <v>68152000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>351.64</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="V2" t="n">
+        <v>28</v>
+      </c>
+      <c r="W2" t="n">
+        <v>187</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>23.34166666666667</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>179.4185185185185</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>74.99907407407407</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>40047.97979797979</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>14668333.33333333</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>81.07685185185186</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.396296296296296</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>23.8690836940837</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>181.3700487012987</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>75.6312049062049</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>25923.61111111111</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>12535948.5479798</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>81.02594696969696</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.393614718614719</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>20.62352492953997</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>178.8517909547985</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>70.71331801726539</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>16142.85714285714</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9377380.554561006</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>81.50757885250366</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.106596619754515</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>26.38708028083028</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>179.3694368131868</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>74.19342555592556</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>23353.33333333333</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7961124.228780478</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>77.92028688903689</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.265542096792097</v>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>pCcFFE7M</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>UapruDaf</t>
         </is>
@@ -795,40 +979,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
+      <c r="N3" t="n">
+        <v>25.15277777777778</v>
+      </c>
+      <c r="O3" t="n">
+        <v>182.8148148148148</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>107.8333333333333</v>
+      </c>
+      <c r="R3" t="n">
+        <v>22277.77777777778</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5216666.666666667</v>
+      </c>
+      <c r="T3" t="n">
+        <v>113.3888888888889</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="V3" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>182.4074074074074</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.407407407407407</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>103.3703703703704</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>29185.18518518519</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>14107407.40740741</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>113.5185185185185</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>25.71378066378066</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>181.5382756132756</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>72.52442279942279</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>15441.08946608947</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3563956.52958153</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>75.48510101010102</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.177164502164502</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23.37242424242424</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>181.5987878787879</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>75.25545454545454</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>29989.83957219251</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>13209121.21212121</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>81.30727272727272</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.47030303030303</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>24.57324929971989</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>181.8454677871148</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>69.936162464986</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>12559.31465919701</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2691325.536881419</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>74.15611764705882</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.162082166199814</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>22.49895995435211</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>182.4739936715427</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>72.54773057371096</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>22019.84126984127</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>9999914.410208531</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>79.69411245979873</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.266109036207076</v>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0tIbS515</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
@@ -891,67 +1179,143 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>25.20833333333333</v>
+        <v>28</v>
       </c>
       <c r="O4" t="n">
-        <v>183.2083333333333</v>
+        <v>180.25</v>
       </c>
       <c r="P4" t="n">
-        <v>70.04166666666667</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>5500</v>
+        <v>280</v>
       </c>
       <c r="R4" t="n">
-        <v>2276041.666666667</v>
+        <v>21000</v>
       </c>
       <c r="S4" t="n">
-        <v>74.25</v>
+        <v>6675000</v>
       </c>
       <c r="T4" t="n">
+        <v>284</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>26.44304029304029</v>
+      </c>
+      <c r="W4" t="n">
+        <v>173.5783882783882</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.769230769230769</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>206.0769230769231</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>68769.23076923077</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>18984615.38461538</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.807692307692307</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>25.89806149732621</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>181.9194518716578</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>70.39405080213903</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>6352.617079889807</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2197284.425133689</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>73.64505347593582</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>25.19046558017146</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>181.2374108734403</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>68.242960062813</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>4698.585115864527</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1752228.031364061</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>73.13605063237415</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AK4" t="n">
+        <v>25.71014957264957</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>180.3595085470086</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>76.8534188034188</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29090.59829059829</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>12672617.52136752</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>79.91228632478632</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>25.06676724118674</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>181.2043421741371</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>68.17481453373483</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5074.794395872827</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1725631.054156112</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>73.16747227732135</v>
+      </c>
+      <c r="AX4" t="n">
         <v>1</v>
       </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
+      <c r="AY4" t="n">
+        <v>27.08825994911521</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>178.5726760082023</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>74.25448588326877</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>23266.6507651705</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6790493.931324524</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>76.10922239310396</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.404473779144832</v>
+      </c>
+      <c r="BF4" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>K6b7RoBp</t>
         </is>
@@ -1013,54 +1377,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>25.63735632183908</v>
+      </c>
+      <c r="O5" t="n">
+        <v>189.7293103448276</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.413793103448276</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>269.5862068965517</v>
+      </c>
+      <c r="R5" t="n">
+        <v>234827.5862068966</v>
+      </c>
+      <c r="S5" t="n">
+        <v>110794827.5862069</v>
+      </c>
+      <c r="T5" t="n">
+        <v>282.1379310344827</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7.448275862068965</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.60333333333334</v>
+      </c>
+      <c r="W5" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>159.76</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>39440</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>8360800</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>168.48</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>22.71296296296296</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>184.574074074074</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>81.17592592592592</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>85513.88888888889</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>55655555.55555555</v>
+      </c>
       <c r="AI5" t="n">
-        <v>22.6</v>
+        <v>86.7962962962963</v>
       </c>
       <c r="AJ5" t="n">
-        <v>183.8</v>
+        <v>2.074074074074074</v>
       </c>
       <c r="AK5" t="n">
-        <v>69.2</v>
+        <v>23.24084967320261</v>
       </c>
       <c r="AL5" t="n">
-        <v>3600</v>
+        <v>183.1442810457517</v>
       </c>
       <c r="AM5" t="n">
-        <v>2725000</v>
+        <v>71.11143790849674</v>
       </c>
       <c r="AN5" t="n">
-        <v>77.59999999999999</v>
+        <v>13266.01307189542</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="inlineStr">
+        <v>4596258.169934641</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>78.17532679738561</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.241993464052287</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>23.2547952047952</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>183.9831002331002</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>80.01316183816184</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>84948.40367965367</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>47297179.07092907</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>85.13105228105226</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2.011538461538461</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>24.38129148629149</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>182.5140163540163</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>71.1423617123617</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>12341.98618841476</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3676548.03992304</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>76.75659211159213</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.325454545454545</v>
+      </c>
+      <c r="BF5" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>K6b7RoBp</t>
         </is>
@@ -1122,40 +1576,142 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>23.73611111111111</v>
+      </c>
+      <c r="O6" t="n">
+        <v>184.7268518518518</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>127.7777777777778</v>
+      </c>
+      <c r="R6" t="n">
+        <v>13500</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4898611.111111111</v>
+      </c>
+      <c r="T6" t="n">
+        <v>140.3888888888889</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="V6" t="n">
+        <v>23.81578947368421</v>
+      </c>
+      <c r="W6" t="n">
+        <v>176.9385964912281</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>148.8947368421053</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>72277.77777777778</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>21394736.84210526</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>159.421052631579</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.631578947368421</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>23.16180555555555</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>186.2359722222222</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>66.45569444444445</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5116.898148148148</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1767809.027777778</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>73.83027777777778</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>74.5625</v>
+      </c>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr">
+      <c r="AO6" t="n">
+        <v>12468750</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>78.8125</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>24.42377633070772</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>181.3382884294069</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>65.77923752834468</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4142.176870748299</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1442170.931420814</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>72.32949673290368</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>27.99833333333333</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>178.1766666666667</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>78.09</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>44565</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>14795000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>79.00500000000001</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.998333333333334</v>
+      </c>
+      <c r="BF6" t="inlineStr">
         <is>
           <t>0tIbS515</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>YTLwacK1</t>
         </is>
@@ -1218,79 +1774,141 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>25.80555555555556</v>
+        <v>22.67380952380952</v>
       </c>
       <c r="O7" t="n">
-        <v>182.4027777777777</v>
+        <v>185.302380952381</v>
       </c>
       <c r="P7" t="n">
-        <v>68.44907407407408</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="Q7" t="n">
-        <v>4162.037037037037</v>
+        <v>178.7142857142857</v>
       </c>
       <c r="R7" t="n">
-        <v>1726620.37037037</v>
+        <v>4000</v>
       </c>
       <c r="S7" t="n">
-        <v>71.72685185185185</v>
+        <v>3814285.714285714</v>
       </c>
       <c r="T7" t="n">
+        <v>200.7142857142857</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="V7" t="n">
+        <v>20.068</v>
+      </c>
+      <c r="W7" t="n">
+        <v>178.6546666666667</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>15222.22222222222</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4496000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>25.95185728250244</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>181.0536412512219</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>68.52146464646465</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4427.420759317311</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1664599.625285109</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>71.19937275985663</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="n">
-        <v>24.61955266955267</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>180.470498215235</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>66.26481734639628</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="n">
-        <v>1442597.022860181</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>71.2538353459406</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AK7" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>184.85</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>16593.75</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>6512500</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>23.23470212327355</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>181.6011497358114</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>65.16514652431945</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>1320450.449717367</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>71.73958896158145</v>
+      </c>
+      <c r="AX7" t="n">
         <v>1</v>
       </c>
-      <c r="AI7" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>186</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>77</v>
-      </c>
-      <c r="AO7" t="n">
+      <c r="AY7" t="n">
+        <v>23.17482993197279</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>186.1051587301587</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>69.19631519274375</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>10722.8835978836</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2894994.33106576</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>75.49625850340136</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1</v>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>
@@ -1352,40 +1970,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr">
+      <c r="N8" t="n">
+        <v>24.13066666666667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>178.336</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>168.76</v>
+      </c>
+      <c r="R8" t="n">
+        <v>56800</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15286000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>174.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>22.86538461538462</v>
+      </c>
+      <c r="W8" t="n">
+        <v>177.6948717948717</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.615384615384615</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>196.0384615384615</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>76038.46153846153</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>29100000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>210.2692307692308</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>25.19537037037037</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>182.4864814814815</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>73.54574074074074</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>22036.11111111111</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>6491884.259259259</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>77.39629629629628</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.438518518518519</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>24.37231240981241</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>185.2401334776335</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>75.62306096681097</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>31253.90512265512</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>11180403.13852814</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>80.20913600288601</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.395265151515151</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>24.76525106837607</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>182.7132459554335</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>70.30262133699632</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>17424.00793650794</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4600432.434752747</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>75.50518353174603</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.209149877899878</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>21.98486829075064</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>181.0441188849277</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>72.20219350366409</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>24598.33341585793</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8236831.65395788</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>79.01152703505645</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.316728560110913</v>
+      </c>
+      <c r="BF8" t="inlineStr">
         <is>
           <t>YHU1oFVQ</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
         </is>
@@ -1447,64 +2169,138 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>21.92222222222223</v>
+      </c>
+      <c r="O9" t="n">
+        <v>180.7805555555556</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>179.7083333333333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>26227.27272727273</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10943750</v>
+      </c>
+      <c r="T9" t="n">
+        <v>201.8333333333333</v>
+      </c>
       <c r="U9" t="n">
-        <v>25.07013888888889</v>
+        <v>2.583333333333333</v>
       </c>
       <c r="V9" t="n">
-        <v>183.7805555555555</v>
+        <v>22.01190476190476</v>
       </c>
       <c r="W9" t="n">
-        <v>67.73472222222222</v>
-      </c>
-      <c r="X9" t="inlineStr"/>
+        <v>181.0119047619048</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.714285714285714</v>
+      </c>
       <c r="Y9" t="n">
-        <v>1621319.444444444</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>72.88541666666666</v>
-      </c>
+        <v>174.1428571428571</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
+        <v>2707142.857142857</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>196.8571428571429</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22.27976190476191</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>185.443783068783</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>69.23068783068783</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>3984679.232804233</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>77.98518518518519</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1</v>
       </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="n">
-        <v>25.65997899159664</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>180.9702746315918</v>
-      </c>
       <c r="AK9" t="n">
-        <v>66.17083790037753</v>
-      </c>
-      <c r="AL9" t="inlineStr"/>
+        <v>27.44285827020202</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>183.1825126262626</v>
+      </c>
       <c r="AM9" t="n">
-        <v>1177785.592497869</v>
+        <v>69.2972380050505</v>
       </c>
       <c r="AN9" t="n">
-        <v>71.48811655096821</v>
+        <v>5002.797202797203</v>
       </c>
       <c r="AO9" t="n">
+        <v>1650427.714646465</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>72.08510890151516</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1</v>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="AR9" t="n">
+        <v>21.35565476190476</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>180.9291294642857</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>67.58143601190476</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7713.095238095239</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2881141.183035715</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>77.26112351190476</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>24.46664781297134</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>181.8867184532676</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>65.20751137913361</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>1121297.0452395</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>71.16623660166407</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF9" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
         </is>
@@ -1566,40 +2362,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr">
+      <c r="N10" t="n">
+        <v>24.51987179487179</v>
+      </c>
+      <c r="O10" t="n">
+        <v>178.4583333333333</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>237</v>
+      </c>
+      <c r="R10" t="n">
+        <v>45230.76923076923</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11777884.61538462</v>
+      </c>
+      <c r="T10" t="n">
+        <v>257.4230769230769</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.076923076923077</v>
+      </c>
+      <c r="V10" t="n">
+        <v>23.56866666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>183.6266666666667</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>96440</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>38692000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>312.56</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>25.88611111111111</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>179.7277777777778</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>73.26666666666667</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>16344.13580246914</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>6943229.166666666</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>77.29583333333332</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.394444444444444</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>25.10069444444444</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>182.2638888888889</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>77.14583333333333</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>37447.91666666666</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>15792968.75</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>81.07986111111111</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.180555555555556</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>23.37037407037407</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>180.179425019425</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>68.70418248418248</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>10680.54672600127</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3142481.573981574</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>76.50067932067932</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.20987234987235</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>23.94808080808081</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>182.8925252525253</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>75.01339105339105</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>28849.89898989899</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>10478535.35353535</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>80.0346608946609</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.181298701298701</v>
+      </c>
+      <c r="BF10" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
         </is>
@@ -1661,40 +2561,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr">
+      <c r="N11" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>182.4074074074074</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.407407407407407</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>103.3703703703704</v>
+      </c>
+      <c r="R11" t="n">
+        <v>29185.18518518519</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14107407.40740741</v>
+      </c>
+      <c r="T11" t="n">
+        <v>113.5185185185185</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.555555555555556</v>
+      </c>
+      <c r="V11" t="n">
+        <v>23.73611111111111</v>
+      </c>
+      <c r="W11" t="n">
+        <v>184.7268518518518</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>127.7777777777778</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13500</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4898611.111111111</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>140.3888888888889</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>23.37242424242424</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>181.5987878787879</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>75.25545454545454</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>29989.83957219251</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>13209121.21212121</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>81.30727272727272</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.47030303030303</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>23.16180555555555</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>186.2359722222222</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>66.45569444444445</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>5116.898148148148</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1767809.027777778</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>73.83027777777778</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>22.49895995435211</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>182.4739936715427</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>72.54773057371096</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>22019.84126984127</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9999914.410208531</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>79.69411245979873</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.266109036207076</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>24.42377633070772</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>181.3382884294069</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>65.77923752834468</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4142.176870748299</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1442170.931420814</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>72.32949673290368</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="inlineStr">
         <is>
           <t>pCcFFE7M</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>dWZTBmVT</t>
         </is>
@@ -1757,91 +2761,139 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>25.07013888888889</v>
+        <v>22.01190476190476</v>
       </c>
       <c r="O12" t="n">
-        <v>183.7805555555555</v>
+        <v>181.0119047619048</v>
       </c>
       <c r="P12" t="n">
-        <v>67.73472222222222</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
-        <v>1621319.444444444</v>
-      </c>
+        <v>2.714285714285714</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>174.1428571428571</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>72.88541666666666</v>
+        <v>2707142.857142857</v>
       </c>
       <c r="T12" t="n">
+        <v>196.8571428571429</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="V12" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="W12" t="n">
+        <v>178.1944444444445</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.555555555555555</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>178.4444444444445</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>15555.55555555555</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4563888.888888889</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>182.4444444444445</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.555555555555555</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>27.44285827020202</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>183.1825126262626</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>69.2972380050505</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5002.797202797203</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1650427.714646465</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>72.08510890151516</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>25.20833333333333</v>
-      </c>
-      <c r="V12" t="n">
-        <v>183.2083333333333</v>
-      </c>
-      <c r="W12" t="n">
-        <v>70.04166666666667</v>
-      </c>
-      <c r="X12" t="n">
-        <v>5500</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2276041.666666667</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>74.25</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="AK12" t="n">
+        <v>25.89806149732621</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>181.9194518716578</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>70.39405080213903</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>6352.617079889807</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2197284.425133689</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>73.64505347593582</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>1</v>
       </c>
-      <c r="AB12" t="n">
-        <v>25.65997899159664</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>180.9702746315918</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>66.17083790037753</v>
-      </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="n">
-        <v>1177785.592497869</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>71.48811655096821</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AR12" t="n">
+        <v>24.46664781297134</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>181.8867184532676</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>65.20751137913361</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>1121297.0452395</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>71.16623660166407</v>
+      </c>
+      <c r="AX12" t="n">
         <v>1</v>
       </c>
-      <c r="AI12" t="n">
-        <v>25.19046558017146</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>181.2374108734403</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>68.242960062813</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>4698.585115864527</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1752228.031364061</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>73.13605063237415</v>
-      </c>
-      <c r="AO12" t="n">
+      <c r="AY12" t="n">
+        <v>25.06676724118674</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>181.2043421741371</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>68.17481453373483</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5074.794395872827</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1725631.054156112</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>73.16747227732135</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1</v>
       </c>
-      <c r="AP12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>OpNm82MB</t>
         </is>
@@ -1903,54 +2955,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>20.068</v>
+      </c>
+      <c r="O13" t="n">
+        <v>178.6546666666667</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>15222.22222222222</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4496000</v>
+      </c>
+      <c r="T13" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>25.15277777777778</v>
+      </c>
+      <c r="W13" t="n">
+        <v>182.8148148148148</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>107.8333333333333</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>22277.77777777778</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5216666.666666667</v>
+      </c>
       <c r="AB13" t="n">
-        <v>20.5</v>
+        <v>113.3888888888889</v>
       </c>
       <c r="AC13" t="n">
-        <v>186</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AD13" t="n">
-        <v>66.5</v>
+        <v>25.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>6000</v>
+        <v>184.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>2200000</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="AG13" t="n">
-        <v>77</v>
+        <v>16593.75</v>
       </c>
       <c r="AH13" t="n">
+        <v>6512500</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>25.71378066378066</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>181.5382756132756</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>72.52442279942279</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>15441.08946608947</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3563956.52958153</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>75.48510101010102</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.177164502164502</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>23.17482993197279</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>186.1051587301587</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>69.19631519274375</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>10722.8835978836</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2894994.33106576</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>75.49625850340136</v>
+      </c>
+      <c r="AX13" t="n">
         <v>1</v>
       </c>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr">
+      <c r="AY13" t="n">
+        <v>24.57324929971989</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>181.8454677871148</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>69.936162464986</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>12559.31465919701</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2691325.536881419</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>74.15611764705882</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.162082166199814</v>
+      </c>
+      <c r="BF13" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>dWZTBmVT</t>
         </is>
@@ -2012,40 +3154,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr">
+      <c r="N14" t="n">
+        <v>26.44304029304029</v>
+      </c>
+      <c r="O14" t="n">
+        <v>173.5783882783882</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.769230769230769</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>206.0769230769231</v>
+      </c>
+      <c r="R14" t="n">
+        <v>68769.23076923077</v>
+      </c>
+      <c r="S14" t="n">
+        <v>18984615.38461538</v>
+      </c>
+      <c r="T14" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.807692307692307</v>
+      </c>
+      <c r="V14" t="n">
+        <v>24.76436781609195</v>
+      </c>
+      <c r="W14" t="n">
+        <v>183.6206896551724</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.344827586206897</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>101.2758620689655</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>26896.55172413793</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>13158620.68965517</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>107.7241379310345</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.827586206896552</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>25.71014957264957</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>180.3595085470086</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>76.8534188034188</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>29090.59829059829</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>12672617.52136752</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>79.91228632478632</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>23.8690836940837</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>181.3700487012987</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75.6312049062049</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25923.61111111111</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>12535948.5479798</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>81.02594696969696</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.393614718614719</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>27.08825994911521</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>178.5726760082023</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>74.25448588326877</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>23266.6507651705</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>6790493.931324524</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>76.10922239310396</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.404473779144832</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>26.38708028083028</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>179.3694368131868</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>74.19342555592556</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>23353.33333333333</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7961124.228780478</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>77.92028688903689</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.265542096792097</v>
+      </c>
+      <c r="BF14" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>UapruDaf</t>
         </is>
@@ -2107,66 +3353,140 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>23.81578947368421</v>
+      </c>
+      <c r="O15" t="n">
+        <v>176.9385964912281</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>148.8947368421053</v>
+      </c>
+      <c r="R15" t="n">
+        <v>72277.77777777778</v>
+      </c>
+      <c r="S15" t="n">
+        <v>21394736.84210526</v>
+      </c>
+      <c r="T15" t="n">
+        <v>159.421052631579</v>
+      </c>
       <c r="U15" t="n">
-        <v>25.80555555555556</v>
+        <v>3.631578947368421</v>
       </c>
       <c r="V15" t="n">
-        <v>182.4027777777777</v>
+        <v>22.67380952380952</v>
       </c>
       <c r="W15" t="n">
-        <v>68.44907407407408</v>
+        <v>185.302380952381</v>
       </c>
       <c r="X15" t="n">
-        <v>4162.037037037037</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="Y15" t="n">
-        <v>1726620.37037037</v>
+        <v>178.7142857142857</v>
       </c>
       <c r="Z15" t="n">
-        <v>71.72685185185185</v>
+        <v>4000</v>
       </c>
       <c r="AA15" t="n">
+        <v>3814285.714285714</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>200.7142857142857</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>74.5625</v>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="n">
+        <v>12468750</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>78.8125</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>25.95185728250244</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>181.0536412512219</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>68.52146464646465</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>4427.420759317311</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1664599.625285109</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>71.19937275985663</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>1</v>
       </c>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="n">
-        <v>24.61955266955267</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>180.470498215235</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>66.26481734639628</v>
-      </c>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="n">
-        <v>1442597.022860181</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>71.2538353459406</v>
-      </c>
-      <c r="AO15" t="n">
+      <c r="AR15" t="n">
+        <v>27.99833333333333</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>178.1766666666667</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>78.09</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>44565</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>14795000</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>79.00500000000001</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.998333333333334</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>23.23470212327355</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>181.6011497358114</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>65.16514652431945</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
+        <v>1320450.449717367</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>71.73958896158145</v>
+      </c>
+      <c r="BE15" t="n">
         <v>1</v>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>YHU1oFVQ</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>OpNm82MB</t>
         </is>
@@ -2228,40 +3548,142 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>24.51987179487179</v>
+      </c>
+      <c r="O16" t="n">
+        <v>178.4583333333333</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>237</v>
+      </c>
+      <c r="R16" t="n">
+        <v>45230.76923076923</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11777884.61538462</v>
+      </c>
+      <c r="T16" t="n">
+        <v>257.4230769230769</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.076923076923077</v>
+      </c>
+      <c r="V16" t="n">
+        <v>21.92222222222223</v>
+      </c>
+      <c r="W16" t="n">
+        <v>180.7805555555556</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>179.7083333333333</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>26227.27272727273</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>10943750</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>201.8333333333333</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>25.88611111111111</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>179.7277777777778</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>73.26666666666667</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>16344.13580246914</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>6943229.166666666</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>77.29583333333332</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.394444444444444</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>22.27976190476191</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>185.443783068783</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>69.23068783068783</v>
+      </c>
       <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr">
+      <c r="AO16" t="n">
+        <v>3984679.232804233</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>77.98518518518519</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>23.37037407037407</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>180.179425019425</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>68.70418248418248</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>10680.54672600127</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3142481.573981574</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>76.50067932067932</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.20987234987235</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>21.35565476190476</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>180.9291294642857</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>67.58143601190476</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7713.095238095239</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2881141.183035715</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>77.26112351190476</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF16" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>UapruDaf</t>
         </is>
@@ -2323,40 +3745,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr">
+      <c r="N17" t="n">
+        <v>22.86538461538462</v>
+      </c>
+      <c r="O17" t="n">
+        <v>177.6948717948717</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.615384615384615</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>196.0384615384615</v>
+      </c>
+      <c r="R17" t="n">
+        <v>76038.46153846153</v>
+      </c>
+      <c r="S17" t="n">
+        <v>29100000</v>
+      </c>
+      <c r="T17" t="n">
+        <v>210.2692307692308</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="V17" t="n">
+        <v>23.03166666666667</v>
+      </c>
+      <c r="W17" t="n">
+        <v>179.5224761904762</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>163160</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>68152000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>351.64</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>24.37231240981241</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>185.2401334776335</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>75.62306096681097</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>31253.90512265512</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>11180403.13852814</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>80.20913600288601</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.395265151515151</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>23.34166666666667</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>179.4185185185185</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>74.99907407407407</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>40047.97979797979</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>14668333.33333333</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>81.07685185185186</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.396296296296296</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>21.98486829075064</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>181.0441188849277</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>72.20219350366409</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>24598.33341585793</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>8236831.65395788</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>79.01152703505645</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.316728560110913</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>20.62352492953997</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>178.8517909547985</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>70.71331801726539</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>16142.85714285714</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>9377380.554561006</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>81.50757885250366</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.106596619754515</v>
+      </c>
+      <c r="BF17" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
@@ -2418,54 +3944,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>25.60333333333334</v>
+      </c>
+      <c r="O18" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>159.76</v>
+      </c>
+      <c r="R18" t="n">
+        <v>39440</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8360800</v>
+      </c>
+      <c r="T18" t="n">
+        <v>168.48</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="V18" t="n">
+        <v>24.13066666666667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>178.336</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>168.76</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>56800</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>15286000</v>
+      </c>
       <c r="AB18" t="n">
-        <v>22.6</v>
+        <v>174.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>183.8</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>69.2</v>
+        <v>23.24084967320261</v>
       </c>
       <c r="AE18" t="n">
-        <v>3600</v>
+        <v>183.1442810457517</v>
       </c>
       <c r="AF18" t="n">
-        <v>2725000</v>
+        <v>71.11143790849674</v>
       </c>
       <c r="AG18" t="n">
-        <v>77.59999999999999</v>
+        <v>13266.01307189542</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr">
+        <v>4596258.169934641</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>78.17532679738561</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.241993464052287</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>25.19537037037037</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>182.4864814814815</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>73.54574074074074</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>22036.11111111111</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>6491884.259259259</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>77.39629629629628</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.438518518518519</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>24.38129148629149</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>182.5140163540163</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>71.1423617123617</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>12341.98618841476</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3676548.03992304</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>76.75659211159213</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.325454545454545</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>24.76525106837607</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>182.7132459554335</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>70.30262133699632</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>17424.00793650794</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4600432.434752747</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>75.50518353174603</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.209149877899878</v>
+      </c>
+      <c r="BF18" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>YTLwacK1</t>
         </is>
@@ -2527,40 +4143,144 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr">
+      <c r="N19" t="n">
+        <v>23.56866666666667</v>
+      </c>
+      <c r="O19" t="n">
+        <v>183.6266666666667</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>96440</v>
+      </c>
+      <c r="S19" t="n">
+        <v>38692000</v>
+      </c>
+      <c r="T19" t="n">
+        <v>312.56</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="V19" t="n">
+        <v>25.63735632183908</v>
+      </c>
+      <c r="W19" t="n">
+        <v>189.7293103448276</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.413793103448276</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>269.5862068965517</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>234827.5862068966</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>110794827.5862069</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>282.1379310344827</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.448275862068965</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>25.10069444444444</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>182.2638888888889</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>77.14583333333333</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>37447.91666666666</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>15792968.75</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>81.07986111111111</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.180555555555556</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>22.71296296296296</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>184.574074074074</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>81.17592592592592</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>85513.88888888889</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>55655555.55555555</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>86.7962962962963</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2.074074074074074</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>23.94808080808081</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>182.8925252525253</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>75.01339105339105</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>28849.89898989899</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>10478535.35353535</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>80.0346608946609</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.181298701298701</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>23.2547952047952</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>183.9831002331002</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>80.01316183816184</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>84948.40367965367</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>47297179.07092907</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>85.13105228105226</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.011538461538461</v>
+      </c>
+      <c r="BF19" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>
       </c>
-      <c r="AQ19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG6"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25178</v>
+        <v>29778</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,135 +781,137 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>23.37242424242424</v>
+      </c>
+      <c r="O2" t="n">
+        <v>181.5987878787879</v>
+      </c>
+      <c r="P2" t="n">
+        <v>75.25545454545454</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>29989.83957219251</v>
+      </c>
+      <c r="R2" t="n">
+        <v>13209121.21212121</v>
+      </c>
+      <c r="S2" t="n">
+        <v>81.30727272727272</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.47030303030303</v>
+      </c>
+      <c r="U2" t="n">
+        <v>23.16180555555555</v>
+      </c>
+      <c r="V2" t="n">
+        <v>186.2359722222222</v>
+      </c>
+      <c r="W2" t="n">
+        <v>66.45569444444445</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5116.898148148148</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1767809.027777778</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>73.83027777777778</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>22.49895995435211</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>182.4739936715427</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>72.54773057371096</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>22019.84126984127</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9999914.410208531</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>79.69411245979873</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.266109036207076</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>24.42377633070772</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>181.3382884294069</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>65.77923752834468</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>4142.176870748299</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1442170.931420814</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>72.32949673290368</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>21.125</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>182.6428571428571</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.392857142857143</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>28642.85714285714</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>13707142.85714286</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.535714285714286</v>
+      </c>
+      <c r="AX2" t="n">
         <v>23.73611111111111</v>
       </c>
-      <c r="O2" t="n">
+      <c r="AY2" t="n">
         <v>184.7268518518518</v>
       </c>
-      <c r="P2" t="n">
+      <c r="AZ2" t="n">
         <v>1.888888888888889</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="BA2" t="n">
         <v>127.7777777777778</v>
       </c>
-      <c r="R2" t="n">
+      <c r="BB2" t="n">
         <v>13500</v>
       </c>
-      <c r="S2" t="n">
+      <c r="BC2" t="n">
         <v>4898611.111111111</v>
       </c>
-      <c r="T2" t="n">
+      <c r="BD2" t="n">
         <v>140.3888888888889</v>
       </c>
-      <c r="U2" t="n">
+      <c r="BE2" t="n">
         <v>1.888888888888889</v>
       </c>
-      <c r="V2" t="n">
-        <v>23.81578947368421</v>
-      </c>
-      <c r="W2" t="n">
-        <v>176.9385964912281</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>148.8947368421053</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>72277.77777777778</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>21394736.84210526</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>159.421052631579</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.631578947368421</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>23.16180555555555</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>186.2359722222222</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>66.45569444444445</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>5116.898148148148</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1767809.027777778</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>73.83027777777778</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>180.625</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>74.5625</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>12468750</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>78.8125</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>24.42377633070772</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>181.3382884294069</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>65.77923752834468</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4142.176870748299</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1442170.931420814</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>72.32949673290368</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>27.99833333333333</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>178.1766666666667</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>78.09</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>44565</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>14795000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>79.00500000000001</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.998333333333334</v>
-      </c>
       <c r="BF2" t="inlineStr">
         <is>
           <t>0tIbS515</t>
@@ -917,42 +919,42 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17924</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -978,178 +980,176 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24.4</v>
+        <v>27.35368074686256</v>
       </c>
       <c r="O3" t="n">
-        <v>185.8</v>
+        <v>183.1428910315274</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>69.23520048974594</v>
       </c>
       <c r="Q3" t="n">
-        <v>328</v>
+        <v>5002.797202797203</v>
       </c>
       <c r="R3" t="n">
-        <v>4000</v>
+        <v>1649846.57177839</v>
       </c>
       <c r="S3" t="n">
-        <v>6150000</v>
+        <v>72.10146923783287</v>
       </c>
       <c r="T3" t="n">
-        <v>359</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>25.86196524064171</v>
       </c>
       <c r="V3" t="n">
-        <v>20.068</v>
+        <v>181.8967245989305</v>
       </c>
       <c r="W3" t="n">
-        <v>178.6546666666667</v>
+        <v>70.39104278074866</v>
       </c>
       <c r="X3" t="n">
-        <v>1.72</v>
+        <v>6351.584022038567</v>
       </c>
       <c r="Y3" t="n">
-        <v>116.6</v>
+        <v>2207244.318181818</v>
       </c>
       <c r="Z3" t="n">
-        <v>15222.22222222222</v>
+        <v>73.68282085561498</v>
       </c>
       <c r="AA3" t="n">
-        <v>4496000</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>134.8</v>
+        <v>24.56052298055974</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.8</v>
+        <v>181.8599506329845</v>
       </c>
       <c r="AD3" t="n">
-        <v>25.95185728250244</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>181.0536412512219</v>
-      </c>
+        <v>65.24020871261921</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>68.52146464646465</v>
+        <v>1113707.597401651</v>
       </c>
       <c r="AG3" t="n">
-        <v>4427.420759317311</v>
+        <v>71.15948216614777</v>
       </c>
       <c r="AH3" t="n">
-        <v>1664599.625285109</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>71.19937275985663</v>
+        <v>25.00711811837973</v>
       </c>
       <c r="AJ3" t="n">
+        <v>181.1599812718814</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>68.16729573674233</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5072.677993756424</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1737015.765935561</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>73.2196026031359</v>
+      </c>
+      <c r="AO3" t="n">
         <v>1</v>
       </c>
-      <c r="AK3" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>184.85</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>73.34999999999999</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>16593.75</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>6512500</v>
-      </c>
       <c r="AP3" t="n">
-        <v>78.15000000000001</v>
+        <v>22.23958333333334</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.125</v>
+        <v>181.3229166666667</v>
       </c>
       <c r="AR3" t="n">
-        <v>23.23470212327355</v>
+        <v>3.125</v>
       </c>
       <c r="AS3" t="n">
-        <v>181.6011497358114</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>65.16514652431945</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>202</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>3356250</v>
+      </c>
       <c r="AV3" t="n">
-        <v>1320450.449717367</v>
+        <v>226.75</v>
       </c>
       <c r="AW3" t="n">
-        <v>71.73958896158145</v>
+        <v>3.125</v>
       </c>
       <c r="AX3" t="n">
-        <v>1</v>
+        <v>26.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>23.17482993197279</v>
+        <v>178.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>186.1051587301587</v>
+        <v>2.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>69.19631519274375</v>
+        <v>188.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>10722.8835978836</v>
+        <v>16100</v>
       </c>
       <c r="BC3" t="n">
-        <v>2894994.33106576</v>
+        <v>4775000</v>
       </c>
       <c r="BD3" t="n">
-        <v>75.49625850340136</v>
+        <v>192.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35322</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1175,180 +1175,180 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>24.13066666666667</v>
+        <v>25.25</v>
       </c>
       <c r="O4" t="n">
-        <v>178.336</v>
+        <v>184.85</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>168.76</v>
+        <v>16593.75</v>
       </c>
       <c r="R4" t="n">
-        <v>56800</v>
+        <v>6512500</v>
       </c>
       <c r="S4" t="n">
-        <v>15286000</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>174.88</v>
+        <v>1.125</v>
       </c>
       <c r="U4" t="n">
-        <v>2.8</v>
+        <v>25.71378066378066</v>
       </c>
       <c r="V4" t="n">
-        <v>22.86538461538462</v>
+        <v>181.5382756132756</v>
       </c>
       <c r="W4" t="n">
-        <v>177.6948717948717</v>
+        <v>72.52442279942279</v>
       </c>
       <c r="X4" t="n">
-        <v>2.615384615384615</v>
+        <v>15441.08946608947</v>
       </c>
       <c r="Y4" t="n">
-        <v>196.0384615384615</v>
+        <v>3563956.52958153</v>
       </c>
       <c r="Z4" t="n">
-        <v>76038.46153846153</v>
+        <v>75.48510101010102</v>
       </c>
       <c r="AA4" t="n">
-        <v>29100000</v>
+        <v>1.177164502164502</v>
       </c>
       <c r="AB4" t="n">
-        <v>210.2692307692308</v>
+        <v>23.17482993197279</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.384615384615385</v>
+        <v>186.1051587301587</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.19537037037037</v>
+        <v>69.19631519274375</v>
       </c>
       <c r="AE4" t="n">
-        <v>182.4864814814815</v>
+        <v>10722.8835978836</v>
       </c>
       <c r="AF4" t="n">
-        <v>73.54574074074074</v>
+        <v>2894994.33106576</v>
       </c>
       <c r="AG4" t="n">
-        <v>22036.11111111111</v>
+        <v>75.49625850340136</v>
       </c>
       <c r="AH4" t="n">
-        <v>6491884.259259259</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>77.39629629629628</v>
+        <v>24.57324929971989</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.438518518518519</v>
+        <v>181.8454677871148</v>
       </c>
       <c r="AK4" t="n">
-        <v>24.37231240981241</v>
+        <v>69.936162464986</v>
       </c>
       <c r="AL4" t="n">
-        <v>185.2401334776335</v>
+        <v>12559.31465919701</v>
       </c>
       <c r="AM4" t="n">
-        <v>75.62306096681097</v>
+        <v>2691325.536881419</v>
       </c>
       <c r="AN4" t="n">
-        <v>31253.90512265512</v>
+        <v>74.15611764705882</v>
       </c>
       <c r="AO4" t="n">
-        <v>11180403.13852814</v>
+        <v>1.162082166199814</v>
       </c>
       <c r="AP4" t="n">
-        <v>80.20913600288601</v>
+        <v>20.068</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.395265151515151</v>
+        <v>178.6546666666667</v>
       </c>
       <c r="AR4" t="n">
-        <v>24.76525106837607</v>
+        <v>1.72</v>
       </c>
       <c r="AS4" t="n">
-        <v>182.7132459554335</v>
+        <v>116.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>70.30262133699632</v>
+        <v>15222.22222222222</v>
       </c>
       <c r="AU4" t="n">
-        <v>17424.00793650794</v>
+        <v>4496000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4600432.434752747</v>
+        <v>134.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>75.50518353174603</v>
+        <v>1.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.209149877899878</v>
+        <v>25.15277777777778</v>
       </c>
       <c r="AY4" t="n">
-        <v>21.98486829075064</v>
+        <v>182.8148148148148</v>
       </c>
       <c r="AZ4" t="n">
-        <v>181.0441188849277</v>
+        <v>1.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>72.20219350366409</v>
+        <v>107.8333333333333</v>
       </c>
       <c r="BB4" t="n">
-        <v>24598.33341585793</v>
+        <v>22277.77777777778</v>
       </c>
       <c r="BC4" t="n">
-        <v>8236831.65395788</v>
+        <v>5216666.666666667</v>
       </c>
       <c r="BD4" t="n">
-        <v>79.01152703505645</v>
+        <v>113.3888888888889</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.316728560110913</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>38223</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1374,338 +1374,2915 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21.92222222222223</v>
+        <v>25.71014957264957</v>
       </c>
       <c r="O5" t="n">
-        <v>180.7805555555556</v>
+        <v>180.3595085470086</v>
       </c>
       <c r="P5" t="n">
-        <v>2.583333333333333</v>
+        <v>76.8534188034188</v>
       </c>
       <c r="Q5" t="n">
-        <v>179.7083333333333</v>
+        <v>29090.59829059829</v>
       </c>
       <c r="R5" t="n">
-        <v>26227.27272727273</v>
+        <v>12672617.52136752</v>
       </c>
       <c r="S5" t="n">
-        <v>10943750</v>
+        <v>79.91228632478632</v>
       </c>
       <c r="T5" t="n">
-        <v>201.8333333333333</v>
+        <v>1.15</v>
       </c>
       <c r="U5" t="n">
-        <v>2.583333333333333</v>
+        <v>23.8690836940837</v>
       </c>
       <c r="V5" t="n">
-        <v>23.75</v>
+        <v>181.3700487012987</v>
       </c>
       <c r="W5" t="n">
-        <v>182</v>
+        <v>75.6312049062049</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>25923.61111111111</v>
       </c>
       <c r="Y5" t="n">
-        <v>260</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>12535948.5479798</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>81.02594696969696</v>
+      </c>
       <c r="AA5" t="n">
-        <v>4500000</v>
+        <v>1.393614718614719</v>
       </c>
       <c r="AB5" t="n">
-        <v>289</v>
+        <v>27.08825994911521</v>
       </c>
       <c r="AC5" t="n">
-        <v>4</v>
+        <v>178.5726760082023</v>
       </c>
       <c r="AD5" t="n">
-        <v>22.27976190476191</v>
+        <v>74.25448588326877</v>
       </c>
       <c r="AE5" t="n">
-        <v>185.443783068783</v>
+        <v>23266.6507651705</v>
       </c>
       <c r="AF5" t="n">
-        <v>69.23068783068783</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>6790493.931324524</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>76.10922239310396</v>
+      </c>
       <c r="AH5" t="n">
-        <v>3984679.232804233</v>
+        <v>1.404473779144832</v>
       </c>
       <c r="AI5" t="n">
-        <v>77.98518518518519</v>
+        <v>26.38708028083028</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>179.3694368131868</v>
       </c>
       <c r="AK5" t="n">
-        <v>27.44285827020202</v>
+        <v>74.19342555592556</v>
       </c>
       <c r="AL5" t="n">
-        <v>183.1825126262626</v>
+        <v>23353.33333333333</v>
       </c>
       <c r="AM5" t="n">
-        <v>69.2972380050505</v>
+        <v>7961124.228780478</v>
       </c>
       <c r="AN5" t="n">
-        <v>5002.797202797203</v>
+        <v>77.92028688903689</v>
       </c>
       <c r="AO5" t="n">
-        <v>1650427.714646465</v>
+        <v>1.265542096792097</v>
       </c>
       <c r="AP5" t="n">
-        <v>72.08510890151516</v>
+        <v>26.44304029304029</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>173.5783882783882</v>
       </c>
       <c r="AR5" t="n">
-        <v>21.35565476190476</v>
+        <v>2.769230769230769</v>
       </c>
       <c r="AS5" t="n">
-        <v>180.9291294642857</v>
+        <v>206.0769230769231</v>
       </c>
       <c r="AT5" t="n">
-        <v>67.58143601190476</v>
+        <v>68769.23076923077</v>
       </c>
       <c r="AU5" t="n">
-        <v>7713.095238095239</v>
+        <v>18984615.38461538</v>
       </c>
       <c r="AV5" t="n">
-        <v>2881141.183035715</v>
+        <v>211.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>77.26112351190476</v>
+        <v>2.807692307692307</v>
       </c>
       <c r="AX5" t="n">
-        <v>1</v>
+        <v>24.87222222222222</v>
       </c>
       <c r="AY5" t="n">
-        <v>24.46664781297134</v>
+        <v>183.7333333333333</v>
       </c>
       <c r="AZ5" t="n">
-        <v>181.8867184532676</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BA5" t="n">
-        <v>65.20751137913361</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
+        <v>100.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>26300</v>
+      </c>
       <c r="BC5" t="n">
-        <v>1121297.0452395</v>
+        <v>12903333.33333333</v>
       </c>
       <c r="BD5" t="n">
-        <v>71.16623660166407</v>
+        <v>106.6666666666667</v>
       </c>
       <c r="BE5" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
           <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45585.65625</v>
+        <v>45592.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>551</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="P6" t="n">
+        <v>74.5625</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>12468750</v>
+      </c>
+      <c r="S6" t="n">
+        <v>78.8125</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>25.95185728250244</v>
+      </c>
+      <c r="V6" t="n">
+        <v>181.0536412512219</v>
+      </c>
+      <c r="W6" t="n">
+        <v>68.52146464646465</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4427.420759317311</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1664599.625285109</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>71.19937275985663</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>27.99833333333333</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>178.1766666666667</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>78.09</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>44565</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14795000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>79.00500000000001</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.998333333333334</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>23.25781224947892</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>181.5992659468536</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>65.18092949123651</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>1318632.381669662</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>71.70237815709307</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>23.81578947368421</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>176.9385964912281</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>148.8947368421053</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>72277.77777777778</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>21394736.84210526</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>159.421052631579</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3.631578947368421</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>22.88125</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>185.30625</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>182</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>551</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>25.88611111111111</v>
+      </c>
+      <c r="O7" t="n">
+        <v>179.7277777777778</v>
+      </c>
+      <c r="P7" t="n">
+        <v>73.26666666666667</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>16344.13580246914</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6943229.166666666</v>
+      </c>
+      <c r="S7" t="n">
+        <v>77.29583333333332</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.394444444444444</v>
+      </c>
+      <c r="U7" t="n">
+        <v>22.27976190476191</v>
+      </c>
+      <c r="V7" t="n">
+        <v>185.443783068783</v>
+      </c>
+      <c r="W7" t="n">
+        <v>69.23068783068783</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="n">
+        <v>3984679.232804233</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>77.98518518518519</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>23.37037407037407</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>180.179425019425</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>68.70418248418248</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>10680.54672600127</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3142481.573981574</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>76.50067932067932</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.20987234987235</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>21.35565476190476</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>180.9291294642857</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>67.58143601190476</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>7713.095238095239</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2881141.183035715</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>77.26112351190476</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>24.51987179487179</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>178.4583333333333</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>237</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>45230.76923076923</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>11777884.61538462</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>257.4230769230769</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.076923076923077</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>21.92222222222223</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>180.7805555555556</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>179.7083333333333</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>26227.27272727273</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>10943750</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>201.8333333333333</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>24.35276842499065</v>
+      </c>
+      <c r="O8" t="n">
+        <v>185.2675458286569</v>
+      </c>
+      <c r="P8" t="n">
+        <v>75.62391507669284</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>31152.19790497568</v>
+      </c>
+      <c r="R8" t="n">
+        <v>11218195.84736251</v>
+      </c>
+      <c r="S8" t="n">
+        <v>80.22428918817806</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.395089786756453</v>
+      </c>
+      <c r="U8" t="n">
+        <v>23.34166666666667</v>
+      </c>
+      <c r="V8" t="n">
+        <v>179.4185185185185</v>
+      </c>
+      <c r="W8" t="n">
+        <v>74.99907407407407</v>
+      </c>
+      <c r="X8" t="n">
+        <v>40047.97979797979</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>14668333.33333333</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>81.07685185185186</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.396296296296296</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>22.06633113138303</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>180.8820082310999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>72.1787931215267</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>24998.23538149663</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>8089586.457131873</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>78.92985215476565</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.311830240117437</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>20.62352492953997</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>178.8517909547985</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>70.71331801726539</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>16142.85714285714</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>9377380.554561006</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>81.50757885250366</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.106596619754515</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>22.83333333333334</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>177.776</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>194.84</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>75320</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>29104000</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>209.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>23.03166666666667</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>179.5224761904762</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>163160</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>68152000</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>351.64</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>23.24084967320261</v>
+      </c>
+      <c r="O9" t="n">
+        <v>183.1442810457517</v>
+      </c>
+      <c r="P9" t="n">
+        <v>71.11143790849674</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>13266.01307189542</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4596258.169934641</v>
+      </c>
+      <c r="S9" t="n">
+        <v>78.17532679738561</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.241993464052287</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.19537037037037</v>
+      </c>
+      <c r="V9" t="n">
+        <v>182.4864814814815</v>
+      </c>
+      <c r="W9" t="n">
+        <v>73.54574074074074</v>
+      </c>
+      <c r="X9" t="n">
+        <v>22036.11111111111</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6491884.259259259</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>77.39629629629628</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.438518518518519</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>24.24287743506494</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>182.6277236652236</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>70.99804743867244</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>11730.29822029822</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3610565.870761184</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>76.77180510461761</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.305113636363636</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>24.76525106837607</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>182.7132459554335</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>70.30262133699632</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>17424.00793650794</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>4600432.434752747</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>75.50518353174603</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.209149877899878</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>25.60333333333334</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>159.76</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>39440</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8360800</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>168.48</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>24.13066666666667</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>178.336</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>168.76</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>56800</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>15286000</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>174.88</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>25.10069444444444</v>
+      </c>
+      <c r="O10" t="n">
+        <v>182.2638888888889</v>
+      </c>
+      <c r="P10" t="n">
+        <v>77.14583333333333</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>37447.91666666666</v>
+      </c>
+      <c r="R10" t="n">
+        <v>15792968.75</v>
+      </c>
+      <c r="S10" t="n">
+        <v>81.07986111111111</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.180555555555556</v>
+      </c>
+      <c r="U10" t="n">
+        <v>22.71296296296296</v>
+      </c>
+      <c r="V10" t="n">
+        <v>184.574074074074</v>
+      </c>
+      <c r="W10" t="n">
+        <v>81.17592592592592</v>
+      </c>
+      <c r="X10" t="n">
+        <v>85513.88888888889</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>55655555.55555555</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>86.7962962962963</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.074074074074074</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>23.94808080808081</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>182.8925252525253</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>75.01339105339105</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>28849.89898989899</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10478535.35353535</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>80.0346608946609</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.181298701298701</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>23.2547952047952</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>183.9831002331002</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>80.01316183816184</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>84948.40367965367</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>47297179.07092907</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>85.13105228105226</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.011538461538461</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>23.56866666666667</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>183.6266666666667</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>96440</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>38692000</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>312.56</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>25.63735632183908</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>189.7293103448276</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.413793103448276</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>269.5862068965517</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>234827.5862068966</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>110794827.5862069</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>282.1379310344827</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.448275862068965</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>23.34166666666667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>179.4185185185185</v>
+      </c>
+      <c r="P11" t="n">
+        <v>74.99907407407407</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>40047.97979797979</v>
+      </c>
+      <c r="R11" t="n">
+        <v>14668333.33333333</v>
+      </c>
+      <c r="S11" t="n">
+        <v>81.07685185185186</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.396296296296296</v>
+      </c>
+      <c r="U11" t="n">
+        <v>27.35368074686256</v>
+      </c>
+      <c r="V11" t="n">
+        <v>183.1428910315274</v>
+      </c>
+      <c r="W11" t="n">
+        <v>69.23520048974594</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5002.797202797203</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1649846.57177839</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>72.10146923783287</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>20.62352492953997</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>178.8517909547985</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>70.71331801726539</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>16142.85714285714</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>9377380.554561006</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>81.50757885250366</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.106596619754515</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>24.56052298055974</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>181.8599506329845</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>65.24020871261921</v>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>1113707.597401651</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.15948216614777</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>23.03166666666667</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>179.5224761904762</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>163160</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>68152000</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>351.64</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>22.23958333333334</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>181.3229166666667</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>202</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
+        <v>3356250</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>226.75</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>23.8690836940837</v>
+      </c>
+      <c r="O12" t="n">
+        <v>181.3700487012987</v>
+      </c>
+      <c r="P12" t="n">
+        <v>75.6312049062049</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>25923.61111111111</v>
+      </c>
+      <c r="R12" t="n">
+        <v>12535948.5479798</v>
+      </c>
+      <c r="S12" t="n">
+        <v>81.02594696969696</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.393614718614719</v>
+      </c>
+      <c r="U12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="W12" t="n">
+        <v>74.5625</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>12468750</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>78.8125</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>26.38708028083028</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>179.3694368131868</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>74.19342555592556</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>23353.33333333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>7961124.228780478</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>77.92028688903689</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.265542096792097</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>27.99833333333333</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>178.1766666666667</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>78.09</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>44565</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>14795000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>79.00500000000001</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.998333333333334</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>24.87222222222222</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>183.7333333333333</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>26300</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>12903333.33333333</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>106.6666666666667</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>23.81578947368421</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>176.9385964912281</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>148.8947368421053</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>72277.77777777778</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>21394736.84210526</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>159.421052631579</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.631578947368421</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>22.71296296296296</v>
+      </c>
+      <c r="O13" t="n">
+        <v>184.574074074074</v>
+      </c>
+      <c r="P13" t="n">
+        <v>81.17592592592592</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>85513.88888888889</v>
+      </c>
+      <c r="R13" t="n">
+        <v>55655555.55555555</v>
+      </c>
+      <c r="S13" t="n">
+        <v>86.7962962962963</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.074074074074074</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25.71014957264957</v>
+      </c>
+      <c r="V13" t="n">
+        <v>180.3595085470086</v>
+      </c>
+      <c r="W13" t="n">
+        <v>76.8534188034188</v>
+      </c>
+      <c r="X13" t="n">
+        <v>29090.59829059829</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12672617.52136752</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>79.91228632478632</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>23.2547952047952</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>183.9831002331002</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>80.01316183816184</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>84948.40367965367</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>47297179.07092907</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>85.13105228105226</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.011538461538461</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>27.08825994911521</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>178.5726760082023</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>74.25448588326877</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>23266.6507651705</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>6790493.931324524</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>76.10922239310396</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.404473779144832</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>25.63735632183908</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>189.7293103448276</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.413793103448276</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>269.5862068965517</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>234827.5862068966</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>110794827.5862069</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>282.1379310344827</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.448275862068965</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>26.44304029304029</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>173.5783882783882</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.769230769230769</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>206.0769230769231</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>68769.23076923077</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>18984615.38461538</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.807692307692307</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>25.71378066378066</v>
+      </c>
+      <c r="O14" t="n">
+        <v>181.5382756132756</v>
+      </c>
+      <c r="P14" t="n">
+        <v>72.52442279942279</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>15441.08946608947</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3563956.52958153</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75.48510101010102</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.177164502164502</v>
+      </c>
+      <c r="U14" t="n">
+        <v>24.35276842499065</v>
+      </c>
+      <c r="V14" t="n">
+        <v>185.2675458286569</v>
+      </c>
+      <c r="W14" t="n">
+        <v>75.62391507669284</v>
+      </c>
+      <c r="X14" t="n">
+        <v>31152.19790497568</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11218195.84736251</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>80.22428918817806</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.395089786756453</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>24.57324929971989</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>181.8454677871148</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>69.936162464986</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>12559.31465919701</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2691325.536881419</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>74.15611764705882</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.162082166199814</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>22.06633113138303</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>180.8820082310999</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>72.1787931215267</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>24998.23538149663</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>8089586.457131873</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>78.92985215476565</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.311830240117437</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>25.15277777777778</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>182.8148148148148</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>107.8333333333333</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>22277.77777777778</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5216666.666666667</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>113.3888888888889</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>22.83333333333334</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>177.776</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>194.84</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>75320</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>29104000</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>209.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>25.86196524064171</v>
+      </c>
+      <c r="O15" t="n">
+        <v>181.8967245989305</v>
+      </c>
+      <c r="P15" t="n">
+        <v>70.39104278074866</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6351.584022038567</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2207244.318181818</v>
+      </c>
+      <c r="S15" t="n">
+        <v>73.68282085561498</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>23.24084967320261</v>
+      </c>
+      <c r="V15" t="n">
+        <v>183.1442810457517</v>
+      </c>
+      <c r="W15" t="n">
+        <v>71.11143790849674</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13266.01307189542</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4596258.169934641</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>78.17532679738561</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.241993464052287</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>25.00711811837973</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>181.1599812718814</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>68.16729573674233</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>5072.677993756424</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1737015.765935561</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>73.2196026031359</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>24.24287743506494</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>182.6277236652236</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>70.99804743867244</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>11730.29822029822</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>3610565.870761184</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>76.77180510461761</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.305113636363636</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>188.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>16100</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4775000</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>25.60333333333334</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>159.76</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>39440</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>8360800</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>168.48</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>22.27976190476191</v>
+      </c>
+      <c r="O16" t="n">
+        <v>185.443783068783</v>
+      </c>
+      <c r="P16" t="n">
+        <v>69.23068783068783</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>3984679.232804233</v>
+      </c>
+      <c r="S16" t="n">
+        <v>77.98518518518519</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>184.85</v>
+      </c>
+      <c r="W16" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>16593.75</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6512500</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>21.35565476190476</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>180.9291294642857</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>67.58143601190476</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>7713.095238095239</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2881141.183035715</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>77.26112351190476</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>23.17482993197279</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>186.1051587301587</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>69.19631519274375</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>10722.8835978836</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>2894994.33106576</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>75.49625850340136</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>21.92222222222223</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>180.7805555555556</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>179.7083333333333</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>26227.27272727273</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>10943750</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>201.8333333333333</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.583333333333333</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>20.068</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>178.6546666666667</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>15222.22222222222</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4496000</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>25.95185728250244</v>
+      </c>
+      <c r="O17" t="n">
+        <v>181.0536412512219</v>
+      </c>
+      <c r="P17" t="n">
+        <v>68.52146464646465</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4427.420759317311</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1664599.625285109</v>
+      </c>
+      <c r="S17" t="n">
+        <v>71.19937275985663</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>23.37242424242424</v>
+      </c>
+      <c r="V17" t="n">
+        <v>181.5987878787879</v>
+      </c>
+      <c r="W17" t="n">
+        <v>75.25545454545454</v>
+      </c>
+      <c r="X17" t="n">
+        <v>29989.83957219251</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13209121.21212121</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>81.30727272727272</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.47030303030303</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>23.25781224947892</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>181.5992659468536</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>65.18092949123651</v>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="n">
+        <v>1318632.381669662</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>71.70237815709307</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>22.49895995435211</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>182.4739936715427</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>72.54773057371096</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>22019.84126984127</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>9999914.410208531</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>79.69411245979873</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.266109036207076</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>22.88125</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>185.30625</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>182</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7500</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>21.125</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>182.6428571428571</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.392857142857143</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>28642.85714285714</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>13707142.85714286</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.535714285714286</v>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Eyf00syR</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>23.16180555555555</v>
+      </c>
+      <c r="O18" t="n">
+        <v>186.2359722222222</v>
+      </c>
+      <c r="P18" t="n">
+        <v>66.45569444444445</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5116.898148148148</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1767809.027777778</v>
+      </c>
+      <c r="S18" t="n">
+        <v>73.83027777777778</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>25.88611111111111</v>
+      </c>
+      <c r="V18" t="n">
+        <v>179.7277777777778</v>
+      </c>
+      <c r="W18" t="n">
+        <v>73.26666666666667</v>
+      </c>
+      <c r="X18" t="n">
+        <v>16344.13580246914</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6943229.166666666</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>77.29583333333332</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.394444444444444</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24.42377633070772</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>181.3382884294069</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>65.77923752834468</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>4142.176870748299</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1442170.931420814</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>72.32949673290368</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>23.37037407037407</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>180.179425019425</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>68.70418248418248</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>10680.54672600127</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>3142481.573981574</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>76.50067932067932</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.20987234987235</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>23.73611111111111</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>184.7268518518518</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>127.7777777777778</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>13500</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4898611.111111111</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>140.3888888888889</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>24.51987179487179</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>178.4583333333333</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.384615384615385</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>237</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>45230.76923076923</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>11777884.61538462</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>257.4230769230769</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.076923076923077</v>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>SblU3Hee</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H19" t="n">
         <v>55</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I19" t="n">
         <v>551</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K19" t="n">
         <v>20242025</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>24.51987179487179</v>
-      </c>
-      <c r="O6" t="n">
-        <v>178.4583333333333</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.384615384615385</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>237</v>
-      </c>
-      <c r="R6" t="n">
-        <v>45230.76923076923</v>
-      </c>
-      <c r="S6" t="n">
-        <v>11777884.61538462</v>
-      </c>
-      <c r="T6" t="n">
-        <v>257.4230769230769</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4.076923076923077</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="N19" t="n">
+        <v>25.19537037037037</v>
+      </c>
+      <c r="O19" t="n">
+        <v>182.4864814814815</v>
+      </c>
+      <c r="P19" t="n">
+        <v>73.54574074074074</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>22036.11111111111</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6491884.259259259</v>
+      </c>
+      <c r="S19" t="n">
+        <v>77.39629629629628</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.438518518518519</v>
+      </c>
+      <c r="U19" t="n">
+        <v>25.10069444444444</v>
+      </c>
+      <c r="V19" t="n">
+        <v>182.2638888888889</v>
+      </c>
+      <c r="W19" t="n">
+        <v>77.14583333333333</v>
+      </c>
+      <c r="X19" t="n">
+        <v>37447.91666666666</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15792968.75</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>81.07986111111111</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.180555555555556</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>24.76525106837607</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>182.7132459554335</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>70.30262133699632</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>17424.00793650794</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4600432.434752747</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>75.50518353174603</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.209149877899878</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>23.94808080808081</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>182.8925252525253</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>75.01339105339105</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>28849.89898989899</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>10478535.35353535</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>80.0346608946609</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.181298701298701</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>24.13066666666667</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>178.336</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>168.76</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>56800</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>15286000</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>174.88</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AX19" t="n">
         <v>23.56866666666667</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AY19" t="n">
         <v>183.6266666666667</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AZ19" t="n">
         <v>4.08</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="BA19" t="n">
         <v>289.6</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="BB19" t="n">
         <v>96440</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="BC19" t="n">
         <v>38692000</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="BD19" t="n">
         <v>312.56</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="BE19" t="n">
         <v>5.24</v>
       </c>
-      <c r="AD6" t="n">
-        <v>25.88611111111111</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>179.7277777777778</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>73.26666666666667</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16344.13580246914</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>6943229.166666666</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>77.29583333333332</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.394444444444444</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>25.10069444444444</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>182.2638888888889</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>77.14583333333333</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>37447.91666666666</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>15792968.75</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>81.07986111111111</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.180555555555556</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>23.37037407037407</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>180.179425019425</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>68.70418248418248</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>10680.54672600127</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3142481.573981574</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>76.50067932067932</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.20987234987235</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>23.94808080808081</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>182.8925252525253</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>75.01339105339105</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>28849.89898989899</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>10478535.35353535</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>80.0346608946609</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.181298701298701</v>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>lYpTkOLs</t>
+          <t>0ljCkFRb</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.65625</v>
+        <v>45597.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">kherradji a 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29778</v>
+        <v>18523</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +781,176 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>23.29464285714286</v>
       </c>
       <c r="O2" t="n">
-        <v>189</v>
+        <v>179.421626984127</v>
       </c>
       <c r="P2" t="n">
+        <v>74.90079365079364</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39515.27777777777</v>
+      </c>
+      <c r="R2" t="n">
+        <v>14623214.28571429</v>
+      </c>
+      <c r="S2" t="n">
+        <v>81.09126984126985</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.388888888888889</v>
+      </c>
+      <c r="U2" t="n">
+        <v>27.25588460361188</v>
+      </c>
+      <c r="V2" t="n">
+        <v>183.0784970921335</v>
+      </c>
+      <c r="W2" t="n">
+        <v>69.14911233547598</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5002.797202797203</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1645008.417508418</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>72.09837006427915</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>72</v>
-      </c>
-      <c r="R2" t="n">
-        <v>14000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>78</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="AB2" t="n">
+        <v>20.67970117601697</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>178.9777138358717</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>70.69898391812866</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>15412.69841269841</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9421249.582289057</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>81.41629112846218</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.11192645074224</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>24.56479648483325</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>181.8168594648934</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>65.21314318555366</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>1105961.870905925</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>71.17728843395405</v>
+      </c>
+      <c r="AO2" t="n">
         <v>1</v>
       </c>
-      <c r="V2" t="n">
-        <v>23.6421568627451</v>
-      </c>
-      <c r="W2" t="n">
-        <v>184.8088235294118</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.823529411764706</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>123.3529411764706</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13705.88235294118</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4939705.882352941</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>135.8823529411765</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.823529411764706</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>23.38871473354232</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>181.6228840125392</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>75.26426332288401</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>29989.83957219251</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>13195297.80564263</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>81.27304075235108</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.469278996865204</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>23.16180555555555</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>186.2359722222222</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>66.45569444444445</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>5116.898148148148</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1767809.027777778</v>
-      </c>
       <c r="AP2" t="n">
-        <v>73.83027777777778</v>
+        <v>23.01909722222222</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>179.5303571428572</v>
       </c>
       <c r="AR2" t="n">
-        <v>22.47419467787115</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="AS2" t="n">
-        <v>182.3328835380306</v>
+        <v>330.5833333333333</v>
       </c>
       <c r="AT2" t="n">
-        <v>72.55231361775479</v>
+        <v>164791.6666666667</v>
       </c>
       <c r="AU2" t="n">
-        <v>21761.90476190477</v>
+        <v>68554166.66666667</v>
       </c>
       <c r="AV2" t="n">
-        <v>10038922.10730446</v>
+        <v>355.9583333333333</v>
       </c>
       <c r="AW2" t="n">
-        <v>79.74828162034045</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.265354988149106</v>
+        <v>22.41666666666667</v>
       </c>
       <c r="AY2" t="n">
-        <v>24.47187915777097</v>
+        <v>181.5648148148148</v>
       </c>
       <c r="AZ2" t="n">
-        <v>181.3045213341997</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="BA2" t="n">
-        <v>65.8358759553204</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4142.176870748299</v>
-      </c>
+        <v>223.6666666666667</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>1455885.595547511</v>
+        <v>3861111.111111111</v>
       </c>
       <c r="BD2" t="n">
-        <v>72.34170031560382</v>
+        <v>250</v>
       </c>
       <c r="BE2" t="n">
-        <v>1</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p0vxl2jf</t>
+          <t>bqYbtBlo</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45591.5</v>
+        <v>45597.70833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bollengier m 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
+          <t xml:space="preserve">stade pierre mauroy
+  villeneuve d ascq </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>50186</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -980,176 +976,178 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23.83333333333333</v>
+        <v>23.87246539468762</v>
       </c>
       <c r="O3" t="n">
-        <v>183.5</v>
+        <v>181.3137953610176</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>75.65046763935653</v>
       </c>
       <c r="Q3" t="n">
-        <v>397</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>25923.61111111111</v>
+      </c>
+      <c r="R3" t="n">
+        <v>12626168.86457164</v>
+      </c>
       <c r="S3" t="n">
-        <v>7900000</v>
+        <v>81.03102319491208</v>
       </c>
       <c r="T3" t="n">
-        <v>436</v>
+        <v>1.395847362514029</v>
       </c>
       <c r="U3" t="n">
-        <v>6</v>
+        <v>24.5</v>
       </c>
       <c r="V3" t="n">
-        <v>28</v>
+        <v>180.625</v>
       </c>
       <c r="W3" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4</v>
-      </c>
+        <v>74.5625</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>280</v>
+        <v>12468750</v>
       </c>
       <c r="Z3" t="n">
-        <v>21000</v>
+        <v>78.8125</v>
       </c>
       <c r="AA3" t="n">
-        <v>6675000</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>284</v>
+        <v>26.31317848817849</v>
       </c>
       <c r="AC3" t="n">
-        <v>4</v>
+        <v>179.5484765234765</v>
       </c>
       <c r="AD3" t="n">
-        <v>27.34200599747474</v>
+        <v>74.06555515191879</v>
       </c>
       <c r="AE3" t="n">
-        <v>183.1161063762626</v>
+        <v>23014.81481481481</v>
       </c>
       <c r="AF3" t="n">
-        <v>69.2084595959596</v>
+        <v>7551680.976851431</v>
       </c>
       <c r="AG3" t="n">
-        <v>5002.797202797203</v>
+        <v>77.91304024258569</v>
       </c>
       <c r="AH3" t="n">
-        <v>1645438.368055556</v>
+        <v>1.253318651045924</v>
       </c>
       <c r="AI3" t="n">
-        <v>72.08191287878788</v>
+        <v>27.99833333333333</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>178.1766666666667</v>
       </c>
       <c r="AK3" t="n">
-        <v>25.86880165289256</v>
+        <v>78.09</v>
       </c>
       <c r="AL3" t="n">
-        <v>181.888085399449</v>
+        <v>44565</v>
       </c>
       <c r="AM3" t="n">
-        <v>70.40840220385675</v>
+        <v>14795000</v>
       </c>
       <c r="AN3" t="n">
-        <v>6388.139204545454</v>
+        <v>79.00500000000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>2214075.41322314</v>
+        <v>1.998333333333334</v>
       </c>
       <c r="AP3" t="n">
-        <v>73.68698347107438</v>
+        <v>25.07222222222223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>183.6333333333333</v>
       </c>
       <c r="AR3" t="n">
-        <v>24.51939506571859</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AS3" t="n">
-        <v>181.8511873177364</v>
+        <v>100.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>65.19945277107497</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>25833.33333333333</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>12736666.66666667</v>
+      </c>
       <c r="AV3" t="n">
-        <v>1109813.528755984</v>
+        <v>106.4666666666667</v>
       </c>
       <c r="AW3" t="n">
-        <v>71.1735626089901</v>
+        <v>1.866666666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>1</v>
+        <v>23.81578947368421</v>
       </c>
       <c r="AY3" t="n">
-        <v>24.94553443818149</v>
+        <v>176.9385964912281</v>
       </c>
       <c r="AZ3" t="n">
-        <v>181.1295560552913</v>
+        <v>2</v>
       </c>
       <c r="BA3" t="n">
-        <v>68.20656627788981</v>
+        <v>148.8947368421053</v>
       </c>
       <c r="BB3" t="n">
-        <v>5072.677993756424</v>
+        <v>72277.77777777778</v>
       </c>
       <c r="BC3" t="n">
-        <v>1754715.033740769</v>
+        <v>21394736.84210526</v>
       </c>
       <c r="BD3" t="n">
-        <v>73.27959186268011</v>
+        <v>159.421052631579</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>3.631578947368421</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hQspntL6</t>
+          <t>rX720WuH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45591.58333333334</v>
+        <v>45598.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21029</v>
+        <v>48229</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1175,180 +1173,180 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>20.07083333333333</v>
+        <v>22.71296296296296</v>
       </c>
       <c r="O4" t="n">
-        <v>178.8902777777778</v>
+        <v>184.574074074074</v>
       </c>
       <c r="P4" t="n">
-        <v>1.708333333333333</v>
+        <v>81.17592592592592</v>
       </c>
       <c r="Q4" t="n">
-        <v>115.75</v>
+        <v>85513.88888888889</v>
       </c>
       <c r="R4" t="n">
-        <v>15222.22222222222</v>
+        <v>55655555.55555555</v>
       </c>
       <c r="S4" t="n">
-        <v>4308333.333333333</v>
+        <v>86.7962962962963</v>
       </c>
       <c r="T4" t="n">
-        <v>133.6666666666667</v>
+        <v>2.074074074074074</v>
       </c>
       <c r="U4" t="n">
-        <v>1.791666666666667</v>
+        <v>25.69855555555555</v>
       </c>
       <c r="V4" t="n">
-        <v>25.15277777777778</v>
+        <v>180.3138888888889</v>
       </c>
       <c r="W4" t="n">
-        <v>182.8148148148148</v>
+        <v>76.84355555555555</v>
       </c>
       <c r="X4" t="n">
-        <v>1.5</v>
+        <v>29050.22222222222</v>
       </c>
       <c r="Y4" t="n">
-        <v>107.8333333333333</v>
+        <v>12655522.22222222</v>
       </c>
       <c r="Z4" t="n">
-        <v>22277.77777777778</v>
+        <v>79.90477777777778</v>
       </c>
       <c r="AA4" t="n">
-        <v>5216666.666666667</v>
+        <v>1.148</v>
       </c>
       <c r="AB4" t="n">
-        <v>113.3888888888889</v>
+        <v>23.2547952047952</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.777777777777778</v>
+        <v>183.9831002331002</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.25</v>
+        <v>80.01316183816184</v>
       </c>
       <c r="AE4" t="n">
-        <v>184.85</v>
+        <v>84948.40367965367</v>
       </c>
       <c r="AF4" t="n">
-        <v>73.34999999999999</v>
+        <v>47297179.07092907</v>
       </c>
       <c r="AG4" t="n">
-        <v>16593.75</v>
+        <v>85.13105228105226</v>
       </c>
       <c r="AH4" t="n">
-        <v>6512500</v>
+        <v>2.011538461538461</v>
       </c>
       <c r="AI4" t="n">
-        <v>78.15000000000001</v>
+        <v>27.0399234251637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.125</v>
+        <v>178.467140182472</v>
       </c>
       <c r="AK4" t="n">
-        <v>25.7099139543584</v>
+        <v>74.25685483471524</v>
       </c>
       <c r="AL4" t="n">
-        <v>181.5110736999626</v>
+        <v>23365.20079843879</v>
       </c>
       <c r="AM4" t="n">
-        <v>72.51017583239805</v>
+        <v>6827906.710947329</v>
       </c>
       <c r="AN4" t="n">
-        <v>15430.49008604564</v>
+        <v>76.15744945367371</v>
       </c>
       <c r="AO4" t="n">
-        <v>3558244.481855593</v>
+        <v>1.404668291281564</v>
       </c>
       <c r="AP4" t="n">
-        <v>75.47949869060982</v>
+        <v>25.65987654320988</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.17699214365881</v>
+        <v>189.8358024691358</v>
       </c>
       <c r="AR4" t="n">
-        <v>23.17482993197279</v>
+        <v>3.407407407407407</v>
       </c>
       <c r="AS4" t="n">
-        <v>186.1051587301587</v>
+        <v>268.9259259259259</v>
       </c>
       <c r="AT4" t="n">
-        <v>69.19631519274375</v>
+        <v>234703.7037037037</v>
       </c>
       <c r="AU4" t="n">
-        <v>10722.8835978836</v>
+        <v>110846296.2962963</v>
       </c>
       <c r="AV4" t="n">
-        <v>2894994.33106576</v>
+        <v>281.4444444444445</v>
       </c>
       <c r="AW4" t="n">
-        <v>75.49625850340136</v>
+        <v>7.444444444444445</v>
       </c>
       <c r="AX4" t="n">
-        <v>1</v>
+        <v>26.4607619047619</v>
       </c>
       <c r="AY4" t="n">
-        <v>24.59118230625583</v>
+        <v>173.6415238095238</v>
       </c>
       <c r="AZ4" t="n">
-        <v>181.8568860877685</v>
+        <v>2.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>69.97516923436041</v>
+        <v>208.52</v>
       </c>
       <c r="BB4" t="n">
-        <v>12612.38134142546</v>
+        <v>69920</v>
       </c>
       <c r="BC4" t="n">
-        <v>2703017.672346717</v>
+        <v>19484000</v>
       </c>
       <c r="BD4" t="n">
-        <v>74.15667016806722</v>
+        <v>213.96</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.162883208839091</v>
+        <v>2.84</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vaZNtoqR</t>
+          <t>n5Eg2hB4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45591.66666666666</v>
+        <v>45598.625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade bollaert delelis
-  lens </t>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38223</v>
+        <v>15220</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1374,180 +1372,180 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>26.4607619047619</v>
+        <v>25.7099139543584</v>
       </c>
       <c r="O5" t="n">
-        <v>173.6415238095238</v>
+        <v>181.5110736999626</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>72.51017583239805</v>
       </c>
       <c r="Q5" t="n">
-        <v>208.52</v>
+        <v>15430.49008604564</v>
       </c>
       <c r="R5" t="n">
-        <v>69920</v>
+        <v>3558244.481855593</v>
       </c>
       <c r="S5" t="n">
-        <v>19484000</v>
+        <v>75.47949869060982</v>
       </c>
       <c r="T5" t="n">
-        <v>213.96</v>
+        <v>1.17699214365881</v>
       </c>
       <c r="U5" t="n">
-        <v>2.84</v>
+        <v>24.35276842499065</v>
       </c>
       <c r="V5" t="n">
-        <v>28</v>
+        <v>185.2675458286569</v>
       </c>
       <c r="W5" t="n">
-        <v>187</v>
+        <v>75.62391507669284</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>31152.19790497568</v>
       </c>
       <c r="Y5" t="n">
-        <v>75</v>
+        <v>11218195.84736251</v>
       </c>
       <c r="Z5" t="n">
-        <v>9000</v>
+        <v>80.22428918817806</v>
       </c>
       <c r="AA5" t="n">
-        <v>5500000</v>
+        <v>1.395089786756453</v>
       </c>
       <c r="AB5" t="n">
-        <v>76</v>
+        <v>24.59118230625583</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>181.8568860877685</v>
       </c>
       <c r="AD5" t="n">
-        <v>25.69855555555555</v>
+        <v>69.97516923436041</v>
       </c>
       <c r="AE5" t="n">
-        <v>180.3138888888889</v>
+        <v>12612.38134142546</v>
       </c>
       <c r="AF5" t="n">
-        <v>76.84355555555555</v>
+        <v>2703017.672346717</v>
       </c>
       <c r="AG5" t="n">
-        <v>29050.22222222222</v>
+        <v>74.15667016806722</v>
       </c>
       <c r="AH5" t="n">
-        <v>12655522.22222222</v>
+        <v>1.162883208839091</v>
       </c>
       <c r="AI5" t="n">
-        <v>79.90477777777778</v>
+        <v>22.06633113138303</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.148</v>
+        <v>180.8820082310999</v>
       </c>
       <c r="AK5" t="n">
-        <v>23.87246539468762</v>
+        <v>72.1787931215267</v>
       </c>
       <c r="AL5" t="n">
-        <v>181.3137953610176</v>
+        <v>24998.23538149663</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.65046763935653</v>
+        <v>8089586.457131873</v>
       </c>
       <c r="AN5" t="n">
-        <v>25923.61111111111</v>
+        <v>78.92985215476565</v>
       </c>
       <c r="AO5" t="n">
-        <v>12626168.86457164</v>
+        <v>1.311830240117437</v>
       </c>
       <c r="AP5" t="n">
-        <v>81.03102319491208</v>
+        <v>25.15277777777778</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.395847362514029</v>
+        <v>182.8148148148148</v>
       </c>
       <c r="AR5" t="n">
-        <v>27.0399234251637</v>
+        <v>1.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>178.467140182472</v>
+        <v>107.8333333333333</v>
       </c>
       <c r="AT5" t="n">
-        <v>74.25685483471524</v>
+        <v>22277.77777777778</v>
       </c>
       <c r="AU5" t="n">
-        <v>23365.20079843879</v>
+        <v>5216666.666666667</v>
       </c>
       <c r="AV5" t="n">
-        <v>6827906.710947329</v>
+        <v>113.3888888888889</v>
       </c>
       <c r="AW5" t="n">
-        <v>76.15744945367371</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.404668291281564</v>
+        <v>22.83333333333334</v>
       </c>
       <c r="AY5" t="n">
-        <v>26.31317848817849</v>
+        <v>177.776</v>
       </c>
       <c r="AZ5" t="n">
-        <v>179.5484765234765</v>
+        <v>2.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>74.06555515191879</v>
+        <v>194.84</v>
       </c>
       <c r="BB5" t="n">
-        <v>23014.81481481481</v>
+        <v>75320</v>
       </c>
       <c r="BC5" t="n">
-        <v>7551680.976851431</v>
+        <v>29104000</v>
       </c>
       <c r="BD5" t="n">
-        <v>77.91304024258569</v>
+        <v>209.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.253318651045924</v>
+        <v>3.36</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>vuBo4Eth</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45598.70833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59186</v>
+        <v>42000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1573,176 +1571,180 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>23.81578947368421</v>
+        <v>25.87606534090909</v>
       </c>
       <c r="O6" t="n">
-        <v>176.9385964912281</v>
+        <v>181.87890625</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>70.42684659090909</v>
       </c>
       <c r="Q6" t="n">
-        <v>148.8947368421053</v>
+        <v>6427.052785923754</v>
       </c>
       <c r="R6" t="n">
-        <v>72277.77777777778</v>
+        <v>2221333.451704545</v>
       </c>
       <c r="S6" t="n">
-        <v>21394736.84210526</v>
+        <v>73.69140625</v>
       </c>
       <c r="T6" t="n">
-        <v>159.421052631579</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>3.631578947368421</v>
+        <v>23.25590277777778</v>
       </c>
       <c r="V6" t="n">
-        <v>24</v>
+        <v>182.9970486111112</v>
       </c>
       <c r="W6" t="n">
-        <v>187</v>
+        <v>71.08715277777779</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>13196.70138888889</v>
       </c>
       <c r="Y6" t="n">
-        <v>138</v>
+        <v>4563993.055555556</v>
       </c>
       <c r="Z6" t="n">
-        <v>8000</v>
+        <v>78.15503472222221</v>
       </c>
       <c r="AA6" t="n">
-        <v>4800000</v>
+        <v>1.241493055555555</v>
       </c>
       <c r="AB6" t="n">
-        <v>152</v>
+        <v>24.89512688777394</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>181.1851116108469</v>
       </c>
       <c r="AD6" t="n">
-        <v>24.5</v>
+        <v>68.22415529547884</v>
       </c>
       <c r="AE6" t="n">
-        <v>180.625</v>
+        <v>5069.97879571409</v>
       </c>
       <c r="AF6" t="n">
-        <v>74.5625</v>
-      </c>
-      <c r="AG6" t="inlineStr"/>
+        <v>1769547.723573459</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>73.32184840493665</v>
+      </c>
       <c r="AH6" t="n">
-        <v>12468750</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>78.8125</v>
+        <v>23.9500202922078</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.75</v>
+        <v>182.7759379509379</v>
       </c>
       <c r="AK6" t="n">
-        <v>25.94116161616162</v>
+        <v>70.70697601010102</v>
       </c>
       <c r="AL6" t="n">
-        <v>181.0887626262626</v>
+        <v>10760.77441077441</v>
       </c>
       <c r="AM6" t="n">
-        <v>68.51157407407409</v>
+        <v>3498735.513618326</v>
       </c>
       <c r="AN6" t="n">
-        <v>4361.516955266956</v>
+        <v>76.91644796176045</v>
       </c>
       <c r="AO6" t="n">
-        <v>1667055.976430976</v>
+        <v>1.278327922077922</v>
       </c>
       <c r="AP6" t="n">
-        <v>71.21510942760943</v>
+        <v>26.68181818181818</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>178.5681818181818</v>
       </c>
       <c r="AR6" t="n">
-        <v>27.99833333333333</v>
+        <v>2.818181818181818</v>
       </c>
       <c r="AS6" t="n">
-        <v>178.1766666666667</v>
+        <v>196.9090909090909</v>
       </c>
       <c r="AT6" t="n">
-        <v>78.09</v>
+        <v>16545.45454545454</v>
       </c>
       <c r="AU6" t="n">
-        <v>44565</v>
+        <v>4947727.272727272</v>
       </c>
       <c r="AV6" t="n">
-        <v>14795000</v>
+        <v>200.9090909090909</v>
       </c>
       <c r="AW6" t="n">
-        <v>79.00500000000001</v>
+        <v>2.818181818181818</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.998333333333334</v>
+        <v>25.48263888888889</v>
       </c>
       <c r="AY6" t="n">
-        <v>23.25701504844362</v>
+        <v>184.34375</v>
       </c>
       <c r="AZ6" t="n">
-        <v>181.5061837494168</v>
+        <v>2.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>65.14528257874122</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
+        <v>160.875</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>40708.33333333334</v>
+      </c>
       <c r="BC6" t="n">
-        <v>1309572.898696959</v>
+        <v>8658750</v>
       </c>
       <c r="BD6" t="n">
-        <v>71.67346651260185</v>
+        <v>169.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1</v>
+        <v>3.791666666666667</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>4Md3iycn</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45599.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20484</v>
+        <v>33150</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1768,178 +1770,178 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24.38066666666667</v>
+        <v>22.25</v>
       </c>
       <c r="O7" t="n">
-        <v>178.4566666666666</v>
+        <v>185.5097222222222</v>
       </c>
       <c r="P7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>240.6</v>
-      </c>
+        <v>69.21722222222222</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>46000</v>
+        <v>4004538.194444445</v>
       </c>
       <c r="S7" t="n">
-        <v>11957000</v>
+        <v>78.02819444444444</v>
       </c>
       <c r="T7" t="n">
-        <v>261.64</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>4.08</v>
+        <v>25.25</v>
       </c>
       <c r="V7" t="n">
+        <v>184.85</v>
+      </c>
+      <c r="W7" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>16593.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6512500</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>21.35714285714286</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>180.8799603174603</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>67.58686507936507</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>7713.095238095239</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2859606.150793651</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>77.20075396825396</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>23.17482993197279</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>186.1051587301587</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>69.19631519274375</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>10722.8835978836</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2894994.33106576</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>75.49625850340136</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
         <v>21.93333333333333</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AQ7" t="n">
         <v>180.9159420289855</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AR7" t="n">
         <v>2.565217391304348</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AS7" t="n">
         <v>178.5217391304348</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AT7" t="n">
         <v>26190.47619047619</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AU7" t="n">
         <v>10876086.95652174</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AV7" t="n">
         <v>200.4782608695652</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AW7" t="n">
         <v>2.565217391304348</v>
       </c>
-      <c r="AD7" t="n">
-        <v>25.93518518518518</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>179.6234567901235</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>73.28395061728395</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>16456.59722222222</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>6948958.333333333</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>77.26697530864197</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.401234567901235</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>185.5097222222222</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>69.21722222222222</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>4004538.194444445</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>78.02819444444444</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>23.35601303458446</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>180.0697921126493</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>68.73407306978734</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>10680.54672600127</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3195515.972123115</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>76.51603396603397</v>
-      </c>
       <c r="AX7" t="n">
-        <v>1.204455068740783</v>
+        <v>20.07083333333333</v>
       </c>
       <c r="AY7" t="n">
-        <v>21.35714285714286</v>
+        <v>178.8902777777778</v>
       </c>
       <c r="AZ7" t="n">
-        <v>180.8799603174603</v>
+        <v>1.708333333333333</v>
       </c>
       <c r="BA7" t="n">
-        <v>67.58686507936507</v>
+        <v>115.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>7713.095238095239</v>
+        <v>15222.22222222222</v>
       </c>
       <c r="BC7" t="n">
-        <v>2859606.150793651</v>
+        <v>4308333.333333333</v>
       </c>
       <c r="BD7" t="n">
-        <v>77.20075396825396</v>
+        <v>133.6666666666667</v>
       </c>
       <c r="BE7" t="n">
-        <v>1</v>
+        <v>1.791666666666667</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>EuWhpKkJ</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45599.54166666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>36178</v>
+        <v>17924</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1965,180 +1967,178 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>22.83333333333334</v>
+        <v>25.91483382209189</v>
       </c>
       <c r="O8" t="n">
-        <v>177.776</v>
+        <v>181.1181573802541</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>68.45071684587815</v>
       </c>
       <c r="Q8" t="n">
-        <v>194.84</v>
+        <v>4361.516955266956</v>
       </c>
       <c r="R8" t="n">
-        <v>75320</v>
+        <v>1657231.590094493</v>
       </c>
       <c r="S8" t="n">
-        <v>29104000</v>
+        <v>71.21220267188009</v>
       </c>
       <c r="T8" t="n">
-        <v>209.2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>3.36</v>
+        <v>23.38871473354232</v>
       </c>
       <c r="V8" t="n">
-        <v>23.01909722222222</v>
+        <v>181.6228840125392</v>
       </c>
       <c r="W8" t="n">
-        <v>179.5303571428572</v>
+        <v>75.26426332288401</v>
       </c>
       <c r="X8" t="n">
-        <v>4.333333333333333</v>
+        <v>29989.83957219251</v>
       </c>
       <c r="Y8" t="n">
-        <v>330.5833333333333</v>
+        <v>13195297.80564263</v>
       </c>
       <c r="Z8" t="n">
-        <v>164791.6666666667</v>
+        <v>81.27304075235108</v>
       </c>
       <c r="AA8" t="n">
-        <v>68554166.66666667</v>
+        <v>1.469278996865204</v>
       </c>
       <c r="AB8" t="n">
-        <v>355.9583333333333</v>
+        <v>23.29812135557749</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.833333333333333</v>
+        <v>181.4862751364944</v>
       </c>
       <c r="AD8" t="n">
-        <v>24.35276842499065</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>185.2675458286569</v>
-      </c>
+        <v>65.19972648371771</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>75.62391507669284</v>
+        <v>1313766.049171751</v>
       </c>
       <c r="AG8" t="n">
-        <v>31152.19790497568</v>
+        <v>71.66937899251495</v>
       </c>
       <c r="AH8" t="n">
-        <v>11218195.84736251</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>80.22428918817806</v>
+        <v>22.47419467787115</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.395089786756453</v>
+        <v>182.3328835380306</v>
       </c>
       <c r="AK8" t="n">
-        <v>23.29464285714286</v>
+        <v>72.55231361775479</v>
       </c>
       <c r="AL8" t="n">
-        <v>179.421626984127</v>
+        <v>21761.90476190477</v>
       </c>
       <c r="AM8" t="n">
-        <v>74.90079365079364</v>
+        <v>10038922.10730446</v>
       </c>
       <c r="AN8" t="n">
-        <v>39515.27777777777</v>
+        <v>79.74828162034045</v>
       </c>
       <c r="AO8" t="n">
-        <v>14623214.28571429</v>
+        <v>1.265354988149106</v>
       </c>
       <c r="AP8" t="n">
-        <v>81.09126984126985</v>
+        <v>23.00555555555556</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.388888888888889</v>
+        <v>185.3833333333333</v>
       </c>
       <c r="AR8" t="n">
-        <v>22.06633113138303</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="AS8" t="n">
-        <v>180.8820082310999</v>
+        <v>183.7777777777778</v>
       </c>
       <c r="AT8" t="n">
-        <v>72.1787931215267</v>
+        <v>8000</v>
       </c>
       <c r="AU8" t="n">
-        <v>24998.23538149663</v>
+        <v>4233333.333333333</v>
       </c>
       <c r="AV8" t="n">
-        <v>8089586.457131873</v>
+        <v>205.2222222222222</v>
       </c>
       <c r="AW8" t="n">
-        <v>78.92985215476565</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.311830240117437</v>
+        <v>21.08928571428572</v>
       </c>
       <c r="AY8" t="n">
-        <v>20.67970117601697</v>
+        <v>182.6071428571429</v>
       </c>
       <c r="AZ8" t="n">
-        <v>178.9777138358717</v>
+        <v>1.392857142857143</v>
       </c>
       <c r="BA8" t="n">
-        <v>70.69898391812866</v>
+        <v>102.5357142857143</v>
       </c>
       <c r="BB8" t="n">
-        <v>15412.69841269841</v>
+        <v>29107.14285714286</v>
       </c>
       <c r="BC8" t="n">
-        <v>9421249.582289057</v>
+        <v>13760714.28571429</v>
       </c>
       <c r="BD8" t="n">
-        <v>81.41629112846218</v>
+        <v>112.2857142857143</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.11192645074224</v>
+        <v>1.535714285714286</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>Y1lKmgdB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45599.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
+          <t xml:space="preserve">frappart s 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26109</v>
+        <v>25178</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2164,344 +2164,2125 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>25.48263888888889</v>
+        <v>23.16180555555555</v>
       </c>
       <c r="O9" t="n">
-        <v>184.34375</v>
+        <v>186.2359722222222</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>66.45569444444445</v>
       </c>
       <c r="Q9" t="n">
-        <v>160.875</v>
+        <v>5116.898148148148</v>
       </c>
       <c r="R9" t="n">
-        <v>40708.33333333334</v>
+        <v>1767809.027777778</v>
       </c>
       <c r="S9" t="n">
-        <v>8658750</v>
+        <v>73.83027777777778</v>
       </c>
       <c r="T9" t="n">
-        <v>169.25</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>3.791666666666667</v>
+        <v>25.99652777777778</v>
       </c>
       <c r="V9" t="n">
-        <v>24.05277777777778</v>
+        <v>179.4930555555556</v>
       </c>
       <c r="W9" t="n">
-        <v>178.1833333333333</v>
+        <v>73.30555555555556</v>
       </c>
       <c r="X9" t="n">
-        <v>2.375</v>
+        <v>16601.19047619048</v>
       </c>
       <c r="Y9" t="n">
-        <v>172.75</v>
+        <v>6956119.791666666</v>
       </c>
       <c r="Z9" t="n">
-        <v>58375</v>
+        <v>77.23090277777777</v>
       </c>
       <c r="AA9" t="n">
-        <v>15785416.66666667</v>
+        <v>1.409722222222222</v>
       </c>
       <c r="AB9" t="n">
-        <v>179.0833333333333</v>
+        <v>24.47187915777097</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.875</v>
+        <v>181.3045213341997</v>
       </c>
       <c r="AD9" t="n">
-        <v>23.25590277777778</v>
+        <v>65.8358759553204</v>
       </c>
       <c r="AE9" t="n">
-        <v>182.9970486111112</v>
+        <v>4142.176870748299</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.08715277777779</v>
+        <v>1455885.595547511</v>
       </c>
       <c r="AG9" t="n">
-        <v>13196.70138888889</v>
+        <v>72.34170031560382</v>
       </c>
       <c r="AH9" t="n">
-        <v>4563993.055555556</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.15503472222221</v>
+        <v>23.33944260867338</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.241493055555555</v>
+        <v>179.943292604831</v>
       </c>
       <c r="AK9" t="n">
-        <v>25.24503968253968</v>
+        <v>68.76856220702373</v>
       </c>
       <c r="AL9" t="n">
-        <v>182.6498015873016</v>
+        <v>10680.54672600127</v>
       </c>
       <c r="AM9" t="n">
-        <v>73.56329365079364</v>
+        <v>3256709.508440278</v>
       </c>
       <c r="AN9" t="n">
-        <v>22473.45679012346</v>
+        <v>76.5337508645201</v>
       </c>
       <c r="AO9" t="n">
-        <v>6532018.84920635</v>
+        <v>1.198204359742821</v>
       </c>
       <c r="AP9" t="n">
-        <v>77.37460317460318</v>
+        <v>23.6421568627451</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.441269841269841</v>
+        <v>184.8088235294118</v>
       </c>
       <c r="AR9" t="n">
-        <v>24.04002164502165</v>
+        <v>1.823529411764706</v>
       </c>
       <c r="AS9" t="n">
-        <v>182.7076671476671</v>
+        <v>123.3529411764706</v>
       </c>
       <c r="AT9" t="n">
-        <v>70.80744107744108</v>
+        <v>13705.88235294118</v>
       </c>
       <c r="AU9" t="n">
-        <v>11272.2582972583</v>
+        <v>4939705.882352941</v>
       </c>
       <c r="AV9" t="n">
-        <v>3550317.881192881</v>
+        <v>135.8823529411765</v>
       </c>
       <c r="AW9" t="n">
-        <v>76.87087782587783</v>
+        <v>1.823529411764706</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.296883116883117</v>
+        <v>24.39652777777778</v>
       </c>
       <c r="AY9" t="n">
-        <v>24.74055183946488</v>
+        <v>178.8090277777777</v>
       </c>
       <c r="AZ9" t="n">
-        <v>182.6500537505972</v>
+        <v>3.541666666666667</v>
       </c>
       <c r="BA9" t="n">
-        <v>70.24331501831502</v>
+        <v>247.5833333333333</v>
       </c>
       <c r="BB9" t="n">
-        <v>17189.82683982684</v>
+        <v>48636.36363636364</v>
       </c>
       <c r="BC9" t="n">
-        <v>4655523.700031852</v>
+        <v>12263541.66666667</v>
       </c>
       <c r="BD9" t="n">
-        <v>75.51265527950309</v>
+        <v>269.2916666666667</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.210996974040452</v>
+        <v>4.208333333333333</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>UTsToXQN</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45592.69791666666</v>
+        <v>45599.69791666666</v>
       </c>
       <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>55</v>
+      </c>
+      <c r="I10" t="n">
+        <v>551</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>25.24503968253968</v>
+      </c>
+      <c r="O10" t="n">
+        <v>182.6498015873016</v>
+      </c>
+      <c r="P10" t="n">
+        <v>73.56329365079364</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22473.45679012346</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6532018.84920635</v>
+      </c>
+      <c r="S10" t="n">
+        <v>77.37460317460318</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.441269841269841</v>
+      </c>
+      <c r="U10" t="n">
+        <v>25.10069444444444</v>
+      </c>
+      <c r="V10" t="n">
+        <v>182.2638888888889</v>
+      </c>
+      <c r="W10" t="n">
+        <v>77.14583333333333</v>
+      </c>
+      <c r="X10" t="n">
+        <v>37447.91666666666</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15792968.75</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>81.07986111111111</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.180555555555556</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24.74055183946488</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>182.6500537505972</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>70.24331501831502</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>17189.82683982684</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>4655523.700031852</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>75.51265527950309</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.210996974040452</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>23.94808080808081</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>182.8925252525253</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>75.01339105339105</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>28849.89898989899</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>10478535.35353535</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>80.0346608946609</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.181298701298701</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>24.05277777777778</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>178.1833333333333</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>58375</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>15785416.66666667</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>179.0833333333333</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>23.56866666666667</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>183.6266666666667</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>96440</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>38692000</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>312.56</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Gp6AbAAT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>25.10069444444444</v>
+      </c>
+      <c r="O11" t="n">
+        <v>182.2638888888889</v>
+      </c>
+      <c r="P11" t="n">
+        <v>77.14583333333333</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>37447.91666666666</v>
+      </c>
+      <c r="R11" t="n">
+        <v>15792968.75</v>
+      </c>
+      <c r="S11" t="n">
+        <v>81.07986111111111</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.180555555555556</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.91483382209189</v>
+      </c>
+      <c r="V11" t="n">
+        <v>181.1181573802541</v>
+      </c>
+      <c r="W11" t="n">
+        <v>68.45071684587815</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4361.516955266956</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1657231.590094493</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>71.21220267188009</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>23.94808080808081</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>182.8925252525253</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>75.01339105339105</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>28849.89898989899</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>10478535.35353535</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>80.0346608946609</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.181298701298701</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>23.29812135557749</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>181.4862751364944</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>65.19972648371771</v>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>1313766.049171751</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.66937899251495</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>23.56866666666667</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>183.6266666666667</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>96440</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>38692000</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>312.56</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>23.00555555555556</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>185.3833333333333</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4233333.333333333</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>205.2222222222222</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45605.54166666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>23.25590277777778</v>
+      </c>
+      <c r="O12" t="n">
+        <v>182.9970486111112</v>
+      </c>
+      <c r="P12" t="n">
+        <v>71.08715277777779</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>13196.70138888889</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4563993.055555556</v>
+      </c>
+      <c r="S12" t="n">
+        <v>78.15503472222221</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.241493055555555</v>
+      </c>
+      <c r="U12" t="n">
+        <v>23.29464285714286</v>
+      </c>
+      <c r="V12" t="n">
+        <v>179.421626984127</v>
+      </c>
+      <c r="W12" t="n">
+        <v>74.90079365079364</v>
+      </c>
+      <c r="X12" t="n">
+        <v>39515.27777777777</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>14623214.28571429</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>81.09126984126985</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.388888888888889</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>23.9500202922078</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>182.7759379509379</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>70.70697601010102</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>10760.77441077441</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3498735.513618326</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>76.91644796176045</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.278327922077922</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>20.67970117601697</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>178.9777138358717</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>70.69898391812866</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>15412.69841269841</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>9421249.582289057</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>81.41629112846218</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.11192645074224</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>25.48263888888889</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>184.34375</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>160.875</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>40708.33333333334</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8658750</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>169.25</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.791666666666667</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>23.01909722222222</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>179.5303571428572</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>330.5833333333333</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>164791.6666666667</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>68554166.66666667</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>355.9583333333333</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bJl87mmp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>25.69855555555555</v>
+      </c>
+      <c r="O13" t="n">
+        <v>180.3138888888889</v>
+      </c>
+      <c r="P13" t="n">
+        <v>76.84355555555555</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>29050.22222222222</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12655522.22222222</v>
+      </c>
+      <c r="S13" t="n">
+        <v>79.90477777777778</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25.24503968253968</v>
+      </c>
+      <c r="V13" t="n">
+        <v>182.6498015873016</v>
+      </c>
+      <c r="W13" t="n">
+        <v>73.56329365079364</v>
+      </c>
+      <c r="X13" t="n">
+        <v>22473.45679012346</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6532018.84920635</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>77.37460317460318</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.441269841269841</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>27.0399234251637</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>178.467140182472</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>74.25685483471524</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>23365.20079843879</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>6827906.710947329</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>76.15744945367371</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.404668291281564</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>24.74055183946488</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>182.6500537505972</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>70.24331501831502</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>17189.82683982684</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4655523.700031852</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>75.51265527950309</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.210996974040452</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>26.4607619047619</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>173.6415238095238</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>208.52</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>69920</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>19484000</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>213.96</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>24.05277777777778</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>178.1833333333333</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>58375</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>15785416.66666667</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>179.0833333333333</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dYK8BH5F</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>CjhkPw0k</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H14" t="n">
         <v>55</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I14" t="n">
         <v>551</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K14" t="n">
         <v>20242025</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>23.56866666666667</v>
-      </c>
-      <c r="O10" t="n">
-        <v>183.6266666666667</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>289.6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>96440</v>
-      </c>
-      <c r="S10" t="n">
-        <v>38692000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>312.56</v>
-      </c>
-      <c r="U10" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="V10" t="n">
-        <v>25.67202380952381</v>
-      </c>
-      <c r="W10" t="n">
-        <v>189.7791666666666</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.428571428571428</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>270.7142857142857</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>236214.2857142857</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>111194642.8571429</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>283.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>25.10069444444444</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>182.2638888888889</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>77.14583333333333</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>37447.91666666666</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>15792968.75</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>81.07986111111111</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.180555555555556</v>
-      </c>
-      <c r="AK10" t="n">
+      <c r="N14" t="n">
+        <v>27.25588460361188</v>
+      </c>
+      <c r="O14" t="n">
+        <v>183.0784970921335</v>
+      </c>
+      <c r="P14" t="n">
+        <v>69.14911233547598</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5002.797202797203</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1645008.417508418</v>
+      </c>
+      <c r="S14" t="n">
+        <v>72.09837006427915</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
         <v>22.71296296296296</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="V14" t="n">
         <v>184.574074074074</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="W14" t="n">
         <v>81.17592592592592</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="X14" t="n">
         <v>85513.88888888889</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="Y14" t="n">
         <v>55655555.55555555</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="Z14" t="n">
         <v>86.7962962962963</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AA14" t="n">
         <v>2.074074074074074</v>
       </c>
-      <c r="AR10" t="n">
-        <v>23.94808080808081</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>182.8925252525253</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>75.01339105339105</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>28849.89898989899</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10478535.35353535</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>80.0346608946609</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.181298701298701</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="AB14" t="n">
+        <v>24.56479648483325</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>181.8168594648934</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>65.21314318555366</v>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>1105961.870905925</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>71.17728843395405</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
         <v>23.2547952047952</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="AJ14" t="n">
         <v>183.9831002331002</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="AK14" t="n">
         <v>80.01316183816184</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="AL14" t="n">
         <v>84948.40367965367</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="AM14" t="n">
         <v>47297179.07092907</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="AN14" t="n">
         <v>85.13105228105226</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="AO14" t="n">
         <v>2.011538461538461</v>
       </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
+      <c r="AP14" t="n">
+        <v>22.41666666666667</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>181.5648148148148</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.444444444444445</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>223.6666666666667</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>3861111.111111111</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>250</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3.444444444444445</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>25.65987654320988</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>189.8358024691358</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.407407407407407</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>268.9259259259259</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>234703.7037037037</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>110846296.2962963</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>281.4444444444445</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.444444444444445</v>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>l8H0Dwy3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>551</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>24.35276842499065</v>
+      </c>
+      <c r="O15" t="n">
+        <v>185.2675458286569</v>
+      </c>
+      <c r="P15" t="n">
+        <v>75.62391507669284</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>31152.19790497568</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11218195.84736251</v>
+      </c>
+      <c r="S15" t="n">
+        <v>80.22428918817806</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.395089786756453</v>
+      </c>
+      <c r="U15" t="n">
+        <v>23.87246539468762</v>
+      </c>
+      <c r="V15" t="n">
+        <v>181.3137953610176</v>
+      </c>
+      <c r="W15" t="n">
+        <v>75.65046763935653</v>
+      </c>
+      <c r="X15" t="n">
+        <v>25923.61111111111</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12626168.86457164</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>81.03102319491208</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.395847362514029</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>22.06633113138303</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>180.8820082310999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>72.1787931215267</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>24998.23538149663</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>8089586.457131873</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>78.92985215476565</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.311830240117437</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>26.31317848817849</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>179.5484765234765</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>74.06555515191879</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>23014.81481481481</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>7551680.976851431</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>77.91304024258569</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.253318651045924</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>22.83333333333334</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>177.776</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>194.84</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>75320</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>29104000</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>209.2</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>25.07222222222223</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>183.6333333333333</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>25833.33333333333</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>12736666.66666667</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>106.4666666666667</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.866666666666667</v>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>nRkUEVfA</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45606.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>551</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>23.16180555555555</v>
+      </c>
+      <c r="O16" t="n">
+        <v>186.2359722222222</v>
+      </c>
+      <c r="P16" t="n">
+        <v>66.45569444444445</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5116.898148148148</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1767809.027777778</v>
+      </c>
+      <c r="S16" t="n">
+        <v>73.83027777777778</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>184.85</v>
+      </c>
+      <c r="W16" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>16593.75</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6512500</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>24.47187915777097</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>181.3045213341997</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>65.8358759553204</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>4142.176870748299</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1455885.595547511</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>72.34170031560382</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>23.17482993197279</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>186.1051587301587</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>69.19631519274375</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>10722.8835978836</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>2894994.33106576</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>75.49625850340136</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>23.6421568627451</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>184.8088235294118</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.823529411764706</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>123.3529411764706</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>13705.88235294118</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4939705.882352941</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>135.8823529411765</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.823529411764706</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>20.07083333333333</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>178.8902777777778</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.708333333333333</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>15222.22222222222</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4308333.333333333</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>133.6666666666667</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.791666666666667</v>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QB1LGiQc</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45606.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>25.99652777777778</v>
+      </c>
+      <c r="O17" t="n">
+        <v>179.4930555555556</v>
+      </c>
+      <c r="P17" t="n">
+        <v>73.30555555555556</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>16601.19047619048</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6956119.791666666</v>
+      </c>
+      <c r="S17" t="n">
+        <v>77.23090277777777</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.409722222222222</v>
+      </c>
+      <c r="U17" t="n">
+        <v>25.7099139543584</v>
+      </c>
+      <c r="V17" t="n">
+        <v>181.5110736999626</v>
+      </c>
+      <c r="W17" t="n">
+        <v>72.51017583239805</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15430.49008604564</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3558244.481855593</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>75.47949869060982</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.17699214365881</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>23.33944260867338</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>179.943292604831</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>68.76856220702373</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>10680.54672600127</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3256709.508440278</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>76.5337508645201</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.198204359742821</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>24.59118230625583</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>181.8568860877685</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>69.97516923436041</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>12612.38134142546</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>2703017.672346717</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>74.15667016806722</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.162883208839091</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>24.39652777777778</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>178.8090277777777</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.541666666666667</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>247.5833333333333</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>48636.36363636364</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>12263541.66666667</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>269.2916666666667</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.208333333333333</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>25.15277777777778</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>182.8148148148148</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>107.8333333333333</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>22277.77777777778</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5216666.666666667</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>113.3888888888889</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WWnG5RHd</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45606.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>23.38871473354232</v>
+      </c>
+      <c r="O18" t="n">
+        <v>181.6228840125392</v>
+      </c>
+      <c r="P18" t="n">
+        <v>75.26426332288401</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>29989.83957219251</v>
+      </c>
+      <c r="R18" t="n">
+        <v>13195297.80564263</v>
+      </c>
+      <c r="S18" t="n">
+        <v>81.27304075235108</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.469278996865204</v>
+      </c>
+      <c r="U18" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="V18" t="n">
+        <v>185.5097222222222</v>
+      </c>
+      <c r="W18" t="n">
+        <v>69.21722222222222</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>4004538.194444445</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>78.02819444444444</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>22.47419467787115</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>182.3328835380306</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>72.55231361775479</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>21761.90476190477</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10038922.10730446</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>79.74828162034045</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.265354988149106</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>21.35714285714286</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>180.8799603174603</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>67.58686507936507</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>7713.095238095239</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2859606.150793651</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>77.20075396825396</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>21.08928571428572</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>182.6071428571429</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.392857142857143</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>102.5357142857143</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>29107.14285714286</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>13760714.28571429</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>112.2857142857143</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.535714285714286</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>21.93333333333333</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>180.9159420289855</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.565217391304348</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>178.5217391304348</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>26190.47619047619</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>10876086.95652174</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>200.4782608695652</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.565217391304348</v>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>b59ZhlYj</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45606.69791666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>551</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="P19" t="n">
+        <v>74.5625</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>12468750</v>
+      </c>
+      <c r="S19" t="n">
+        <v>78.8125</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>25.87606534090909</v>
+      </c>
+      <c r="V19" t="n">
+        <v>181.87890625</v>
+      </c>
+      <c r="W19" t="n">
+        <v>70.42684659090909</v>
+      </c>
+      <c r="X19" t="n">
+        <v>6427.052785923754</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2221333.451704545</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>73.69140625</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>27.99833333333333</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>178.1766666666667</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>78.09</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>44565</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>14795000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>79.00500000000001</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.998333333333334</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>24.89512688777394</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>181.1851116108469</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>68.22415529547884</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>5069.97879571409</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1769547.723573459</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>73.32184840493665</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>23.81578947368421</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>176.9385964912281</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>148.8947368421053</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>72277.77777777778</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>21394736.84210526</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>159.421052631579</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.631578947368421</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>26.68181818181818</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>178.5681818181818</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.818181818181818</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>196.9090909090909</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>16545.45454545454</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4947727.272727272</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>200.9090909090909</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.818181818181818</v>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.625</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kherradji a 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade louis ii
-  monaco </t>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18523</v>
+        <v>67394</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,176 +781,178 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>23.07427536231884</v>
+        <v>25.10069444444444</v>
       </c>
       <c r="O2" t="n">
-        <v>179.5534161490683</v>
+        <v>182.2638888888889</v>
       </c>
       <c r="P2" t="n">
-        <v>4.347826086956522</v>
+        <v>77.14583333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>331.7391304347826</v>
+        <v>37447.91666666666</v>
       </c>
       <c r="R2" t="n">
-        <v>166304.3478260869</v>
+        <v>15792968.75</v>
       </c>
       <c r="S2" t="n">
-        <v>68804347.82608695</v>
+        <v>81.07986111111111</v>
       </c>
       <c r="T2" t="n">
-        <v>356.9130434782609</v>
+        <v>1.180555555555556</v>
       </c>
       <c r="U2" t="n">
-        <v>5.869565217391305</v>
+        <v>25.93926767676767</v>
       </c>
       <c r="V2" t="n">
-        <v>23.83333333333333</v>
+        <v>181.0948232323232</v>
       </c>
       <c r="W2" t="n">
-        <v>183.5</v>
+        <v>68.45664983164983</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>4388.374485596708</v>
       </c>
       <c r="Y2" t="n">
-        <v>397</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>1655502.946127946</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>71.18594276094275</v>
+      </c>
       <c r="AA2" t="n">
-        <v>7900000</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>436</v>
+        <v>23.94808080808081</v>
       </c>
       <c r="AC2" t="n">
-        <v>6</v>
+        <v>182.8925252525253</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.35576923076923</v>
+        <v>75.01339105339105</v>
       </c>
       <c r="AE2" t="n">
-        <v>179.1752136752137</v>
+        <v>28849.89898989899</v>
       </c>
       <c r="AF2" t="n">
-        <v>74.97970085470085</v>
+        <v>10478535.35353535</v>
       </c>
       <c r="AG2" t="n">
-        <v>40016.97530864197</v>
+        <v>80.0346608946609</v>
       </c>
       <c r="AH2" t="n">
-        <v>14835576.92307692</v>
+        <v>1.181298701298701</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.12713675213675</v>
+        <v>23.3342324666886</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.389957264957265</v>
+        <v>181.5045291047484</v>
       </c>
       <c r="AK2" t="n">
-        <v>27.2184264520202</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>183.0837910353536</v>
-      </c>
+        <v>65.25091695990818</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>69.10831755050505</v>
+        <v>1319624.184092386</v>
       </c>
       <c r="AN2" t="n">
-        <v>4987.878787878789</v>
+        <v>71.67691867505465</v>
       </c>
       <c r="AO2" t="n">
-        <v>1640733.112373738</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>72.10144412878788</v>
+        <v>23.63402777777778</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>183.3611111111111</v>
       </c>
       <c r="AR2" t="n">
-        <v>20.61021176422839</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="AS2" t="n">
-        <v>179.1344356167071</v>
+        <v>295.875</v>
       </c>
       <c r="AT2" t="n">
-        <v>70.61735149276701</v>
+        <v>98916.66666666667</v>
       </c>
       <c r="AU2" t="n">
-        <v>15412.69841269841</v>
+        <v>39633333.33333334</v>
       </c>
       <c r="AV2" t="n">
-        <v>9326315.349777956</v>
+        <v>319.125</v>
       </c>
       <c r="AW2" t="n">
-        <v>81.42504329311808</v>
+        <v>5.375</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.111238369202358</v>
+        <v>22.98</v>
       </c>
       <c r="AY2" t="n">
-        <v>24.57140971773325</v>
+        <v>185.32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>181.8211506876998</v>
+        <v>2.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>65.20494727656948</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>191.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>1104227.448169903</v>
+        <v>4395000</v>
       </c>
       <c r="BD2" t="n">
-        <v>71.16806810349559</v>
+        <v>214.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45605.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade pierre mauroy
-  villeneuve d ascq </t>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>26109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -976,178 +978,180 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>23.24333333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>187</v>
+        <v>182.8857407407408</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>71.02629629629631</v>
       </c>
       <c r="Q3" t="n">
-        <v>75</v>
+        <v>13054.25925925926</v>
       </c>
       <c r="R3" t="n">
-        <v>9000</v>
+        <v>4513444.444444444</v>
       </c>
       <c r="S3" t="n">
-        <v>5500000</v>
+        <v>78.15055555555554</v>
       </c>
       <c r="T3" t="n">
-        <v>76</v>
+        <v>1.242777777777778</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>23.35576923076923</v>
       </c>
       <c r="V3" t="n">
-        <v>23.88888888888889</v>
+        <v>179.1752136752137</v>
       </c>
       <c r="W3" t="n">
-        <v>177.1296296296296</v>
+        <v>74.97970085470085</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>40016.97530864197</v>
       </c>
       <c r="Y3" t="n">
-        <v>149.0555555555555</v>
+        <v>14835576.92307692</v>
       </c>
       <c r="Z3" t="n">
-        <v>72470.58823529411</v>
+        <v>81.12713675213675</v>
       </c>
       <c r="AA3" t="n">
-        <v>21350000</v>
+        <v>1.389957264957265</v>
       </c>
       <c r="AB3" t="n">
-        <v>159.1666666666667</v>
+        <v>23.8355772005772</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.611111111111111</v>
+        <v>182.8498893698894</v>
       </c>
       <c r="AD3" t="n">
-        <v>23.86275252525252</v>
+        <v>70.67632996632997</v>
       </c>
       <c r="AE3" t="n">
-        <v>181.2633644133644</v>
+        <v>10553.21067821068</v>
       </c>
       <c r="AF3" t="n">
-        <v>75.67067793317793</v>
+        <v>3519762.325637326</v>
       </c>
       <c r="AG3" t="n">
-        <v>25923.61111111111</v>
+        <v>76.99976671476671</v>
       </c>
       <c r="AH3" t="n">
-        <v>12732463.82090132</v>
+        <v>1.263549783549784</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.04663947163947</v>
+        <v>20.61021176422839</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.396649184149184</v>
+        <v>179.1344356167071</v>
       </c>
       <c r="AK3" t="n">
-        <v>24.25</v>
+        <v>70.61735149276701</v>
       </c>
       <c r="AL3" t="n">
-        <v>181</v>
+        <v>15412.69841269841</v>
       </c>
       <c r="AM3" t="n">
-        <v>74.375</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>9326315.349777956</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>81.42504329311808</v>
+      </c>
       <c r="AO3" t="n">
-        <v>11812500</v>
+        <v>1.111238369202358</v>
       </c>
       <c r="AP3" t="n">
-        <v>78.625</v>
+        <v>24.89492753623189</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.75</v>
+        <v>184.3152173913043</v>
       </c>
       <c r="AR3" t="n">
-        <v>26.22782967032967</v>
+        <v>2.304347826086957</v>
       </c>
       <c r="AS3" t="n">
-        <v>179.8366575091575</v>
+        <v>164.7826086956522</v>
       </c>
       <c r="AT3" t="n">
-        <v>73.93877733377732</v>
+        <v>42173.91304347826</v>
       </c>
       <c r="AU3" t="n">
-        <v>22641.66666666666</v>
+        <v>9026086.956521738</v>
       </c>
       <c r="AV3" t="n">
-        <v>7199765.741203241</v>
+        <v>173.5217391304348</v>
       </c>
       <c r="AW3" t="n">
-        <v>77.97101093351094</v>
+        <v>3.869565217391304</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.245317182817183</v>
+        <v>23.07427536231884</v>
       </c>
       <c r="AY3" t="n">
-        <v>27.99833333333333</v>
+        <v>179.5534161490683</v>
       </c>
       <c r="AZ3" t="n">
-        <v>178.1766666666667</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="BA3" t="n">
-        <v>78.09</v>
+        <v>331.7391304347826</v>
       </c>
       <c r="BB3" t="n">
-        <v>44565</v>
+        <v>166304.3478260869</v>
       </c>
       <c r="BC3" t="n">
-        <v>14795000</v>
+        <v>68804347.82608695</v>
       </c>
       <c r="BD3" t="n">
-        <v>79.00500000000001</v>
+        <v>356.9130434782609</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.998333333333334</v>
+        <v>5.869565217391305</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.54166666666</v>
+        <v>45605.625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48229</v>
+        <v>38223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1173,180 +1177,180 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>25.65987654320988</v>
+        <v>25.66284722222222</v>
       </c>
       <c r="O4" t="n">
-        <v>189.8358024691358</v>
+        <v>180.1741898148148</v>
       </c>
       <c r="P4" t="n">
-        <v>3.407407407407407</v>
+        <v>76.86018518518519</v>
       </c>
       <c r="Q4" t="n">
-        <v>268.9259259259259</v>
+        <v>29126.38888888889</v>
       </c>
       <c r="R4" t="n">
-        <v>234703.7037037037</v>
+        <v>12699965.27777778</v>
       </c>
       <c r="S4" t="n">
-        <v>110846296.2962963</v>
+        <v>79.97025462962962</v>
       </c>
       <c r="T4" t="n">
-        <v>281.4444444444445</v>
+        <v>1.149537037037037</v>
       </c>
       <c r="U4" t="n">
-        <v>7.444444444444445</v>
+        <v>25.30235042735043</v>
       </c>
       <c r="V4" t="n">
+        <v>182.7863247863248</v>
+      </c>
+      <c r="W4" t="n">
+        <v>73.52970085470085</v>
+      </c>
+      <c r="X4" t="n">
+        <v>22438.88888888889</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6497943.376068377</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>77.3457264957265</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.446367521367521</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>27.0417381263075</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>178.4959495847056</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>74.19277247871746</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>23207.55841048903</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>6711372.167505541</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>76.05096988338614</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.400335031794362</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>24.80018731268732</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>182.5627185314685</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>70.29982933732934</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>17189.82683982684</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>4764053.998085248</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>75.47102272727271</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.214094239094239</v>
+      </c>
+      <c r="AP4" t="n">
         <v>26.52162698412698</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AQ4" t="n">
         <v>173.7620039682539</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AR4" t="n">
         <v>2.75</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AS4" t="n">
         <v>205.0416666666667</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AT4" t="n">
         <v>69125</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AU4" t="n">
         <v>19491666.66666667</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AV4" t="n">
         <v>210.1666666666667</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AW4" t="n">
         <v>2.791666666666667</v>
       </c>
-      <c r="AD4" t="n">
-        <v>22.71296296296296</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>184.574074074074</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>81.17592592592592</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>85513.88888888889</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>55655555.55555555</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>86.7962962962963</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.074074074074074</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>25.66284722222222</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>180.1741898148148</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>76.86018518518519</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>29126.38888888889</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>12699965.27777778</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>79.97025462962962</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.149537037037037</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>23.2547952047952</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>183.9831002331002</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>80.01316183816184</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>84948.40367965367</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>47297179.07092907</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>85.13105228105226</v>
-      </c>
       <c r="AX4" t="n">
-        <v>2.011538461538461</v>
+        <v>23.96811594202898</v>
       </c>
       <c r="AY4" t="n">
-        <v>27.0417381263075</v>
+        <v>178.0173913043478</v>
       </c>
       <c r="AZ4" t="n">
-        <v>178.4959495847056</v>
+        <v>2.434782608695652</v>
       </c>
       <c r="BA4" t="n">
-        <v>74.19277247871746</v>
+        <v>177.0869565217391</v>
       </c>
       <c r="BB4" t="n">
-        <v>23207.55841048903</v>
+        <v>60086.95652173913</v>
       </c>
       <c r="BC4" t="n">
-        <v>6711372.167505541</v>
+        <v>16328260.86956522</v>
       </c>
       <c r="BD4" t="n">
-        <v>76.05096988338614</v>
+        <v>183.6521739130435</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.400335031794362</v>
+        <v>2.956521739130435</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
           <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.625</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15220</v>
+        <v>18752</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1372,180 +1376,176 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>24.75</v>
+        <v>27.2184264520202</v>
       </c>
       <c r="O5" t="n">
-        <v>182.7450980392157</v>
+        <v>183.0837910353536</v>
       </c>
       <c r="P5" t="n">
-        <v>1.529411764705882</v>
+        <v>69.10831755050505</v>
       </c>
       <c r="Q5" t="n">
-        <v>109.8823529411765</v>
+        <v>4987.878787878789</v>
       </c>
       <c r="R5" t="n">
-        <v>22235.29411764706</v>
+        <v>1640733.112373738</v>
       </c>
       <c r="S5" t="n">
-        <v>5405882.352941177</v>
+        <v>72.10144412878788</v>
       </c>
       <c r="T5" t="n">
-        <v>115.7647058823529</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.764705882352941</v>
+        <v>22.71296296296296</v>
       </c>
       <c r="V5" t="n">
-        <v>22.76388888888889</v>
+        <v>184.574074074074</v>
       </c>
       <c r="W5" t="n">
-        <v>177.85</v>
+        <v>81.17592592592592</v>
       </c>
       <c r="X5" t="n">
-        <v>2.625</v>
+        <v>85513.88888888889</v>
       </c>
       <c r="Y5" t="n">
-        <v>196.75</v>
+        <v>55655555.55555555</v>
       </c>
       <c r="Z5" t="n">
-        <v>76000</v>
+        <v>86.7962962962963</v>
       </c>
       <c r="AA5" t="n">
-        <v>29816666.66666667</v>
+        <v>2.074074074074074</v>
       </c>
       <c r="AB5" t="n">
-        <v>211.5</v>
+        <v>24.59072241075917</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.375</v>
+        <v>181.7409335389674</v>
       </c>
       <c r="AD5" t="n">
-        <v>25.7057498057498</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>181.4817793317793</v>
-      </c>
+        <v>65.19555059296107</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>72.49483294483295</v>
+        <v>1098415.574609628</v>
       </c>
       <c r="AG5" t="n">
-        <v>15419.07536907537</v>
+        <v>71.16710324876885</v>
       </c>
       <c r="AH5" t="n">
-        <v>3552093.045843046</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>75.47346542346541</v>
+        <v>23.2547952047952</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.176806526806527</v>
+        <v>183.9831002331002</v>
       </c>
       <c r="AK5" t="n">
-        <v>24.34710567210567</v>
+        <v>80.01316183816184</v>
       </c>
       <c r="AL5" t="n">
-        <v>185.2509129759129</v>
+        <v>84948.40367965367</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.58637334887334</v>
+        <v>47297179.07092907</v>
       </c>
       <c r="AN5" t="n">
-        <v>31150.35936285936</v>
+        <v>85.13105228105226</v>
       </c>
       <c r="AO5" t="n">
-        <v>11134280.3030303</v>
+        <v>2.011538461538461</v>
       </c>
       <c r="AP5" t="n">
-        <v>80.19445415695415</v>
+        <v>22.655</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.394900932400932</v>
+        <v>181.8483333333334</v>
       </c>
       <c r="AR5" t="n">
-        <v>24.66761052246986</v>
+        <v>3.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>181.8868956278164</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>70.04655340397028</v>
-      </c>
+        <v>234.3</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>12754.94864612512</v>
+        <v>4055000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2712750.324767588</v>
+        <v>260.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>74.14898916088174</v>
+        <v>3.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.169965087484269</v>
+        <v>25.6698717948718</v>
       </c>
       <c r="AY5" t="n">
-        <v>22.13297682709447</v>
+        <v>189.9525641025641</v>
       </c>
       <c r="AZ5" t="n">
-        <v>180.8496337455437</v>
+        <v>3.346153846153846</v>
       </c>
       <c r="BA5" t="n">
-        <v>72.2399676916221</v>
+        <v>263.7692307692308</v>
       </c>
       <c r="BB5" t="n">
-        <v>25023.12509284017</v>
+        <v>229615.3846153846</v>
       </c>
       <c r="BC5" t="n">
-        <v>8185185.610702615</v>
+        <v>108413461.5384615</v>
       </c>
       <c r="BD5" t="n">
-        <v>78.91296791443851</v>
+        <v>276.1538461538461</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.318819630124777</v>
+        <v>7.307692307692307</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.70833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42000</v>
+        <v>36178</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1571,175 +1571,175 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>28</v>
+        <v>24.3689898989899</v>
       </c>
       <c r="O6" t="n">
-        <v>180.25</v>
+        <v>185.2609494949494</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>75.59782828282827</v>
       </c>
       <c r="Q6" t="n">
-        <v>280</v>
+        <v>31232.37373737373</v>
       </c>
       <c r="R6" t="n">
-        <v>21000</v>
+        <v>11140451.51515152</v>
       </c>
       <c r="S6" t="n">
-        <v>6675000</v>
+        <v>80.19023232323232</v>
       </c>
       <c r="T6" t="n">
-        <v>284</v>
+        <v>1.39469696969697</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>23.86275252525252</v>
       </c>
       <c r="V6" t="n">
-        <v>24.89492753623189</v>
+        <v>181.2633644133644</v>
       </c>
       <c r="W6" t="n">
-        <v>184.3152173913043</v>
+        <v>75.67067793317793</v>
       </c>
       <c r="X6" t="n">
-        <v>2.304347826086957</v>
+        <v>25923.61111111111</v>
       </c>
       <c r="Y6" t="n">
-        <v>164.7826086956522</v>
+        <v>12732463.82090132</v>
       </c>
       <c r="Z6" t="n">
-        <v>42173.91304347826</v>
+        <v>81.04663947163947</v>
       </c>
       <c r="AA6" t="n">
-        <v>9026086.956521738</v>
+        <v>1.396649184149184</v>
       </c>
       <c r="AB6" t="n">
-        <v>173.5217391304348</v>
+        <v>22.11517528223411</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.869565217391304</v>
+        <v>180.7996093285799</v>
       </c>
       <c r="AD6" t="n">
-        <v>25.87606534090909</v>
+        <v>72.13596553773026</v>
       </c>
       <c r="AE6" t="n">
-        <v>181.87890625</v>
+        <v>24771.33343236284</v>
       </c>
       <c r="AF6" t="n">
-        <v>70.42684659090909</v>
+        <v>7977531.31808279</v>
       </c>
       <c r="AG6" t="n">
-        <v>6427.052785923754</v>
+        <v>78.82716577540107</v>
       </c>
       <c r="AH6" t="n">
-        <v>2221333.451704545</v>
+        <v>1.326740938799762</v>
       </c>
       <c r="AI6" t="n">
-        <v>73.69140625</v>
+        <v>26.22782967032967</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>179.8366575091575</v>
       </c>
       <c r="AK6" t="n">
-        <v>23.24333333333333</v>
+        <v>73.93877733377732</v>
       </c>
       <c r="AL6" t="n">
-        <v>182.8857407407408</v>
+        <v>22641.66666666666</v>
       </c>
       <c r="AM6" t="n">
-        <v>71.02629629629631</v>
+        <v>7199765.741203241</v>
       </c>
       <c r="AN6" t="n">
-        <v>13054.25925925926</v>
+        <v>77.97101093351094</v>
       </c>
       <c r="AO6" t="n">
-        <v>4513444.444444444</v>
+        <v>1.245317182817183</v>
       </c>
       <c r="AP6" t="n">
-        <v>78.15055555555554</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.242777777777778</v>
+        <v>177.9739130434782</v>
       </c>
       <c r="AR6" t="n">
-        <v>24.89512688777394</v>
+        <v>2.652173913043478</v>
       </c>
       <c r="AS6" t="n">
-        <v>181.1851116108469</v>
+        <v>198.8695652173913</v>
       </c>
       <c r="AT6" t="n">
-        <v>68.22415529547884</v>
+        <v>76695.65217391304</v>
       </c>
       <c r="AU6" t="n">
-        <v>5069.97879571409</v>
+        <v>30678260.86956522</v>
       </c>
       <c r="AV6" t="n">
-        <v>1769547.723573459</v>
+        <v>214.0869565217391</v>
       </c>
       <c r="AW6" t="n">
-        <v>73.32184840493665</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>25.28888888888889</v>
       </c>
       <c r="AY6" t="n">
-        <v>23.8355772005772</v>
+        <v>183.6166666666667</v>
       </c>
       <c r="AZ6" t="n">
-        <v>182.8498893698894</v>
+        <v>1.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>70.67632996632997</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>10553.21067821068</v>
+        <v>24733.33333333333</v>
       </c>
       <c r="BC6" t="n">
-        <v>3519762.325637326</v>
+        <v>12170000</v>
       </c>
       <c r="BD6" t="n">
-        <v>76.99976671476671</v>
+        <v>103.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.263549783549784</v>
+        <v>1.866666666666667</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
+          <t xml:space="preserve">stade oceane
+  le havre </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33150</v>
+        <v>25178</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1770,178 +1770,180 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>21.94545454545455</v>
+        <v>23.09795321637427</v>
       </c>
       <c r="O7" t="n">
-        <v>181.0636363636364</v>
+        <v>186.2812865497076</v>
       </c>
       <c r="P7" t="n">
-        <v>2.545454545454545</v>
+        <v>66.34809941520467</v>
       </c>
       <c r="Q7" t="n">
-        <v>177.2272727272727</v>
+        <v>4922.979797979798</v>
       </c>
       <c r="R7" t="n">
-        <v>26150</v>
+        <v>1736509.502923977</v>
       </c>
       <c r="S7" t="n">
-        <v>10802272.72727273</v>
+        <v>73.84108187134503</v>
       </c>
       <c r="T7" t="n">
-        <v>199</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.545454545454545</v>
+        <v>25.08333333333333</v>
       </c>
       <c r="V7" t="n">
-        <v>20.24782608695652</v>
+        <v>184.7083333333333</v>
       </c>
       <c r="W7" t="n">
-        <v>179.1463768115942</v>
+        <v>73.16666666666667</v>
       </c>
       <c r="X7" t="n">
-        <v>1.739130434782609</v>
+        <v>16437.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>118.0869565217391</v>
+        <v>6375000</v>
       </c>
       <c r="Z7" t="n">
+        <v>78.16666666666667</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24.46805033416875</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>181.2887611657349</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>65.89549755799756</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>4142.176870748299</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1475480.096475162</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>72.38780966840177</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>23.17482993197279</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>186.1051587301587</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>69.19631519274375</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>10722.8835978836</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2894994.33106576</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>75.49625850340136</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>23.765625</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>184.734375</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>118.625</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>14187.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4935937.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>130.375</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>20.44090909090909</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>179.4257575757576</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.772727272727273</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>120.6363636363636</v>
+      </c>
+      <c r="BB7" t="n">
         <v>15222.22222222222</v>
       </c>
-      <c r="AA7" t="n">
-        <v>4452173.913043479</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>135.9130434782609</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.826086956521739</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>22.2171052631579</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>185.5036549707602</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>69.16286549707603</v>
-      </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
-        <v>3981750.730994152</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>78.04283625730994</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>25.21875</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>184.65625</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>73.34375</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>16625</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>6465625</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>78.125</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>21.34693877551021</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>180.8475765306123</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>67.59306972789115</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7998.611111111112</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2901958.971088436</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>77.22699829931972</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>23.17482993197279</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>186.1051587301587</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>69.19631519274375</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>10722.8835978836</v>
-      </c>
       <c r="BC7" t="n">
-        <v>2894994.33106576</v>
+        <v>4609090.909090909</v>
       </c>
       <c r="BD7" t="n">
-        <v>75.49625850340136</v>
+        <v>138.3636363636364</v>
       </c>
       <c r="BE7" t="n">
-        <v>1</v>
+        <v>1.863636363636364</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
+          <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17924</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1967,178 +1969,180 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>24</v>
+        <v>26.15674603174603</v>
       </c>
       <c r="O8" t="n">
-        <v>186</v>
+        <v>179.5099206349207</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>73.38492063492063</v>
       </c>
       <c r="Q8" t="n">
-        <v>198</v>
+        <v>16951.38888888889</v>
       </c>
       <c r="R8" t="n">
-        <v>9000</v>
+        <v>6894047.619047618</v>
       </c>
       <c r="S8" t="n">
-        <v>5300000</v>
+        <v>77.12103174603173</v>
       </c>
       <c r="T8" t="n">
-        <v>219</v>
+        <v>1.41468253968254</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>25.7057498057498</v>
       </c>
       <c r="V8" t="n">
-        <v>20</v>
+        <v>181.4817793317793</v>
       </c>
       <c r="W8" t="n">
-        <v>189</v>
+        <v>72.49483294483295</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>15419.07536907537</v>
       </c>
       <c r="Y8" t="n">
-        <v>72</v>
+        <v>3552093.045843046</v>
       </c>
       <c r="Z8" t="n">
-        <v>14000</v>
+        <v>75.47346542346541</v>
       </c>
       <c r="AA8" t="n">
-        <v>2900000</v>
+        <v>1.176806526806527</v>
       </c>
       <c r="AB8" t="n">
-        <v>78</v>
+        <v>23.33944260867338</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>179.943292604831</v>
       </c>
       <c r="AD8" t="n">
-        <v>25.93926767676767</v>
+        <v>68.76856220702373</v>
       </c>
       <c r="AE8" t="n">
-        <v>181.0948232323232</v>
+        <v>10680.54672600127</v>
       </c>
       <c r="AF8" t="n">
-        <v>68.45664983164983</v>
+        <v>3256709.508440278</v>
       </c>
       <c r="AG8" t="n">
-        <v>4388.374485596708</v>
+        <v>76.5337508645201</v>
       </c>
       <c r="AH8" t="n">
-        <v>1655502.946127946</v>
+        <v>1.198204359742821</v>
       </c>
       <c r="AI8" t="n">
-        <v>71.18594276094275</v>
+        <v>24.66761052246986</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>181.8868956278164</v>
       </c>
       <c r="AK8" t="n">
-        <v>23.37045454545454</v>
+        <v>70.04655340397028</v>
       </c>
       <c r="AL8" t="n">
-        <v>181.6451298701299</v>
+        <v>12754.94864612512</v>
       </c>
       <c r="AM8" t="n">
-        <v>75.23441558441559</v>
+        <v>2712750.324767588</v>
       </c>
       <c r="AN8" t="n">
-        <v>29989.83957219251</v>
+        <v>74.14898916088174</v>
       </c>
       <c r="AO8" t="n">
-        <v>13073344.15584416</v>
+        <v>1.169965087484269</v>
       </c>
       <c r="AP8" t="n">
-        <v>81.24707792207791</v>
+        <v>24.34130434782608</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.46461038961039</v>
+        <v>178.7282608695652</v>
       </c>
       <c r="AR8" t="n">
-        <v>23.27806768002257</v>
+        <v>3.565217391304348</v>
       </c>
       <c r="AS8" t="n">
-        <v>181.5246585077412</v>
+        <v>248.9565217391304</v>
       </c>
       <c r="AT8" t="n">
-        <v>65.1809431587627</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
+        <v>48900</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>12405434.7826087</v>
+      </c>
       <c r="AV8" t="n">
-        <v>1314363.446495025</v>
+        <v>271.2173913043478</v>
       </c>
       <c r="AW8" t="n">
-        <v>71.70483063719905</v>
+        <v>4.260869565217392</v>
       </c>
       <c r="AX8" t="n">
-        <v>1</v>
+        <v>24.75</v>
       </c>
       <c r="AY8" t="n">
-        <v>22.47982913165266</v>
+        <v>182.7450980392157</v>
       </c>
       <c r="AZ8" t="n">
-        <v>182.3061988795518</v>
+        <v>1.529411764705882</v>
       </c>
       <c r="BA8" t="n">
-        <v>72.53440616246499</v>
+        <v>109.8823529411765</v>
       </c>
       <c r="BB8" t="n">
-        <v>21821.42857142857</v>
+        <v>22235.29411764706</v>
       </c>
       <c r="BC8" t="n">
-        <v>10151812.32492997</v>
+        <v>5405882.352941177</v>
       </c>
       <c r="BD8" t="n">
-        <v>79.7315462184874</v>
+        <v>115.7647058823529</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.269302521008403</v>
+        <v>1.764705882352941</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">frappart s 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade oceane
-  le havre </t>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25178</v>
+        <v>29778</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2164,180 +2168,178 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>23.765625</v>
+        <v>23.37045454545454</v>
       </c>
       <c r="O9" t="n">
-        <v>184.734375</v>
+        <v>181.6451298701299</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>75.23441558441559</v>
       </c>
       <c r="Q9" t="n">
-        <v>118.625</v>
+        <v>29989.83957219251</v>
       </c>
       <c r="R9" t="n">
-        <v>14187.5</v>
+        <v>13073344.15584416</v>
       </c>
       <c r="S9" t="n">
-        <v>4935937.5</v>
+        <v>81.24707792207791</v>
       </c>
       <c r="T9" t="n">
-        <v>130.375</v>
+        <v>1.46461038961039</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>22.2171052631579</v>
       </c>
       <c r="V9" t="n">
-        <v>24.39652777777778</v>
+        <v>185.5036549707602</v>
       </c>
       <c r="W9" t="n">
-        <v>178.8090277777777</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.541666666666667</v>
-      </c>
+        <v>69.16286549707603</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>247.5833333333333</v>
+        <v>3981750.730994152</v>
       </c>
       <c r="Z9" t="n">
-        <v>48636.36363636364</v>
+        <v>78.04283625730994</v>
       </c>
       <c r="AA9" t="n">
-        <v>12263541.66666667</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>269.2916666666667</v>
+        <v>22.47982913165266</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.208333333333333</v>
+        <v>182.3061988795518</v>
       </c>
       <c r="AD9" t="n">
-        <v>23.09795321637427</v>
+        <v>72.53440616246499</v>
       </c>
       <c r="AE9" t="n">
-        <v>186.2812865497076</v>
+        <v>21821.42857142857</v>
       </c>
       <c r="AF9" t="n">
-        <v>66.34809941520467</v>
+        <v>10151812.32492997</v>
       </c>
       <c r="AG9" t="n">
-        <v>4922.979797979798</v>
+        <v>79.7315462184874</v>
       </c>
       <c r="AH9" t="n">
-        <v>1736509.502923977</v>
+        <v>1.269302521008403</v>
       </c>
       <c r="AI9" t="n">
-        <v>73.84108187134503</v>
+        <v>21.34693877551021</v>
       </c>
       <c r="AJ9" t="n">
+        <v>180.8475765306123</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>67.59306972789115</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>7998.611111111112</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2901958.971088436</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>77.22699829931972</v>
+      </c>
+      <c r="AO9" t="n">
         <v>1</v>
       </c>
-      <c r="AK9" t="n">
-        <v>25.99652777777778</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>179.4930555555556</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>73.30555555555556</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>16601.19047619048</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>6956119.791666666</v>
-      </c>
       <c r="AP9" t="n">
-        <v>77.23090277777777</v>
+        <v>21.05357142857143</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.409722222222222</v>
+        <v>182.5714285714286</v>
       </c>
       <c r="AR9" t="n">
-        <v>24.46805033416875</v>
+        <v>1.392857142857143</v>
       </c>
       <c r="AS9" t="n">
-        <v>181.2887611657349</v>
+        <v>102.8214285714286</v>
       </c>
       <c r="AT9" t="n">
-        <v>65.89549755799756</v>
+        <v>29571.42857142857</v>
       </c>
       <c r="AU9" t="n">
-        <v>4142.176870748299</v>
+        <v>13814285.71428571</v>
       </c>
       <c r="AV9" t="n">
-        <v>1475480.096475162</v>
+        <v>112.3214285714286</v>
       </c>
       <c r="AW9" t="n">
-        <v>72.38780966840177</v>
+        <v>1.535714285714286</v>
       </c>
       <c r="AX9" t="n">
-        <v>1</v>
+        <v>21.94545454545455</v>
       </c>
       <c r="AY9" t="n">
-        <v>23.33944260867338</v>
+        <v>181.0636363636364</v>
       </c>
       <c r="AZ9" t="n">
-        <v>179.943292604831</v>
+        <v>2.545454545454545</v>
       </c>
       <c r="BA9" t="n">
-        <v>68.76856220702373</v>
+        <v>177.2272727272727</v>
       </c>
       <c r="BB9" t="n">
-        <v>10680.54672600127</v>
+        <v>26150</v>
       </c>
       <c r="BC9" t="n">
-        <v>3256709.508440278</v>
+        <v>10802272.72727273</v>
       </c>
       <c r="BD9" t="n">
-        <v>76.5337508645201</v>
+        <v>199</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.198204359742821</v>
+        <v>2.545454545454545</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35322</v>
+        <v>59186</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2363,145 +2365,143 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>23.96811594202898</v>
+        <v>24.25</v>
       </c>
       <c r="O10" t="n">
-        <v>178.0173913043478</v>
+        <v>181</v>
       </c>
       <c r="P10" t="n">
-        <v>2.434782608695652</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>177.0869565217391</v>
-      </c>
+        <v>74.375</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>60086.95652173913</v>
+        <v>11812500</v>
       </c>
       <c r="S10" t="n">
-        <v>16328260.86956522</v>
+        <v>78.625</v>
       </c>
       <c r="T10" t="n">
-        <v>183.6521739130435</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.956521739130435</v>
+        <v>25.81542699724518</v>
       </c>
       <c r="V10" t="n">
-        <v>23.63402777777778</v>
+        <v>181.8295454545455</v>
       </c>
       <c r="W10" t="n">
-        <v>183.3611111111111</v>
+        <v>70.37982093663912</v>
       </c>
       <c r="X10" t="n">
-        <v>4.166666666666667</v>
+        <v>6359.019886363636</v>
       </c>
       <c r="Y10" t="n">
-        <v>295.875</v>
+        <v>2219929.407713498</v>
       </c>
       <c r="Z10" t="n">
-        <v>98916.66666666667</v>
+        <v>73.71969696969697</v>
       </c>
       <c r="AA10" t="n">
-        <v>39633333.33333334</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>319.125</v>
+        <v>27.99833333333333</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.375</v>
+        <v>178.1766666666667</v>
       </c>
       <c r="AD10" t="n">
-        <v>25.30235042735043</v>
+        <v>78.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>182.7863247863248</v>
+        <v>44565</v>
       </c>
       <c r="AF10" t="n">
-        <v>73.52970085470085</v>
+        <v>14795000</v>
       </c>
       <c r="AG10" t="n">
-        <v>22438.88888888889</v>
+        <v>79.00500000000001</v>
       </c>
       <c r="AH10" t="n">
-        <v>6497943.376068377</v>
+        <v>1.998333333333334</v>
       </c>
       <c r="AI10" t="n">
-        <v>77.3457264957265</v>
+        <v>24.93242618020095</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.446367521367521</v>
+        <v>181.2213586737194</v>
       </c>
       <c r="AK10" t="n">
-        <v>25.10069444444444</v>
+        <v>68.2791117350715</v>
       </c>
       <c r="AL10" t="n">
-        <v>182.2638888888889</v>
+        <v>5095.164766243198</v>
       </c>
       <c r="AM10" t="n">
-        <v>77.14583333333333</v>
+        <v>1780423.112426789</v>
       </c>
       <c r="AN10" t="n">
-        <v>37447.91666666666</v>
+        <v>73.3133787100699</v>
       </c>
       <c r="AO10" t="n">
-        <v>15792968.75</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>81.07986111111111</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.180555555555556</v>
+        <v>177.1296296296296</v>
       </c>
       <c r="AR10" t="n">
-        <v>24.80018731268732</v>
+        <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>182.5627185314685</v>
+        <v>149.0555555555555</v>
       </c>
       <c r="AT10" t="n">
-        <v>70.29982933732934</v>
+        <v>72470.58823529411</v>
       </c>
       <c r="AU10" t="n">
-        <v>17189.82683982684</v>
+        <v>21350000</v>
       </c>
       <c r="AV10" t="n">
-        <v>4764053.998085248</v>
+        <v>159.1666666666667</v>
       </c>
       <c r="AW10" t="n">
-        <v>75.47102272727271</v>
+        <v>3.611111111111111</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.214094239094239</v>
+        <v>26.90277777777778</v>
       </c>
       <c r="AY10" t="n">
-        <v>23.94808080808081</v>
+        <v>178.7986111111111</v>
       </c>
       <c r="AZ10" t="n">
-        <v>182.8925252525253</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="BA10" t="n">
-        <v>75.01339105339105</v>
+        <v>197.9166666666667</v>
       </c>
       <c r="BB10" t="n">
-        <v>28849.89898989899</v>
+        <v>16500</v>
       </c>
       <c r="BC10" t="n">
-        <v>10478535.35353535</v>
+        <v>4891666.666666667</v>
       </c>
       <c r="BD10" t="n">
-        <v>80.0346608946609</v>
+        <v>201.6666666666667</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.181298701298701</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
           <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -802,22 +802,22 @@
         <v>1.180555555555556</v>
       </c>
       <c r="U2" t="n">
-        <v>25.93926767676767</v>
+        <v>25.92149947753396</v>
       </c>
       <c r="V2" t="n">
-        <v>181.0948232323232</v>
+        <v>181.135710553814</v>
       </c>
       <c r="W2" t="n">
-        <v>68.45664983164983</v>
+        <v>68.4379136189481</v>
       </c>
       <c r="X2" t="n">
-        <v>4388.374485596708</v>
+        <v>4385.829448329448</v>
       </c>
       <c r="Y2" t="n">
-        <v>1655502.946127946</v>
+        <v>1653968.564959944</v>
       </c>
       <c r="Z2" t="n">
-        <v>71.18594276094275</v>
+        <v>71.19548937652385</v>
       </c>
       <c r="AA2" t="n">
         <v>1</v>
@@ -844,20 +844,20 @@
         <v>1.181298701298701</v>
       </c>
       <c r="AI2" t="n">
-        <v>23.3342324666886</v>
+        <v>23.38459829226747</v>
       </c>
       <c r="AJ2" t="n">
-        <v>181.5045291047484</v>
+        <v>181.4862911608024</v>
       </c>
       <c r="AK2" t="n">
-        <v>65.25091695990818</v>
+        <v>65.3070656077423</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>1319624.184092386</v>
+        <v>1325490.997515434</v>
       </c>
       <c r="AN2" t="n">
-        <v>71.67691867505465</v>
+        <v>71.69217757597457</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -999,25 +999,25 @@
         <v>1.242777777777778</v>
       </c>
       <c r="U3" t="n">
-        <v>23.35576923076923</v>
+        <v>23.3125</v>
       </c>
       <c r="V3" t="n">
-        <v>179.1752136752137</v>
+        <v>178.9710648148148</v>
       </c>
       <c r="W3" t="n">
-        <v>74.97970085470085</v>
+        <v>74.98842592592592</v>
       </c>
       <c r="X3" t="n">
-        <v>40016.97530864197</v>
+        <v>40128.47222222222</v>
       </c>
       <c r="Y3" t="n">
-        <v>14835576.92307692</v>
+        <v>14885416.66666667</v>
       </c>
       <c r="Z3" t="n">
-        <v>81.12713675213675</v>
+        <v>81.16898148148148</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.389957264957265</v>
+        <v>1.380787037037037</v>
       </c>
       <c r="AB3" t="n">
         <v>23.8355772005772</v>
@@ -1041,25 +1041,25 @@
         <v>1.263549783549784</v>
       </c>
       <c r="AI3" t="n">
-        <v>20.61021176422839</v>
+        <v>20.60939019557441</v>
       </c>
       <c r="AJ3" t="n">
-        <v>179.1344356167071</v>
+        <v>179.3085709287464</v>
       </c>
       <c r="AK3" t="n">
-        <v>70.61735149276701</v>
+        <v>70.5683154645874</v>
       </c>
       <c r="AL3" t="n">
         <v>15412.69841269841</v>
       </c>
       <c r="AM3" t="n">
-        <v>9326315.349777956</v>
+        <v>9307638.42476562</v>
       </c>
       <c r="AN3" t="n">
-        <v>81.42504329311808</v>
+        <v>81.42087903162464</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.111238369202358</v>
+        <v>1.117418278602489</v>
       </c>
       <c r="AP3" t="n">
         <v>24.89492753623189</v>
@@ -1086,28 +1086,28 @@
         <v>3.869565217391304</v>
       </c>
       <c r="AX3" t="n">
-        <v>23.07427536231884</v>
+        <v>23.1344696969697</v>
       </c>
       <c r="AY3" t="n">
-        <v>179.5534161490683</v>
+        <v>179.4876623376623</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.347826086956522</v>
+        <v>4.363636363636363</v>
       </c>
       <c r="BA3" t="n">
-        <v>331.7391304347826</v>
+        <v>333.0909090909091</v>
       </c>
       <c r="BB3" t="n">
-        <v>166304.3478260869</v>
+        <v>167818.1818181818</v>
       </c>
       <c r="BC3" t="n">
-        <v>68804347.82608695</v>
+        <v>69372727.27272727</v>
       </c>
       <c r="BD3" t="n">
-        <v>356.9130434782609</v>
+        <v>358.0454545454546</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.869565217391305</v>
+        <v>5.909090909090909</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1376,22 +1376,22 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>27.2184264520202</v>
+        <v>27.17855164548713</v>
       </c>
       <c r="O5" t="n">
-        <v>183.0837910353536</v>
+        <v>183.0894265232975</v>
       </c>
       <c r="P5" t="n">
-        <v>69.10831755050505</v>
+        <v>69.0648908439231</v>
       </c>
       <c r="Q5" t="n">
-        <v>4987.878787878789</v>
+        <v>4970.247933884298</v>
       </c>
       <c r="R5" t="n">
-        <v>1640733.112373738</v>
+        <v>1636181.981101336</v>
       </c>
       <c r="S5" t="n">
-        <v>72.10144412878788</v>
+        <v>72.10471652003909</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1418,20 +1418,20 @@
         <v>2.074074074074074</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.59072241075917</v>
+        <v>24.59807638439992</v>
       </c>
       <c r="AC5" t="n">
-        <v>181.7409335389674</v>
+        <v>181.7430554496046</v>
       </c>
       <c r="AD5" t="n">
-        <v>65.19555059296107</v>
+        <v>65.18685203847424</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>1098415.574609628</v>
+        <v>1096465.543407999</v>
       </c>
       <c r="AG5" t="n">
-        <v>71.16710324876885</v>
+        <v>71.15759191301939</v>
       </c>
       <c r="AH5" t="n">
         <v>1</v>
@@ -1770,22 +1770,22 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>23.09795321637427</v>
+        <v>23.13117283950617</v>
       </c>
       <c r="O7" t="n">
-        <v>186.2812865497076</v>
+        <v>186.1927469135802</v>
       </c>
       <c r="P7" t="n">
-        <v>66.34809941520467</v>
+        <v>66.33966049382715</v>
       </c>
       <c r="Q7" t="n">
         <v>4922.979797979798</v>
       </c>
       <c r="R7" t="n">
-        <v>1736509.502923977</v>
+        <v>1705551.697530864</v>
       </c>
       <c r="S7" t="n">
-        <v>73.84108187134503</v>
+        <v>73.79058641975308</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1812,22 +1812,22 @@
         <v>1.125</v>
       </c>
       <c r="AB7" t="n">
-        <v>24.46805033416875</v>
+        <v>24.39534377610693</v>
       </c>
       <c r="AC7" t="n">
-        <v>181.2887611657349</v>
+        <v>181.33459732665</v>
       </c>
       <c r="AD7" t="n">
-        <v>65.89549755799756</v>
+        <v>65.83988888888889</v>
       </c>
       <c r="AE7" t="n">
-        <v>4142.176870748299</v>
+        <v>4142.063492063492</v>
       </c>
       <c r="AF7" t="n">
-        <v>1475480.096475162</v>
+        <v>1483499.300334169</v>
       </c>
       <c r="AG7" t="n">
-        <v>72.38780966840177</v>
+        <v>72.43189348370926</v>
       </c>
       <c r="AH7" t="n">
         <v>1</v>
@@ -1854,28 +1854,28 @@
         <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>23.765625</v>
+        <v>23.85</v>
       </c>
       <c r="AQ7" t="n">
-        <v>184.734375</v>
+        <v>184.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.75</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="AS7" t="n">
-        <v>118.625</v>
+        <v>117.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>14187.5</v>
+        <v>14866.66666666667</v>
       </c>
       <c r="AU7" t="n">
-        <v>4935937.5</v>
+        <v>5098333.333333333</v>
       </c>
       <c r="AV7" t="n">
-        <v>130.375</v>
+        <v>129.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.75</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="AX7" t="n">
         <v>20.44090909090909</v>
@@ -2384,22 +2384,22 @@
         <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>25.81542699724518</v>
+        <v>25.8125</v>
       </c>
       <c r="V10" t="n">
-        <v>181.8295454545455</v>
+        <v>181.8043323863636</v>
       </c>
       <c r="W10" t="n">
-        <v>70.37982093663912</v>
+        <v>70.37748579545455</v>
       </c>
       <c r="X10" t="n">
-        <v>6359.019886363636</v>
+        <v>6364.736070381232</v>
       </c>
       <c r="Y10" t="n">
-        <v>2219929.407713498</v>
+        <v>2223677.201704545</v>
       </c>
       <c r="Z10" t="n">
-        <v>73.71969696969697</v>
+        <v>73.72514204545453</v>
       </c>
       <c r="AA10" t="n">
         <v>1</v>
@@ -2426,22 +2426,22 @@
         <v>1.998333333333334</v>
       </c>
       <c r="AI10" t="n">
-        <v>24.93242618020095</v>
+        <v>24.84179677194383</v>
       </c>
       <c r="AJ10" t="n">
-        <v>181.2213586737194</v>
+        <v>181.1848702981056</v>
       </c>
       <c r="AK10" t="n">
-        <v>68.2791117350715</v>
+        <v>68.27121128003482</v>
       </c>
       <c r="AL10" t="n">
-        <v>5095.164766243198</v>
+        <v>5131.791982527276</v>
       </c>
       <c r="AM10" t="n">
-        <v>1780423.112426789</v>
+        <v>1793600.571063807</v>
       </c>
       <c r="AN10" t="n">
-        <v>73.3133787100699</v>
+        <v>73.3681804512687</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>

--- a/data/france/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -781,134 +781,134 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>185</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>64</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>84</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>330</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7850000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>366</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD2" t="n">
         <v>25.10069444444444</v>
       </c>
-      <c r="O2" t="n">
+      <c r="AE2" t="n">
         <v>182.2638888888889</v>
       </c>
-      <c r="P2" t="n">
+      <c r="AF2" t="n">
         <v>77.14583333333333</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AG2" t="n">
         <v>37447.91666666666</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AH2" t="n">
         <v>15792968.75</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AI2" t="n">
         <v>81.07986111111111</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AJ2" t="n">
         <v>1.180555555555556</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AK2" t="n">
         <v>25.92149947753396</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AL2" t="n">
         <v>181.135710553814</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AM2" t="n">
         <v>68.4379136189481</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AN2" t="n">
         <v>4385.829448329448</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AO2" t="n">
         <v>1653968.564959944</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AP2" t="n">
         <v>71.19548937652385</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AQ2" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AR2" t="n">
         <v>23.94808080808081</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AS2" t="n">
         <v>182.8925252525253</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AT2" t="n">
         <v>75.01339105339105</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AU2" t="n">
         <v>28849.89898989899</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AV2" t="n">
         <v>10478535.35353535</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AW2" t="n">
         <v>80.0346608946609</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AX2" t="n">
         <v>1.181298701298701</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AY2" t="n">
         <v>23.38459829226747</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AZ2" t="n">
         <v>181.4862911608024</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="BA2" t="n">
         <v>65.3070656077423</v>
       </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
         <v>1325490.997515434</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="BD2" t="n">
         <v>71.69217757597457</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="BE2" t="n">
         <v>1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23.63402777777778</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>183.3611111111111</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>295.875</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>98916.66666666667</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>39633333.33333334</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>319.125</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.375</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>185.32</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>191.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4395000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>214.1</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.9</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -978,136 +978,136 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>24.89492753623189</v>
+      </c>
+      <c r="O3" t="n">
+        <v>184.3152173913043</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.304347826086957</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>164.7826086956522</v>
+      </c>
+      <c r="R3" t="n">
+        <v>42173.91304347826</v>
+      </c>
+      <c r="S3" t="n">
+        <v>9026086.956521738</v>
+      </c>
+      <c r="T3" t="n">
+        <v>173.5217391304348</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.869565217391304</v>
+      </c>
+      <c r="V3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>158</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>175000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>56500000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>168</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" t="n">
         <v>23.24333333333333</v>
       </c>
-      <c r="O3" t="n">
+      <c r="AE3" t="n">
         <v>182.8857407407408</v>
       </c>
-      <c r="P3" t="n">
+      <c r="AF3" t="n">
         <v>71.02629629629631</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="AG3" t="n">
         <v>13054.25925925926</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AH3" t="n">
         <v>4513444.444444444</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AI3" t="n">
         <v>78.15055555555554</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AJ3" t="n">
         <v>1.242777777777778</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AK3" t="n">
         <v>23.3125</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AL3" t="n">
         <v>178.9710648148148</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AM3" t="n">
         <v>74.98842592592592</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AN3" t="n">
         <v>40128.47222222222</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AO3" t="n">
         <v>14885416.66666667</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AP3" t="n">
         <v>81.16898148148148</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AQ3" t="n">
         <v>1.380787037037037</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AR3" t="n">
         <v>23.8355772005772</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AS3" t="n">
         <v>182.8498893698894</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AT3" t="n">
         <v>70.67632996632997</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AU3" t="n">
         <v>10553.21067821068</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AV3" t="n">
         <v>3519762.325637326</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AW3" t="n">
         <v>76.99976671476671</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AX3" t="n">
         <v>1.263549783549784</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AY3" t="n">
         <v>20.60939019557441</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AZ3" t="n">
         <v>179.3085709287464</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="BA3" t="n">
         <v>70.5683154645874</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="BB3" t="n">
         <v>15412.69841269841</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="BC3" t="n">
         <v>9307638.42476562</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="BD3" t="n">
         <v>81.42087903162464</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="BE3" t="n">
         <v>1.117418278602489</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>24.89492753623189</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>184.3152173913043</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.304347826086957</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>164.7826086956522</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>42173.91304347826</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9026086.956521738</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>173.5217391304348</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>3.869565217391304</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>23.1344696969697</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>179.4876623376623</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.363636363636363</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>333.0909090909091</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>167818.1818181818</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>69372727.27272727</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>358.0454545454546</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.909090909090909</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1177,136 +1177,136 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>25.66284722222222</v>
+        <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>180.1741898148148</v>
+        <v>185</v>
       </c>
       <c r="P4" t="n">
-        <v>76.86018518518519</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>29126.38888888889</v>
+        <v>78</v>
       </c>
       <c r="R4" t="n">
-        <v>12699965.27777778</v>
+        <v>57000</v>
       </c>
       <c r="S4" t="n">
-        <v>79.97025462962962</v>
+        <v>17000000</v>
       </c>
       <c r="T4" t="n">
-        <v>1.149537037037037</v>
+        <v>79</v>
       </c>
       <c r="U4" t="n">
-        <v>25.30235042735043</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>182.7863247863248</v>
+        <v>27</v>
       </c>
       <c r="W4" t="n">
-        <v>73.52970085470085</v>
+        <v>182</v>
       </c>
       <c r="X4" t="n">
-        <v>22438.88888888889</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>6497943.376068377</v>
+        <v>71</v>
       </c>
       <c r="Z4" t="n">
-        <v>77.3457264957265</v>
+        <v>14000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.446367521367521</v>
+        <v>1800000</v>
       </c>
       <c r="AB4" t="n">
-        <v>27.0417381263075</v>
+        <v>71</v>
       </c>
       <c r="AC4" t="n">
-        <v>178.4959495847056</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>74.19277247871746</v>
+        <v>25.64384057971014</v>
       </c>
       <c r="AE4" t="n">
-        <v>23207.55841048903</v>
+        <v>180.1208937198068</v>
       </c>
       <c r="AF4" t="n">
-        <v>6711372.167505541</v>
+        <v>76.85410628019324</v>
       </c>
       <c r="AG4" t="n">
-        <v>76.05096988338614</v>
+        <v>29088.40579710144</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.400335031794362</v>
+        <v>12691702.89855072</v>
       </c>
       <c r="AI4" t="n">
-        <v>24.80018731268732</v>
+        <v>79.968961352657</v>
       </c>
       <c r="AJ4" t="n">
-        <v>182.5627185314685</v>
+        <v>1.147342995169082</v>
       </c>
       <c r="AK4" t="n">
-        <v>70.29982933732934</v>
+        <v>25.32754629629629</v>
       </c>
       <c r="AL4" t="n">
-        <v>17189.82683982684</v>
+        <v>182.9768518518519</v>
       </c>
       <c r="AM4" t="n">
-        <v>4764053.998085248</v>
+        <v>73.4988425925926</v>
       </c>
       <c r="AN4" t="n">
-        <v>75.47102272727271</v>
+        <v>22515.87301587302</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.214094239094239</v>
+        <v>6506105.324074075</v>
       </c>
       <c r="AP4" t="n">
-        <v>26.52162698412698</v>
+        <v>77.34953703703704</v>
       </c>
       <c r="AQ4" t="n">
-        <v>173.7620039682539</v>
+        <v>1.450231481481482</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.75</v>
+        <v>27.0505283772201</v>
       </c>
       <c r="AS4" t="n">
-        <v>205.0416666666667</v>
+        <v>178.5263689526847</v>
       </c>
       <c r="AT4" t="n">
-        <v>69125</v>
+        <v>74.1951493994727</v>
       </c>
       <c r="AU4" t="n">
-        <v>19491666.66666667</v>
+        <v>23258.25847085246</v>
       </c>
       <c r="AV4" t="n">
-        <v>210.1666666666667</v>
+        <v>6727900.093849341</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.791666666666667</v>
+        <v>76.06019974177869</v>
       </c>
       <c r="AX4" t="n">
-        <v>23.96811594202898</v>
+        <v>1.40579316256008</v>
       </c>
       <c r="AY4" t="n">
-        <v>178.0173913043478</v>
+        <v>24.81448194662481</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.434782608695652</v>
+        <v>182.5101495726496</v>
       </c>
       <c r="BA4" t="n">
-        <v>177.0869565217391</v>
+        <v>70.28236089307518</v>
       </c>
       <c r="BB4" t="n">
-        <v>60086.95652173913</v>
+        <v>17542.14285714286</v>
       </c>
       <c r="BC4" t="n">
-        <v>16328260.86956522</v>
+        <v>4869485.140851213</v>
       </c>
       <c r="BD4" t="n">
-        <v>183.6521739130435</v>
+        <v>75.44583333333333</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.956521739130435</v>
+        <v>1.216352694924123</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -1376,132 +1376,132 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>330</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>359</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.6698717948718</v>
+      </c>
+      <c r="W5" t="n">
+        <v>189.9525641025641</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.346153846153846</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>263.7692307692308</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>229615.3846153846</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>108413461.5384615</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>276.1538461538461</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.307692307692307</v>
+      </c>
+      <c r="AD5" t="n">
         <v>27.17855164548713</v>
       </c>
-      <c r="O5" t="n">
+      <c r="AE5" t="n">
         <v>183.0894265232975</v>
       </c>
-      <c r="P5" t="n">
+      <c r="AF5" t="n">
         <v>69.0648908439231</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="AG5" t="n">
         <v>4970.247933884298</v>
       </c>
-      <c r="R5" t="n">
+      <c r="AH5" t="n">
         <v>1636181.981101336</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AI5" t="n">
         <v>72.10471652003909</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AJ5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AK5" t="n">
         <v>22.71296296296296</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AL5" t="n">
         <v>184.574074074074</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AM5" t="n">
         <v>81.17592592592592</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AN5" t="n">
         <v>85513.88888888889</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AO5" t="n">
         <v>55655555.55555555</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AP5" t="n">
         <v>86.7962962962963</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AQ5" t="n">
         <v>2.074074074074074</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AR5" t="n">
         <v>24.59807638439992</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AS5" t="n">
         <v>181.7430554496046</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AT5" t="n">
         <v>65.18685203847424</v>
       </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="n">
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
         <v>1096465.543407999</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AW5" t="n">
         <v>71.15759191301939</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AX5" t="n">
         <v>1</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AY5" t="n">
         <v>23.2547952047952</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AZ5" t="n">
         <v>183.9831002331002</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="BA5" t="n">
         <v>80.01316183816184</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="BB5" t="n">
         <v>84948.40367965367</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="BC5" t="n">
         <v>47297179.07092907</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="BD5" t="n">
         <v>85.13105228105226</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="BE5" t="n">
         <v>2.011538461538461</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>22.655</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>181.8483333333334</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>234.3</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="n">
-        <v>4055000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>260.9</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>25.6698717948718</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>189.9525641025641</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.346153846153846</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>263.7692307692308</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>229615.3846153846</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>108413461.5384615</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>276.1538461538461</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.307692307692307</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -1571,136 +1571,136 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="O6" t="n">
+        <v>177.9739130434782</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.652173913043478</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>198.8695652173913</v>
+      </c>
+      <c r="R6" t="n">
+        <v>76695.65217391304</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30678260.86956522</v>
+      </c>
+      <c r="T6" t="n">
+        <v>214.0869565217391</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="V6" t="n">
+        <v>31</v>
+      </c>
+      <c r="W6" t="n">
+        <v>191</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" t="n">
         <v>24.3689898989899</v>
       </c>
-      <c r="O6" t="n">
+      <c r="AE6" t="n">
         <v>185.2609494949494</v>
       </c>
-      <c r="P6" t="n">
+      <c r="AF6" t="n">
         <v>75.59782828282827</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="AG6" t="n">
         <v>31232.37373737373</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AH6" t="n">
         <v>11140451.51515152</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AI6" t="n">
         <v>80.19023232323232</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AJ6" t="n">
         <v>1.39469696969697</v>
       </c>
-      <c r="U6" t="n">
-        <v>23.86275252525252</v>
-      </c>
-      <c r="V6" t="n">
-        <v>181.2633644133644</v>
-      </c>
-      <c r="W6" t="n">
-        <v>75.67067793317793</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="AK6" t="n">
+        <v>23.86170707070707</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>181.2427878787879</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>75.66639393939394</v>
+      </c>
+      <c r="AN6" t="n">
         <v>25923.61111111111</v>
       </c>
-      <c r="Y6" t="n">
-        <v>12732463.82090132</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>81.04663947163947</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.396649184149184</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AO6" t="n">
+        <v>12722206.81818182</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>81.0440606060606</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.394737373737374</v>
+      </c>
+      <c r="AR6" t="n">
         <v>22.11517528223411</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AS6" t="n">
         <v>180.7996093285799</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AT6" t="n">
         <v>72.13596553773026</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AU6" t="n">
         <v>24771.33343236284</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AV6" t="n">
         <v>7977531.31808279</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AW6" t="n">
         <v>78.82716577540107</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AX6" t="n">
         <v>1.326740938799762</v>
       </c>
-      <c r="AI6" t="n">
-        <v>26.22782967032967</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>179.8366575091575</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>73.93877733377732</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>22641.66666666666</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>7199765.741203241</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>77.97101093351094</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1.245317182817183</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>177.9739130434782</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.652173913043478</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>198.8695652173913</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>76695.65217391304</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>30678260.86956522</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>214.0869565217391</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3.347826086956522</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>25.28888888888889</v>
-      </c>
       <c r="AY6" t="n">
-        <v>183.6166666666667</v>
+        <v>26.00869963369964</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.3</v>
+        <v>180.1518416768417</v>
       </c>
       <c r="BA6" t="n">
-        <v>97.90000000000001</v>
+        <v>73.90975259308593</v>
       </c>
       <c r="BB6" t="n">
-        <v>24733.33333333333</v>
+        <v>22590.47619047619</v>
       </c>
       <c r="BC6" t="n">
-        <v>12170000</v>
+        <v>7368073.045781379</v>
       </c>
       <c r="BD6" t="n">
-        <v>103.5</v>
+        <v>78.21223437056771</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.866666666666667</v>
+        <v>1.250352425352426</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -1770,136 +1770,136 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>184.75</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>14866.66666666667</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5098333.333333333</v>
+      </c>
+      <c r="T7" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="V7" t="n">
+        <v>20.44090909090909</v>
+      </c>
+      <c r="W7" t="n">
+        <v>179.4257575757576</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.772727272727273</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>120.6363636363636</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>15222.22222222222</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4609090.909090909</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>138.3636363636364</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.863636363636364</v>
+      </c>
+      <c r="AD7" t="n">
         <v>23.13117283950617</v>
       </c>
-      <c r="O7" t="n">
+      <c r="AE7" t="n">
         <v>186.1927469135802</v>
       </c>
-      <c r="P7" t="n">
+      <c r="AF7" t="n">
         <v>66.33966049382715</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="AG7" t="n">
         <v>4922.979797979798</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AH7" t="n">
         <v>1705551.697530864</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AI7" t="n">
         <v>73.79058641975308</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AJ7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AK7" t="n">
         <v>25.08333333333333</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AL7" t="n">
         <v>184.7083333333333</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AM7" t="n">
         <v>73.16666666666667</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AN7" t="n">
         <v>16437.5</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AO7" t="n">
         <v>6375000</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AP7" t="n">
         <v>78.16666666666667</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AQ7" t="n">
         <v>1.125</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AR7" t="n">
         <v>24.39534377610693</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AS7" t="n">
         <v>181.33459732665</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AT7" t="n">
         <v>65.83988888888889</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AU7" t="n">
         <v>4142.063492063492</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AV7" t="n">
         <v>1483499.300334169</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AW7" t="n">
         <v>72.43189348370926</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AX7" t="n">
         <v>1</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AY7" t="n">
         <v>23.17482993197279</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AZ7" t="n">
         <v>186.1051587301587</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="BA7" t="n">
         <v>69.19631519274375</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="BB7" t="n">
         <v>10722.8835978836</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="BC7" t="n">
         <v>2894994.33106576</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="BD7" t="n">
         <v>75.49625850340136</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="BE7" t="n">
         <v>1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>184.75</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.733333333333333</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>117.8</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>14866.66666666667</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5098333.333333333</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>129.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.733333333333333</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>20.44090909090909</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>179.4257575757576</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.772727272727273</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>120.6363636363636</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>15222.22222222222</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4609090.909090909</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>138.3636363636364</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.863636363636364</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -1969,136 +1969,136 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>24.34130434782608</v>
+      </c>
+      <c r="O8" t="n">
+        <v>178.7282608695652</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.565217391304348</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>248.9565217391304</v>
+      </c>
+      <c r="R8" t="n">
+        <v>48900</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12405434.7826087</v>
+      </c>
+      <c r="T8" t="n">
+        <v>271.2173913043478</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.260869565217392</v>
+      </c>
+      <c r="V8" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="W8" t="n">
+        <v>182.7450980392157</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.529411764705882</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>109.8823529411765</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>22235.29411764706</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5405882.352941177</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>115.7647058823529</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.764705882352941</v>
+      </c>
+      <c r="AD8" t="n">
         <v>26.15674603174603</v>
       </c>
-      <c r="O8" t="n">
+      <c r="AE8" t="n">
         <v>179.5099206349207</v>
       </c>
-      <c r="P8" t="n">
+      <c r="AF8" t="n">
         <v>73.38492063492063</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="AG8" t="n">
         <v>16951.38888888889</v>
       </c>
-      <c r="R8" t="n">
+      <c r="AH8" t="n">
         <v>6894047.619047618</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AI8" t="n">
         <v>77.12103174603173</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AJ8" t="n">
         <v>1.41468253968254</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AK8" t="n">
         <v>25.7057498057498</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AL8" t="n">
         <v>181.4817793317793</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AM8" t="n">
         <v>72.49483294483295</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AN8" t="n">
         <v>15419.07536907537</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AO8" t="n">
         <v>3552093.045843046</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AP8" t="n">
         <v>75.47346542346541</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AQ8" t="n">
         <v>1.176806526806527</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AR8" t="n">
         <v>23.33944260867338</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AS8" t="n">
         <v>179.943292604831</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AT8" t="n">
         <v>68.76856220702373</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AU8" t="n">
         <v>10680.54672600127</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AV8" t="n">
         <v>3256709.508440278</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AW8" t="n">
         <v>76.5337508645201</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AX8" t="n">
         <v>1.198204359742821</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AY8" t="n">
         <v>24.66761052246986</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AZ8" t="n">
         <v>181.8868956278164</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="BA8" t="n">
         <v>70.04655340397028</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="BB8" t="n">
         <v>12754.94864612512</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="BC8" t="n">
         <v>2712750.324767588</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="BD8" t="n">
         <v>74.14898916088174</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="BE8" t="n">
         <v>1.169965087484269</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>24.34130434782608</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>178.7282608695652</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3.565217391304348</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>248.9565217391304</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>48900</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>12405434.7826087</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>271.2173913043478</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.260869565217392</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>182.7450980392157</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.529411764705882</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>109.8823529411765</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>22235.29411764706</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5405882.352941177</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>115.7647058823529</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.764705882352941</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -2168,134 +2168,134 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>23.37045454545454</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>181.6451298701299</v>
+        <v>189</v>
       </c>
       <c r="P9" t="n">
-        <v>75.23441558441559</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>29989.83957219251</v>
+        <v>72</v>
       </c>
       <c r="R9" t="n">
-        <v>13073344.15584416</v>
+        <v>14000</v>
       </c>
       <c r="S9" t="n">
-        <v>81.24707792207791</v>
+        <v>2900000</v>
       </c>
       <c r="T9" t="n">
-        <v>1.46461038961039</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>22.2171052631579</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>185.5036549707602</v>
+        <v>21.95873015873016</v>
       </c>
       <c r="W9" t="n">
-        <v>69.16286549707603</v>
-      </c>
-      <c r="X9" t="inlineStr"/>
+        <v>181.2253968253968</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.523809523809524</v>
+      </c>
       <c r="Y9" t="n">
-        <v>3981750.730994152</v>
+        <v>175.8095238095238</v>
       </c>
       <c r="Z9" t="n">
-        <v>78.04283625730994</v>
+        <v>26105.26315789474</v>
       </c>
       <c r="AA9" t="n">
+        <v>10721428.57142857</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>197.3809523809524</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.523809523809524</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>23.35824915824915</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>181.6060606060606</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>75.25050505050505</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>30107.95454545454</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>13053468.01346801</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>81.26734006734006</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.463299663299664</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>22.17361111111111</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>185.3858024691358</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>69.09552469135802</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>3952264.660493827</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>78.03132716049383</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1</v>
       </c>
-      <c r="AB9" t="n">
-        <v>22.47982913165266</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>182.3061988795518</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>72.53440616246499</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AR9" t="n">
+        <v>22.50577439309057</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>182.2891952614379</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>72.55667308590102</v>
+      </c>
+      <c r="AU9" t="n">
         <v>21821.42857142857</v>
       </c>
-      <c r="AF9" t="n">
-        <v>10151812.32492997</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>79.7315462184874</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.269302521008403</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>21.34693877551021</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>180.8475765306123</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>67.59306972789115</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="AV9" t="n">
+        <v>10186114.02894491</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>79.70250350140056</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.268618697478992</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>21.46593406593407</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>180.9743131868132</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>67.77715201465202</v>
+      </c>
+      <c r="BB9" t="n">
         <v>7998.611111111112</v>
       </c>
-      <c r="AM9" t="n">
-        <v>2901958.971088436</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>77.22699829931972</v>
-      </c>
-      <c r="AO9" t="n">
+      <c r="BC9" t="n">
+        <v>2981725.045787546</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>77.1367673992674</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>21.05357142857143</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>182.5714285714286</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.392857142857143</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>102.8214285714286</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>29571.42857142857</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>13814285.71428571</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>112.3214285714286</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.535714285714286</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>21.94545454545455</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>181.0636363636364</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.545454545454545</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>177.2272727272727</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>26150</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>10802272.72727273</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>199</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.545454545454545</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -2365,143 +2365,925 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>24.25</v>
+        <v>34</v>
       </c>
       <c r="O10" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="P10" t="n">
-        <v>74.375</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>81</v>
+      </c>
       <c r="R10" t="n">
-        <v>11812500</v>
+        <v>68000</v>
       </c>
       <c r="S10" t="n">
-        <v>78.625</v>
+        <v>9000000</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>81</v>
       </c>
       <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>282</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>24000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7575000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>283</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="n">
         <v>25.8125</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AL10" t="n">
         <v>181.8043323863636</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AM10" t="n">
         <v>70.37748579545455</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AN10" t="n">
         <v>6364.736070381232</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AO10" t="n">
         <v>2223677.201704545</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AP10" t="n">
         <v>73.72514204545453</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AQ10" t="n">
         <v>1</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AR10" t="n">
         <v>27.99833333333333</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AS10" t="n">
         <v>178.1766666666667</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AT10" t="n">
         <v>78.09</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AU10" t="n">
         <v>44565</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AV10" t="n">
         <v>14795000</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AW10" t="n">
         <v>79.00500000000001</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AX10" t="n">
         <v>1.998333333333334</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AY10" t="n">
         <v>24.84179677194383</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AZ10" t="n">
         <v>181.1848702981056</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="BA10" t="n">
         <v>68.27121128003482</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="BB10" t="n">
         <v>5131.791982527276</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="BC10" t="n">
         <v>1793600.571063807</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="BD10" t="n">
         <v>73.3681804512687</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="BE10" t="n">
         <v>1</v>
       </c>
-      <c r="AP10" t="n">
-        <v>23.88888888888889</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>177.1296296296296</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>149.0555555555555</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>72470.58823529411</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>21350000</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>159.1666666666667</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.611111111111111</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45618.625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade louis ii
+  monaco </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>55</v>
+      </c>
+      <c r="I11" t="n">
+        <v>551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>23.1344696969697</v>
+      </c>
+      <c r="O11" t="n">
+        <v>179.4876623376623</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.363636363636363</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>333.0909090909091</v>
+      </c>
+      <c r="R11" t="n">
+        <v>167818.1818181818</v>
+      </c>
+      <c r="S11" t="n">
+        <v>69372727.27272727</v>
+      </c>
+      <c r="T11" t="n">
+        <v>358.0454545454546</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5.909090909090909</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>182.7450980392157</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.529411764705882</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>109.8823529411765</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>22235.29411764706</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5405882.352941177</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>115.7647058823529</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.764705882352941</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>23.3125</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>178.9710648148148</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>74.98842592592592</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>40128.47222222222</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>14885416.66666667</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>81.16898148148148</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.380787037037037</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>25.7057498057498</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>181.4817793317793</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>72.49483294483295</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>15419.07536907537</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>3552093.045843046</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>75.47346542346541</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.176806526806527</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>20.60939019557441</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>179.3085709287464</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>70.5683154645874</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>15412.69841269841</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9307638.42476562</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>81.42087903162464</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.117418278602489</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>24.66761052246986</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>181.8868956278164</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>70.04655340397028</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>12754.94864612512</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2712750.324767588</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>74.14898916088174</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.169965087484269</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45618.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>551</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>25.6698717948718</v>
+      </c>
+      <c r="O12" t="n">
+        <v>189.9525641025641</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.346153846153846</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>263.7692307692308</v>
+      </c>
+      <c r="R12" t="n">
+        <v>229615.3846153846</v>
+      </c>
+      <c r="S12" t="n">
+        <v>108413461.5384615</v>
+      </c>
+      <c r="T12" t="n">
+        <v>276.1538461538461</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7.307692307692307</v>
+      </c>
+      <c r="V12" t="n">
+        <v>21.95873015873016</v>
+      </c>
+      <c r="W12" t="n">
+        <v>181.2253968253968</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.523809523809524</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>175.8095238095238</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>26105.26315789474</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>10721428.57142857</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>197.3809523809524</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.523809523809524</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>22.71296296296296</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>184.574074074074</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>81.17592592592592</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>85513.88888888889</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>55655555.55555555</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>86.7962962962963</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.074074074074074</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>22.17361111111111</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>185.3858024691358</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>69.09552469135802</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>3952264.660493827</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>78.03132716049383</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>23.2547952047952</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>183.9831002331002</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>80.01316183816184</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>84948.40367965367</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>47297179.07092907</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>85.13105228105226</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.011538461538461</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>21.46593406593407</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>180.9743131868132</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>67.77715201465202</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7998.611111111112</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2981725.045787546</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>77.1367673992674</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade bollaert delelis
+  lens </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>551</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>26.54430641821946</v>
+      </c>
+      <c r="O13" t="n">
+        <v>173.8386128364389</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.782608695652174</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>207.6521739130435</v>
+      </c>
+      <c r="R13" t="n">
+        <v>70391.30434782608</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20056521.73913043</v>
+      </c>
+      <c r="T13" t="n">
+        <v>212.7826086956522</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.826086956521739</v>
+      </c>
+      <c r="V13" t="n">
+        <v>23.63260869565217</v>
+      </c>
+      <c r="W13" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.217391304347826</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>299.2608695652174</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>99695.65217391304</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>39852173.91304348</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>322.8260869565217</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.434782608695652</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>25.64384057971014</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>180.1208937198068</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>76.85410628019324</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>29088.40579710144</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>12691702.89855072</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>79.968961352657</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.147342995169082</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>25.10069444444444</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>182.2638888888889</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>77.14583333333333</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>37447.91666666666</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>15792968.75</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>81.07986111111111</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.180555555555556</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>27.0505283772201</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>178.5263689526847</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>74.1951493994727</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>23258.25847085246</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>6727900.093849341</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>76.06019974177869</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.40579316256008</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>23.94808080808081</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>182.8925252525253</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>75.01339105339105</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>28849.89898989899</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>10478535.35353535</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>80.0346608946609</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.181298701298701</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>551</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
         <v>26.90277777777778</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="O14" t="n">
         <v>178.7986111111111</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="P14" t="n">
         <v>2.833333333333333</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="Q14" t="n">
         <v>197.9166666666667</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="R14" t="n">
         <v>16500</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="S14" t="n">
         <v>4891666.666666667</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="T14" t="n">
         <v>201.6666666666667</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="U14" t="n">
         <v>2.833333333333333</v>
       </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
+      <c r="V14" t="n">
+        <v>24.34130434782608</v>
+      </c>
+      <c r="W14" t="n">
+        <v>178.7282608695652</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.565217391304348</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>248.9565217391304</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>48900</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>12405434.7826087</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>271.2173913043478</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.260869565217392</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>25.8125</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>181.8043323863636</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>70.37748579545455</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>6364.736070381232</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2223677.201704545</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>73.72514204545453</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>26.15674603174603</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>179.5099206349207</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>73.38492063492063</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>16951.38888888889</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>6894047.619047618</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>77.12103174603173</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.41468253968254</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>24.84179677194383</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>181.1848702981056</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>68.27121128003482</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5131.791982527276</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1793600.571063807</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>73.3681804512687</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>23.33944260867338</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>179.943292604831</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>68.76856220702373</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>10680.54672600127</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3256709.508440278</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>76.5337508645201</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.198204359742821</v>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
         </is>
       </c>
     </row>
